--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/South Korea K League 1_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/South Korea K League 1_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="79">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -218,12 +218,48 @@
   </si>
   <si>
     <t>Nº</t>
+  </si>
+  <si>
+    <t>South Korea K League 1</t>
+  </si>
+  <si>
+    <t>2025</t>
+  </si>
+  <si>
+    <t>Pohang Steelers</t>
+  </si>
+  <si>
+    <t>Jeju United</t>
+  </si>
+  <si>
+    <t>Gwangju</t>
+  </si>
+  <si>
+    <t>Daejeon Citizen</t>
+  </si>
+  <si>
+    <t>FC Seoul</t>
+  </si>
+  <si>
+    <t>Suwon</t>
+  </si>
+  <si>
+    <t>[]</t>
+  </si>
+  <si>
+    <t>['15', '57']</t>
+  </si>
+  <si>
+    <t>['32', '87', '90']</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -276,11 +312,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -575,7 +612,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP1"/>
+  <dimension ref="A1:BP4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -784,6 +821,624 @@
         <v>66</v>
       </c>
     </row>
+    <row r="2" spans="1:68">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>7806758</v>
+      </c>
+      <c r="C2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D2" t="s">
+        <v>69</v>
+      </c>
+      <c r="E2" s="2">
+        <v>45703.04166666666</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2" t="s">
+        <v>70</v>
+      </c>
+      <c r="H2" t="s">
+        <v>73</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>3</v>
+      </c>
+      <c r="N2">
+        <v>3</v>
+      </c>
+      <c r="O2" t="s">
+        <v>76</v>
+      </c>
+      <c r="P2" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q2">
+        <v>2.75</v>
+      </c>
+      <c r="R2">
+        <v>2.05</v>
+      </c>
+      <c r="S2">
+        <v>4.33</v>
+      </c>
+      <c r="T2">
+        <v>1.44</v>
+      </c>
+      <c r="U2">
+        <v>2.63</v>
+      </c>
+      <c r="V2">
+        <v>3.25</v>
+      </c>
+      <c r="W2">
+        <v>1.33</v>
+      </c>
+      <c r="X2">
+        <v>10</v>
+      </c>
+      <c r="Y2">
+        <v>1.06</v>
+      </c>
+      <c r="Z2">
+        <v>2.02</v>
+      </c>
+      <c r="AA2">
+        <v>3.35</v>
+      </c>
+      <c r="AB2">
+        <v>3.62</v>
+      </c>
+      <c r="AC2">
+        <v>1.02</v>
+      </c>
+      <c r="AD2">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AE2">
+        <v>1.36</v>
+      </c>
+      <c r="AF2">
+        <v>2.95</v>
+      </c>
+      <c r="AG2">
+        <v>2.1</v>
+      </c>
+      <c r="AH2">
+        <v>1.61</v>
+      </c>
+      <c r="AI2">
+        <v>1.83</v>
+      </c>
+      <c r="AJ2">
+        <v>1.83</v>
+      </c>
+      <c r="AK2">
+        <v>1.27</v>
+      </c>
+      <c r="AL2">
+        <v>1.29</v>
+      </c>
+      <c r="AM2">
+        <v>1.7</v>
+      </c>
+      <c r="AN2">
+        <v>0</v>
+      </c>
+      <c r="AO2">
+        <v>0</v>
+      </c>
+      <c r="AP2">
+        <v>0</v>
+      </c>
+      <c r="AQ2">
+        <v>3</v>
+      </c>
+      <c r="AR2">
+        <v>0</v>
+      </c>
+      <c r="AS2">
+        <v>0</v>
+      </c>
+      <c r="AT2">
+        <v>0</v>
+      </c>
+      <c r="AU2">
+        <v>4</v>
+      </c>
+      <c r="AV2">
+        <v>5</v>
+      </c>
+      <c r="AW2">
+        <v>14</v>
+      </c>
+      <c r="AX2">
+        <v>5</v>
+      </c>
+      <c r="AY2">
+        <v>22</v>
+      </c>
+      <c r="AZ2">
+        <v>14</v>
+      </c>
+      <c r="BA2">
+        <v>7</v>
+      </c>
+      <c r="BB2">
+        <v>2</v>
+      </c>
+      <c r="BC2">
+        <v>9</v>
+      </c>
+      <c r="BD2">
+        <v>1.71</v>
+      </c>
+      <c r="BE2">
+        <v>6.4</v>
+      </c>
+      <c r="BF2">
+        <v>2.4</v>
+      </c>
+      <c r="BG2">
+        <v>1.46</v>
+      </c>
+      <c r="BH2">
+        <v>2.48</v>
+      </c>
+      <c r="BI2">
+        <v>1.77</v>
+      </c>
+      <c r="BJ2">
+        <v>1.93</v>
+      </c>
+      <c r="BK2">
+        <v>2.23</v>
+      </c>
+      <c r="BL2">
+        <v>1.56</v>
+      </c>
+      <c r="BM2">
+        <v>2.9</v>
+      </c>
+      <c r="BN2">
+        <v>1.35</v>
+      </c>
+      <c r="BO2">
+        <v>3.9</v>
+      </c>
+      <c r="BP2">
+        <v>1.21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:68">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>7806759</v>
+      </c>
+      <c r="C3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D3" t="s">
+        <v>69</v>
+      </c>
+      <c r="E3" s="2">
+        <v>45703.14583333334</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3" t="s">
+        <v>71</v>
+      </c>
+      <c r="H3" t="s">
+        <v>74</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>2</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3">
+        <v>2</v>
+      </c>
+      <c r="O3" t="s">
+        <v>77</v>
+      </c>
+      <c r="P3" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q3">
+        <v>4</v>
+      </c>
+      <c r="R3">
+        <v>2.05</v>
+      </c>
+      <c r="S3">
+        <v>2.88</v>
+      </c>
+      <c r="T3">
+        <v>1.44</v>
+      </c>
+      <c r="U3">
+        <v>2.63</v>
+      </c>
+      <c r="V3">
+        <v>3.25</v>
+      </c>
+      <c r="W3">
+        <v>1.33</v>
+      </c>
+      <c r="X3">
+        <v>9</v>
+      </c>
+      <c r="Y3">
+        <v>1.07</v>
+      </c>
+      <c r="Z3">
+        <v>3.39</v>
+      </c>
+      <c r="AA3">
+        <v>3.23</v>
+      </c>
+      <c r="AB3">
+        <v>2.15</v>
+      </c>
+      <c r="AC3">
+        <v>1.02</v>
+      </c>
+      <c r="AD3">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AE3">
+        <v>1.35</v>
+      </c>
+      <c r="AF3">
+        <v>3.36</v>
+      </c>
+      <c r="AG3">
+        <v>2</v>
+      </c>
+      <c r="AH3">
+        <v>1.67</v>
+      </c>
+      <c r="AI3">
+        <v>1.83</v>
+      </c>
+      <c r="AJ3">
+        <v>1.83</v>
+      </c>
+      <c r="AK3">
+        <v>1.65</v>
+      </c>
+      <c r="AL3">
+        <v>1.32</v>
+      </c>
+      <c r="AM3">
+        <v>1.32</v>
+      </c>
+      <c r="AN3">
+        <v>0</v>
+      </c>
+      <c r="AO3">
+        <v>0</v>
+      </c>
+      <c r="AP3">
+        <v>3</v>
+      </c>
+      <c r="AQ3">
+        <v>0</v>
+      </c>
+      <c r="AR3">
+        <v>0</v>
+      </c>
+      <c r="AS3">
+        <v>0</v>
+      </c>
+      <c r="AT3">
+        <v>0</v>
+      </c>
+      <c r="AU3">
+        <v>4</v>
+      </c>
+      <c r="AV3">
+        <v>3</v>
+      </c>
+      <c r="AW3">
+        <v>6</v>
+      </c>
+      <c r="AX3">
+        <v>5</v>
+      </c>
+      <c r="AY3">
+        <v>11</v>
+      </c>
+      <c r="AZ3">
+        <v>8</v>
+      </c>
+      <c r="BA3">
+        <v>1</v>
+      </c>
+      <c r="BB3">
+        <v>4</v>
+      </c>
+      <c r="BC3">
+        <v>5</v>
+      </c>
+      <c r="BD3">
+        <v>2.1</v>
+      </c>
+      <c r="BE3">
+        <v>8</v>
+      </c>
+      <c r="BF3">
+        <v>1.91</v>
+      </c>
+      <c r="BG3">
+        <v>1.36</v>
+      </c>
+      <c r="BH3">
+        <v>2.78</v>
+      </c>
+      <c r="BI3">
+        <v>1.7</v>
+      </c>
+      <c r="BJ3">
+        <v>2.05</v>
+      </c>
+      <c r="BK3">
+        <v>1.95</v>
+      </c>
+      <c r="BL3">
+        <v>1.77</v>
+      </c>
+      <c r="BM3">
+        <v>2.83</v>
+      </c>
+      <c r="BN3">
+        <v>1.33</v>
+      </c>
+      <c r="BO3">
+        <v>4</v>
+      </c>
+      <c r="BP3">
+        <v>1.17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:68">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>7806760</v>
+      </c>
+      <c r="C4" t="s">
+        <v>68</v>
+      </c>
+      <c r="D4" t="s">
+        <v>69</v>
+      </c>
+      <c r="E4" s="2">
+        <v>45703.1875</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4" t="s">
+        <v>72</v>
+      </c>
+      <c r="H4" t="s">
+        <v>75</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>0</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4">
+        <v>0</v>
+      </c>
+      <c r="O4" t="s">
+        <v>76</v>
+      </c>
+      <c r="P4" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q4">
+        <v>2.75</v>
+      </c>
+      <c r="R4">
+        <v>2.04</v>
+      </c>
+      <c r="S4">
+        <v>4</v>
+      </c>
+      <c r="T4">
+        <v>1.47</v>
+      </c>
+      <c r="U4">
+        <v>2.5</v>
+      </c>
+      <c r="V4">
+        <v>3</v>
+      </c>
+      <c r="W4">
+        <v>1.36</v>
+      </c>
+      <c r="X4">
+        <v>7.5</v>
+      </c>
+      <c r="Y4">
+        <v>1.07</v>
+      </c>
+      <c r="Z4">
+        <v>2.13</v>
+      </c>
+      <c r="AA4">
+        <v>3.21</v>
+      </c>
+      <c r="AB4">
+        <v>3.45</v>
+      </c>
+      <c r="AC4">
+        <v>1.02</v>
+      </c>
+      <c r="AD4">
+        <v>8.1</v>
+      </c>
+      <c r="AE4">
+        <v>1.37</v>
+      </c>
+      <c r="AF4">
+        <v>2.95</v>
+      </c>
+      <c r="AG4">
+        <v>2.05</v>
+      </c>
+      <c r="AH4">
+        <v>1.65</v>
+      </c>
+      <c r="AI4">
+        <v>1.87</v>
+      </c>
+      <c r="AJ4">
+        <v>1.84</v>
+      </c>
+      <c r="AK4">
+        <v>1.3</v>
+      </c>
+      <c r="AL4">
+        <v>1.3</v>
+      </c>
+      <c r="AM4">
+        <v>1.63</v>
+      </c>
+      <c r="AN4">
+        <v>0</v>
+      </c>
+      <c r="AO4">
+        <v>0</v>
+      </c>
+      <c r="AP4">
+        <v>1</v>
+      </c>
+      <c r="AQ4">
+        <v>1</v>
+      </c>
+      <c r="AR4">
+        <v>0</v>
+      </c>
+      <c r="AS4">
+        <v>0</v>
+      </c>
+      <c r="AT4">
+        <v>0</v>
+      </c>
+      <c r="AU4">
+        <v>3</v>
+      </c>
+      <c r="AV4">
+        <v>2</v>
+      </c>
+      <c r="AW4">
+        <v>6</v>
+      </c>
+      <c r="AX4">
+        <v>2</v>
+      </c>
+      <c r="AY4">
+        <v>10</v>
+      </c>
+      <c r="AZ4">
+        <v>4</v>
+      </c>
+      <c r="BA4">
+        <v>3</v>
+      </c>
+      <c r="BB4">
+        <v>2</v>
+      </c>
+      <c r="BC4">
+        <v>5</v>
+      </c>
+      <c r="BD4">
+        <v>1.75</v>
+      </c>
+      <c r="BE4">
+        <v>6.1</v>
+      </c>
+      <c r="BF4">
+        <v>2.33</v>
+      </c>
+      <c r="BG4">
+        <v>1.46</v>
+      </c>
+      <c r="BH4">
+        <v>2.5</v>
+      </c>
+      <c r="BI4">
+        <v>1.8</v>
+      </c>
+      <c r="BJ4">
+        <v>2</v>
+      </c>
+      <c r="BK4">
+        <v>2.2</v>
+      </c>
+      <c r="BL4">
+        <v>1.58</v>
+      </c>
+      <c r="BM4">
+        <v>2.9</v>
+      </c>
+      <c r="BN4">
+        <v>1.35</v>
+      </c>
+      <c r="BO4">
+        <v>3.9</v>
+      </c>
+      <c r="BP4">
+        <v>1.21</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/South Korea K League 1_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/South Korea K League 1_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="90">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -235,6 +235,15 @@
     <t>Gwangju</t>
   </si>
   <si>
+    <t>Ulsan</t>
+  </si>
+  <si>
+    <t>Jeonbuk Motors</t>
+  </si>
+  <si>
+    <t>Daegu</t>
+  </si>
+  <si>
     <t>Daejeon Citizen</t>
   </si>
   <si>
@@ -244,13 +253,37 @@
     <t>Suwon</t>
   </si>
   <si>
+    <t>Anyang</t>
+  </si>
+  <si>
+    <t>Sangju Sangmu</t>
+  </si>
+  <si>
+    <t>Gangwon</t>
+  </si>
+  <si>
     <t>[]</t>
   </si>
   <si>
     <t>['15', '57']</t>
   </si>
   <si>
+    <t>['45+6', '81']</t>
+  </si>
+  <si>
+    <t>['56', '90+3']</t>
+  </si>
+  <si>
     <t>['32', '87', '90']</t>
+  </si>
+  <si>
+    <t>['90+2']</t>
+  </si>
+  <si>
+    <t>['14']</t>
+  </si>
+  <si>
+    <t>['44']</t>
   </si>
 </sst>
 </file>
@@ -612,7 +645,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP4"/>
+  <dimension ref="A1:BP7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -844,7 +877,7 @@
         <v>70</v>
       </c>
       <c r="H2" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -865,10 +898,10 @@
         <v>3</v>
       </c>
       <c r="O2" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="P2" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="Q2">
         <v>2.75</v>
@@ -1050,7 +1083,7 @@
         <v>71</v>
       </c>
       <c r="H3" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="I3">
         <v>1</v>
@@ -1071,10 +1104,10 @@
         <v>2</v>
       </c>
       <c r="O3" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="P3" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="Q3">
         <v>4</v>
@@ -1256,7 +1289,7 @@
         <v>72</v>
       </c>
       <c r="H4" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -1277,10 +1310,10 @@
         <v>0</v>
       </c>
       <c r="O4" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="P4" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="Q4">
         <v>2.75</v>
@@ -1437,6 +1470,624 @@
       </c>
       <c r="BP4">
         <v>1.21</v>
+      </c>
+    </row>
+    <row r="5" spans="1:68">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>7806761</v>
+      </c>
+      <c r="C5" t="s">
+        <v>68</v>
+      </c>
+      <c r="D5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E5" s="2">
+        <v>45704.08333333334</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5" t="s">
+        <v>73</v>
+      </c>
+      <c r="H5" t="s">
+        <v>79</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>0</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>1</v>
+      </c>
+      <c r="N5">
+        <v>1</v>
+      </c>
+      <c r="O5" t="s">
+        <v>82</v>
+      </c>
+      <c r="P5" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q5">
+        <v>2.1</v>
+      </c>
+      <c r="R5">
+        <v>2.15</v>
+      </c>
+      <c r="S5">
+        <v>5.25</v>
+      </c>
+      <c r="T5">
+        <v>1.38</v>
+      </c>
+      <c r="U5">
+        <v>2.75</v>
+      </c>
+      <c r="V5">
+        <v>2.75</v>
+      </c>
+      <c r="W5">
+        <v>1.39</v>
+      </c>
+      <c r="X5">
+        <v>7</v>
+      </c>
+      <c r="Y5">
+        <v>1.08</v>
+      </c>
+      <c r="Z5">
+        <v>1.56</v>
+      </c>
+      <c r="AA5">
+        <v>3.96</v>
+      </c>
+      <c r="AB5">
+        <v>5.7</v>
+      </c>
+      <c r="AC5">
+        <v>1.05</v>
+      </c>
+      <c r="AD5">
+        <v>9</v>
+      </c>
+      <c r="AE5">
+        <v>1.3</v>
+      </c>
+      <c r="AF5">
+        <v>3.48</v>
+      </c>
+      <c r="AG5">
+        <v>1.92</v>
+      </c>
+      <c r="AH5">
+        <v>1.82</v>
+      </c>
+      <c r="AI5">
+        <v>1.98</v>
+      </c>
+      <c r="AJ5">
+        <v>1.72</v>
+      </c>
+      <c r="AK5">
+        <v>1.14</v>
+      </c>
+      <c r="AL5">
+        <v>1.24</v>
+      </c>
+      <c r="AM5">
+        <v>2.3</v>
+      </c>
+      <c r="AN5">
+        <v>0</v>
+      </c>
+      <c r="AO5">
+        <v>0</v>
+      </c>
+      <c r="AP5">
+        <v>0</v>
+      </c>
+      <c r="AQ5">
+        <v>3</v>
+      </c>
+      <c r="AR5">
+        <v>0</v>
+      </c>
+      <c r="AS5">
+        <v>0</v>
+      </c>
+      <c r="AT5">
+        <v>0</v>
+      </c>
+      <c r="AU5">
+        <v>7</v>
+      </c>
+      <c r="AV5">
+        <v>5</v>
+      </c>
+      <c r="AW5">
+        <v>12</v>
+      </c>
+      <c r="AX5">
+        <v>3</v>
+      </c>
+      <c r="AY5">
+        <v>24</v>
+      </c>
+      <c r="AZ5">
+        <v>10</v>
+      </c>
+      <c r="BA5">
+        <v>5</v>
+      </c>
+      <c r="BB5">
+        <v>1</v>
+      </c>
+      <c r="BC5">
+        <v>6</v>
+      </c>
+      <c r="BD5">
+        <v>0</v>
+      </c>
+      <c r="BE5">
+        <v>0</v>
+      </c>
+      <c r="BF5">
+        <v>0</v>
+      </c>
+      <c r="BG5">
+        <v>0</v>
+      </c>
+      <c r="BH5">
+        <v>0</v>
+      </c>
+      <c r="BI5">
+        <v>0</v>
+      </c>
+      <c r="BJ5">
+        <v>0</v>
+      </c>
+      <c r="BK5">
+        <v>0</v>
+      </c>
+      <c r="BL5">
+        <v>0</v>
+      </c>
+      <c r="BM5">
+        <v>0</v>
+      </c>
+      <c r="BN5">
+        <v>0</v>
+      </c>
+      <c r="BO5">
+        <v>0</v>
+      </c>
+      <c r="BP5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:68">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>7806762</v>
+      </c>
+      <c r="C6" t="s">
+        <v>68</v>
+      </c>
+      <c r="D6" t="s">
+        <v>69</v>
+      </c>
+      <c r="E6" s="2">
+        <v>45704.1875</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6" t="s">
+        <v>74</v>
+      </c>
+      <c r="H6" t="s">
+        <v>80</v>
+      </c>
+      <c r="I6">
+        <v>1</v>
+      </c>
+      <c r="J6">
+        <v>1</v>
+      </c>
+      <c r="K6">
+        <v>2</v>
+      </c>
+      <c r="L6">
+        <v>2</v>
+      </c>
+      <c r="M6">
+        <v>1</v>
+      </c>
+      <c r="N6">
+        <v>3</v>
+      </c>
+      <c r="O6" t="s">
+        <v>84</v>
+      </c>
+      <c r="P6" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q6">
+        <v>3.1</v>
+      </c>
+      <c r="R6">
+        <v>2.1</v>
+      </c>
+      <c r="S6">
+        <v>3.5</v>
+      </c>
+      <c r="T6">
+        <v>1.44</v>
+      </c>
+      <c r="U6">
+        <v>2.63</v>
+      </c>
+      <c r="V6">
+        <v>3</v>
+      </c>
+      <c r="W6">
+        <v>1.36</v>
+      </c>
+      <c r="X6">
+        <v>9</v>
+      </c>
+      <c r="Y6">
+        <v>1.07</v>
+      </c>
+      <c r="Z6">
+        <v>2.46</v>
+      </c>
+      <c r="AA6">
+        <v>3.2</v>
+      </c>
+      <c r="AB6">
+        <v>2.85</v>
+      </c>
+      <c r="AC6">
+        <v>1.02</v>
+      </c>
+      <c r="AD6">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="AE6">
+        <v>1.32</v>
+      </c>
+      <c r="AF6">
+        <v>3.2</v>
+      </c>
+      <c r="AG6">
+        <v>1.98</v>
+      </c>
+      <c r="AH6">
+        <v>1.77</v>
+      </c>
+      <c r="AI6">
+        <v>1.8</v>
+      </c>
+      <c r="AJ6">
+        <v>1.91</v>
+      </c>
+      <c r="AK6">
+        <v>1.38</v>
+      </c>
+      <c r="AL6">
+        <v>1.3</v>
+      </c>
+      <c r="AM6">
+        <v>1.52</v>
+      </c>
+      <c r="AN6">
+        <v>0</v>
+      </c>
+      <c r="AO6">
+        <v>0</v>
+      </c>
+      <c r="AP6">
+        <v>3</v>
+      </c>
+      <c r="AQ6">
+        <v>0</v>
+      </c>
+      <c r="AR6">
+        <v>0</v>
+      </c>
+      <c r="AS6">
+        <v>0</v>
+      </c>
+      <c r="AT6">
+        <v>0</v>
+      </c>
+      <c r="AU6">
+        <v>6</v>
+      </c>
+      <c r="AV6">
+        <v>6</v>
+      </c>
+      <c r="AW6">
+        <v>5</v>
+      </c>
+      <c r="AX6">
+        <v>5</v>
+      </c>
+      <c r="AY6">
+        <v>18</v>
+      </c>
+      <c r="AZ6">
+        <v>13</v>
+      </c>
+      <c r="BA6">
+        <v>10</v>
+      </c>
+      <c r="BB6">
+        <v>1</v>
+      </c>
+      <c r="BC6">
+        <v>11</v>
+      </c>
+      <c r="BD6">
+        <v>1.92</v>
+      </c>
+      <c r="BE6">
+        <v>6.25</v>
+      </c>
+      <c r="BF6">
+        <v>2.08</v>
+      </c>
+      <c r="BG6">
+        <v>1.65</v>
+      </c>
+      <c r="BH6">
+        <v>2.08</v>
+      </c>
+      <c r="BI6">
+        <v>2.07</v>
+      </c>
+      <c r="BJ6">
+        <v>1.67</v>
+      </c>
+      <c r="BK6">
+        <v>2.7</v>
+      </c>
+      <c r="BL6">
+        <v>1.4</v>
+      </c>
+      <c r="BM6">
+        <v>3.65</v>
+      </c>
+      <c r="BN6">
+        <v>1.24</v>
+      </c>
+      <c r="BO6">
+        <v>4.9</v>
+      </c>
+      <c r="BP6">
+        <v>1.13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:68">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>7806763</v>
+      </c>
+      <c r="C7" t="s">
+        <v>68</v>
+      </c>
+      <c r="D7" t="s">
+        <v>69</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45704.1875</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+      <c r="G7" t="s">
+        <v>75</v>
+      </c>
+      <c r="H7" t="s">
+        <v>81</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>1</v>
+      </c>
+      <c r="K7">
+        <v>1</v>
+      </c>
+      <c r="L7">
+        <v>2</v>
+      </c>
+      <c r="M7">
+        <v>1</v>
+      </c>
+      <c r="N7">
+        <v>3</v>
+      </c>
+      <c r="O7" t="s">
+        <v>85</v>
+      </c>
+      <c r="P7" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q7">
+        <v>3.5</v>
+      </c>
+      <c r="R7">
+        <v>2.05</v>
+      </c>
+      <c r="S7">
+        <v>3.25</v>
+      </c>
+      <c r="T7">
+        <v>1.44</v>
+      </c>
+      <c r="U7">
+        <v>2.63</v>
+      </c>
+      <c r="V7">
+        <v>3.4</v>
+      </c>
+      <c r="W7">
+        <v>1.3</v>
+      </c>
+      <c r="X7">
+        <v>10</v>
+      </c>
+      <c r="Y7">
+        <v>1.06</v>
+      </c>
+      <c r="Z7">
+        <v>2.81</v>
+      </c>
+      <c r="AA7">
+        <v>3.06</v>
+      </c>
+      <c r="AB7">
+        <v>2.58</v>
+      </c>
+      <c r="AC7">
+        <v>1.02</v>
+      </c>
+      <c r="AD7">
+        <v>8</v>
+      </c>
+      <c r="AE7">
+        <v>1.37</v>
+      </c>
+      <c r="AF7">
+        <v>2.95</v>
+      </c>
+      <c r="AG7">
+        <v>2.05</v>
+      </c>
+      <c r="AH7">
+        <v>1.61</v>
+      </c>
+      <c r="AI7">
+        <v>1.83</v>
+      </c>
+      <c r="AJ7">
+        <v>1.83</v>
+      </c>
+      <c r="AK7">
+        <v>1.46</v>
+      </c>
+      <c r="AL7">
+        <v>1.32</v>
+      </c>
+      <c r="AM7">
+        <v>1.41</v>
+      </c>
+      <c r="AN7">
+        <v>0</v>
+      </c>
+      <c r="AO7">
+        <v>0</v>
+      </c>
+      <c r="AP7">
+        <v>3</v>
+      </c>
+      <c r="AQ7">
+        <v>0</v>
+      </c>
+      <c r="AR7">
+        <v>0</v>
+      </c>
+      <c r="AS7">
+        <v>0</v>
+      </c>
+      <c r="AT7">
+        <v>0</v>
+      </c>
+      <c r="AU7">
+        <v>4</v>
+      </c>
+      <c r="AV7">
+        <v>4</v>
+      </c>
+      <c r="AW7">
+        <v>16</v>
+      </c>
+      <c r="AX7">
+        <v>5</v>
+      </c>
+      <c r="AY7">
+        <v>23</v>
+      </c>
+      <c r="AZ7">
+        <v>9</v>
+      </c>
+      <c r="BA7">
+        <v>3</v>
+      </c>
+      <c r="BB7">
+        <v>4</v>
+      </c>
+      <c r="BC7">
+        <v>7</v>
+      </c>
+      <c r="BD7">
+        <v>2.05</v>
+      </c>
+      <c r="BE7">
+        <v>6.1</v>
+      </c>
+      <c r="BF7">
+        <v>1.97</v>
+      </c>
+      <c r="BG7">
+        <v>1.56</v>
+      </c>
+      <c r="BH7">
+        <v>2.23</v>
+      </c>
+      <c r="BI7">
+        <v>1.98</v>
+      </c>
+      <c r="BJ7">
+        <v>1.82</v>
+      </c>
+      <c r="BK7">
+        <v>2.48</v>
+      </c>
+      <c r="BL7">
+        <v>1.47</v>
+      </c>
+      <c r="BM7">
+        <v>3.3</v>
+      </c>
+      <c r="BN7">
+        <v>1.27</v>
+      </c>
+      <c r="BO7">
+        <v>4.5</v>
+      </c>
+      <c r="BP7">
+        <v>1.16</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/South Korea K League 1_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/South Korea K League 1_2025.xlsx
@@ -997,19 +997,19 @@
         <v>4</v>
       </c>
       <c r="AV2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AW2">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AX2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AY2">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AZ2">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="BA2">
         <v>7</v>
@@ -1406,22 +1406,22 @@
         <v>0</v>
       </c>
       <c r="AU4">
+        <v>5</v>
+      </c>
+      <c r="AV4">
         <v>3</v>
       </c>
-      <c r="AV4">
-        <v>2</v>
-      </c>
       <c r="AW4">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AX4">
         <v>2</v>
       </c>
       <c r="AY4">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="AZ4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="BA4">
         <v>3</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/South Korea K League 1_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/South Korea K League 1_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="96">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -244,12 +244,12 @@
     <t>Daegu</t>
   </si>
   <si>
+    <t>FC Seoul</t>
+  </si>
+  <si>
     <t>Daejeon Citizen</t>
   </si>
   <si>
-    <t>FC Seoul</t>
-  </si>
-  <si>
     <t>Suwon</t>
   </si>
   <si>
@@ -274,6 +274,15 @@
     <t>['56', '90+3']</t>
   </si>
   <si>
+    <t>['30', '58']</t>
+  </si>
+  <si>
+    <t>['48', '79']</t>
+  </si>
+  <si>
+    <t>['19', '53', '70']</t>
+  </si>
+  <si>
     <t>['32', '87', '90']</t>
   </si>
   <si>
@@ -284,6 +293,15 @@
   </si>
   <si>
     <t>['44']</t>
+  </si>
+  <si>
+    <t>['50', '63', '90']</t>
+  </si>
+  <si>
+    <t>['90+3']</t>
+  </si>
+  <si>
+    <t>['90+4']</t>
   </si>
 </sst>
 </file>
@@ -645,7 +663,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP7"/>
+  <dimension ref="A1:BP10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -877,7 +895,7 @@
         <v>70</v>
       </c>
       <c r="H2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -901,7 +919,7 @@
         <v>82</v>
       </c>
       <c r="P2" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="Q2">
         <v>2.75</v>
@@ -1083,7 +1101,7 @@
         <v>71</v>
       </c>
       <c r="H3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I3">
         <v>1</v>
@@ -1185,7 +1203,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="AQ3">
         <v>0</v>
@@ -1394,7 +1412,7 @@
         <v>1</v>
       </c>
       <c r="AQ4">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -1519,7 +1537,7 @@
         <v>82</v>
       </c>
       <c r="P5" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="Q5">
         <v>2.1</v>
@@ -1600,7 +1618,7 @@
         <v>0</v>
       </c>
       <c r="AQ5">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -1725,7 +1743,7 @@
         <v>84</v>
       </c>
       <c r="P6" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="Q6">
         <v>3.1</v>
@@ -1806,7 +1824,7 @@
         <v>3</v>
       </c>
       <c r="AQ6">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -1931,7 +1949,7 @@
         <v>85</v>
       </c>
       <c r="P7" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="Q7">
         <v>3.5</v>
@@ -2088,6 +2106,624 @@
       </c>
       <c r="BP7">
         <v>1.16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:68">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>7806764</v>
+      </c>
+      <c r="C8" t="s">
+        <v>68</v>
+      </c>
+      <c r="D8" t="s">
+        <v>69</v>
+      </c>
+      <c r="E8" s="2">
+        <v>45710.08333333334</v>
+      </c>
+      <c r="F8">
+        <v>2</v>
+      </c>
+      <c r="G8" t="s">
+        <v>71</v>
+      </c>
+      <c r="H8" t="s">
+        <v>80</v>
+      </c>
+      <c r="I8">
+        <v>1</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>1</v>
+      </c>
+      <c r="L8">
+        <v>2</v>
+      </c>
+      <c r="M8">
+        <v>3</v>
+      </c>
+      <c r="N8">
+        <v>5</v>
+      </c>
+      <c r="O8" t="s">
+        <v>86</v>
+      </c>
+      <c r="P8" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q8">
+        <v>3.4</v>
+      </c>
+      <c r="R8">
+        <v>2.15</v>
+      </c>
+      <c r="S8">
+        <v>2.9</v>
+      </c>
+      <c r="T8">
+        <v>1.4</v>
+      </c>
+      <c r="U8">
+        <v>2.75</v>
+      </c>
+      <c r="V8">
+        <v>2.65</v>
+      </c>
+      <c r="W8">
+        <v>1.42</v>
+      </c>
+      <c r="X8">
+        <v>6.25</v>
+      </c>
+      <c r="Y8">
+        <v>1.06</v>
+      </c>
+      <c r="Z8">
+        <v>2.85</v>
+      </c>
+      <c r="AA8">
+        <v>3.2</v>
+      </c>
+      <c r="AB8">
+        <v>2.46</v>
+      </c>
+      <c r="AC8">
+        <v>1.06</v>
+      </c>
+      <c r="AD8">
+        <v>8.5</v>
+      </c>
+      <c r="AE8">
+        <v>1.27</v>
+      </c>
+      <c r="AF8">
+        <v>3.5</v>
+      </c>
+      <c r="AG8">
+        <v>1.95</v>
+      </c>
+      <c r="AH8">
+        <v>1.79</v>
+      </c>
+      <c r="AI8">
+        <v>1.66</v>
+      </c>
+      <c r="AJ8">
+        <v>2.09</v>
+      </c>
+      <c r="AK8">
+        <v>1.51</v>
+      </c>
+      <c r="AL8">
+        <v>1.3</v>
+      </c>
+      <c r="AM8">
+        <v>1.38</v>
+      </c>
+      <c r="AN8">
+        <v>3</v>
+      </c>
+      <c r="AO8">
+        <v>0</v>
+      </c>
+      <c r="AP8">
+        <v>1.5</v>
+      </c>
+      <c r="AQ8">
+        <v>1.5</v>
+      </c>
+      <c r="AR8">
+        <v>1.38</v>
+      </c>
+      <c r="AS8">
+        <v>1.58</v>
+      </c>
+      <c r="AT8">
+        <v>2.96</v>
+      </c>
+      <c r="AU8">
+        <v>5</v>
+      </c>
+      <c r="AV8">
+        <v>6</v>
+      </c>
+      <c r="AW8">
+        <v>1</v>
+      </c>
+      <c r="AX8">
+        <v>3</v>
+      </c>
+      <c r="AY8">
+        <v>6</v>
+      </c>
+      <c r="AZ8">
+        <v>9</v>
+      </c>
+      <c r="BA8">
+        <v>0</v>
+      </c>
+      <c r="BB8">
+        <v>5</v>
+      </c>
+      <c r="BC8">
+        <v>5</v>
+      </c>
+      <c r="BD8">
+        <v>2.12</v>
+      </c>
+      <c r="BE8">
+        <v>6.25</v>
+      </c>
+      <c r="BF8">
+        <v>1.89</v>
+      </c>
+      <c r="BG8">
+        <v>1.4</v>
+      </c>
+      <c r="BH8">
+        <v>2.7</v>
+      </c>
+      <c r="BI8">
+        <v>1.68</v>
+      </c>
+      <c r="BJ8">
+        <v>2.05</v>
+      </c>
+      <c r="BK8">
+        <v>2.08</v>
+      </c>
+      <c r="BL8">
+        <v>1.66</v>
+      </c>
+      <c r="BM8">
+        <v>2.65</v>
+      </c>
+      <c r="BN8">
+        <v>1.41</v>
+      </c>
+      <c r="BO8">
+        <v>3.45</v>
+      </c>
+      <c r="BP8">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:68">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9">
+        <v>7806765</v>
+      </c>
+      <c r="C9" t="s">
+        <v>68</v>
+      </c>
+      <c r="D9" t="s">
+        <v>69</v>
+      </c>
+      <c r="E9" s="2">
+        <v>45710.1875</v>
+      </c>
+      <c r="F9">
+        <v>2</v>
+      </c>
+      <c r="G9" t="s">
+        <v>76</v>
+      </c>
+      <c r="H9" t="s">
+        <v>79</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9">
+        <v>0</v>
+      </c>
+      <c r="L9">
+        <v>2</v>
+      </c>
+      <c r="M9">
+        <v>1</v>
+      </c>
+      <c r="N9">
+        <v>3</v>
+      </c>
+      <c r="O9" t="s">
+        <v>87</v>
+      </c>
+      <c r="P9" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q9">
+        <v>2.45</v>
+      </c>
+      <c r="R9">
+        <v>2</v>
+      </c>
+      <c r="S9">
+        <v>4.6</v>
+      </c>
+      <c r="T9">
+        <v>1.46</v>
+      </c>
+      <c r="U9">
+        <v>2.5</v>
+      </c>
+      <c r="V9">
+        <v>3.1</v>
+      </c>
+      <c r="W9">
+        <v>1.32</v>
+      </c>
+      <c r="X9">
+        <v>8.5</v>
+      </c>
+      <c r="Y9">
+        <v>1.06</v>
+      </c>
+      <c r="Z9">
+        <v>1.82</v>
+      </c>
+      <c r="AA9">
+        <v>3.55</v>
+      </c>
+      <c r="AB9">
+        <v>4.2</v>
+      </c>
+      <c r="AC9">
+        <v>1.07</v>
+      </c>
+      <c r="AD9">
+        <v>8</v>
+      </c>
+      <c r="AE9">
+        <v>1.3</v>
+      </c>
+      <c r="AF9">
+        <v>3.08</v>
+      </c>
+      <c r="AG9">
+        <v>2</v>
+      </c>
+      <c r="AH9">
+        <v>1.67</v>
+      </c>
+      <c r="AI9">
+        <v>1.93</v>
+      </c>
+      <c r="AJ9">
+        <v>1.75</v>
+      </c>
+      <c r="AK9">
+        <v>1.21</v>
+      </c>
+      <c r="AL9">
+        <v>1.29</v>
+      </c>
+      <c r="AM9">
+        <v>1.93</v>
+      </c>
+      <c r="AN9">
+        <v>0</v>
+      </c>
+      <c r="AO9">
+        <v>3</v>
+      </c>
+      <c r="AP9">
+        <v>3</v>
+      </c>
+      <c r="AQ9">
+        <v>1.5</v>
+      </c>
+      <c r="AR9">
+        <v>0</v>
+      </c>
+      <c r="AS9">
+        <v>1.19</v>
+      </c>
+      <c r="AT9">
+        <v>1.19</v>
+      </c>
+      <c r="AU9">
+        <v>5</v>
+      </c>
+      <c r="AV9">
+        <v>3</v>
+      </c>
+      <c r="AW9">
+        <v>6</v>
+      </c>
+      <c r="AX9">
+        <v>1</v>
+      </c>
+      <c r="AY9">
+        <v>11</v>
+      </c>
+      <c r="AZ9">
+        <v>4</v>
+      </c>
+      <c r="BA9">
+        <v>4</v>
+      </c>
+      <c r="BB9">
+        <v>2</v>
+      </c>
+      <c r="BC9">
+        <v>6</v>
+      </c>
+      <c r="BD9">
+        <v>1.54</v>
+      </c>
+      <c r="BE9">
+        <v>6.4</v>
+      </c>
+      <c r="BF9">
+        <v>2.75</v>
+      </c>
+      <c r="BG9">
+        <v>1.46</v>
+      </c>
+      <c r="BH9">
+        <v>2.48</v>
+      </c>
+      <c r="BI9">
+        <v>1.76</v>
+      </c>
+      <c r="BJ9">
+        <v>1.94</v>
+      </c>
+      <c r="BK9">
+        <v>2.2</v>
+      </c>
+      <c r="BL9">
+        <v>1.58</v>
+      </c>
+      <c r="BM9">
+        <v>2.9</v>
+      </c>
+      <c r="BN9">
+        <v>1.35</v>
+      </c>
+      <c r="BO9">
+        <v>3.8</v>
+      </c>
+      <c r="BP9">
+        <v>1.21</v>
+      </c>
+    </row>
+    <row r="10" spans="1:68">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10">
+        <v>7806766</v>
+      </c>
+      <c r="C10" t="s">
+        <v>68</v>
+      </c>
+      <c r="D10" t="s">
+        <v>69</v>
+      </c>
+      <c r="E10" s="2">
+        <v>45710.1875</v>
+      </c>
+      <c r="F10">
+        <v>2</v>
+      </c>
+      <c r="G10" t="s">
+        <v>75</v>
+      </c>
+      <c r="H10" t="s">
+        <v>78</v>
+      </c>
+      <c r="I10">
+        <v>1</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>1</v>
+      </c>
+      <c r="L10">
+        <v>3</v>
+      </c>
+      <c r="M10">
+        <v>1</v>
+      </c>
+      <c r="N10">
+        <v>4</v>
+      </c>
+      <c r="O10" t="s">
+        <v>88</v>
+      </c>
+      <c r="P10" t="s">
+        <v>95</v>
+      </c>
+      <c r="Q10">
+        <v>3.35</v>
+      </c>
+      <c r="R10">
+        <v>2.05</v>
+      </c>
+      <c r="S10">
+        <v>3</v>
+      </c>
+      <c r="T10">
+        <v>1.4</v>
+      </c>
+      <c r="U10">
+        <v>2.75</v>
+      </c>
+      <c r="V10">
+        <v>2.75</v>
+      </c>
+      <c r="W10">
+        <v>1.4</v>
+      </c>
+      <c r="X10">
+        <v>7.4</v>
+      </c>
+      <c r="Y10">
+        <v>1.03</v>
+      </c>
+      <c r="Z10">
+        <v>2.66</v>
+      </c>
+      <c r="AA10">
+        <v>3.28</v>
+      </c>
+      <c r="AB10">
+        <v>2.58</v>
+      </c>
+      <c r="AC10">
+        <v>1.06</v>
+      </c>
+      <c r="AD10">
+        <v>8.5</v>
+      </c>
+      <c r="AE10">
+        <v>1.33</v>
+      </c>
+      <c r="AF10">
+        <v>3.25</v>
+      </c>
+      <c r="AG10">
+        <v>1.94</v>
+      </c>
+      <c r="AH10">
+        <v>1.8</v>
+      </c>
+      <c r="AI10">
+        <v>1.7</v>
+      </c>
+      <c r="AJ10">
+        <v>2</v>
+      </c>
+      <c r="AK10">
+        <v>1.53</v>
+      </c>
+      <c r="AL10">
+        <v>1.28</v>
+      </c>
+      <c r="AM10">
+        <v>1.4</v>
+      </c>
+      <c r="AN10">
+        <v>3</v>
+      </c>
+      <c r="AO10">
+        <v>1</v>
+      </c>
+      <c r="AP10">
+        <v>3</v>
+      </c>
+      <c r="AQ10">
+        <v>0.5</v>
+      </c>
+      <c r="AR10">
+        <v>1.95</v>
+      </c>
+      <c r="AS10">
+        <v>0.9</v>
+      </c>
+      <c r="AT10">
+        <v>2.85</v>
+      </c>
+      <c r="AU10">
+        <v>5</v>
+      </c>
+      <c r="AV10">
+        <v>4</v>
+      </c>
+      <c r="AW10">
+        <v>10</v>
+      </c>
+      <c r="AX10">
+        <v>2</v>
+      </c>
+      <c r="AY10">
+        <v>18</v>
+      </c>
+      <c r="AZ10">
+        <v>7</v>
+      </c>
+      <c r="BA10">
+        <v>9</v>
+      </c>
+      <c r="BB10">
+        <v>5</v>
+      </c>
+      <c r="BC10">
+        <v>14</v>
+      </c>
+      <c r="BD10">
+        <v>2.05</v>
+      </c>
+      <c r="BE10">
+        <v>6.25</v>
+      </c>
+      <c r="BF10">
+        <v>1.95</v>
+      </c>
+      <c r="BG10">
+        <v>1.42</v>
+      </c>
+      <c r="BH10">
+        <v>2.65</v>
+      </c>
+      <c r="BI10">
+        <v>1.71</v>
+      </c>
+      <c r="BJ10">
+        <v>2</v>
+      </c>
+      <c r="BK10">
+        <v>2.15</v>
+      </c>
+      <c r="BL10">
+        <v>1.63</v>
+      </c>
+      <c r="BM10">
+        <v>2.8</v>
+      </c>
+      <c r="BN10">
+        <v>1.38</v>
+      </c>
+      <c r="BO10">
+        <v>3.65</v>
+      </c>
+      <c r="BP10">
+        <v>1.23</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/South Korea K League 1_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/South Korea K League 1_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="100">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -250,6 +250,9 @@
     <t>Daejeon Citizen</t>
   </si>
   <si>
+    <t>Gangwon</t>
+  </si>
+  <si>
     <t>Suwon</t>
   </si>
   <si>
@@ -259,9 +262,6 @@
     <t>Sangju Sangmu</t>
   </si>
   <si>
-    <t>Gangwon</t>
-  </si>
-  <si>
     <t>[]</t>
   </si>
   <si>
@@ -283,6 +283,12 @@
     <t>['19', '53', '70']</t>
   </si>
   <si>
+    <t>['82', '90+3']</t>
+  </si>
+  <si>
+    <t>['21', '66']</t>
+  </si>
+  <si>
     <t>['32', '87', '90']</t>
   </si>
   <si>
@@ -302,6 +308,12 @@
   </si>
   <si>
     <t>['90+4']</t>
+  </si>
+  <si>
+    <t>['8', '59']</t>
+  </si>
+  <si>
+    <t>['14', '64']</t>
   </si>
 </sst>
 </file>
@@ -663,7 +675,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP10"/>
+  <dimension ref="A1:BP13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -919,7 +931,7 @@
         <v>82</v>
       </c>
       <c r="P2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="Q2">
         <v>2.75</v>
@@ -1307,7 +1319,7 @@
         <v>72</v>
       </c>
       <c r="H4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -1513,7 +1525,7 @@
         <v>73</v>
       </c>
       <c r="H5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -1537,7 +1549,7 @@
         <v>82</v>
       </c>
       <c r="P5" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="Q5">
         <v>2.1</v>
@@ -1719,7 +1731,7 @@
         <v>74</v>
       </c>
       <c r="H6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I6">
         <v>1</v>
@@ -1743,7 +1755,7 @@
         <v>84</v>
       </c>
       <c r="P6" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="Q6">
         <v>3.1</v>
@@ -1821,7 +1833,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AQ6">
         <v>1.5</v>
@@ -1925,7 +1937,7 @@
         <v>75</v>
       </c>
       <c r="H7" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -1949,7 +1961,7 @@
         <v>85</v>
       </c>
       <c r="P7" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="Q7">
         <v>3.5</v>
@@ -2131,7 +2143,7 @@
         <v>71</v>
       </c>
       <c r="H8" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I8">
         <v>1</v>
@@ -2155,7 +2167,7 @@
         <v>86</v>
       </c>
       <c r="P8" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="Q8">
         <v>3.4</v>
@@ -2337,7 +2349,7 @@
         <v>76</v>
       </c>
       <c r="H9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -2361,7 +2373,7 @@
         <v>87</v>
       </c>
       <c r="P9" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="Q9">
         <v>2.45</v>
@@ -2543,7 +2555,7 @@
         <v>75</v>
       </c>
       <c r="H10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I10">
         <v>1</v>
@@ -2567,7 +2579,7 @@
         <v>88</v>
       </c>
       <c r="P10" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="Q10">
         <v>3.35</v>
@@ -2724,6 +2736,624 @@
       </c>
       <c r="BP10">
         <v>1.23</v>
+      </c>
+    </row>
+    <row r="11" spans="1:68">
+      <c r="A11" s="1">
+        <v>10</v>
+      </c>
+      <c r="B11">
+        <v>7806767</v>
+      </c>
+      <c r="C11" t="s">
+        <v>68</v>
+      </c>
+      <c r="D11" t="s">
+        <v>69</v>
+      </c>
+      <c r="E11" s="2">
+        <v>45711.08333333334</v>
+      </c>
+      <c r="F11">
+        <v>2</v>
+      </c>
+      <c r="G11" t="s">
+        <v>77</v>
+      </c>
+      <c r="H11" t="s">
+        <v>73</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>1</v>
+      </c>
+      <c r="K11">
+        <v>1</v>
+      </c>
+      <c r="L11">
+        <v>0</v>
+      </c>
+      <c r="M11">
+        <v>2</v>
+      </c>
+      <c r="N11">
+        <v>2</v>
+      </c>
+      <c r="O11" t="s">
+        <v>82</v>
+      </c>
+      <c r="P11" t="s">
+        <v>98</v>
+      </c>
+      <c r="Q11">
+        <v>3.45</v>
+      </c>
+      <c r="R11">
+        <v>2.07</v>
+      </c>
+      <c r="S11">
+        <v>3.05</v>
+      </c>
+      <c r="T11">
+        <v>1.44</v>
+      </c>
+      <c r="U11">
+        <v>2.6</v>
+      </c>
+      <c r="V11">
+        <v>2.88</v>
+      </c>
+      <c r="W11">
+        <v>1.36</v>
+      </c>
+      <c r="X11">
+        <v>7</v>
+      </c>
+      <c r="Y11">
+        <v>1.08</v>
+      </c>
+      <c r="Z11">
+        <v>2.88</v>
+      </c>
+      <c r="AA11">
+        <v>3.17</v>
+      </c>
+      <c r="AB11">
+        <v>2.46</v>
+      </c>
+      <c r="AC11">
+        <v>1.07</v>
+      </c>
+      <c r="AD11">
+        <v>8</v>
+      </c>
+      <c r="AE11">
+        <v>1.33</v>
+      </c>
+      <c r="AF11">
+        <v>3.15</v>
+      </c>
+      <c r="AG11">
+        <v>1.87</v>
+      </c>
+      <c r="AH11">
+        <v>1.87</v>
+      </c>
+      <c r="AI11">
+        <v>1.77</v>
+      </c>
+      <c r="AJ11">
+        <v>1.94</v>
+      </c>
+      <c r="AK11">
+        <v>1.5</v>
+      </c>
+      <c r="AL11">
+        <v>1.3</v>
+      </c>
+      <c r="AM11">
+        <v>1.4</v>
+      </c>
+      <c r="AN11">
+        <v>0</v>
+      </c>
+      <c r="AO11">
+        <v>0</v>
+      </c>
+      <c r="AP11">
+        <v>0</v>
+      </c>
+      <c r="AQ11">
+        <v>3</v>
+      </c>
+      <c r="AR11">
+        <v>0</v>
+      </c>
+      <c r="AS11">
+        <v>0</v>
+      </c>
+      <c r="AT11">
+        <v>0</v>
+      </c>
+      <c r="AU11">
+        <v>2</v>
+      </c>
+      <c r="AV11">
+        <v>5</v>
+      </c>
+      <c r="AW11">
+        <v>5</v>
+      </c>
+      <c r="AX11">
+        <v>10</v>
+      </c>
+      <c r="AY11">
+        <v>10</v>
+      </c>
+      <c r="AZ11">
+        <v>21</v>
+      </c>
+      <c r="BA11">
+        <v>5</v>
+      </c>
+      <c r="BB11">
+        <v>4</v>
+      </c>
+      <c r="BC11">
+        <v>9</v>
+      </c>
+      <c r="BD11">
+        <v>2.12</v>
+      </c>
+      <c r="BE11">
+        <v>6.1</v>
+      </c>
+      <c r="BF11">
+        <v>1.9</v>
+      </c>
+      <c r="BG11">
+        <v>1.45</v>
+      </c>
+      <c r="BH11">
+        <v>2.55</v>
+      </c>
+      <c r="BI11">
+        <v>1.75</v>
+      </c>
+      <c r="BJ11">
+        <v>1.95</v>
+      </c>
+      <c r="BK11">
+        <v>2.2</v>
+      </c>
+      <c r="BL11">
+        <v>1.58</v>
+      </c>
+      <c r="BM11">
+        <v>2.9</v>
+      </c>
+      <c r="BN11">
+        <v>1.35</v>
+      </c>
+      <c r="BO11">
+        <v>3.8</v>
+      </c>
+      <c r="BP11">
+        <v>1.21</v>
+      </c>
+    </row>
+    <row r="12" spans="1:68">
+      <c r="A12" s="1">
+        <v>11</v>
+      </c>
+      <c r="B12">
+        <v>7806769</v>
+      </c>
+      <c r="C12" t="s">
+        <v>68</v>
+      </c>
+      <c r="D12" t="s">
+        <v>69</v>
+      </c>
+      <c r="E12" s="2">
+        <v>45711.1875</v>
+      </c>
+      <c r="F12">
+        <v>2</v>
+      </c>
+      <c r="G12" t="s">
+        <v>78</v>
+      </c>
+      <c r="H12" t="s">
+        <v>70</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>1</v>
+      </c>
+      <c r="K12">
+        <v>1</v>
+      </c>
+      <c r="L12">
+        <v>2</v>
+      </c>
+      <c r="M12">
+        <v>1</v>
+      </c>
+      <c r="N12">
+        <v>3</v>
+      </c>
+      <c r="O12" t="s">
+        <v>89</v>
+      </c>
+      <c r="P12" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q12">
+        <v>2.95</v>
+      </c>
+      <c r="R12">
+        <v>2.05</v>
+      </c>
+      <c r="S12">
+        <v>3.6</v>
+      </c>
+      <c r="T12">
+        <v>1.46</v>
+      </c>
+      <c r="U12">
+        <v>2.55</v>
+      </c>
+      <c r="V12">
+        <v>2.88</v>
+      </c>
+      <c r="W12">
+        <v>1.36</v>
+      </c>
+      <c r="X12">
+        <v>7.5</v>
+      </c>
+      <c r="Y12">
+        <v>1.07</v>
+      </c>
+      <c r="Z12">
+        <v>2.39</v>
+      </c>
+      <c r="AA12">
+        <v>3.14</v>
+      </c>
+      <c r="AB12">
+        <v>3</v>
+      </c>
+      <c r="AC12">
+        <v>1.07</v>
+      </c>
+      <c r="AD12">
+        <v>8</v>
+      </c>
+      <c r="AE12">
+        <v>1.34</v>
+      </c>
+      <c r="AF12">
+        <v>3.05</v>
+      </c>
+      <c r="AG12">
+        <v>1.95</v>
+      </c>
+      <c r="AH12">
+        <v>1.7</v>
+      </c>
+      <c r="AI12">
+        <v>1.8</v>
+      </c>
+      <c r="AJ12">
+        <v>1.91</v>
+      </c>
+      <c r="AK12">
+        <v>1.37</v>
+      </c>
+      <c r="AL12">
+        <v>1.31</v>
+      </c>
+      <c r="AM12">
+        <v>1.53</v>
+      </c>
+      <c r="AN12">
+        <v>0</v>
+      </c>
+      <c r="AO12">
+        <v>0</v>
+      </c>
+      <c r="AP12">
+        <v>3</v>
+      </c>
+      <c r="AQ12">
+        <v>0</v>
+      </c>
+      <c r="AR12">
+        <v>0</v>
+      </c>
+      <c r="AS12">
+        <v>0</v>
+      </c>
+      <c r="AT12">
+        <v>0</v>
+      </c>
+      <c r="AU12">
+        <v>7</v>
+      </c>
+      <c r="AV12">
+        <v>4</v>
+      </c>
+      <c r="AW12">
+        <v>11</v>
+      </c>
+      <c r="AX12">
+        <v>2</v>
+      </c>
+      <c r="AY12">
+        <v>22</v>
+      </c>
+      <c r="AZ12">
+        <v>6</v>
+      </c>
+      <c r="BA12">
+        <v>4</v>
+      </c>
+      <c r="BB12">
+        <v>3</v>
+      </c>
+      <c r="BC12">
+        <v>7</v>
+      </c>
+      <c r="BD12">
+        <v>1.89</v>
+      </c>
+      <c r="BE12">
+        <v>6.1</v>
+      </c>
+      <c r="BF12">
+        <v>2.15</v>
+      </c>
+      <c r="BG12">
+        <v>1.46</v>
+      </c>
+      <c r="BH12">
+        <v>2.5</v>
+      </c>
+      <c r="BI12">
+        <v>1.77</v>
+      </c>
+      <c r="BJ12">
+        <v>1.93</v>
+      </c>
+      <c r="BK12">
+        <v>2.23</v>
+      </c>
+      <c r="BL12">
+        <v>1.57</v>
+      </c>
+      <c r="BM12">
+        <v>2.9</v>
+      </c>
+      <c r="BN12">
+        <v>1.35</v>
+      </c>
+      <c r="BO12">
+        <v>3.8</v>
+      </c>
+      <c r="BP12">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="13" spans="1:68">
+      <c r="A13" s="1">
+        <v>12</v>
+      </c>
+      <c r="B13">
+        <v>7806768</v>
+      </c>
+      <c r="C13" t="s">
+        <v>68</v>
+      </c>
+      <c r="D13" t="s">
+        <v>69</v>
+      </c>
+      <c r="E13" s="2">
+        <v>45711.1875</v>
+      </c>
+      <c r="F13">
+        <v>2</v>
+      </c>
+      <c r="G13" t="s">
+        <v>74</v>
+      </c>
+      <c r="H13" t="s">
+        <v>72</v>
+      </c>
+      <c r="I13">
+        <v>1</v>
+      </c>
+      <c r="J13">
+        <v>1</v>
+      </c>
+      <c r="K13">
+        <v>2</v>
+      </c>
+      <c r="L13">
+        <v>2</v>
+      </c>
+      <c r="M13">
+        <v>2</v>
+      </c>
+      <c r="N13">
+        <v>4</v>
+      </c>
+      <c r="O13" t="s">
+        <v>90</v>
+      </c>
+      <c r="P13" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q13">
+        <v>2.75</v>
+      </c>
+      <c r="R13">
+        <v>2.08</v>
+      </c>
+      <c r="S13">
+        <v>3.85</v>
+      </c>
+      <c r="T13">
+        <v>1.44</v>
+      </c>
+      <c r="U13">
+        <v>2.6</v>
+      </c>
+      <c r="V13">
+        <v>2.88</v>
+      </c>
+      <c r="W13">
+        <v>1.36</v>
+      </c>
+      <c r="X13">
+        <v>7.5</v>
+      </c>
+      <c r="Y13">
+        <v>1.07</v>
+      </c>
+      <c r="Z13">
+        <v>2.18</v>
+      </c>
+      <c r="AA13">
+        <v>3.25</v>
+      </c>
+      <c r="AB13">
+        <v>3.29</v>
+      </c>
+      <c r="AC13">
+        <v>1.07</v>
+      </c>
+      <c r="AD13">
+        <v>8</v>
+      </c>
+      <c r="AE13">
+        <v>1.33</v>
+      </c>
+      <c r="AF13">
+        <v>3.1</v>
+      </c>
+      <c r="AG13">
+        <v>1.95</v>
+      </c>
+      <c r="AH13">
+        <v>1.7</v>
+      </c>
+      <c r="AI13">
+        <v>1.8</v>
+      </c>
+      <c r="AJ13">
+        <v>1.91</v>
+      </c>
+      <c r="AK13">
+        <v>1.31</v>
+      </c>
+      <c r="AL13">
+        <v>1.3</v>
+      </c>
+      <c r="AM13">
+        <v>1.62</v>
+      </c>
+      <c r="AN13">
+        <v>3</v>
+      </c>
+      <c r="AO13">
+        <v>0</v>
+      </c>
+      <c r="AP13">
+        <v>2</v>
+      </c>
+      <c r="AQ13">
+        <v>1</v>
+      </c>
+      <c r="AR13">
+        <v>1.8</v>
+      </c>
+      <c r="AS13">
+        <v>0</v>
+      </c>
+      <c r="AT13">
+        <v>1.8</v>
+      </c>
+      <c r="AU13">
+        <v>5</v>
+      </c>
+      <c r="AV13">
+        <v>3</v>
+      </c>
+      <c r="AW13">
+        <v>6</v>
+      </c>
+      <c r="AX13">
+        <v>2</v>
+      </c>
+      <c r="AY13">
+        <v>16</v>
+      </c>
+      <c r="AZ13">
+        <v>5</v>
+      </c>
+      <c r="BA13">
+        <v>4</v>
+      </c>
+      <c r="BB13">
+        <v>1</v>
+      </c>
+      <c r="BC13">
+        <v>5</v>
+      </c>
+      <c r="BD13">
+        <v>1.73</v>
+      </c>
+      <c r="BE13">
+        <v>6.25</v>
+      </c>
+      <c r="BF13">
+        <v>2.35</v>
+      </c>
+      <c r="BG13">
+        <v>1.47</v>
+      </c>
+      <c r="BH13">
+        <v>2.48</v>
+      </c>
+      <c r="BI13">
+        <v>1.77</v>
+      </c>
+      <c r="BJ13">
+        <v>1.92</v>
+      </c>
+      <c r="BK13">
+        <v>2.23</v>
+      </c>
+      <c r="BL13">
+        <v>1.57</v>
+      </c>
+      <c r="BM13">
+        <v>2.9</v>
+      </c>
+      <c r="BN13">
+        <v>1.35</v>
+      </c>
+      <c r="BO13">
+        <v>3.9</v>
+      </c>
+      <c r="BP13">
+        <v>1.21</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/South Korea K League 1_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/South Korea K League 1_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="103">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -289,6 +289,12 @@
     <t>['21', '66']</t>
   </si>
   <si>
+    <t>['66']</t>
+  </si>
+  <si>
+    <t>['57', '89']</t>
+  </si>
+  <si>
     <t>['32', '87', '90']</t>
   </si>
   <si>
@@ -314,6 +320,9 @@
   </si>
   <si>
     <t>['14', '64']</t>
+  </si>
+  <si>
+    <t>['16']</t>
   </si>
 </sst>
 </file>
@@ -675,7 +684,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP13"/>
+  <dimension ref="A1:BP16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -931,7 +940,7 @@
         <v>82</v>
       </c>
       <c r="P2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="Q2">
         <v>2.75</v>
@@ -1009,7 +1018,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AQ2">
         <v>3</v>
@@ -1421,7 +1430,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AQ4">
         <v>0.5</v>
@@ -1549,7 +1558,7 @@
         <v>82</v>
       </c>
       <c r="P5" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="Q5">
         <v>2.1</v>
@@ -1627,10 +1636,10 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AQ5">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -1755,7 +1764,7 @@
         <v>84</v>
       </c>
       <c r="P6" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="Q6">
         <v>3.1</v>
@@ -1961,7 +1970,7 @@
         <v>85</v>
       </c>
       <c r="P7" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="Q7">
         <v>3.5</v>
@@ -2167,7 +2176,7 @@
         <v>86</v>
       </c>
       <c r="P8" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="Q8">
         <v>3.4</v>
@@ -2373,7 +2382,7 @@
         <v>87</v>
       </c>
       <c r="P9" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="Q9">
         <v>2.45</v>
@@ -2454,7 +2463,7 @@
         <v>3</v>
       </c>
       <c r="AQ9">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -2579,7 +2588,7 @@
         <v>88</v>
       </c>
       <c r="P10" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="Q10">
         <v>3.35</v>
@@ -2785,7 +2794,7 @@
         <v>82</v>
       </c>
       <c r="P11" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="Q11">
         <v>3.45</v>
@@ -2991,7 +3000,7 @@
         <v>89</v>
       </c>
       <c r="P12" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="Q12">
         <v>2.95</v>
@@ -3197,7 +3206,7 @@
         <v>90</v>
       </c>
       <c r="P13" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="Q13">
         <v>2.75</v>
@@ -3354,6 +3363,624 @@
       </c>
       <c r="BP13">
         <v>1.21</v>
+      </c>
+    </row>
+    <row r="14" spans="1:68">
+      <c r="A14" s="1">
+        <v>13</v>
+      </c>
+      <c r="B14">
+        <v>7806770</v>
+      </c>
+      <c r="C14" t="s">
+        <v>68</v>
+      </c>
+      <c r="D14" t="s">
+        <v>69</v>
+      </c>
+      <c r="E14" s="2">
+        <v>45717.08333333334</v>
+      </c>
+      <c r="F14">
+        <v>3</v>
+      </c>
+      <c r="G14" t="s">
+        <v>73</v>
+      </c>
+      <c r="H14" t="s">
+        <v>74</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <v>0</v>
+      </c>
+      <c r="L14">
+        <v>1</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14">
+        <v>1</v>
+      </c>
+      <c r="O14" t="s">
+        <v>91</v>
+      </c>
+      <c r="P14" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q14">
+        <v>2.9</v>
+      </c>
+      <c r="R14">
+        <v>2.11</v>
+      </c>
+      <c r="S14">
+        <v>3.45</v>
+      </c>
+      <c r="T14">
+        <v>1.42</v>
+      </c>
+      <c r="U14">
+        <v>2.7</v>
+      </c>
+      <c r="V14">
+        <v>2.7</v>
+      </c>
+      <c r="W14">
+        <v>1.41</v>
+      </c>
+      <c r="X14">
+        <v>7.5</v>
+      </c>
+      <c r="Y14">
+        <v>1.03</v>
+      </c>
+      <c r="Z14">
+        <v>2.54</v>
+      </c>
+      <c r="AA14">
+        <v>3.25</v>
+      </c>
+      <c r="AB14">
+        <v>2.72</v>
+      </c>
+      <c r="AC14">
+        <v>1.06</v>
+      </c>
+      <c r="AD14">
+        <v>8.5</v>
+      </c>
+      <c r="AE14">
+        <v>1.3</v>
+      </c>
+      <c r="AF14">
+        <v>3.3</v>
+      </c>
+      <c r="AG14">
+        <v>1.91</v>
+      </c>
+      <c r="AH14">
+        <v>1.83</v>
+      </c>
+      <c r="AI14">
+        <v>1.72</v>
+      </c>
+      <c r="AJ14">
+        <v>2.01</v>
+      </c>
+      <c r="AK14">
+        <v>1.38</v>
+      </c>
+      <c r="AL14">
+        <v>1.3</v>
+      </c>
+      <c r="AM14">
+        <v>1.53</v>
+      </c>
+      <c r="AN14">
+        <v>0</v>
+      </c>
+      <c r="AO14">
+        <v>0</v>
+      </c>
+      <c r="AP14">
+        <v>1.5</v>
+      </c>
+      <c r="AQ14">
+        <v>0</v>
+      </c>
+      <c r="AR14">
+        <v>2.51</v>
+      </c>
+      <c r="AS14">
+        <v>0</v>
+      </c>
+      <c r="AT14">
+        <v>2.51</v>
+      </c>
+      <c r="AU14">
+        <v>6</v>
+      </c>
+      <c r="AV14">
+        <v>3</v>
+      </c>
+      <c r="AW14">
+        <v>7</v>
+      </c>
+      <c r="AX14">
+        <v>5</v>
+      </c>
+      <c r="AY14">
+        <v>15</v>
+      </c>
+      <c r="AZ14">
+        <v>10</v>
+      </c>
+      <c r="BA14">
+        <v>5</v>
+      </c>
+      <c r="BB14">
+        <v>4</v>
+      </c>
+      <c r="BC14">
+        <v>9</v>
+      </c>
+      <c r="BD14">
+        <v>1.9</v>
+      </c>
+      <c r="BE14">
+        <v>6.25</v>
+      </c>
+      <c r="BF14">
+        <v>2.1</v>
+      </c>
+      <c r="BG14">
+        <v>1.42</v>
+      </c>
+      <c r="BH14">
+        <v>2.65</v>
+      </c>
+      <c r="BI14">
+        <v>1.7</v>
+      </c>
+      <c r="BJ14">
+        <v>2.02</v>
+      </c>
+      <c r="BK14">
+        <v>2.12</v>
+      </c>
+      <c r="BL14">
+        <v>1.63</v>
+      </c>
+      <c r="BM14">
+        <v>2.75</v>
+      </c>
+      <c r="BN14">
+        <v>1.38</v>
+      </c>
+      <c r="BO14">
+        <v>3.65</v>
+      </c>
+      <c r="BP14">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="15" spans="1:68">
+      <c r="A15" s="1">
+        <v>14</v>
+      </c>
+      <c r="B15">
+        <v>7806771</v>
+      </c>
+      <c r="C15" t="s">
+        <v>68</v>
+      </c>
+      <c r="D15" t="s">
+        <v>69</v>
+      </c>
+      <c r="E15" s="2">
+        <v>45717.1875</v>
+      </c>
+      <c r="F15">
+        <v>3</v>
+      </c>
+      <c r="G15" t="s">
+        <v>70</v>
+      </c>
+      <c r="H15" t="s">
+        <v>75</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15">
+        <v>0</v>
+      </c>
+      <c r="L15">
+        <v>0</v>
+      </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
+      <c r="N15">
+        <v>0</v>
+      </c>
+      <c r="O15" t="s">
+        <v>82</v>
+      </c>
+      <c r="P15" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q15">
+        <v>2.95</v>
+      </c>
+      <c r="R15">
+        <v>2.12</v>
+      </c>
+      <c r="S15">
+        <v>3.4</v>
+      </c>
+      <c r="T15">
+        <v>1.4</v>
+      </c>
+      <c r="U15">
+        <v>2.75</v>
+      </c>
+      <c r="V15">
+        <v>2.7</v>
+      </c>
+      <c r="W15">
+        <v>1.41</v>
+      </c>
+      <c r="X15">
+        <v>6.8</v>
+      </c>
+      <c r="Y15">
+        <v>1.04</v>
+      </c>
+      <c r="Z15">
+        <v>1.94</v>
+      </c>
+      <c r="AA15">
+        <v>3.47</v>
+      </c>
+      <c r="AB15">
+        <v>3.76</v>
+      </c>
+      <c r="AC15">
+        <v>1.06</v>
+      </c>
+      <c r="AD15">
+        <v>8.5</v>
+      </c>
+      <c r="AE15">
+        <v>1.29</v>
+      </c>
+      <c r="AF15">
+        <v>3.4</v>
+      </c>
+      <c r="AG15">
+        <v>1.98</v>
+      </c>
+      <c r="AH15">
+        <v>1.77</v>
+      </c>
+      <c r="AI15">
+        <v>1.7</v>
+      </c>
+      <c r="AJ15">
+        <v>2.03</v>
+      </c>
+      <c r="AK15">
+        <v>1.39</v>
+      </c>
+      <c r="AL15">
+        <v>1.3</v>
+      </c>
+      <c r="AM15">
+        <v>1.52</v>
+      </c>
+      <c r="AN15">
+        <v>0</v>
+      </c>
+      <c r="AO15">
+        <v>0</v>
+      </c>
+      <c r="AP15">
+        <v>0.5</v>
+      </c>
+      <c r="AQ15">
+        <v>1</v>
+      </c>
+      <c r="AR15">
+        <v>1.87</v>
+      </c>
+      <c r="AS15">
+        <v>0</v>
+      </c>
+      <c r="AT15">
+        <v>1.87</v>
+      </c>
+      <c r="AU15">
+        <v>6</v>
+      </c>
+      <c r="AV15">
+        <v>4</v>
+      </c>
+      <c r="AW15">
+        <v>10</v>
+      </c>
+      <c r="AX15">
+        <v>5</v>
+      </c>
+      <c r="AY15">
+        <v>20</v>
+      </c>
+      <c r="AZ15">
+        <v>10</v>
+      </c>
+      <c r="BA15">
+        <v>7</v>
+      </c>
+      <c r="BB15">
+        <v>2</v>
+      </c>
+      <c r="BC15">
+        <v>9</v>
+      </c>
+      <c r="BD15">
+        <v>1.9</v>
+      </c>
+      <c r="BE15">
+        <v>6.25</v>
+      </c>
+      <c r="BF15">
+        <v>2.12</v>
+      </c>
+      <c r="BG15">
+        <v>1.41</v>
+      </c>
+      <c r="BH15">
+        <v>2.65</v>
+      </c>
+      <c r="BI15">
+        <v>1.68</v>
+      </c>
+      <c r="BJ15">
+        <v>2.05</v>
+      </c>
+      <c r="BK15">
+        <v>2.08</v>
+      </c>
+      <c r="BL15">
+        <v>1.65</v>
+      </c>
+      <c r="BM15">
+        <v>2.7</v>
+      </c>
+      <c r="BN15">
+        <v>1.4</v>
+      </c>
+      <c r="BO15">
+        <v>3.55</v>
+      </c>
+      <c r="BP15">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="16" spans="1:68">
+      <c r="A16" s="1">
+        <v>15</v>
+      </c>
+      <c r="B16">
+        <v>7806772</v>
+      </c>
+      <c r="C16" t="s">
+        <v>68</v>
+      </c>
+      <c r="D16" t="s">
+        <v>69</v>
+      </c>
+      <c r="E16" s="2">
+        <v>45717.1875</v>
+      </c>
+      <c r="F16">
+        <v>3</v>
+      </c>
+      <c r="G16" t="s">
+        <v>72</v>
+      </c>
+      <c r="H16" t="s">
+        <v>80</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>1</v>
+      </c>
+      <c r="K16">
+        <v>1</v>
+      </c>
+      <c r="L16">
+        <v>2</v>
+      </c>
+      <c r="M16">
+        <v>1</v>
+      </c>
+      <c r="N16">
+        <v>3</v>
+      </c>
+      <c r="O16" t="s">
+        <v>92</v>
+      </c>
+      <c r="P16" t="s">
+        <v>102</v>
+      </c>
+      <c r="Q16">
+        <v>2.75</v>
+      </c>
+      <c r="R16">
+        <v>2.05</v>
+      </c>
+      <c r="S16">
+        <v>4.33</v>
+      </c>
+      <c r="T16">
+        <v>1.5</v>
+      </c>
+      <c r="U16">
+        <v>2.5</v>
+      </c>
+      <c r="V16">
+        <v>3.4</v>
+      </c>
+      <c r="W16">
+        <v>1.3</v>
+      </c>
+      <c r="X16">
+        <v>10</v>
+      </c>
+      <c r="Y16">
+        <v>1.06</v>
+      </c>
+      <c r="Z16">
+        <v>2.27</v>
+      </c>
+      <c r="AA16">
+        <v>3.39</v>
+      </c>
+      <c r="AB16">
+        <v>2.99</v>
+      </c>
+      <c r="AC16">
+        <v>1.08</v>
+      </c>
+      <c r="AD16">
+        <v>7.25</v>
+      </c>
+      <c r="AE16">
+        <v>1.37</v>
+      </c>
+      <c r="AF16">
+        <v>3</v>
+      </c>
+      <c r="AG16">
+        <v>1.92</v>
+      </c>
+      <c r="AH16">
+        <v>1.82</v>
+      </c>
+      <c r="AI16">
+        <v>2</v>
+      </c>
+      <c r="AJ16">
+        <v>1.73</v>
+      </c>
+      <c r="AK16">
+        <v>1.26</v>
+      </c>
+      <c r="AL16">
+        <v>1.32</v>
+      </c>
+      <c r="AM16">
+        <v>1.73</v>
+      </c>
+      <c r="AN16">
+        <v>1</v>
+      </c>
+      <c r="AO16">
+        <v>1.5</v>
+      </c>
+      <c r="AP16">
+        <v>2</v>
+      </c>
+      <c r="AQ16">
+        <v>1</v>
+      </c>
+      <c r="AR16">
+        <v>1.8</v>
+      </c>
+      <c r="AS16">
+        <v>0.95</v>
+      </c>
+      <c r="AT16">
+        <v>2.75</v>
+      </c>
+      <c r="AU16">
+        <v>5</v>
+      </c>
+      <c r="AV16">
+        <v>3</v>
+      </c>
+      <c r="AW16">
+        <v>4</v>
+      </c>
+      <c r="AX16">
+        <v>6</v>
+      </c>
+      <c r="AY16">
+        <v>10</v>
+      </c>
+      <c r="AZ16">
+        <v>11</v>
+      </c>
+      <c r="BA16">
+        <v>2</v>
+      </c>
+      <c r="BB16">
+        <v>1</v>
+      </c>
+      <c r="BC16">
+        <v>3</v>
+      </c>
+      <c r="BD16">
+        <v>1.68</v>
+      </c>
+      <c r="BE16">
+        <v>6.4</v>
+      </c>
+      <c r="BF16">
+        <v>2.43</v>
+      </c>
+      <c r="BG16">
+        <v>1.49</v>
+      </c>
+      <c r="BH16">
+        <v>2.43</v>
+      </c>
+      <c r="BI16">
+        <v>1.8</v>
+      </c>
+      <c r="BJ16">
+        <v>1.89</v>
+      </c>
+      <c r="BK16">
+        <v>2.3</v>
+      </c>
+      <c r="BL16">
+        <v>1.54</v>
+      </c>
+      <c r="BM16">
+        <v>2.95</v>
+      </c>
+      <c r="BN16">
+        <v>1.33</v>
+      </c>
+      <c r="BO16">
+        <v>3.95</v>
+      </c>
+      <c r="BP16">
+        <v>1.2</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/South Korea K League 1_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/South Korea K League 1_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="104">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -293,6 +293,9 @@
   </si>
   <si>
     <t>['57', '89']</t>
+  </si>
+  <si>
+    <t>['88']</t>
   </si>
   <si>
     <t>['32', '87', '90']</t>
@@ -684,7 +687,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP16"/>
+  <dimension ref="A1:BP18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -940,7 +943,7 @@
         <v>82</v>
       </c>
       <c r="P2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="Q2">
         <v>2.75</v>
@@ -1433,7 +1436,7 @@
         <v>2</v>
       </c>
       <c r="AQ4">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -1558,7 +1561,7 @@
         <v>82</v>
       </c>
       <c r="P5" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="Q5">
         <v>2.1</v>
@@ -1764,7 +1767,7 @@
         <v>84</v>
       </c>
       <c r="P6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="Q6">
         <v>3.1</v>
@@ -1970,7 +1973,7 @@
         <v>85</v>
       </c>
       <c r="P7" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="Q7">
         <v>3.5</v>
@@ -2176,7 +2179,7 @@
         <v>86</v>
       </c>
       <c r="P8" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="Q8">
         <v>3.4</v>
@@ -2382,7 +2385,7 @@
         <v>87</v>
       </c>
       <c r="P9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="Q9">
         <v>2.45</v>
@@ -2588,7 +2591,7 @@
         <v>88</v>
       </c>
       <c r="P10" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="Q10">
         <v>3.35</v>
@@ -2669,7 +2672,7 @@
         <v>3</v>
       </c>
       <c r="AQ10">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="AR10">
         <v>1.95</v>
@@ -2794,7 +2797,7 @@
         <v>82</v>
       </c>
       <c r="P11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="Q11">
         <v>3.45</v>
@@ -2872,7 +2875,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AQ11">
         <v>3</v>
@@ -3000,7 +3003,7 @@
         <v>89</v>
       </c>
       <c r="P12" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="Q12">
         <v>2.95</v>
@@ -3078,7 +3081,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AQ12">
         <v>0</v>
@@ -3206,7 +3209,7 @@
         <v>90</v>
       </c>
       <c r="P13" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="Q13">
         <v>2.75</v>
@@ -3824,7 +3827,7 @@
         <v>92</v>
       </c>
       <c r="P16" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="Q16">
         <v>2.75</v>
@@ -3980,6 +3983,418 @@
         <v>3.95</v>
       </c>
       <c r="BP16">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:68">
+      <c r="A17" s="1">
+        <v>16</v>
+      </c>
+      <c r="B17">
+        <v>7806773</v>
+      </c>
+      <c r="C17" t="s">
+        <v>68</v>
+      </c>
+      <c r="D17" t="s">
+        <v>69</v>
+      </c>
+      <c r="E17" s="2">
+        <v>45718.08333333334</v>
+      </c>
+      <c r="F17">
+        <v>3</v>
+      </c>
+      <c r="G17" t="s">
+        <v>77</v>
+      </c>
+      <c r="H17" t="s">
+        <v>79</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17">
+        <v>0</v>
+      </c>
+      <c r="L17">
+        <v>1</v>
+      </c>
+      <c r="M17">
+        <v>0</v>
+      </c>
+      <c r="N17">
+        <v>1</v>
+      </c>
+      <c r="O17" t="s">
+        <v>93</v>
+      </c>
+      <c r="P17" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q17">
+        <v>2.8</v>
+      </c>
+      <c r="R17">
+        <v>2.07</v>
+      </c>
+      <c r="S17">
+        <v>3.75</v>
+      </c>
+      <c r="T17">
+        <v>1.45</v>
+      </c>
+      <c r="U17">
+        <v>2.6</v>
+      </c>
+      <c r="V17">
+        <v>2.88</v>
+      </c>
+      <c r="W17">
+        <v>1.36</v>
+      </c>
+      <c r="X17">
+        <v>7.5</v>
+      </c>
+      <c r="Y17">
+        <v>1.07</v>
+      </c>
+      <c r="Z17">
+        <v>2.28</v>
+      </c>
+      <c r="AA17">
+        <v>3.25</v>
+      </c>
+      <c r="AB17">
+        <v>3.09</v>
+      </c>
+      <c r="AC17">
+        <v>1.07</v>
+      </c>
+      <c r="AD17">
+        <v>8</v>
+      </c>
+      <c r="AE17">
+        <v>1.34</v>
+      </c>
+      <c r="AF17">
+        <v>3.1</v>
+      </c>
+      <c r="AG17">
+        <v>1.95</v>
+      </c>
+      <c r="AH17">
+        <v>1.7</v>
+      </c>
+      <c r="AI17">
+        <v>1.8</v>
+      </c>
+      <c r="AJ17">
+        <v>1.91</v>
+      </c>
+      <c r="AK17">
+        <v>1.33</v>
+      </c>
+      <c r="AL17">
+        <v>1.3</v>
+      </c>
+      <c r="AM17">
+        <v>1.6</v>
+      </c>
+      <c r="AN17">
+        <v>0</v>
+      </c>
+      <c r="AO17">
+        <v>0.5</v>
+      </c>
+      <c r="AP17">
+        <v>1.5</v>
+      </c>
+      <c r="AQ17">
+        <v>0.33</v>
+      </c>
+      <c r="AR17">
+        <v>1.3</v>
+      </c>
+      <c r="AS17">
+        <v>1.1</v>
+      </c>
+      <c r="AT17">
+        <v>2.4</v>
+      </c>
+      <c r="AU17">
+        <v>4</v>
+      </c>
+      <c r="AV17">
+        <v>0</v>
+      </c>
+      <c r="AW17">
+        <v>9</v>
+      </c>
+      <c r="AX17">
+        <v>5</v>
+      </c>
+      <c r="AY17">
+        <v>17</v>
+      </c>
+      <c r="AZ17">
+        <v>8</v>
+      </c>
+      <c r="BA17">
+        <v>2</v>
+      </c>
+      <c r="BB17">
+        <v>2</v>
+      </c>
+      <c r="BC17">
+        <v>4</v>
+      </c>
+      <c r="BD17">
+        <v>1.84</v>
+      </c>
+      <c r="BE17">
+        <v>6.4</v>
+      </c>
+      <c r="BF17">
+        <v>2.18</v>
+      </c>
+      <c r="BG17">
+        <v>1.44</v>
+      </c>
+      <c r="BH17">
+        <v>2.55</v>
+      </c>
+      <c r="BI17">
+        <v>1.74</v>
+      </c>
+      <c r="BJ17">
+        <v>1.97</v>
+      </c>
+      <c r="BK17">
+        <v>2.17</v>
+      </c>
+      <c r="BL17">
+        <v>1.6</v>
+      </c>
+      <c r="BM17">
+        <v>2.8</v>
+      </c>
+      <c r="BN17">
+        <v>1.38</v>
+      </c>
+      <c r="BO17">
+        <v>3.7</v>
+      </c>
+      <c r="BP17">
+        <v>1.23</v>
+      </c>
+    </row>
+    <row r="18" spans="1:68">
+      <c r="A18" s="1">
+        <v>17</v>
+      </c>
+      <c r="B18">
+        <v>7806774</v>
+      </c>
+      <c r="C18" t="s">
+        <v>68</v>
+      </c>
+      <c r="D18" t="s">
+        <v>69</v>
+      </c>
+      <c r="E18" s="2">
+        <v>45718.1875</v>
+      </c>
+      <c r="F18">
+        <v>3</v>
+      </c>
+      <c r="G18" t="s">
+        <v>78</v>
+      </c>
+      <c r="H18" t="s">
+        <v>71</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>0</v>
+      </c>
+      <c r="K18">
+        <v>0</v>
+      </c>
+      <c r="L18">
+        <v>0</v>
+      </c>
+      <c r="M18">
+        <v>0</v>
+      </c>
+      <c r="N18">
+        <v>0</v>
+      </c>
+      <c r="O18" t="s">
+        <v>82</v>
+      </c>
+      <c r="P18" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q18">
+        <v>2.75</v>
+      </c>
+      <c r="R18">
+        <v>2.02</v>
+      </c>
+      <c r="S18">
+        <v>4.1</v>
+      </c>
+      <c r="T18">
+        <v>1.49</v>
+      </c>
+      <c r="U18">
+        <v>2.45</v>
+      </c>
+      <c r="V18">
+        <v>3.2</v>
+      </c>
+      <c r="W18">
+        <v>1.3</v>
+      </c>
+      <c r="X18">
+        <v>7.5</v>
+      </c>
+      <c r="Y18">
+        <v>1.07</v>
+      </c>
+      <c r="Z18">
+        <v>2.07</v>
+      </c>
+      <c r="AA18">
+        <v>3.25</v>
+      </c>
+      <c r="AB18">
+        <v>3.58</v>
+      </c>
+      <c r="AC18">
+        <v>1.07</v>
+      </c>
+      <c r="AD18">
+        <v>8</v>
+      </c>
+      <c r="AE18">
+        <v>1.39</v>
+      </c>
+      <c r="AF18">
+        <v>2.85</v>
+      </c>
+      <c r="AG18">
+        <v>2.05</v>
+      </c>
+      <c r="AH18">
+        <v>1.61</v>
+      </c>
+      <c r="AI18">
+        <v>1.92</v>
+      </c>
+      <c r="AJ18">
+        <v>1.79</v>
+      </c>
+      <c r="AK18">
+        <v>1.29</v>
+      </c>
+      <c r="AL18">
+        <v>1.3</v>
+      </c>
+      <c r="AM18">
+        <v>1.66</v>
+      </c>
+      <c r="AN18">
+        <v>3</v>
+      </c>
+      <c r="AO18">
+        <v>0</v>
+      </c>
+      <c r="AP18">
+        <v>2</v>
+      </c>
+      <c r="AQ18">
+        <v>1</v>
+      </c>
+      <c r="AR18">
+        <v>2.13</v>
+      </c>
+      <c r="AS18">
+        <v>0</v>
+      </c>
+      <c r="AT18">
+        <v>2.13</v>
+      </c>
+      <c r="AU18">
+        <v>4</v>
+      </c>
+      <c r="AV18">
+        <v>7</v>
+      </c>
+      <c r="AW18">
+        <v>4</v>
+      </c>
+      <c r="AX18">
+        <v>5</v>
+      </c>
+      <c r="AY18">
+        <v>8</v>
+      </c>
+      <c r="AZ18">
+        <v>14</v>
+      </c>
+      <c r="BA18">
+        <v>6</v>
+      </c>
+      <c r="BB18">
+        <v>5</v>
+      </c>
+      <c r="BC18">
+        <v>11</v>
+      </c>
+      <c r="BD18">
+        <v>1.73</v>
+      </c>
+      <c r="BE18">
+        <v>6.4</v>
+      </c>
+      <c r="BF18">
+        <v>2.35</v>
+      </c>
+      <c r="BG18">
+        <v>1.49</v>
+      </c>
+      <c r="BH18">
+        <v>2.43</v>
+      </c>
+      <c r="BI18">
+        <v>1.8</v>
+      </c>
+      <c r="BJ18">
+        <v>1.89</v>
+      </c>
+      <c r="BK18">
+        <v>2.28</v>
+      </c>
+      <c r="BL18">
+        <v>1.54</v>
+      </c>
+      <c r="BM18">
+        <v>2.95</v>
+      </c>
+      <c r="BN18">
+        <v>1.33</v>
+      </c>
+      <c r="BO18">
+        <v>4</v>
+      </c>
+      <c r="BP18">
         <v>1.2</v>
       </c>
     </row>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/South Korea K League 1_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/South Korea K League 1_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="104">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -687,7 +687,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP18"/>
+  <dimension ref="A1:BP19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1848,7 +1848,7 @@
         <v>2</v>
       </c>
       <c r="AQ6">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2260,7 +2260,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ8">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AR8">
         <v>1.38</v>
@@ -2463,7 +2463,7 @@
         <v>3</v>
       </c>
       <c r="AP9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AQ9">
         <v>1</v>
@@ -4396,6 +4396,212 @@
       </c>
       <c r="BP18">
         <v>1.2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:68">
+      <c r="A19" s="1">
+        <v>18</v>
+      </c>
+      <c r="B19">
+        <v>7806775</v>
+      </c>
+      <c r="C19" t="s">
+        <v>68</v>
+      </c>
+      <c r="D19" t="s">
+        <v>69</v>
+      </c>
+      <c r="E19" s="2">
+        <v>45719.08333333334</v>
+      </c>
+      <c r="F19">
+        <v>3</v>
+      </c>
+      <c r="G19" t="s">
+        <v>76</v>
+      </c>
+      <c r="H19" t="s">
+        <v>81</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19">
+        <v>0</v>
+      </c>
+      <c r="L19">
+        <v>0</v>
+      </c>
+      <c r="M19">
+        <v>0</v>
+      </c>
+      <c r="N19">
+        <v>0</v>
+      </c>
+      <c r="O19" t="s">
+        <v>82</v>
+      </c>
+      <c r="P19" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q19">
+        <v>2.88</v>
+      </c>
+      <c r="R19">
+        <v>2.1</v>
+      </c>
+      <c r="S19">
+        <v>3.75</v>
+      </c>
+      <c r="T19">
+        <v>1.44</v>
+      </c>
+      <c r="U19">
+        <v>2.63</v>
+      </c>
+      <c r="V19">
+        <v>3.25</v>
+      </c>
+      <c r="W19">
+        <v>1.33</v>
+      </c>
+      <c r="X19">
+        <v>9</v>
+      </c>
+      <c r="Y19">
+        <v>1.07</v>
+      </c>
+      <c r="Z19">
+        <v>2.2</v>
+      </c>
+      <c r="AA19">
+        <v>3.25</v>
+      </c>
+      <c r="AB19">
+        <v>3.26</v>
+      </c>
+      <c r="AC19">
+        <v>1.07</v>
+      </c>
+      <c r="AD19">
+        <v>8</v>
+      </c>
+      <c r="AE19">
+        <v>1.32</v>
+      </c>
+      <c r="AF19">
+        <v>3.2</v>
+      </c>
+      <c r="AG19">
+        <v>1.98</v>
+      </c>
+      <c r="AH19">
+        <v>1.77</v>
+      </c>
+      <c r="AI19">
+        <v>1.8</v>
+      </c>
+      <c r="AJ19">
+        <v>1.91</v>
+      </c>
+      <c r="AK19">
+        <v>1.31</v>
+      </c>
+      <c r="AL19">
+        <v>1.3</v>
+      </c>
+      <c r="AM19">
+        <v>1.61</v>
+      </c>
+      <c r="AN19">
+        <v>3</v>
+      </c>
+      <c r="AO19">
+        <v>1.5</v>
+      </c>
+      <c r="AP19">
+        <v>2</v>
+      </c>
+      <c r="AQ19">
+        <v>1.33</v>
+      </c>
+      <c r="AR19">
+        <v>1.46</v>
+      </c>
+      <c r="AS19">
+        <v>1.54</v>
+      </c>
+      <c r="AT19">
+        <v>3</v>
+      </c>
+      <c r="AU19">
+        <v>-1</v>
+      </c>
+      <c r="AV19">
+        <v>-1</v>
+      </c>
+      <c r="AW19">
+        <v>-1</v>
+      </c>
+      <c r="AX19">
+        <v>-1</v>
+      </c>
+      <c r="AY19">
+        <v>-1</v>
+      </c>
+      <c r="AZ19">
+        <v>-1</v>
+      </c>
+      <c r="BA19">
+        <v>0</v>
+      </c>
+      <c r="BB19">
+        <v>3</v>
+      </c>
+      <c r="BC19">
+        <v>3</v>
+      </c>
+      <c r="BD19">
+        <v>1.77</v>
+      </c>
+      <c r="BE19">
+        <v>6.1</v>
+      </c>
+      <c r="BF19">
+        <v>2.3</v>
+      </c>
+      <c r="BG19">
+        <v>1.4</v>
+      </c>
+      <c r="BH19">
+        <v>2.65</v>
+      </c>
+      <c r="BI19">
+        <v>1.68</v>
+      </c>
+      <c r="BJ19">
+        <v>2.05</v>
+      </c>
+      <c r="BK19">
+        <v>2.08</v>
+      </c>
+      <c r="BL19">
+        <v>1.65</v>
+      </c>
+      <c r="BM19">
+        <v>2.65</v>
+      </c>
+      <c r="BN19">
+        <v>1.41</v>
+      </c>
+      <c r="BO19">
+        <v>3.55</v>
+      </c>
+      <c r="BP19">
+        <v>1.24</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/South Korea K League 1_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/South Korea K League 1_2025.xlsx
@@ -4538,22 +4538,22 @@
         <v>3</v>
       </c>
       <c r="AU19">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AV19">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AW19">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AX19">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AY19">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AZ19">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="BA19">
         <v>0</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/South Korea K League 1_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/South Korea K League 1_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="108">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -298,6 +298,12 @@
     <t>['88']</t>
   </si>
   <si>
+    <t>['71']</t>
+  </si>
+  <si>
+    <t>['18']</t>
+  </si>
+  <si>
     <t>['32', '87', '90']</t>
   </si>
   <si>
@@ -326,6 +332,12 @@
   </si>
   <si>
     <t>['16']</t>
+  </si>
+  <si>
+    <t>['7', '10']</t>
+  </si>
+  <si>
+    <t>['20', '36', '38']</t>
   </si>
 </sst>
 </file>
@@ -687,7 +699,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP19"/>
+  <dimension ref="A1:BP22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -943,7 +955,7 @@
         <v>82</v>
       </c>
       <c r="P2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="Q2">
         <v>2.75</v>
@@ -1230,7 +1242,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ3">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -1561,7 +1573,7 @@
         <v>82</v>
       </c>
       <c r="P5" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="Q5">
         <v>2.1</v>
@@ -1767,7 +1779,7 @@
         <v>84</v>
       </c>
       <c r="P6" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="Q6">
         <v>3.1</v>
@@ -1848,7 +1860,7 @@
         <v>2</v>
       </c>
       <c r="AQ6">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -1973,7 +1985,7 @@
         <v>85</v>
       </c>
       <c r="P7" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="Q7">
         <v>3.5</v>
@@ -2051,7 +2063,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AQ7">
         <v>0</v>
@@ -2179,7 +2191,7 @@
         <v>86</v>
       </c>
       <c r="P8" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="Q8">
         <v>3.4</v>
@@ -2260,7 +2272,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ8">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="AR8">
         <v>1.38</v>
@@ -2385,7 +2397,7 @@
         <v>87</v>
       </c>
       <c r="P9" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="Q9">
         <v>2.45</v>
@@ -2591,7 +2603,7 @@
         <v>88</v>
       </c>
       <c r="P10" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="Q10">
         <v>3.35</v>
@@ -2669,7 +2681,7 @@
         <v>1</v>
       </c>
       <c r="AP10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AQ10">
         <v>0.33</v>
@@ -2797,7 +2809,7 @@
         <v>82</v>
       </c>
       <c r="P11" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="Q11">
         <v>3.45</v>
@@ -3003,7 +3015,7 @@
         <v>89</v>
       </c>
       <c r="P12" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="Q12">
         <v>2.95</v>
@@ -3209,7 +3221,7 @@
         <v>90</v>
       </c>
       <c r="P13" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="Q13">
         <v>2.75</v>
@@ -3827,7 +3839,7 @@
         <v>92</v>
       </c>
       <c r="P16" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="Q16">
         <v>2.75</v>
@@ -4526,7 +4538,7 @@
         <v>2</v>
       </c>
       <c r="AQ19">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="AR19">
         <v>1.46</v>
@@ -4602,6 +4614,624 @@
       </c>
       <c r="BP19">
         <v>1.24</v>
+      </c>
+    </row>
+    <row r="20" spans="1:68">
+      <c r="A20" s="1">
+        <v>19</v>
+      </c>
+      <c r="B20">
+        <v>7806776</v>
+      </c>
+      <c r="C20" t="s">
+        <v>68</v>
+      </c>
+      <c r="D20" t="s">
+        <v>69</v>
+      </c>
+      <c r="E20" s="2">
+        <v>45724.08333333334</v>
+      </c>
+      <c r="F20">
+        <v>4</v>
+      </c>
+      <c r="G20" t="s">
+        <v>79</v>
+      </c>
+      <c r="H20" t="s">
+        <v>76</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>0</v>
+      </c>
+      <c r="K20">
+        <v>0</v>
+      </c>
+      <c r="L20">
+        <v>0</v>
+      </c>
+      <c r="M20">
+        <v>0</v>
+      </c>
+      <c r="N20">
+        <v>0</v>
+      </c>
+      <c r="O20" t="s">
+        <v>82</v>
+      </c>
+      <c r="P20" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q20">
+        <v>3.65</v>
+      </c>
+      <c r="R20">
+        <v>2.05</v>
+      </c>
+      <c r="S20">
+        <v>2.8</v>
+      </c>
+      <c r="T20">
+        <v>1.4</v>
+      </c>
+      <c r="U20">
+        <v>2.75</v>
+      </c>
+      <c r="V20">
+        <v>2.75</v>
+      </c>
+      <c r="W20">
+        <v>1.4</v>
+      </c>
+      <c r="X20">
+        <v>7.8</v>
+      </c>
+      <c r="Y20">
+        <v>1.02</v>
+      </c>
+      <c r="Z20">
+        <v>3.2</v>
+      </c>
+      <c r="AA20">
+        <v>3.25</v>
+      </c>
+      <c r="AB20">
+        <v>2.22</v>
+      </c>
+      <c r="AC20">
+        <v>1.07</v>
+      </c>
+      <c r="AD20">
+        <v>8</v>
+      </c>
+      <c r="AE20">
+        <v>1.36</v>
+      </c>
+      <c r="AF20">
+        <v>3.1</v>
+      </c>
+      <c r="AG20">
+        <v>2</v>
+      </c>
+      <c r="AH20">
+        <v>1.75</v>
+      </c>
+      <c r="AI20">
+        <v>1.77</v>
+      </c>
+      <c r="AJ20">
+        <v>1.91</v>
+      </c>
+      <c r="AK20">
+        <v>1.62</v>
+      </c>
+      <c r="AL20">
+        <v>1.28</v>
+      </c>
+      <c r="AM20">
+        <v>1.33</v>
+      </c>
+      <c r="AN20">
+        <v>0</v>
+      </c>
+      <c r="AO20">
+        <v>0</v>
+      </c>
+      <c r="AP20">
+        <v>1</v>
+      </c>
+      <c r="AQ20">
+        <v>0.5</v>
+      </c>
+      <c r="AR20">
+        <v>0</v>
+      </c>
+      <c r="AS20">
+        <v>1.36</v>
+      </c>
+      <c r="AT20">
+        <v>1.36</v>
+      </c>
+      <c r="AU20">
+        <v>5</v>
+      </c>
+      <c r="AV20">
+        <v>6</v>
+      </c>
+      <c r="AW20">
+        <v>4</v>
+      </c>
+      <c r="AX20">
+        <v>4</v>
+      </c>
+      <c r="AY20">
+        <v>10</v>
+      </c>
+      <c r="AZ20">
+        <v>11</v>
+      </c>
+      <c r="BA20">
+        <v>4</v>
+      </c>
+      <c r="BB20">
+        <v>4</v>
+      </c>
+      <c r="BC20">
+        <v>8</v>
+      </c>
+      <c r="BD20">
+        <v>2.25</v>
+      </c>
+      <c r="BE20">
+        <v>6.25</v>
+      </c>
+      <c r="BF20">
+        <v>1.79</v>
+      </c>
+      <c r="BG20">
+        <v>1.44</v>
+      </c>
+      <c r="BH20">
+        <v>2.55</v>
+      </c>
+      <c r="BI20">
+        <v>1.74</v>
+      </c>
+      <c r="BJ20">
+        <v>1.97</v>
+      </c>
+      <c r="BK20">
+        <v>2.17</v>
+      </c>
+      <c r="BL20">
+        <v>1.6</v>
+      </c>
+      <c r="BM20">
+        <v>2.8</v>
+      </c>
+      <c r="BN20">
+        <v>1.38</v>
+      </c>
+      <c r="BO20">
+        <v>3.65</v>
+      </c>
+      <c r="BP20">
+        <v>1.23</v>
+      </c>
+    </row>
+    <row r="21" spans="1:68">
+      <c r="A21" s="1">
+        <v>20</v>
+      </c>
+      <c r="B21">
+        <v>7806777</v>
+      </c>
+      <c r="C21" t="s">
+        <v>68</v>
+      </c>
+      <c r="D21" t="s">
+        <v>69</v>
+      </c>
+      <c r="E21" s="2">
+        <v>45724.1875</v>
+      </c>
+      <c r="F21">
+        <v>4</v>
+      </c>
+      <c r="G21" t="s">
+        <v>75</v>
+      </c>
+      <c r="H21" t="s">
+        <v>77</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>2</v>
+      </c>
+      <c r="K21">
+        <v>2</v>
+      </c>
+      <c r="L21">
+        <v>1</v>
+      </c>
+      <c r="M21">
+        <v>2</v>
+      </c>
+      <c r="N21">
+        <v>3</v>
+      </c>
+      <c r="O21" t="s">
+        <v>94</v>
+      </c>
+      <c r="P21" t="s">
+        <v>106</v>
+      </c>
+      <c r="Q21">
+        <v>3.1</v>
+      </c>
+      <c r="R21">
+        <v>2.05</v>
+      </c>
+      <c r="S21">
+        <v>3.25</v>
+      </c>
+      <c r="T21">
+        <v>1.4</v>
+      </c>
+      <c r="U21">
+        <v>2.75</v>
+      </c>
+      <c r="V21">
+        <v>2.8</v>
+      </c>
+      <c r="W21">
+        <v>1.38</v>
+      </c>
+      <c r="X21">
+        <v>8</v>
+      </c>
+      <c r="Y21">
+        <v>1.02</v>
+      </c>
+      <c r="Z21">
+        <v>2.15</v>
+      </c>
+      <c r="AA21">
+        <v>3.26</v>
+      </c>
+      <c r="AB21">
+        <v>3.35</v>
+      </c>
+      <c r="AC21">
+        <v>1.07</v>
+      </c>
+      <c r="AD21">
+        <v>8</v>
+      </c>
+      <c r="AE21">
+        <v>1.33</v>
+      </c>
+      <c r="AF21">
+        <v>3.25</v>
+      </c>
+      <c r="AG21">
+        <v>1.85</v>
+      </c>
+      <c r="AH21">
+        <v>1.89</v>
+      </c>
+      <c r="AI21">
+        <v>1.7</v>
+      </c>
+      <c r="AJ21">
+        <v>2</v>
+      </c>
+      <c r="AK21">
+        <v>1.42</v>
+      </c>
+      <c r="AL21">
+        <v>1.3</v>
+      </c>
+      <c r="AM21">
+        <v>1.5</v>
+      </c>
+      <c r="AN21">
+        <v>3</v>
+      </c>
+      <c r="AO21">
+        <v>3</v>
+      </c>
+      <c r="AP21">
+        <v>2</v>
+      </c>
+      <c r="AQ21">
+        <v>3</v>
+      </c>
+      <c r="AR21">
+        <v>1.94</v>
+      </c>
+      <c r="AS21">
+        <v>1.18</v>
+      </c>
+      <c r="AT21">
+        <v>3.12</v>
+      </c>
+      <c r="AU21">
+        <v>6</v>
+      </c>
+      <c r="AV21">
+        <v>6</v>
+      </c>
+      <c r="AW21">
+        <v>11</v>
+      </c>
+      <c r="AX21">
+        <v>3</v>
+      </c>
+      <c r="AY21">
+        <v>22</v>
+      </c>
+      <c r="AZ21">
+        <v>11</v>
+      </c>
+      <c r="BA21">
+        <v>6</v>
+      </c>
+      <c r="BB21">
+        <v>2</v>
+      </c>
+      <c r="BC21">
+        <v>8</v>
+      </c>
+      <c r="BD21">
+        <v>1.95</v>
+      </c>
+      <c r="BE21">
+        <v>6.4</v>
+      </c>
+      <c r="BF21">
+        <v>2.05</v>
+      </c>
+      <c r="BG21">
+        <v>1.38</v>
+      </c>
+      <c r="BH21">
+        <v>2.7</v>
+      </c>
+      <c r="BI21">
+        <v>1.66</v>
+      </c>
+      <c r="BJ21">
+        <v>2.08</v>
+      </c>
+      <c r="BK21">
+        <v>2.05</v>
+      </c>
+      <c r="BL21">
+        <v>1.68</v>
+      </c>
+      <c r="BM21">
+        <v>2.6</v>
+      </c>
+      <c r="BN21">
+        <v>1.43</v>
+      </c>
+      <c r="BO21">
+        <v>3.4</v>
+      </c>
+      <c r="BP21">
+        <v>1.26</v>
+      </c>
+    </row>
+    <row r="22" spans="1:68">
+      <c r="A22" s="1">
+        <v>21</v>
+      </c>
+      <c r="B22">
+        <v>7806778</v>
+      </c>
+      <c r="C22" t="s">
+        <v>68</v>
+      </c>
+      <c r="D22" t="s">
+        <v>69</v>
+      </c>
+      <c r="E22" s="2">
+        <v>45724.1875</v>
+      </c>
+      <c r="F22">
+        <v>4</v>
+      </c>
+      <c r="G22" t="s">
+        <v>80</v>
+      </c>
+      <c r="H22" t="s">
+        <v>81</v>
+      </c>
+      <c r="I22">
+        <v>1</v>
+      </c>
+      <c r="J22">
+        <v>3</v>
+      </c>
+      <c r="K22">
+        <v>4</v>
+      </c>
+      <c r="L22">
+        <v>1</v>
+      </c>
+      <c r="M22">
+        <v>3</v>
+      </c>
+      <c r="N22">
+        <v>4</v>
+      </c>
+      <c r="O22" t="s">
+        <v>95</v>
+      </c>
+      <c r="P22" t="s">
+        <v>107</v>
+      </c>
+      <c r="Q22">
+        <v>3.6</v>
+      </c>
+      <c r="R22">
+        <v>2.1</v>
+      </c>
+      <c r="S22">
+        <v>3</v>
+      </c>
+      <c r="T22">
+        <v>1.4</v>
+      </c>
+      <c r="U22">
+        <v>2.75</v>
+      </c>
+      <c r="V22">
+        <v>3</v>
+      </c>
+      <c r="W22">
+        <v>1.36</v>
+      </c>
+      <c r="X22">
+        <v>8</v>
+      </c>
+      <c r="Y22">
+        <v>1.08</v>
+      </c>
+      <c r="Z22">
+        <v>3.34</v>
+      </c>
+      <c r="AA22">
+        <v>3.4</v>
+      </c>
+      <c r="AB22">
+        <v>2.1</v>
+      </c>
+      <c r="AC22">
+        <v>1.06</v>
+      </c>
+      <c r="AD22">
+        <v>8.5</v>
+      </c>
+      <c r="AE22">
+        <v>1.3</v>
+      </c>
+      <c r="AF22">
+        <v>3.4</v>
+      </c>
+      <c r="AG22">
+        <v>1.92</v>
+      </c>
+      <c r="AH22">
+        <v>1.82</v>
+      </c>
+      <c r="AI22">
+        <v>1.73</v>
+      </c>
+      <c r="AJ22">
+        <v>2</v>
+      </c>
+      <c r="AK22">
+        <v>1.57</v>
+      </c>
+      <c r="AL22">
+        <v>1.3</v>
+      </c>
+      <c r="AM22">
+        <v>1.4</v>
+      </c>
+      <c r="AN22">
+        <v>0</v>
+      </c>
+      <c r="AO22">
+        <v>1.33</v>
+      </c>
+      <c r="AP22">
+        <v>0</v>
+      </c>
+      <c r="AQ22">
+        <v>1.75</v>
+      </c>
+      <c r="AR22">
+        <v>0</v>
+      </c>
+      <c r="AS22">
+        <v>1.11</v>
+      </c>
+      <c r="AT22">
+        <v>1.11</v>
+      </c>
+      <c r="AU22">
+        <v>4</v>
+      </c>
+      <c r="AV22">
+        <v>7</v>
+      </c>
+      <c r="AW22">
+        <v>3</v>
+      </c>
+      <c r="AX22">
+        <v>9</v>
+      </c>
+      <c r="AY22">
+        <v>9</v>
+      </c>
+      <c r="AZ22">
+        <v>18</v>
+      </c>
+      <c r="BA22">
+        <v>5</v>
+      </c>
+      <c r="BB22">
+        <v>5</v>
+      </c>
+      <c r="BC22">
+        <v>10</v>
+      </c>
+      <c r="BD22">
+        <v>2.15</v>
+      </c>
+      <c r="BE22">
+        <v>6.25</v>
+      </c>
+      <c r="BF22">
+        <v>1.88</v>
+      </c>
+      <c r="BG22">
+        <v>1.41</v>
+      </c>
+      <c r="BH22">
+        <v>2.65</v>
+      </c>
+      <c r="BI22">
+        <v>1.77</v>
+      </c>
+      <c r="BJ22">
+        <v>1.95</v>
+      </c>
+      <c r="BK22">
+        <v>2.12</v>
+      </c>
+      <c r="BL22">
+        <v>1.63</v>
+      </c>
+      <c r="BM22">
+        <v>2.7</v>
+      </c>
+      <c r="BN22">
+        <v>1.38</v>
+      </c>
+      <c r="BO22">
+        <v>3.65</v>
+      </c>
+      <c r="BP22">
+        <v>1.23</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/South Korea K League 1_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/South Korea K League 1_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="110">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -304,6 +304,9 @@
     <t>['18']</t>
   </si>
   <si>
+    <t>['33', '71']</t>
+  </si>
+  <si>
     <t>['32', '87', '90']</t>
   </si>
   <si>
@@ -338,6 +341,9 @@
   </si>
   <si>
     <t>['20', '36', '38']</t>
+  </si>
+  <si>
+    <t>['90']</t>
   </si>
 </sst>
 </file>
@@ -699,7 +705,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP22"/>
+  <dimension ref="A1:BP24"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -955,7 +961,7 @@
         <v>82</v>
       </c>
       <c r="P2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="Q2">
         <v>2.75</v>
@@ -1573,7 +1579,7 @@
         <v>82</v>
       </c>
       <c r="P5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="Q5">
         <v>2.1</v>
@@ -1651,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AQ5">
         <v>1</v>
@@ -1779,7 +1785,7 @@
         <v>84</v>
       </c>
       <c r="P6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="Q6">
         <v>3.1</v>
@@ -1857,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>2</v>
+        <v>1.33</v>
       </c>
       <c r="AQ6">
         <v>1.75</v>
@@ -1985,7 +1991,7 @@
         <v>85</v>
       </c>
       <c r="P7" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="Q7">
         <v>3.5</v>
@@ -2066,7 +2072,7 @@
         <v>2</v>
       </c>
       <c r="AQ7">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2191,7 +2197,7 @@
         <v>86</v>
       </c>
       <c r="P8" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="Q8">
         <v>3.4</v>
@@ -2397,7 +2403,7 @@
         <v>87</v>
       </c>
       <c r="P9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="Q9">
         <v>2.45</v>
@@ -2603,7 +2609,7 @@
         <v>88</v>
       </c>
       <c r="P10" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="Q10">
         <v>3.35</v>
@@ -2809,7 +2815,7 @@
         <v>82</v>
       </c>
       <c r="P11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Q11">
         <v>3.45</v>
@@ -3015,7 +3021,7 @@
         <v>89</v>
       </c>
       <c r="P12" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="Q12">
         <v>2.95</v>
@@ -3221,7 +3227,7 @@
         <v>90</v>
       </c>
       <c r="P13" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="Q13">
         <v>2.75</v>
@@ -3299,7 +3305,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>2</v>
+        <v>1.33</v>
       </c>
       <c r="AQ13">
         <v>1</v>
@@ -3505,7 +3511,7 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AQ14">
         <v>0</v>
@@ -3839,7 +3845,7 @@
         <v>92</v>
       </c>
       <c r="P16" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="Q16">
         <v>2.75</v>
@@ -4332,7 +4338,7 @@
         <v>2</v>
       </c>
       <c r="AQ18">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AR18">
         <v>2.13</v>
@@ -4869,7 +4875,7 @@
         <v>94</v>
       </c>
       <c r="P21" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="Q21">
         <v>3.1</v>
@@ -5075,7 +5081,7 @@
         <v>95</v>
       </c>
       <c r="P22" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="Q22">
         <v>3.6</v>
@@ -5232,6 +5238,418 @@
       </c>
       <c r="BP22">
         <v>1.23</v>
+      </c>
+    </row>
+    <row r="23" spans="1:68">
+      <c r="A23" s="1">
+        <v>22</v>
+      </c>
+      <c r="B23">
+        <v>7806779</v>
+      </c>
+      <c r="C23" t="s">
+        <v>68</v>
+      </c>
+      <c r="D23" t="s">
+        <v>69</v>
+      </c>
+      <c r="E23" s="2">
+        <v>45725.08333333334</v>
+      </c>
+      <c r="F23">
+        <v>4</v>
+      </c>
+      <c r="G23" t="s">
+        <v>73</v>
+      </c>
+      <c r="H23" t="s">
+        <v>71</v>
+      </c>
+      <c r="I23">
+        <v>1</v>
+      </c>
+      <c r="J23">
+        <v>0</v>
+      </c>
+      <c r="K23">
+        <v>1</v>
+      </c>
+      <c r="L23">
+        <v>2</v>
+      </c>
+      <c r="M23">
+        <v>0</v>
+      </c>
+      <c r="N23">
+        <v>2</v>
+      </c>
+      <c r="O23" t="s">
+        <v>96</v>
+      </c>
+      <c r="P23" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q23">
+        <v>2.6</v>
+      </c>
+      <c r="R23">
+        <v>2.2</v>
+      </c>
+      <c r="S23">
+        <v>4.5</v>
+      </c>
+      <c r="T23">
+        <v>1.4</v>
+      </c>
+      <c r="U23">
+        <v>2.75</v>
+      </c>
+      <c r="V23">
+        <v>3</v>
+      </c>
+      <c r="W23">
+        <v>1.36</v>
+      </c>
+      <c r="X23">
+        <v>8</v>
+      </c>
+      <c r="Y23">
+        <v>1.08</v>
+      </c>
+      <c r="Z23">
+        <v>1.9</v>
+      </c>
+      <c r="AA23">
+        <v>3.41</v>
+      </c>
+      <c r="AB23">
+        <v>3.99</v>
+      </c>
+      <c r="AC23">
+        <v>1.06</v>
+      </c>
+      <c r="AD23">
+        <v>8.5</v>
+      </c>
+      <c r="AE23">
+        <v>1.33</v>
+      </c>
+      <c r="AF23">
+        <v>3.3</v>
+      </c>
+      <c r="AG23">
+        <v>1.95</v>
+      </c>
+      <c r="AH23">
+        <v>1.79</v>
+      </c>
+      <c r="AI23">
+        <v>1.8</v>
+      </c>
+      <c r="AJ23">
+        <v>1.91</v>
+      </c>
+      <c r="AK23">
+        <v>1.25</v>
+      </c>
+      <c r="AL23">
+        <v>1.25</v>
+      </c>
+      <c r="AM23">
+        <v>1.83</v>
+      </c>
+      <c r="AN23">
+        <v>1.5</v>
+      </c>
+      <c r="AO23">
+        <v>1</v>
+      </c>
+      <c r="AP23">
+        <v>2</v>
+      </c>
+      <c r="AQ23">
+        <v>0.5</v>
+      </c>
+      <c r="AR23">
+        <v>2.19</v>
+      </c>
+      <c r="AS23">
+        <v>1.68</v>
+      </c>
+      <c r="AT23">
+        <v>3.87</v>
+      </c>
+      <c r="AU23">
+        <v>7</v>
+      </c>
+      <c r="AV23">
+        <v>2</v>
+      </c>
+      <c r="AW23">
+        <v>11</v>
+      </c>
+      <c r="AX23">
+        <v>9</v>
+      </c>
+      <c r="AY23">
+        <v>22</v>
+      </c>
+      <c r="AZ23">
+        <v>12</v>
+      </c>
+      <c r="BA23">
+        <v>8</v>
+      </c>
+      <c r="BB23">
+        <v>6</v>
+      </c>
+      <c r="BC23">
+        <v>14</v>
+      </c>
+      <c r="BD23">
+        <v>1.63</v>
+      </c>
+      <c r="BE23">
+        <v>6.4</v>
+      </c>
+      <c r="BF23">
+        <v>2.55</v>
+      </c>
+      <c r="BG23">
+        <v>1.43</v>
+      </c>
+      <c r="BH23">
+        <v>2.6</v>
+      </c>
+      <c r="BI23">
+        <v>1.73</v>
+      </c>
+      <c r="BJ23">
+        <v>1.98</v>
+      </c>
+      <c r="BK23">
+        <v>2.15</v>
+      </c>
+      <c r="BL23">
+        <v>1.61</v>
+      </c>
+      <c r="BM23">
+        <v>2.8</v>
+      </c>
+      <c r="BN23">
+        <v>1.38</v>
+      </c>
+      <c r="BO23">
+        <v>3.7</v>
+      </c>
+      <c r="BP23">
+        <v>1.23</v>
+      </c>
+    </row>
+    <row r="24" spans="1:68">
+      <c r="A24" s="1">
+        <v>23</v>
+      </c>
+      <c r="B24">
+        <v>7806781</v>
+      </c>
+      <c r="C24" t="s">
+        <v>68</v>
+      </c>
+      <c r="D24" t="s">
+        <v>69</v>
+      </c>
+      <c r="E24" s="2">
+        <v>45725.1875</v>
+      </c>
+      <c r="F24">
+        <v>4</v>
+      </c>
+      <c r="G24" t="s">
+        <v>74</v>
+      </c>
+      <c r="H24" t="s">
+        <v>78</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>0</v>
+      </c>
+      <c r="K24">
+        <v>0</v>
+      </c>
+      <c r="L24">
+        <v>0</v>
+      </c>
+      <c r="M24">
+        <v>1</v>
+      </c>
+      <c r="N24">
+        <v>1</v>
+      </c>
+      <c r="O24" t="s">
+        <v>82</v>
+      </c>
+      <c r="P24" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q24">
+        <v>2.75</v>
+      </c>
+      <c r="R24">
+        <v>2.05</v>
+      </c>
+      <c r="S24">
+        <v>4.33</v>
+      </c>
+      <c r="T24">
+        <v>1.44</v>
+      </c>
+      <c r="U24">
+        <v>2.63</v>
+      </c>
+      <c r="V24">
+        <v>3.25</v>
+      </c>
+      <c r="W24">
+        <v>1.33</v>
+      </c>
+      <c r="X24">
+        <v>10</v>
+      </c>
+      <c r="Y24">
+        <v>1.06</v>
+      </c>
+      <c r="Z24">
+        <v>2.01</v>
+      </c>
+      <c r="AA24">
+        <v>3.25</v>
+      </c>
+      <c r="AB24">
+        <v>3.78</v>
+      </c>
+      <c r="AC24">
+        <v>1.07</v>
+      </c>
+      <c r="AD24">
+        <v>8</v>
+      </c>
+      <c r="AE24">
+        <v>1.35</v>
+      </c>
+      <c r="AF24">
+        <v>3.1</v>
+      </c>
+      <c r="AG24">
+        <v>2</v>
+      </c>
+      <c r="AH24">
+        <v>1.67</v>
+      </c>
+      <c r="AI24">
+        <v>1.83</v>
+      </c>
+      <c r="AJ24">
+        <v>1.83</v>
+      </c>
+      <c r="AK24">
+        <v>1.25</v>
+      </c>
+      <c r="AL24">
+        <v>1.25</v>
+      </c>
+      <c r="AM24">
+        <v>1.77</v>
+      </c>
+      <c r="AN24">
+        <v>2</v>
+      </c>
+      <c r="AO24">
+        <v>0</v>
+      </c>
+      <c r="AP24">
+        <v>1.33</v>
+      </c>
+      <c r="AQ24">
+        <v>1.5</v>
+      </c>
+      <c r="AR24">
+        <v>1.82</v>
+      </c>
+      <c r="AS24">
+        <v>1.13</v>
+      </c>
+      <c r="AT24">
+        <v>2.95</v>
+      </c>
+      <c r="AU24">
+        <v>3</v>
+      </c>
+      <c r="AV24">
+        <v>2</v>
+      </c>
+      <c r="AW24">
+        <v>6</v>
+      </c>
+      <c r="AX24">
+        <v>2</v>
+      </c>
+      <c r="AY24">
+        <v>10</v>
+      </c>
+      <c r="AZ24">
+        <v>6</v>
+      </c>
+      <c r="BA24">
+        <v>5</v>
+      </c>
+      <c r="BB24">
+        <v>0</v>
+      </c>
+      <c r="BC24">
+        <v>5</v>
+      </c>
+      <c r="BD24">
+        <v>1.67</v>
+      </c>
+      <c r="BE24">
+        <v>6.4</v>
+      </c>
+      <c r="BF24">
+        <v>2.48</v>
+      </c>
+      <c r="BG24">
+        <v>1.41</v>
+      </c>
+      <c r="BH24">
+        <v>2.65</v>
+      </c>
+      <c r="BI24">
+        <v>1.7</v>
+      </c>
+      <c r="BJ24">
+        <v>2</v>
+      </c>
+      <c r="BK24">
+        <v>2.12</v>
+      </c>
+      <c r="BL24">
+        <v>1.63</v>
+      </c>
+      <c r="BM24">
+        <v>2.7</v>
+      </c>
+      <c r="BN24">
+        <v>1.38</v>
+      </c>
+      <c r="BO24">
+        <v>3.55</v>
+      </c>
+      <c r="BP24">
+        <v>1.24</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/South Korea K League 1_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/South Korea K League 1_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="114">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -307,6 +307,9 @@
     <t>['33', '71']</t>
   </si>
   <si>
+    <t>['56']</t>
+  </si>
+  <si>
     <t>['32', '87', '90']</t>
   </si>
   <si>
@@ -344,6 +347,15 @@
   </si>
   <si>
     <t>['90']</t>
+  </si>
+  <si>
+    <t>['50', '90+1', '90+4']</t>
+  </si>
+  <si>
+    <t>['19']</t>
+  </si>
+  <si>
+    <t>['20']</t>
   </si>
 </sst>
 </file>
@@ -705,7 +717,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP24"/>
+  <dimension ref="A1:BP27"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -961,7 +973,7 @@
         <v>82</v>
       </c>
       <c r="P2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="Q2">
         <v>2.75</v>
@@ -1245,10 +1257,10 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AQ3">
-        <v>0.5</v>
+        <v>1.33</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -1579,7 +1591,7 @@
         <v>82</v>
       </c>
       <c r="P5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="Q5">
         <v>2.1</v>
@@ -1660,7 +1672,7 @@
         <v>2</v>
       </c>
       <c r="AQ5">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -1785,7 +1797,7 @@
         <v>84</v>
       </c>
       <c r="P6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="Q6">
         <v>3.1</v>
@@ -1991,7 +2003,7 @@
         <v>85</v>
       </c>
       <c r="P7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="Q7">
         <v>3.5</v>
@@ -2069,7 +2081,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AQ7">
         <v>1.5</v>
@@ -2197,7 +2209,7 @@
         <v>86</v>
       </c>
       <c r="P8" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="Q8">
         <v>3.4</v>
@@ -2275,7 +2287,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AQ8">
         <v>1.75</v>
@@ -2403,7 +2415,7 @@
         <v>87</v>
       </c>
       <c r="P9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="Q9">
         <v>2.45</v>
@@ -2484,7 +2496,7 @@
         <v>2</v>
       </c>
       <c r="AQ9">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -2609,7 +2621,7 @@
         <v>88</v>
       </c>
       <c r="P10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Q10">
         <v>3.35</v>
@@ -2687,7 +2699,7 @@
         <v>1</v>
       </c>
       <c r="AP10">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AQ10">
         <v>0.33</v>
@@ -2815,7 +2827,7 @@
         <v>82</v>
       </c>
       <c r="P11" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="Q11">
         <v>3.45</v>
@@ -3021,7 +3033,7 @@
         <v>89</v>
       </c>
       <c r="P12" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="Q12">
         <v>2.95</v>
@@ -3099,7 +3111,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>2</v>
+        <v>1.33</v>
       </c>
       <c r="AQ12">
         <v>0</v>
@@ -3227,7 +3239,7 @@
         <v>90</v>
       </c>
       <c r="P13" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="Q13">
         <v>2.75</v>
@@ -3845,7 +3857,7 @@
         <v>92</v>
       </c>
       <c r="P16" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="Q16">
         <v>2.75</v>
@@ -3926,7 +3938,7 @@
         <v>2</v>
       </c>
       <c r="AQ16">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AR16">
         <v>1.8</v>
@@ -4335,7 +4347,7 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>2</v>
+        <v>1.33</v>
       </c>
       <c r="AQ18">
         <v>0.5</v>
@@ -4750,7 +4762,7 @@
         <v>1</v>
       </c>
       <c r="AQ20">
-        <v>0.5</v>
+        <v>1.33</v>
       </c>
       <c r="AR20">
         <v>0</v>
@@ -4875,7 +4887,7 @@
         <v>94</v>
       </c>
       <c r="P21" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="Q21">
         <v>3.1</v>
@@ -4953,7 +4965,7 @@
         <v>3</v>
       </c>
       <c r="AP21">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AQ21">
         <v>3</v>
@@ -5081,7 +5093,7 @@
         <v>95</v>
       </c>
       <c r="P22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="Q22">
         <v>3.6</v>
@@ -5493,7 +5505,7 @@
         <v>82</v>
       </c>
       <c r="P24" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="Q24">
         <v>2.75</v>
@@ -5650,6 +5662,624 @@
       </c>
       <c r="BP24">
         <v>1.24</v>
+      </c>
+    </row>
+    <row r="25" spans="1:68">
+      <c r="A25" s="1">
+        <v>24</v>
+      </c>
+      <c r="B25">
+        <v>7806782</v>
+      </c>
+      <c r="C25" t="s">
+        <v>68</v>
+      </c>
+      <c r="D25" t="s">
+        <v>69</v>
+      </c>
+      <c r="E25" s="2">
+        <v>45731.08333333334</v>
+      </c>
+      <c r="F25">
+        <v>5</v>
+      </c>
+      <c r="G25" t="s">
+        <v>71</v>
+      </c>
+      <c r="H25" t="s">
+        <v>77</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>0</v>
+      </c>
+      <c r="K25">
+        <v>0</v>
+      </c>
+      <c r="L25">
+        <v>1</v>
+      </c>
+      <c r="M25">
+        <v>3</v>
+      </c>
+      <c r="N25">
+        <v>4</v>
+      </c>
+      <c r="O25" t="s">
+        <v>97</v>
+      </c>
+      <c r="P25" t="s">
+        <v>111</v>
+      </c>
+      <c r="Q25">
+        <v>4</v>
+      </c>
+      <c r="R25">
+        <v>2.05</v>
+      </c>
+      <c r="S25">
+        <v>3</v>
+      </c>
+      <c r="T25">
+        <v>1.44</v>
+      </c>
+      <c r="U25">
+        <v>2.63</v>
+      </c>
+      <c r="V25">
+        <v>3.25</v>
+      </c>
+      <c r="W25">
+        <v>1.33</v>
+      </c>
+      <c r="X25">
+        <v>9</v>
+      </c>
+      <c r="Y25">
+        <v>1.07</v>
+      </c>
+      <c r="Z25">
+        <v>3.04</v>
+      </c>
+      <c r="AA25">
+        <v>2.89</v>
+      </c>
+      <c r="AB25">
+        <v>2.53</v>
+      </c>
+      <c r="AC25">
+        <v>1.07</v>
+      </c>
+      <c r="AD25">
+        <v>8</v>
+      </c>
+      <c r="AE25">
+        <v>1.38</v>
+      </c>
+      <c r="AF25">
+        <v>3</v>
+      </c>
+      <c r="AG25">
+        <v>2</v>
+      </c>
+      <c r="AH25">
+        <v>1.67</v>
+      </c>
+      <c r="AI25">
+        <v>1.8</v>
+      </c>
+      <c r="AJ25">
+        <v>1.91</v>
+      </c>
+      <c r="AK25">
+        <v>1.63</v>
+      </c>
+      <c r="AL25">
+        <v>1.32</v>
+      </c>
+      <c r="AM25">
+        <v>1.32</v>
+      </c>
+      <c r="AN25">
+        <v>1.5</v>
+      </c>
+      <c r="AO25">
+        <v>3</v>
+      </c>
+      <c r="AP25">
+        <v>1</v>
+      </c>
+      <c r="AQ25">
+        <v>3</v>
+      </c>
+      <c r="AR25">
+        <v>1.2</v>
+      </c>
+      <c r="AS25">
+        <v>1.22</v>
+      </c>
+      <c r="AT25">
+        <v>2.42</v>
+      </c>
+      <c r="AU25">
+        <v>2</v>
+      </c>
+      <c r="AV25">
+        <v>6</v>
+      </c>
+      <c r="AW25">
+        <v>8</v>
+      </c>
+      <c r="AX25">
+        <v>6</v>
+      </c>
+      <c r="AY25">
+        <v>11</v>
+      </c>
+      <c r="AZ25">
+        <v>14</v>
+      </c>
+      <c r="BA25">
+        <v>1</v>
+      </c>
+      <c r="BB25">
+        <v>4</v>
+      </c>
+      <c r="BC25">
+        <v>5</v>
+      </c>
+      <c r="BD25">
+        <v>2.03</v>
+      </c>
+      <c r="BE25">
+        <v>6.3</v>
+      </c>
+      <c r="BF25">
+        <v>2.26</v>
+      </c>
+      <c r="BG25">
+        <v>1.38</v>
+      </c>
+      <c r="BH25">
+        <v>2.71</v>
+      </c>
+      <c r="BI25">
+        <v>1.77</v>
+      </c>
+      <c r="BJ25">
+        <v>1.95</v>
+      </c>
+      <c r="BK25">
+        <v>2.17</v>
+      </c>
+      <c r="BL25">
+        <v>1.58</v>
+      </c>
+      <c r="BM25">
+        <v>2.88</v>
+      </c>
+      <c r="BN25">
+        <v>1.32</v>
+      </c>
+      <c r="BO25">
+        <v>4.1</v>
+      </c>
+      <c r="BP25">
+        <v>1.16</v>
+      </c>
+    </row>
+    <row r="26" spans="1:68">
+      <c r="A26" s="1">
+        <v>25</v>
+      </c>
+      <c r="B26">
+        <v>7806783</v>
+      </c>
+      <c r="C26" t="s">
+        <v>68</v>
+      </c>
+      <c r="D26" t="s">
+        <v>69</v>
+      </c>
+      <c r="E26" s="2">
+        <v>45731.1875</v>
+      </c>
+      <c r="F26">
+        <v>5</v>
+      </c>
+      <c r="G26" t="s">
+        <v>78</v>
+      </c>
+      <c r="H26" t="s">
+        <v>76</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>1</v>
+      </c>
+      <c r="K26">
+        <v>1</v>
+      </c>
+      <c r="L26">
+        <v>0</v>
+      </c>
+      <c r="M26">
+        <v>1</v>
+      </c>
+      <c r="N26">
+        <v>1</v>
+      </c>
+      <c r="O26" t="s">
+        <v>82</v>
+      </c>
+      <c r="P26" t="s">
+        <v>112</v>
+      </c>
+      <c r="Q26">
+        <v>3.6</v>
+      </c>
+      <c r="R26">
+        <v>1.95</v>
+      </c>
+      <c r="S26">
+        <v>3.5</v>
+      </c>
+      <c r="T26">
+        <v>1.53</v>
+      </c>
+      <c r="U26">
+        <v>2.38</v>
+      </c>
+      <c r="V26">
+        <v>3.5</v>
+      </c>
+      <c r="W26">
+        <v>1.29</v>
+      </c>
+      <c r="X26">
+        <v>11</v>
+      </c>
+      <c r="Y26">
+        <v>1.05</v>
+      </c>
+      <c r="Z26">
+        <v>2.8</v>
+      </c>
+      <c r="AA26">
+        <v>3.06</v>
+      </c>
+      <c r="AB26">
+        <v>2.59</v>
+      </c>
+      <c r="AC26">
+        <v>1.1</v>
+      </c>
+      <c r="AD26">
+        <v>6.5</v>
+      </c>
+      <c r="AE26">
+        <v>1.53</v>
+      </c>
+      <c r="AF26">
+        <v>2.45</v>
+      </c>
+      <c r="AG26">
+        <v>2.2</v>
+      </c>
+      <c r="AH26">
+        <v>1.55</v>
+      </c>
+      <c r="AI26">
+        <v>2</v>
+      </c>
+      <c r="AJ26">
+        <v>1.73</v>
+      </c>
+      <c r="AK26">
+        <v>1.45</v>
+      </c>
+      <c r="AL26">
+        <v>1.3</v>
+      </c>
+      <c r="AM26">
+        <v>1.42</v>
+      </c>
+      <c r="AN26">
+        <v>2</v>
+      </c>
+      <c r="AO26">
+        <v>0.5</v>
+      </c>
+      <c r="AP26">
+        <v>1.33</v>
+      </c>
+      <c r="AQ26">
+        <v>1.33</v>
+      </c>
+      <c r="AR26">
+        <v>1.64</v>
+      </c>
+      <c r="AS26">
+        <v>1.5</v>
+      </c>
+      <c r="AT26">
+        <v>3.14</v>
+      </c>
+      <c r="AU26">
+        <v>3</v>
+      </c>
+      <c r="AV26">
+        <v>9</v>
+      </c>
+      <c r="AW26">
+        <v>4</v>
+      </c>
+      <c r="AX26">
+        <v>4</v>
+      </c>
+      <c r="AY26">
+        <v>7</v>
+      </c>
+      <c r="AZ26">
+        <v>14</v>
+      </c>
+      <c r="BA26">
+        <v>1</v>
+      </c>
+      <c r="BB26">
+        <v>2</v>
+      </c>
+      <c r="BC26">
+        <v>3</v>
+      </c>
+      <c r="BD26">
+        <v>2.02</v>
+      </c>
+      <c r="BE26">
+        <v>6.2</v>
+      </c>
+      <c r="BF26">
+        <v>2.29</v>
+      </c>
+      <c r="BG26">
+        <v>1.43</v>
+      </c>
+      <c r="BH26">
+        <v>2.54</v>
+      </c>
+      <c r="BI26">
+        <v>1.8</v>
+      </c>
+      <c r="BJ26">
+        <v>1.91</v>
+      </c>
+      <c r="BK26">
+        <v>2.3</v>
+      </c>
+      <c r="BL26">
+        <v>1.52</v>
+      </c>
+      <c r="BM26">
+        <v>3.08</v>
+      </c>
+      <c r="BN26">
+        <v>1.28</v>
+      </c>
+      <c r="BO26">
+        <v>4.45</v>
+      </c>
+      <c r="BP26">
+        <v>1.14</v>
+      </c>
+    </row>
+    <row r="27" spans="1:68">
+      <c r="A27" s="1">
+        <v>26</v>
+      </c>
+      <c r="B27">
+        <v>7806784</v>
+      </c>
+      <c r="C27" t="s">
+        <v>68</v>
+      </c>
+      <c r="D27" t="s">
+        <v>69</v>
+      </c>
+      <c r="E27" s="2">
+        <v>45731.1875</v>
+      </c>
+      <c r="F27">
+        <v>5</v>
+      </c>
+      <c r="G27" t="s">
+        <v>75</v>
+      </c>
+      <c r="H27" t="s">
+        <v>80</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>1</v>
+      </c>
+      <c r="K27">
+        <v>1</v>
+      </c>
+      <c r="L27">
+        <v>0</v>
+      </c>
+      <c r="M27">
+        <v>1</v>
+      </c>
+      <c r="N27">
+        <v>1</v>
+      </c>
+      <c r="O27" t="s">
+        <v>82</v>
+      </c>
+      <c r="P27" t="s">
+        <v>113</v>
+      </c>
+      <c r="Q27">
+        <v>2.75</v>
+      </c>
+      <c r="R27">
+        <v>2.05</v>
+      </c>
+      <c r="S27">
+        <v>4.33</v>
+      </c>
+      <c r="T27">
+        <v>1.44</v>
+      </c>
+      <c r="U27">
+        <v>2.63</v>
+      </c>
+      <c r="V27">
+        <v>3.25</v>
+      </c>
+      <c r="W27">
+        <v>1.33</v>
+      </c>
+      <c r="X27">
+        <v>10</v>
+      </c>
+      <c r="Y27">
+        <v>1.06</v>
+      </c>
+      <c r="Z27">
+        <v>2.14</v>
+      </c>
+      <c r="AA27">
+        <v>3.09</v>
+      </c>
+      <c r="AB27">
+        <v>3.58</v>
+      </c>
+      <c r="AC27">
+        <v>1.07</v>
+      </c>
+      <c r="AD27">
+        <v>8</v>
+      </c>
+      <c r="AE27">
+        <v>1.38</v>
+      </c>
+      <c r="AF27">
+        <v>3</v>
+      </c>
+      <c r="AG27">
+        <v>1.98</v>
+      </c>
+      <c r="AH27">
+        <v>1.77</v>
+      </c>
+      <c r="AI27">
+        <v>1.83</v>
+      </c>
+      <c r="AJ27">
+        <v>1.83</v>
+      </c>
+      <c r="AK27">
+        <v>1.27</v>
+      </c>
+      <c r="AL27">
+        <v>1.3</v>
+      </c>
+      <c r="AM27">
+        <v>1.75</v>
+      </c>
+      <c r="AN27">
+        <v>2</v>
+      </c>
+      <c r="AO27">
+        <v>1</v>
+      </c>
+      <c r="AP27">
+        <v>1.5</v>
+      </c>
+      <c r="AQ27">
+        <v>1.5</v>
+      </c>
+      <c r="AR27">
+        <v>2.02</v>
+      </c>
+      <c r="AS27">
+        <v>1.04</v>
+      </c>
+      <c r="AT27">
+        <v>3.06</v>
+      </c>
+      <c r="AU27">
+        <v>8</v>
+      </c>
+      <c r="AV27">
+        <v>5</v>
+      </c>
+      <c r="AW27">
+        <v>8</v>
+      </c>
+      <c r="AX27">
+        <v>7</v>
+      </c>
+      <c r="AY27">
+        <v>26</v>
+      </c>
+      <c r="AZ27">
+        <v>17</v>
+      </c>
+      <c r="BA27">
+        <v>14</v>
+      </c>
+      <c r="BB27">
+        <v>3</v>
+      </c>
+      <c r="BC27">
+        <v>17</v>
+      </c>
+      <c r="BD27">
+        <v>1.85</v>
+      </c>
+      <c r="BE27">
+        <v>6.3</v>
+      </c>
+      <c r="BF27">
+        <v>2.54</v>
+      </c>
+      <c r="BG27">
+        <v>1.43</v>
+      </c>
+      <c r="BH27">
+        <v>2.54</v>
+      </c>
+      <c r="BI27">
+        <v>1.8</v>
+      </c>
+      <c r="BJ27">
+        <v>1.91</v>
+      </c>
+      <c r="BK27">
+        <v>2.32</v>
+      </c>
+      <c r="BL27">
+        <v>1.51</v>
+      </c>
+      <c r="BM27">
+        <v>3.14</v>
+      </c>
+      <c r="BN27">
+        <v>1.27</v>
+      </c>
+      <c r="BO27">
+        <v>4.5</v>
+      </c>
+      <c r="BP27">
+        <v>1.13</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/South Korea K League 1_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/South Korea K League 1_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="118">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -310,6 +310,12 @@
     <t>['56']</t>
   </si>
   <si>
+    <t>['13']</t>
+  </si>
+  <si>
+    <t>['25', '30']</t>
+  </si>
+  <si>
     <t>['32', '87', '90']</t>
   </si>
   <si>
@@ -356,6 +362,12 @@
   </si>
   <si>
     <t>['20']</t>
+  </si>
+  <si>
+    <t>['73']</t>
+  </si>
+  <si>
+    <t>['51', '84']</t>
   </si>
 </sst>
 </file>
@@ -717,7 +729,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP27"/>
+  <dimension ref="A1:BP30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -973,7 +985,7 @@
         <v>82</v>
       </c>
       <c r="P2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="Q2">
         <v>2.75</v>
@@ -1591,7 +1603,7 @@
         <v>82</v>
       </c>
       <c r="P5" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="Q5">
         <v>2.1</v>
@@ -1797,7 +1809,7 @@
         <v>84</v>
       </c>
       <c r="P6" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="Q6">
         <v>3.1</v>
@@ -1875,7 +1887,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AQ6">
         <v>1.75</v>
@@ -2003,7 +2015,7 @@
         <v>85</v>
       </c>
       <c r="P7" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="Q7">
         <v>3.5</v>
@@ -2209,7 +2221,7 @@
         <v>86</v>
       </c>
       <c r="P8" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="Q8">
         <v>3.4</v>
@@ -2415,7 +2427,7 @@
         <v>87</v>
       </c>
       <c r="P9" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="Q9">
         <v>2.45</v>
@@ -2621,7 +2633,7 @@
         <v>88</v>
       </c>
       <c r="P10" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="Q10">
         <v>3.35</v>
@@ -2827,7 +2839,7 @@
         <v>82</v>
       </c>
       <c r="P11" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="Q11">
         <v>3.45</v>
@@ -2908,7 +2920,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -3033,7 +3045,7 @@
         <v>89</v>
       </c>
       <c r="P12" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="Q12">
         <v>2.95</v>
@@ -3114,7 +3126,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ12">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -3239,7 +3251,7 @@
         <v>90</v>
       </c>
       <c r="P13" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="Q13">
         <v>2.75</v>
@@ -3317,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AQ13">
         <v>1</v>
@@ -3857,7 +3869,7 @@
         <v>92</v>
       </c>
       <c r="P16" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="Q16">
         <v>2.75</v>
@@ -4887,7 +4899,7 @@
         <v>94</v>
       </c>
       <c r="P21" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="Q21">
         <v>3.1</v>
@@ -5093,7 +5105,7 @@
         <v>95</v>
       </c>
       <c r="P22" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="Q22">
         <v>3.6</v>
@@ -5505,7 +5517,7 @@
         <v>82</v>
       </c>
       <c r="P24" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="Q24">
         <v>2.75</v>
@@ -5583,7 +5595,7 @@
         <v>0</v>
       </c>
       <c r="AP24">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AQ24">
         <v>1.5</v>
@@ -5711,7 +5723,7 @@
         <v>97</v>
       </c>
       <c r="P25" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="Q25">
         <v>4</v>
@@ -5917,7 +5929,7 @@
         <v>82</v>
       </c>
       <c r="P26" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="Q26">
         <v>3.6</v>
@@ -6123,7 +6135,7 @@
         <v>82</v>
       </c>
       <c r="P27" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="Q27">
         <v>2.75</v>
@@ -6280,6 +6292,624 @@
       </c>
       <c r="BP27">
         <v>1.13</v>
+      </c>
+    </row>
+    <row r="28" spans="1:68">
+      <c r="A28" s="1">
+        <v>27</v>
+      </c>
+      <c r="B28">
+        <v>7806785</v>
+      </c>
+      <c r="C28" t="s">
+        <v>68</v>
+      </c>
+      <c r="D28" t="s">
+        <v>69</v>
+      </c>
+      <c r="E28" s="2">
+        <v>45732.08333333334</v>
+      </c>
+      <c r="F28">
+        <v>5</v>
+      </c>
+      <c r="G28" t="s">
+        <v>79</v>
+      </c>
+      <c r="H28" t="s">
+        <v>73</v>
+      </c>
+      <c r="I28">
+        <v>1</v>
+      </c>
+      <c r="J28">
+        <v>0</v>
+      </c>
+      <c r="K28">
+        <v>1</v>
+      </c>
+      <c r="L28">
+        <v>1</v>
+      </c>
+      <c r="M28">
+        <v>1</v>
+      </c>
+      <c r="N28">
+        <v>2</v>
+      </c>
+      <c r="O28" t="s">
+        <v>98</v>
+      </c>
+      <c r="P28" t="s">
+        <v>116</v>
+      </c>
+      <c r="Q28">
+        <v>3.75</v>
+      </c>
+      <c r="R28">
+        <v>2.2</v>
+      </c>
+      <c r="S28">
+        <v>2.75</v>
+      </c>
+      <c r="T28">
+        <v>1.36</v>
+      </c>
+      <c r="U28">
+        <v>3</v>
+      </c>
+      <c r="V28">
+        <v>2.75</v>
+      </c>
+      <c r="W28">
+        <v>1.4</v>
+      </c>
+      <c r="X28">
+        <v>8</v>
+      </c>
+      <c r="Y28">
+        <v>1.08</v>
+      </c>
+      <c r="Z28">
+        <v>3.31</v>
+      </c>
+      <c r="AA28">
+        <v>3.41</v>
+      </c>
+      <c r="AB28">
+        <v>2.1</v>
+      </c>
+      <c r="AC28">
+        <v>1.05</v>
+      </c>
+      <c r="AD28">
+        <v>9</v>
+      </c>
+      <c r="AE28">
+        <v>1.28</v>
+      </c>
+      <c r="AF28">
+        <v>3.5</v>
+      </c>
+      <c r="AG28">
+        <v>1.87</v>
+      </c>
+      <c r="AH28">
+        <v>1.87</v>
+      </c>
+      <c r="AI28">
+        <v>1.73</v>
+      </c>
+      <c r="AJ28">
+        <v>2</v>
+      </c>
+      <c r="AK28">
+        <v>1.68</v>
+      </c>
+      <c r="AL28">
+        <v>1.3</v>
+      </c>
+      <c r="AM28">
+        <v>1.31</v>
+      </c>
+      <c r="AN28">
+        <v>1</v>
+      </c>
+      <c r="AO28">
+        <v>3</v>
+      </c>
+      <c r="AP28">
+        <v>1</v>
+      </c>
+      <c r="AQ28">
+        <v>2</v>
+      </c>
+      <c r="AR28">
+        <v>1.36</v>
+      </c>
+      <c r="AS28">
+        <v>1.76</v>
+      </c>
+      <c r="AT28">
+        <v>3.12</v>
+      </c>
+      <c r="AU28">
+        <v>3</v>
+      </c>
+      <c r="AV28">
+        <v>3</v>
+      </c>
+      <c r="AW28">
+        <v>4</v>
+      </c>
+      <c r="AX28">
+        <v>15</v>
+      </c>
+      <c r="AY28">
+        <v>7</v>
+      </c>
+      <c r="AZ28">
+        <v>26</v>
+      </c>
+      <c r="BA28">
+        <v>1</v>
+      </c>
+      <c r="BB28">
+        <v>8</v>
+      </c>
+      <c r="BC28">
+        <v>9</v>
+      </c>
+      <c r="BD28">
+        <v>2.43</v>
+      </c>
+      <c r="BE28">
+        <v>6.35</v>
+      </c>
+      <c r="BF28">
+        <v>1.91</v>
+      </c>
+      <c r="BG28">
+        <v>1.36</v>
+      </c>
+      <c r="BH28">
+        <v>2.78</v>
+      </c>
+      <c r="BI28">
+        <v>1.7</v>
+      </c>
+      <c r="BJ28">
+        <v>2.05</v>
+      </c>
+      <c r="BK28">
+        <v>2.14</v>
+      </c>
+      <c r="BL28">
+        <v>1.6</v>
+      </c>
+      <c r="BM28">
+        <v>2.83</v>
+      </c>
+      <c r="BN28">
+        <v>1.33</v>
+      </c>
+      <c r="BO28">
+        <v>4</v>
+      </c>
+      <c r="BP28">
+        <v>1.17</v>
+      </c>
+    </row>
+    <row r="29" spans="1:68">
+      <c r="A29" s="1">
+        <v>28</v>
+      </c>
+      <c r="B29">
+        <v>7806786</v>
+      </c>
+      <c r="C29" t="s">
+        <v>68</v>
+      </c>
+      <c r="D29" t="s">
+        <v>69</v>
+      </c>
+      <c r="E29" s="2">
+        <v>45732.1875</v>
+      </c>
+      <c r="F29">
+        <v>5</v>
+      </c>
+      <c r="G29" t="s">
+        <v>81</v>
+      </c>
+      <c r="H29" t="s">
+        <v>72</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>0</v>
+      </c>
+      <c r="K29">
+        <v>0</v>
+      </c>
+      <c r="L29">
+        <v>0</v>
+      </c>
+      <c r="M29">
+        <v>0</v>
+      </c>
+      <c r="N29">
+        <v>0</v>
+      </c>
+      <c r="O29" t="s">
+        <v>82</v>
+      </c>
+      <c r="P29" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q29">
+        <v>3</v>
+      </c>
+      <c r="R29">
+        <v>1.95</v>
+      </c>
+      <c r="S29">
+        <v>4.33</v>
+      </c>
+      <c r="T29">
+        <v>1.53</v>
+      </c>
+      <c r="U29">
+        <v>2.38</v>
+      </c>
+      <c r="V29">
+        <v>3.5</v>
+      </c>
+      <c r="W29">
+        <v>1.29</v>
+      </c>
+      <c r="X29">
+        <v>11</v>
+      </c>
+      <c r="Y29">
+        <v>1.05</v>
+      </c>
+      <c r="Z29">
+        <v>2.17</v>
+      </c>
+      <c r="AA29">
+        <v>3.06</v>
+      </c>
+      <c r="AB29">
+        <v>3.55</v>
+      </c>
+      <c r="AC29">
+        <v>1.09</v>
+      </c>
+      <c r="AD29">
+        <v>7</v>
+      </c>
+      <c r="AE29">
+        <v>1.45</v>
+      </c>
+      <c r="AF29">
+        <v>2.7</v>
+      </c>
+      <c r="AG29">
+        <v>2.25</v>
+      </c>
+      <c r="AH29">
+        <v>1.53</v>
+      </c>
+      <c r="AI29">
+        <v>2</v>
+      </c>
+      <c r="AJ29">
+        <v>1.73</v>
+      </c>
+      <c r="AK29">
+        <v>1.3</v>
+      </c>
+      <c r="AL29">
+        <v>1.33</v>
+      </c>
+      <c r="AM29">
+        <v>1.66</v>
+      </c>
+      <c r="AN29">
+        <v>0</v>
+      </c>
+      <c r="AO29">
+        <v>1</v>
+      </c>
+      <c r="AP29">
+        <v>1</v>
+      </c>
+      <c r="AQ29">
+        <v>1</v>
+      </c>
+      <c r="AR29">
+        <v>0</v>
+      </c>
+      <c r="AS29">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="AT29">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="AU29">
+        <v>6</v>
+      </c>
+      <c r="AV29">
+        <v>4</v>
+      </c>
+      <c r="AW29">
+        <v>9</v>
+      </c>
+      <c r="AX29">
+        <v>8</v>
+      </c>
+      <c r="AY29">
+        <v>16</v>
+      </c>
+      <c r="AZ29">
+        <v>14</v>
+      </c>
+      <c r="BA29">
+        <v>4</v>
+      </c>
+      <c r="BB29">
+        <v>2</v>
+      </c>
+      <c r="BC29">
+        <v>6</v>
+      </c>
+      <c r="BD29">
+        <v>1.69</v>
+      </c>
+      <c r="BE29">
+        <v>6.4</v>
+      </c>
+      <c r="BF29">
+        <v>2.89</v>
+      </c>
+      <c r="BG29">
+        <v>1.44</v>
+      </c>
+      <c r="BH29">
+        <v>2.5</v>
+      </c>
+      <c r="BI29">
+        <v>1.85</v>
+      </c>
+      <c r="BJ29">
+        <v>1.85</v>
+      </c>
+      <c r="BK29">
+        <v>2.38</v>
+      </c>
+      <c r="BL29">
+        <v>1.49</v>
+      </c>
+      <c r="BM29">
+        <v>3.2</v>
+      </c>
+      <c r="BN29">
+        <v>1.26</v>
+      </c>
+      <c r="BO29">
+        <v>4.65</v>
+      </c>
+      <c r="BP29">
+        <v>1.12</v>
+      </c>
+    </row>
+    <row r="30" spans="1:68">
+      <c r="A30" s="1">
+        <v>29</v>
+      </c>
+      <c r="B30">
+        <v>7806787</v>
+      </c>
+      <c r="C30" t="s">
+        <v>68</v>
+      </c>
+      <c r="D30" t="s">
+        <v>69</v>
+      </c>
+      <c r="E30" s="2">
+        <v>45732.1875</v>
+      </c>
+      <c r="F30">
+        <v>5</v>
+      </c>
+      <c r="G30" t="s">
+        <v>74</v>
+      </c>
+      <c r="H30" t="s">
+        <v>70</v>
+      </c>
+      <c r="I30">
+        <v>2</v>
+      </c>
+      <c r="J30">
+        <v>0</v>
+      </c>
+      <c r="K30">
+        <v>2</v>
+      </c>
+      <c r="L30">
+        <v>2</v>
+      </c>
+      <c r="M30">
+        <v>2</v>
+      </c>
+      <c r="N30">
+        <v>4</v>
+      </c>
+      <c r="O30" t="s">
+        <v>99</v>
+      </c>
+      <c r="P30" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q30">
+        <v>2.63</v>
+      </c>
+      <c r="R30">
+        <v>2.2</v>
+      </c>
+      <c r="S30">
+        <v>4</v>
+      </c>
+      <c r="T30">
+        <v>1.4</v>
+      </c>
+      <c r="U30">
+        <v>2.75</v>
+      </c>
+      <c r="V30">
+        <v>2.75</v>
+      </c>
+      <c r="W30">
+        <v>1.4</v>
+      </c>
+      <c r="X30">
+        <v>8</v>
+      </c>
+      <c r="Y30">
+        <v>1.08</v>
+      </c>
+      <c r="Z30">
+        <v>2.05</v>
+      </c>
+      <c r="AA30">
+        <v>3.38</v>
+      </c>
+      <c r="AB30">
+        <v>3.5</v>
+      </c>
+      <c r="AC30">
+        <v>1.06</v>
+      </c>
+      <c r="AD30">
+        <v>8.5</v>
+      </c>
+      <c r="AE30">
+        <v>1.3</v>
+      </c>
+      <c r="AF30">
+        <v>3.45</v>
+      </c>
+      <c r="AG30">
+        <v>1.87</v>
+      </c>
+      <c r="AH30">
+        <v>1.87</v>
+      </c>
+      <c r="AI30">
+        <v>1.73</v>
+      </c>
+      <c r="AJ30">
+        <v>2</v>
+      </c>
+      <c r="AK30">
+        <v>1.29</v>
+      </c>
+      <c r="AL30">
+        <v>1.29</v>
+      </c>
+      <c r="AM30">
+        <v>1.73</v>
+      </c>
+      <c r="AN30">
+        <v>1.33</v>
+      </c>
+      <c r="AO30">
+        <v>0</v>
+      </c>
+      <c r="AP30">
+        <v>1.25</v>
+      </c>
+      <c r="AQ30">
+        <v>0.5</v>
+      </c>
+      <c r="AR30">
+        <v>1.76</v>
+      </c>
+      <c r="AS30">
+        <v>0.83</v>
+      </c>
+      <c r="AT30">
+        <v>2.59</v>
+      </c>
+      <c r="AU30">
+        <v>6</v>
+      </c>
+      <c r="AV30">
+        <v>6</v>
+      </c>
+      <c r="AW30">
+        <v>3</v>
+      </c>
+      <c r="AX30">
+        <v>8</v>
+      </c>
+      <c r="AY30">
+        <v>11</v>
+      </c>
+      <c r="AZ30">
+        <v>16</v>
+      </c>
+      <c r="BA30">
+        <v>5</v>
+      </c>
+      <c r="BB30">
+        <v>7</v>
+      </c>
+      <c r="BC30">
+        <v>12</v>
+      </c>
+      <c r="BD30">
+        <v>1.54</v>
+      </c>
+      <c r="BE30">
+        <v>6.75</v>
+      </c>
+      <c r="BF30">
+        <v>3.38</v>
+      </c>
+      <c r="BG30">
+        <v>1.42</v>
+      </c>
+      <c r="BH30">
+        <v>2.57</v>
+      </c>
+      <c r="BI30">
+        <v>1.8</v>
+      </c>
+      <c r="BJ30">
+        <v>1.91</v>
+      </c>
+      <c r="BK30">
+        <v>2.28</v>
+      </c>
+      <c r="BL30">
+        <v>1.53</v>
+      </c>
+      <c r="BM30">
+        <v>3.08</v>
+      </c>
+      <c r="BN30">
+        <v>1.28</v>
+      </c>
+      <c r="BO30">
+        <v>4.4</v>
+      </c>
+      <c r="BP30">
+        <v>1.14</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/South Korea K League 1_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/South Korea K League 1_2025.xlsx
@@ -277,18 +277,18 @@
     <t>['30', '58']</t>
   </si>
   <si>
+    <t>['19', '53', '70']</t>
+  </si>
+  <si>
     <t>['48', '79']</t>
   </si>
   <si>
-    <t>['19', '53', '70']</t>
+    <t>['21', '66']</t>
   </si>
   <si>
     <t>['82', '90+3']</t>
   </si>
   <si>
-    <t>['21', '66']</t>
-  </si>
-  <si>
     <t>['66']</t>
   </si>
   <si>
@@ -331,10 +331,10 @@
     <t>['50', '63', '90']</t>
   </si>
   <si>
+    <t>['90+4']</t>
+  </si>
+  <si>
     <t>['90+3']</t>
-  </si>
-  <si>
-    <t>['90+4']</t>
   </si>
   <si>
     <t>['8', '59']</t>
@@ -2385,7 +2385,7 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>7806765</v>
+        <v>7806766</v>
       </c>
       <c r="C9" t="s">
         <v>68</v>
@@ -2400,28 +2400,28 @@
         <v>2</v>
       </c>
       <c r="G9" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H9" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9">
         <v>0</v>
       </c>
       <c r="K9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M9">
         <v>1</v>
       </c>
       <c r="N9">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O9" t="s">
         <v>87</v>
@@ -2430,160 +2430,160 @@
         <v>105</v>
       </c>
       <c r="Q9">
-        <v>2.45</v>
+        <v>3.35</v>
       </c>
       <c r="R9">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="S9">
-        <v>4.6</v>
+        <v>3</v>
       </c>
       <c r="T9">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="U9">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="V9">
-        <v>3.1</v>
+        <v>2.75</v>
       </c>
       <c r="W9">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="X9">
+        <v>7.4</v>
+      </c>
+      <c r="Y9">
+        <v>1.03</v>
+      </c>
+      <c r="Z9">
+        <v>2.66</v>
+      </c>
+      <c r="AA9">
+        <v>3.28</v>
+      </c>
+      <c r="AB9">
+        <v>2.58</v>
+      </c>
+      <c r="AC9">
+        <v>1.06</v>
+      </c>
+      <c r="AD9">
         <v>8.5</v>
       </c>
-      <c r="Y9">
-        <v>1.06</v>
-      </c>
-      <c r="Z9">
-        <v>1.82</v>
-      </c>
-      <c r="AA9">
-        <v>3.55</v>
-      </c>
-      <c r="AB9">
-        <v>4.2</v>
-      </c>
-      <c r="AC9">
-        <v>1.07</v>
-      </c>
-      <c r="AD9">
-        <v>8</v>
-      </c>
       <c r="AE9">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AF9">
-        <v>3.08</v>
+        <v>3.25</v>
       </c>
       <c r="AG9">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AH9">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AI9">
-        <v>1.93</v>
+        <v>1.7</v>
       </c>
       <c r="AJ9">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AK9">
-        <v>1.21</v>
+        <v>1.53</v>
       </c>
       <c r="AL9">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AM9">
-        <v>1.93</v>
+        <v>1.4</v>
       </c>
       <c r="AN9">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AO9">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AP9">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AQ9">
-        <v>1.5</v>
+        <v>0.33</v>
       </c>
       <c r="AR9">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AS9">
-        <v>1.19</v>
+        <v>0.9</v>
       </c>
       <c r="AT9">
-        <v>1.19</v>
+        <v>2.85</v>
       </c>
       <c r="AU9">
         <v>5</v>
       </c>
       <c r="AV9">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AW9">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AX9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AY9">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="AZ9">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="BA9">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="BB9">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="BC9">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="BD9">
-        <v>1.54</v>
+        <v>2.05</v>
       </c>
       <c r="BE9">
-        <v>6.4</v>
+        <v>6.25</v>
       </c>
       <c r="BF9">
-        <v>2.75</v>
+        <v>1.95</v>
       </c>
       <c r="BG9">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="BH9">
-        <v>2.48</v>
+        <v>2.65</v>
       </c>
       <c r="BI9">
-        <v>1.76</v>
+        <v>1.71</v>
       </c>
       <c r="BJ9">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="BK9">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="BL9">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="BM9">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="BN9">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="BO9">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="BP9">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
     </row>
     <row r="10" spans="1:68">
@@ -2591,7 +2591,7 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>7806766</v>
+        <v>7806765</v>
       </c>
       <c r="C10" t="s">
         <v>68</v>
@@ -2606,28 +2606,28 @@
         <v>2</v>
       </c>
       <c r="G10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J10">
         <v>0</v>
       </c>
       <c r="K10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M10">
         <v>1</v>
       </c>
       <c r="N10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O10" t="s">
         <v>88</v>
@@ -2636,160 +2636,160 @@
         <v>106</v>
       </c>
       <c r="Q10">
-        <v>3.35</v>
+        <v>2.45</v>
       </c>
       <c r="R10">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="S10">
-        <v>3</v>
+        <v>4.6</v>
       </c>
       <c r="T10">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="U10">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="V10">
-        <v>2.75</v>
+        <v>3.1</v>
       </c>
       <c r="W10">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="X10">
-        <v>7.4</v>
+        <v>8.5</v>
       </c>
       <c r="Y10">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Z10">
-        <v>2.66</v>
+        <v>1.82</v>
       </c>
       <c r="AA10">
-        <v>3.28</v>
+        <v>3.55</v>
       </c>
       <c r="AB10">
-        <v>2.58</v>
+        <v>4.2</v>
       </c>
       <c r="AC10">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AD10">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="AE10">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AF10">
-        <v>3.25</v>
+        <v>3.08</v>
       </c>
       <c r="AG10">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="AH10">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AI10">
-        <v>1.7</v>
+        <v>1.93</v>
       </c>
       <c r="AJ10">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AK10">
-        <v>1.53</v>
+        <v>1.21</v>
       </c>
       <c r="AL10">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AM10">
-        <v>1.4</v>
+        <v>1.93</v>
       </c>
       <c r="AN10">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AO10">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AP10">
+        <v>2</v>
+      </c>
+      <c r="AQ10">
         <v>1.5</v>
       </c>
-      <c r="AQ10">
-        <v>0.33</v>
-      </c>
       <c r="AR10">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AS10">
-        <v>0.9</v>
+        <v>1.19</v>
       </c>
       <c r="AT10">
-        <v>2.85</v>
+        <v>1.19</v>
       </c>
       <c r="AU10">
         <v>5</v>
       </c>
       <c r="AV10">
+        <v>3</v>
+      </c>
+      <c r="AW10">
+        <v>6</v>
+      </c>
+      <c r="AX10">
+        <v>1</v>
+      </c>
+      <c r="AY10">
+        <v>11</v>
+      </c>
+      <c r="AZ10">
         <v>4</v>
       </c>
-      <c r="AW10">
-        <v>10</v>
-      </c>
-      <c r="AX10">
-        <v>2</v>
-      </c>
-      <c r="AY10">
-        <v>18</v>
-      </c>
-      <c r="AZ10">
-        <v>7</v>
-      </c>
       <c r="BA10">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="BB10">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="BC10">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="BD10">
-        <v>2.05</v>
+        <v>1.54</v>
       </c>
       <c r="BE10">
-        <v>6.25</v>
+        <v>6.4</v>
       </c>
       <c r="BF10">
-        <v>1.95</v>
+        <v>2.75</v>
       </c>
       <c r="BG10">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="BH10">
-        <v>2.65</v>
+        <v>2.48</v>
       </c>
       <c r="BI10">
-        <v>1.71</v>
+        <v>1.76</v>
       </c>
       <c r="BJ10">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="BK10">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="BL10">
-        <v>1.63</v>
+        <v>1.58</v>
       </c>
       <c r="BM10">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="BN10">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="BO10">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="BP10">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
     </row>
     <row r="11" spans="1:68">
@@ -3003,7 +3003,7 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>7806769</v>
+        <v>7806768</v>
       </c>
       <c r="C12" t="s">
         <v>68</v>
@@ -3018,49 +3018,49 @@
         <v>2</v>
       </c>
       <c r="G12" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="H12" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12">
         <v>1</v>
       </c>
       <c r="K12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L12">
         <v>2</v>
       </c>
       <c r="M12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N12">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O12" t="s">
         <v>89</v>
       </c>
       <c r="P12" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="Q12">
-        <v>2.95</v>
+        <v>2.75</v>
       </c>
       <c r="R12">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="S12">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="T12">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="U12">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="V12">
         <v>2.88</v>
@@ -3075,13 +3075,13 @@
         <v>1.07</v>
       </c>
       <c r="Z12">
-        <v>2.39</v>
+        <v>2.18</v>
       </c>
       <c r="AA12">
-        <v>3.14</v>
+        <v>3.25</v>
       </c>
       <c r="AB12">
-        <v>3</v>
+        <v>3.29</v>
       </c>
       <c r="AC12">
         <v>1.07</v>
@@ -3090,10 +3090,10 @@
         <v>8</v>
       </c>
       <c r="AE12">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AF12">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="AG12">
         <v>1.95</v>
@@ -3108,82 +3108,82 @@
         <v>1.91</v>
       </c>
       <c r="AK12">
-        <v>1.37</v>
+        <v>1.31</v>
       </c>
       <c r="AL12">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AM12">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="AN12">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AO12">
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AQ12">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="AR12">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AS12">
         <v>0</v>
       </c>
       <c r="AT12">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AU12">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AV12">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW12">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="AX12">
         <v>2</v>
       </c>
       <c r="AY12">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="AZ12">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BA12">
         <v>4</v>
       </c>
       <c r="BB12">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BC12">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="BD12">
-        <v>1.89</v>
+        <v>1.73</v>
       </c>
       <c r="BE12">
-        <v>6.1</v>
+        <v>6.25</v>
       </c>
       <c r="BF12">
-        <v>2.15</v>
+        <v>2.35</v>
       </c>
       <c r="BG12">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="BH12">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="BI12">
         <v>1.77</v>
       </c>
       <c r="BJ12">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="BK12">
         <v>2.23</v>
@@ -3198,10 +3198,10 @@
         <v>1.35</v>
       </c>
       <c r="BO12">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="BP12">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
     </row>
     <row r="13" spans="1:68">
@@ -3209,7 +3209,7 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>7806768</v>
+        <v>7806769</v>
       </c>
       <c r="C13" t="s">
         <v>68</v>
@@ -3224,49 +3224,49 @@
         <v>2</v>
       </c>
       <c r="G13" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="H13" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="I13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J13">
         <v>1</v>
       </c>
       <c r="K13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L13">
         <v>2</v>
       </c>
       <c r="M13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N13">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O13" t="s">
         <v>90</v>
       </c>
       <c r="P13" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="Q13">
-        <v>2.75</v>
+        <v>2.95</v>
       </c>
       <c r="R13">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="S13">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="T13">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="U13">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="V13">
         <v>2.88</v>
@@ -3281,13 +3281,13 @@
         <v>1.07</v>
       </c>
       <c r="Z13">
-        <v>2.18</v>
+        <v>2.39</v>
       </c>
       <c r="AA13">
-        <v>3.25</v>
+        <v>3.14</v>
       </c>
       <c r="AB13">
-        <v>3.29</v>
+        <v>3</v>
       </c>
       <c r="AC13">
         <v>1.07</v>
@@ -3296,10 +3296,10 @@
         <v>8</v>
       </c>
       <c r="AE13">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AF13">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="AG13">
         <v>1.95</v>
@@ -3314,82 +3314,82 @@
         <v>1.91</v>
       </c>
       <c r="AK13">
+        <v>1.37</v>
+      </c>
+      <c r="AL13">
         <v>1.31</v>
       </c>
-      <c r="AL13">
-        <v>1.3</v>
-      </c>
       <c r="AM13">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AN13">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AO13">
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AQ13">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AR13">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AS13">
         <v>0</v>
       </c>
       <c r="AT13">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AU13">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AV13">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AW13">
+        <v>11</v>
+      </c>
+      <c r="AX13">
+        <v>2</v>
+      </c>
+      <c r="AY13">
+        <v>22</v>
+      </c>
+      <c r="AZ13">
         <v>6</v>
-      </c>
-      <c r="AX13">
-        <v>2</v>
-      </c>
-      <c r="AY13">
-        <v>16</v>
-      </c>
-      <c r="AZ13">
-        <v>5</v>
       </c>
       <c r="BA13">
         <v>4</v>
       </c>
       <c r="BB13">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BC13">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="BD13">
-        <v>1.73</v>
+        <v>1.89</v>
       </c>
       <c r="BE13">
-        <v>6.25</v>
+        <v>6.1</v>
       </c>
       <c r="BF13">
-        <v>2.35</v>
+        <v>2.15</v>
       </c>
       <c r="BG13">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="BH13">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="BI13">
         <v>1.77</v>
       </c>
       <c r="BJ13">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="BK13">
         <v>2.23</v>
@@ -3404,10 +3404,10 @@
         <v>1.35</v>
       </c>
       <c r="BO13">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="BP13">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
     </row>
     <row r="14" spans="1:68">

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/South Korea K League 1_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/South Korea K League 1_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="120">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -316,6 +316,9 @@
     <t>['25', '30']</t>
   </si>
   <si>
+    <t>['7', '90+2']</t>
+  </si>
+  <si>
     <t>['32', '87', '90']</t>
   </si>
   <si>
@@ -368,6 +371,9 @@
   </si>
   <si>
     <t>['51', '84']</t>
+  </si>
+  <si>
+    <t>['22', '68', '90+11']</t>
   </si>
 </sst>
 </file>
@@ -729,7 +735,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP30"/>
+  <dimension ref="A1:BP31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -985,7 +991,7 @@
         <v>82</v>
       </c>
       <c r="P2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="Q2">
         <v>2.75</v>
@@ -1475,7 +1481,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>2</v>
+        <v>1.33</v>
       </c>
       <c r="AQ4">
         <v>0.33</v>
@@ -1603,7 +1609,7 @@
         <v>82</v>
       </c>
       <c r="P5" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="Q5">
         <v>2.1</v>
@@ -1809,7 +1815,7 @@
         <v>84</v>
       </c>
       <c r="P6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="Q6">
         <v>3.1</v>
@@ -2015,7 +2021,7 @@
         <v>85</v>
       </c>
       <c r="P7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Q7">
         <v>3.5</v>
@@ -2221,7 +2227,7 @@
         <v>86</v>
       </c>
       <c r="P8" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="Q8">
         <v>3.4</v>
@@ -2427,7 +2433,7 @@
         <v>87</v>
       </c>
       <c r="P9" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="Q9">
         <v>3.35</v>
@@ -2633,7 +2639,7 @@
         <v>88</v>
       </c>
       <c r="P10" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="Q10">
         <v>2.45</v>
@@ -2839,7 +2845,7 @@
         <v>82</v>
       </c>
       <c r="P11" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="Q11">
         <v>3.45</v>
@@ -3045,7 +3051,7 @@
         <v>89</v>
       </c>
       <c r="P12" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="Q12">
         <v>2.75</v>
@@ -3251,7 +3257,7 @@
         <v>90</v>
       </c>
       <c r="P13" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Q13">
         <v>2.95</v>
@@ -3332,7 +3338,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ13">
-        <v>0.5</v>
+        <v>1.33</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -3869,7 +3875,7 @@
         <v>92</v>
       </c>
       <c r="P16" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="Q16">
         <v>2.75</v>
@@ -3947,7 +3953,7 @@
         <v>1.5</v>
       </c>
       <c r="AP16">
-        <v>2</v>
+        <v>1.33</v>
       </c>
       <c r="AQ16">
         <v>1.5</v>
@@ -4899,7 +4905,7 @@
         <v>94</v>
       </c>
       <c r="P21" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Q21">
         <v>3.1</v>
@@ -5105,7 +5111,7 @@
         <v>95</v>
       </c>
       <c r="P22" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="Q22">
         <v>3.6</v>
@@ -5517,7 +5523,7 @@
         <v>82</v>
       </c>
       <c r="P24" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="Q24">
         <v>2.75</v>
@@ -5723,7 +5729,7 @@
         <v>97</v>
       </c>
       <c r="P25" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="Q25">
         <v>4</v>
@@ -5929,7 +5935,7 @@
         <v>82</v>
       </c>
       <c r="P26" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="Q26">
         <v>3.6</v>
@@ -6135,7 +6141,7 @@
         <v>82</v>
       </c>
       <c r="P27" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="Q27">
         <v>2.75</v>
@@ -6341,7 +6347,7 @@
         <v>98</v>
       </c>
       <c r="P28" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="Q28">
         <v>3.75</v>
@@ -6753,7 +6759,7 @@
         <v>99</v>
       </c>
       <c r="P30" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="Q30">
         <v>2.63</v>
@@ -6834,7 +6840,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ30">
-        <v>0.5</v>
+        <v>1.33</v>
       </c>
       <c r="AR30">
         <v>1.76</v>
@@ -6910,6 +6916,212 @@
       </c>
       <c r="BP30">
         <v>1.14</v>
+      </c>
+    </row>
+    <row r="31" spans="1:68">
+      <c r="A31" s="1">
+        <v>30</v>
+      </c>
+      <c r="B31">
+        <v>7806780</v>
+      </c>
+      <c r="C31" t="s">
+        <v>68</v>
+      </c>
+      <c r="D31" t="s">
+        <v>69</v>
+      </c>
+      <c r="E31" s="2">
+        <v>45738.1875</v>
+      </c>
+      <c r="F31">
+        <v>4</v>
+      </c>
+      <c r="G31" t="s">
+        <v>72</v>
+      </c>
+      <c r="H31" t="s">
+        <v>70</v>
+      </c>
+      <c r="I31">
+        <v>1</v>
+      </c>
+      <c r="J31">
+        <v>1</v>
+      </c>
+      <c r="K31">
+        <v>2</v>
+      </c>
+      <c r="L31">
+        <v>2</v>
+      </c>
+      <c r="M31">
+        <v>3</v>
+      </c>
+      <c r="N31">
+        <v>5</v>
+      </c>
+      <c r="O31" t="s">
+        <v>100</v>
+      </c>
+      <c r="P31" t="s">
+        <v>119</v>
+      </c>
+      <c r="Q31">
+        <v>3.1</v>
+      </c>
+      <c r="R31">
+        <v>2.05</v>
+      </c>
+      <c r="S31">
+        <v>3.75</v>
+      </c>
+      <c r="T31">
+        <v>1.5</v>
+      </c>
+      <c r="U31">
+        <v>2.5</v>
+      </c>
+      <c r="V31">
+        <v>3.4</v>
+      </c>
+      <c r="W31">
+        <v>1.3</v>
+      </c>
+      <c r="X31">
+        <v>10</v>
+      </c>
+      <c r="Y31">
+        <v>1.06</v>
+      </c>
+      <c r="Z31">
+        <v>2.33</v>
+      </c>
+      <c r="AA31">
+        <v>3.13</v>
+      </c>
+      <c r="AB31">
+        <v>3.11</v>
+      </c>
+      <c r="AC31">
+        <v>1.08</v>
+      </c>
+      <c r="AD31">
+        <v>7.5</v>
+      </c>
+      <c r="AE31">
+        <v>1.4</v>
+      </c>
+      <c r="AF31">
+        <v>2.88</v>
+      </c>
+      <c r="AG31">
+        <v>2.1</v>
+      </c>
+      <c r="AH31">
+        <v>1.61</v>
+      </c>
+      <c r="AI31">
+        <v>1.83</v>
+      </c>
+      <c r="AJ31">
+        <v>1.83</v>
+      </c>
+      <c r="AK31">
+        <v>1.36</v>
+      </c>
+      <c r="AL31">
+        <v>1.3</v>
+      </c>
+      <c r="AM31">
+        <v>1.57</v>
+      </c>
+      <c r="AN31">
+        <v>2</v>
+      </c>
+      <c r="AO31">
+        <v>0.5</v>
+      </c>
+      <c r="AP31">
+        <v>1.33</v>
+      </c>
+      <c r="AQ31">
+        <v>1.33</v>
+      </c>
+      <c r="AR31">
+        <v>1.73</v>
+      </c>
+      <c r="AS31">
+        <v>1.39</v>
+      </c>
+      <c r="AT31">
+        <v>3.12</v>
+      </c>
+      <c r="AU31">
+        <v>3</v>
+      </c>
+      <c r="AV31">
+        <v>5</v>
+      </c>
+      <c r="AW31">
+        <v>3</v>
+      </c>
+      <c r="AX31">
+        <v>7</v>
+      </c>
+      <c r="AY31">
+        <v>9</v>
+      </c>
+      <c r="AZ31">
+        <v>13</v>
+      </c>
+      <c r="BA31">
+        <v>6</v>
+      </c>
+      <c r="BB31">
+        <v>0</v>
+      </c>
+      <c r="BC31">
+        <v>6</v>
+      </c>
+      <c r="BD31">
+        <v>1.85</v>
+      </c>
+      <c r="BE31">
+        <v>6.25</v>
+      </c>
+      <c r="BF31">
+        <v>2.17</v>
+      </c>
+      <c r="BG31">
+        <v>1.5</v>
+      </c>
+      <c r="BH31">
+        <v>2.35</v>
+      </c>
+      <c r="BI31">
+        <v>1.98</v>
+      </c>
+      <c r="BJ31">
+        <v>1.82</v>
+      </c>
+      <c r="BK31">
+        <v>2.33</v>
+      </c>
+      <c r="BL31">
+        <v>1.52</v>
+      </c>
+      <c r="BM31">
+        <v>3.05</v>
+      </c>
+      <c r="BN31">
+        <v>1.3</v>
+      </c>
+      <c r="BO31">
+        <v>4.1</v>
+      </c>
+      <c r="BP31">
+        <v>1.18</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/South Korea K League 1_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/South Korea K League 1_2025.xlsx
@@ -7058,19 +7058,19 @@
         <v>3.12</v>
       </c>
       <c r="AU31">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AV31">
+        <v>7</v>
+      </c>
+      <c r="AW31">
         <v>5</v>
       </c>
-      <c r="AW31">
-        <v>3</v>
-      </c>
       <c r="AX31">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AY31">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AZ31">
         <v>13</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/South Korea K League 1_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/South Korea K League 1_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="123">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -319,6 +319,12 @@
     <t>['7', '90+2']</t>
   </si>
   <si>
+    <t>['45+5', '90+1', '90+4']</t>
+  </si>
+  <si>
+    <t>['80']</t>
+  </si>
+  <si>
     <t>['32', '87', '90']</t>
   </si>
   <si>
@@ -374,6 +380,9 @@
   </si>
   <si>
     <t>['22', '68', '90+11']</t>
+  </si>
+  <si>
+    <t>['58', '80']</t>
   </si>
 </sst>
 </file>
@@ -735,7 +744,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP31"/>
+  <dimension ref="A1:BP33"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -991,7 +1000,7 @@
         <v>82</v>
       </c>
       <c r="P2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="Q2">
         <v>2.75</v>
@@ -1069,7 +1078,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>0.5</v>
+        <v>1.33</v>
       </c>
       <c r="AQ2">
         <v>3</v>
@@ -1609,7 +1618,7 @@
         <v>82</v>
       </c>
       <c r="P5" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="Q5">
         <v>2.1</v>
@@ -1815,7 +1824,7 @@
         <v>84</v>
       </c>
       <c r="P6" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="Q6">
         <v>3.1</v>
@@ -2021,7 +2030,7 @@
         <v>85</v>
       </c>
       <c r="P7" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="Q7">
         <v>3.5</v>
@@ -2227,7 +2236,7 @@
         <v>86</v>
       </c>
       <c r="P8" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="Q8">
         <v>3.4</v>
@@ -2433,7 +2442,7 @@
         <v>87</v>
       </c>
       <c r="P9" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="Q9">
         <v>3.35</v>
@@ -2639,7 +2648,7 @@
         <v>88</v>
       </c>
       <c r="P10" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="Q10">
         <v>2.45</v>
@@ -2717,7 +2726,7 @@
         <v>3</v>
       </c>
       <c r="AP10">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AQ10">
         <v>1.5</v>
@@ -2845,7 +2854,7 @@
         <v>82</v>
       </c>
       <c r="P11" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="Q11">
         <v>3.45</v>
@@ -2926,7 +2935,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ11">
-        <v>2</v>
+        <v>1.33</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -3051,7 +3060,7 @@
         <v>89</v>
       </c>
       <c r="P12" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="Q12">
         <v>2.75</v>
@@ -3257,7 +3266,7 @@
         <v>90</v>
       </c>
       <c r="P13" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="Q13">
         <v>2.95</v>
@@ -3747,10 +3756,10 @@
         <v>0</v>
       </c>
       <c r="AP15">
+        <v>1.33</v>
+      </c>
+      <c r="AQ15">
         <v>0.5</v>
-      </c>
-      <c r="AQ15">
-        <v>1</v>
       </c>
       <c r="AR15">
         <v>1.87</v>
@@ -3875,7 +3884,7 @@
         <v>92</v>
       </c>
       <c r="P16" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="Q16">
         <v>2.75</v>
@@ -4571,7 +4580,7 @@
         <v>1.5</v>
       </c>
       <c r="AP19">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AQ19">
         <v>1.75</v>
@@ -4905,7 +4914,7 @@
         <v>94</v>
       </c>
       <c r="P21" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="Q21">
         <v>3.1</v>
@@ -5111,7 +5120,7 @@
         <v>95</v>
       </c>
       <c r="P22" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="Q22">
         <v>3.6</v>
@@ -5523,7 +5532,7 @@
         <v>82</v>
       </c>
       <c r="P24" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="Q24">
         <v>2.75</v>
@@ -5729,7 +5738,7 @@
         <v>97</v>
       </c>
       <c r="P25" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="Q25">
         <v>4</v>
@@ -5935,7 +5944,7 @@
         <v>82</v>
       </c>
       <c r="P26" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="Q26">
         <v>3.6</v>
@@ -6141,7 +6150,7 @@
         <v>82</v>
       </c>
       <c r="P27" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="Q27">
         <v>2.75</v>
@@ -6347,7 +6356,7 @@
         <v>98</v>
       </c>
       <c r="P28" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="Q28">
         <v>3.75</v>
@@ -6428,7 +6437,7 @@
         <v>1</v>
       </c>
       <c r="AQ28">
-        <v>2</v>
+        <v>1.33</v>
       </c>
       <c r="AR28">
         <v>1.36</v>
@@ -6759,7 +6768,7 @@
         <v>99</v>
       </c>
       <c r="P30" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="Q30">
         <v>2.63</v>
@@ -6965,7 +6974,7 @@
         <v>100</v>
       </c>
       <c r="P31" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="Q31">
         <v>3.1</v>
@@ -7122,6 +7131,418 @@
       </c>
       <c r="BP31">
         <v>1.18</v>
+      </c>
+    </row>
+    <row r="32" spans="1:68">
+      <c r="A32" s="1">
+        <v>31</v>
+      </c>
+      <c r="B32">
+        <v>7806788</v>
+      </c>
+      <c r="C32" t="s">
+        <v>68</v>
+      </c>
+      <c r="D32" t="s">
+        <v>69</v>
+      </c>
+      <c r="E32" s="2">
+        <v>45745.08333333334</v>
+      </c>
+      <c r="F32">
+        <v>6</v>
+      </c>
+      <c r="G32" t="s">
+        <v>76</v>
+      </c>
+      <c r="H32" t="s">
+        <v>75</v>
+      </c>
+      <c r="I32">
+        <v>1</v>
+      </c>
+      <c r="J32">
+        <v>0</v>
+      </c>
+      <c r="K32">
+        <v>1</v>
+      </c>
+      <c r="L32">
+        <v>3</v>
+      </c>
+      <c r="M32">
+        <v>2</v>
+      </c>
+      <c r="N32">
+        <v>5</v>
+      </c>
+      <c r="O32" t="s">
+        <v>101</v>
+      </c>
+      <c r="P32" t="s">
+        <v>122</v>
+      </c>
+      <c r="Q32">
+        <v>2.5</v>
+      </c>
+      <c r="R32">
+        <v>2.1</v>
+      </c>
+      <c r="S32">
+        <v>4.75</v>
+      </c>
+      <c r="T32">
+        <v>1.44</v>
+      </c>
+      <c r="U32">
+        <v>2.63</v>
+      </c>
+      <c r="V32">
+        <v>3.25</v>
+      </c>
+      <c r="W32">
+        <v>1.33</v>
+      </c>
+      <c r="X32">
+        <v>9</v>
+      </c>
+      <c r="Y32">
+        <v>1.07</v>
+      </c>
+      <c r="Z32">
+        <v>1.86</v>
+      </c>
+      <c r="AA32">
+        <v>3.45</v>
+      </c>
+      <c r="AB32">
+        <v>4.1</v>
+      </c>
+      <c r="AC32">
+        <v>1.07</v>
+      </c>
+      <c r="AD32">
+        <v>8</v>
+      </c>
+      <c r="AE32">
+        <v>1.36</v>
+      </c>
+      <c r="AF32">
+        <v>3.1</v>
+      </c>
+      <c r="AG32">
+        <v>1.98</v>
+      </c>
+      <c r="AH32">
+        <v>1.77</v>
+      </c>
+      <c r="AI32">
+        <v>1.83</v>
+      </c>
+      <c r="AJ32">
+        <v>1.83</v>
+      </c>
+      <c r="AK32">
+        <v>1.22</v>
+      </c>
+      <c r="AL32">
+        <v>1.25</v>
+      </c>
+      <c r="AM32">
+        <v>1.85</v>
+      </c>
+      <c r="AN32">
+        <v>2</v>
+      </c>
+      <c r="AO32">
+        <v>1</v>
+      </c>
+      <c r="AP32">
+        <v>2.33</v>
+      </c>
+      <c r="AQ32">
+        <v>0.5</v>
+      </c>
+      <c r="AR32">
+        <v>0.86</v>
+      </c>
+      <c r="AS32">
+        <v>1.13</v>
+      </c>
+      <c r="AT32">
+        <v>1.99</v>
+      </c>
+      <c r="AU32">
+        <v>5</v>
+      </c>
+      <c r="AV32">
+        <v>3</v>
+      </c>
+      <c r="AW32">
+        <v>2</v>
+      </c>
+      <c r="AX32">
+        <v>1</v>
+      </c>
+      <c r="AY32">
+        <v>15</v>
+      </c>
+      <c r="AZ32">
+        <v>4</v>
+      </c>
+      <c r="BA32">
+        <v>8</v>
+      </c>
+      <c r="BB32">
+        <v>4</v>
+      </c>
+      <c r="BC32">
+        <v>12</v>
+      </c>
+      <c r="BD32">
+        <v>1.58</v>
+      </c>
+      <c r="BE32">
+        <v>6.5</v>
+      </c>
+      <c r="BF32">
+        <v>2.63</v>
+      </c>
+      <c r="BG32">
+        <v>1.4</v>
+      </c>
+      <c r="BH32">
+        <v>2.65</v>
+      </c>
+      <c r="BI32">
+        <v>1.68</v>
+      </c>
+      <c r="BJ32">
+        <v>2.05</v>
+      </c>
+      <c r="BK32">
+        <v>2.07</v>
+      </c>
+      <c r="BL32">
+        <v>1.66</v>
+      </c>
+      <c r="BM32">
+        <v>2.65</v>
+      </c>
+      <c r="BN32">
+        <v>1.41</v>
+      </c>
+      <c r="BO32">
+        <v>3.55</v>
+      </c>
+      <c r="BP32">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="33" spans="1:68">
+      <c r="A33" s="1">
+        <v>32</v>
+      </c>
+      <c r="B33">
+        <v>7806789</v>
+      </c>
+      <c r="C33" t="s">
+        <v>68</v>
+      </c>
+      <c r="D33" t="s">
+        <v>69</v>
+      </c>
+      <c r="E33" s="2">
+        <v>45745.1875</v>
+      </c>
+      <c r="F33">
+        <v>6</v>
+      </c>
+      <c r="G33" t="s">
+        <v>70</v>
+      </c>
+      <c r="H33" t="s">
+        <v>73</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>0</v>
+      </c>
+      <c r="K33">
+        <v>0</v>
+      </c>
+      <c r="L33">
+        <v>1</v>
+      </c>
+      <c r="M33">
+        <v>0</v>
+      </c>
+      <c r="N33">
+        <v>1</v>
+      </c>
+      <c r="O33" t="s">
+        <v>102</v>
+      </c>
+      <c r="P33" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q33">
+        <v>3.75</v>
+      </c>
+      <c r="R33">
+        <v>2.1</v>
+      </c>
+      <c r="S33">
+        <v>2.88</v>
+      </c>
+      <c r="T33">
+        <v>1.4</v>
+      </c>
+      <c r="U33">
+        <v>2.75</v>
+      </c>
+      <c r="V33">
+        <v>3</v>
+      </c>
+      <c r="W33">
+        <v>1.36</v>
+      </c>
+      <c r="X33">
+        <v>8</v>
+      </c>
+      <c r="Y33">
+        <v>1.08</v>
+      </c>
+      <c r="Z33">
+        <v>3.11</v>
+      </c>
+      <c r="AA33">
+        <v>3.33</v>
+      </c>
+      <c r="AB33">
+        <v>2.23</v>
+      </c>
+      <c r="AC33">
+        <v>1.06</v>
+      </c>
+      <c r="AD33">
+        <v>8.5</v>
+      </c>
+      <c r="AE33">
+        <v>1.33</v>
+      </c>
+      <c r="AF33">
+        <v>3.3</v>
+      </c>
+      <c r="AG33">
+        <v>1.94</v>
+      </c>
+      <c r="AH33">
+        <v>1.8</v>
+      </c>
+      <c r="AI33">
+        <v>1.73</v>
+      </c>
+      <c r="AJ33">
+        <v>2</v>
+      </c>
+      <c r="AK33">
+        <v>1.6</v>
+      </c>
+      <c r="AL33">
+        <v>1.28</v>
+      </c>
+      <c r="AM33">
+        <v>1.35</v>
+      </c>
+      <c r="AN33">
+        <v>0.5</v>
+      </c>
+      <c r="AO33">
+        <v>2</v>
+      </c>
+      <c r="AP33">
+        <v>1.33</v>
+      </c>
+      <c r="AQ33">
+        <v>1.33</v>
+      </c>
+      <c r="AR33">
+        <v>1.88</v>
+      </c>
+      <c r="AS33">
+        <v>1.93</v>
+      </c>
+      <c r="AT33">
+        <v>3.81</v>
+      </c>
+      <c r="AU33">
+        <v>3</v>
+      </c>
+      <c r="AV33">
+        <v>2</v>
+      </c>
+      <c r="AW33">
+        <v>5</v>
+      </c>
+      <c r="AX33">
+        <v>6</v>
+      </c>
+      <c r="AY33">
+        <v>13</v>
+      </c>
+      <c r="AZ33">
+        <v>9</v>
+      </c>
+      <c r="BA33">
+        <v>5</v>
+      </c>
+      <c r="BB33">
+        <v>4</v>
+      </c>
+      <c r="BC33">
+        <v>9</v>
+      </c>
+      <c r="BD33">
+        <v>2.15</v>
+      </c>
+      <c r="BE33">
+        <v>6.1</v>
+      </c>
+      <c r="BF33">
+        <v>1.88</v>
+      </c>
+      <c r="BG33">
+        <v>1.49</v>
+      </c>
+      <c r="BH33">
+        <v>2.43</v>
+      </c>
+      <c r="BI33">
+        <v>1.8</v>
+      </c>
+      <c r="BJ33">
+        <v>1.89</v>
+      </c>
+      <c r="BK33">
+        <v>2.3</v>
+      </c>
+      <c r="BL33">
+        <v>1.54</v>
+      </c>
+      <c r="BM33">
+        <v>2.95</v>
+      </c>
+      <c r="BN33">
+        <v>1.33</v>
+      </c>
+      <c r="BO33">
+        <v>4</v>
+      </c>
+      <c r="BP33">
+        <v>1.2</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/South Korea K League 1_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/South Korea K League 1_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="128">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -325,6 +325,15 @@
     <t>['80']</t>
   </si>
   <si>
+    <t>['62']</t>
+  </si>
+  <si>
+    <t>['22']</t>
+  </si>
+  <si>
+    <t>['76']</t>
+  </si>
+  <si>
     <t>['32', '87', '90']</t>
   </si>
   <si>
@@ -383,6 +392,12 @@
   </si>
   <si>
     <t>['58', '80']</t>
+  </si>
+  <si>
+    <t>['34']</t>
+  </si>
+  <si>
+    <t>['53']</t>
   </si>
 </sst>
 </file>
@@ -744,7 +759,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP33"/>
+  <dimension ref="A1:BP37"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1000,7 +1015,7 @@
         <v>82</v>
       </c>
       <c r="P2" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="Q2">
         <v>2.75</v>
@@ -1284,7 +1299,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AQ3">
         <v>1.33</v>
@@ -1493,7 +1508,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ4">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -1618,7 +1633,7 @@
         <v>82</v>
       </c>
       <c r="P5" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="Q5">
         <v>2.1</v>
@@ -1824,7 +1839,7 @@
         <v>84</v>
       </c>
       <c r="P6" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="Q6">
         <v>3.1</v>
@@ -2030,7 +2045,7 @@
         <v>85</v>
       </c>
       <c r="P7" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="Q7">
         <v>3.5</v>
@@ -2111,7 +2126,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ7">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2236,7 +2251,7 @@
         <v>86</v>
       </c>
       <c r="P8" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="Q8">
         <v>3.4</v>
@@ -2314,7 +2329,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AQ8">
         <v>1.75</v>
@@ -2442,7 +2457,7 @@
         <v>87</v>
       </c>
       <c r="P9" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="Q9">
         <v>3.35</v>
@@ -2523,7 +2538,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ9">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AR9">
         <v>1.95</v>
@@ -2648,7 +2663,7 @@
         <v>88</v>
       </c>
       <c r="P10" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="Q10">
         <v>2.45</v>
@@ -2854,7 +2869,7 @@
         <v>82</v>
       </c>
       <c r="P11" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="Q11">
         <v>3.45</v>
@@ -2932,7 +2947,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AQ11">
         <v>1.33</v>
@@ -3060,7 +3075,7 @@
         <v>89</v>
       </c>
       <c r="P12" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="Q12">
         <v>2.75</v>
@@ -3266,7 +3281,7 @@
         <v>90</v>
       </c>
       <c r="P13" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="Q13">
         <v>2.95</v>
@@ -3553,7 +3568,7 @@
         <v>2</v>
       </c>
       <c r="AQ14">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AR14">
         <v>2.51</v>
@@ -3884,7 +3899,7 @@
         <v>92</v>
       </c>
       <c r="P16" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="Q16">
         <v>2.75</v>
@@ -4168,10 +4183,10 @@
         <v>0.5</v>
       </c>
       <c r="AP17">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AQ17">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AR17">
         <v>1.3</v>
@@ -4914,7 +4929,7 @@
         <v>94</v>
       </c>
       <c r="P21" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="Q21">
         <v>3.1</v>
@@ -5120,7 +5135,7 @@
         <v>95</v>
       </c>
       <c r="P22" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="Q22">
         <v>3.6</v>
@@ -5532,7 +5547,7 @@
         <v>82</v>
       </c>
       <c r="P24" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="Q24">
         <v>2.75</v>
@@ -5613,7 +5628,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ24">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AR24">
         <v>1.82</v>
@@ -5738,7 +5753,7 @@
         <v>97</v>
       </c>
       <c r="P25" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="Q25">
         <v>4</v>
@@ -5816,7 +5831,7 @@
         <v>3</v>
       </c>
       <c r="AP25">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AQ25">
         <v>3</v>
@@ -5944,7 +5959,7 @@
         <v>82</v>
       </c>
       <c r="P26" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="Q26">
         <v>3.6</v>
@@ -6150,7 +6165,7 @@
         <v>82</v>
       </c>
       <c r="P27" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="Q27">
         <v>2.75</v>
@@ -6356,7 +6371,7 @@
         <v>98</v>
       </c>
       <c r="P28" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="Q28">
         <v>3.75</v>
@@ -6640,7 +6655,7 @@
         <v>1</v>
       </c>
       <c r="AP29">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AQ29">
         <v>1</v>
@@ -6768,7 +6783,7 @@
         <v>99</v>
       </c>
       <c r="P30" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="Q30">
         <v>2.63</v>
@@ -6974,7 +6989,7 @@
         <v>100</v>
       </c>
       <c r="P31" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="Q31">
         <v>3.1</v>
@@ -7180,7 +7195,7 @@
         <v>101</v>
       </c>
       <c r="P32" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="Q32">
         <v>2.5</v>
@@ -7543,6 +7558,830 @@
       </c>
       <c r="BP33">
         <v>1.2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:68">
+      <c r="A34" s="1">
+        <v>33</v>
+      </c>
+      <c r="B34">
+        <v>7806790</v>
+      </c>
+      <c r="C34" t="s">
+        <v>68</v>
+      </c>
+      <c r="D34" t="s">
+        <v>69</v>
+      </c>
+      <c r="E34" s="2">
+        <v>45745.1875</v>
+      </c>
+      <c r="F34">
+        <v>6</v>
+      </c>
+      <c r="G34" t="s">
+        <v>77</v>
+      </c>
+      <c r="H34" t="s">
+        <v>72</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>1</v>
+      </c>
+      <c r="K34">
+        <v>1</v>
+      </c>
+      <c r="L34">
+        <v>1</v>
+      </c>
+      <c r="M34">
+        <v>1</v>
+      </c>
+      <c r="N34">
+        <v>2</v>
+      </c>
+      <c r="O34" t="s">
+        <v>103</v>
+      </c>
+      <c r="P34" t="s">
+        <v>126</v>
+      </c>
+      <c r="Q34">
+        <v>3.2</v>
+      </c>
+      <c r="R34">
+        <v>2</v>
+      </c>
+      <c r="S34">
+        <v>3.75</v>
+      </c>
+      <c r="T34">
+        <v>1.5</v>
+      </c>
+      <c r="U34">
+        <v>2.5</v>
+      </c>
+      <c r="V34">
+        <v>3.4</v>
+      </c>
+      <c r="W34">
+        <v>1.3</v>
+      </c>
+      <c r="X34">
+        <v>10</v>
+      </c>
+      <c r="Y34">
+        <v>1.06</v>
+      </c>
+      <c r="Z34">
+        <v>2.46</v>
+      </c>
+      <c r="AA34">
+        <v>3.13</v>
+      </c>
+      <c r="AB34">
+        <v>2.91</v>
+      </c>
+      <c r="AC34">
+        <v>1.09</v>
+      </c>
+      <c r="AD34">
+        <v>7</v>
+      </c>
+      <c r="AE34">
+        <v>1.42</v>
+      </c>
+      <c r="AF34">
+        <v>2.8</v>
+      </c>
+      <c r="AG34">
+        <v>2.15</v>
+      </c>
+      <c r="AH34">
+        <v>1.57</v>
+      </c>
+      <c r="AI34">
+        <v>1.83</v>
+      </c>
+      <c r="AJ34">
+        <v>1.83</v>
+      </c>
+      <c r="AK34">
+        <v>1.36</v>
+      </c>
+      <c r="AL34">
+        <v>1.33</v>
+      </c>
+      <c r="AM34">
+        <v>1.53</v>
+      </c>
+      <c r="AN34">
+        <v>1.5</v>
+      </c>
+      <c r="AO34">
+        <v>1</v>
+      </c>
+      <c r="AP34">
+        <v>1.33</v>
+      </c>
+      <c r="AQ34">
+        <v>1</v>
+      </c>
+      <c r="AR34">
+        <v>1.58</v>
+      </c>
+      <c r="AS34">
+        <v>1.1</v>
+      </c>
+      <c r="AT34">
+        <v>2.68</v>
+      </c>
+      <c r="AU34">
+        <v>5</v>
+      </c>
+      <c r="AV34">
+        <v>2</v>
+      </c>
+      <c r="AW34">
+        <v>4</v>
+      </c>
+      <c r="AX34">
+        <v>5</v>
+      </c>
+      <c r="AY34">
+        <v>11</v>
+      </c>
+      <c r="AZ34">
+        <v>11</v>
+      </c>
+      <c r="BA34">
+        <v>6</v>
+      </c>
+      <c r="BB34">
+        <v>6</v>
+      </c>
+      <c r="BC34">
+        <v>12</v>
+      </c>
+      <c r="BD34">
+        <v>1.84</v>
+      </c>
+      <c r="BE34">
+        <v>6.25</v>
+      </c>
+      <c r="BF34">
+        <v>2.18</v>
+      </c>
+      <c r="BG34">
+        <v>1.5</v>
+      </c>
+      <c r="BH34">
+        <v>2.4</v>
+      </c>
+      <c r="BI34">
+        <v>1.83</v>
+      </c>
+      <c r="BJ34">
+        <v>1.86</v>
+      </c>
+      <c r="BK34">
+        <v>2.32</v>
+      </c>
+      <c r="BL34">
+        <v>1.53</v>
+      </c>
+      <c r="BM34">
+        <v>3.05</v>
+      </c>
+      <c r="BN34">
+        <v>1.32</v>
+      </c>
+      <c r="BO34">
+        <v>4.1</v>
+      </c>
+      <c r="BP34">
+        <v>1.19</v>
+      </c>
+    </row>
+    <row r="35" spans="1:68">
+      <c r="A35" s="1">
+        <v>34</v>
+      </c>
+      <c r="B35">
+        <v>7806791</v>
+      </c>
+      <c r="C35" t="s">
+        <v>68</v>
+      </c>
+      <c r="D35" t="s">
+        <v>69</v>
+      </c>
+      <c r="E35" s="2">
+        <v>45746.08333333334</v>
+      </c>
+      <c r="F35">
+        <v>6</v>
+      </c>
+      <c r="G35" t="s">
+        <v>71</v>
+      </c>
+      <c r="H35" t="s">
+        <v>79</v>
+      </c>
+      <c r="I35">
+        <v>1</v>
+      </c>
+      <c r="J35">
+        <v>0</v>
+      </c>
+      <c r="K35">
+        <v>1</v>
+      </c>
+      <c r="L35">
+        <v>1</v>
+      </c>
+      <c r="M35">
+        <v>0</v>
+      </c>
+      <c r="N35">
+        <v>1</v>
+      </c>
+      <c r="O35" t="s">
+        <v>104</v>
+      </c>
+      <c r="P35" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q35">
+        <v>3.1</v>
+      </c>
+      <c r="R35">
+        <v>2.1</v>
+      </c>
+      <c r="S35">
+        <v>3.6</v>
+      </c>
+      <c r="T35">
+        <v>1.44</v>
+      </c>
+      <c r="U35">
+        <v>2.63</v>
+      </c>
+      <c r="V35">
+        <v>3.25</v>
+      </c>
+      <c r="W35">
+        <v>1.33</v>
+      </c>
+      <c r="X35">
+        <v>9</v>
+      </c>
+      <c r="Y35">
+        <v>1.07</v>
+      </c>
+      <c r="Z35">
+        <v>2.37</v>
+      </c>
+      <c r="AA35">
+        <v>3.21</v>
+      </c>
+      <c r="AB35">
+        <v>2.98</v>
+      </c>
+      <c r="AC35">
+        <v>1.07</v>
+      </c>
+      <c r="AD35">
+        <v>8</v>
+      </c>
+      <c r="AE35">
+        <v>1.35</v>
+      </c>
+      <c r="AF35">
+        <v>3.1</v>
+      </c>
+      <c r="AG35">
+        <v>1.95</v>
+      </c>
+      <c r="AH35">
+        <v>1.7</v>
+      </c>
+      <c r="AI35">
+        <v>1.8</v>
+      </c>
+      <c r="AJ35">
+        <v>1.91</v>
+      </c>
+      <c r="AK35">
+        <v>1.38</v>
+      </c>
+      <c r="AL35">
+        <v>1.28</v>
+      </c>
+      <c r="AM35">
+        <v>1.55</v>
+      </c>
+      <c r="AN35">
+        <v>1</v>
+      </c>
+      <c r="AO35">
+        <v>0.33</v>
+      </c>
+      <c r="AP35">
+        <v>1.5</v>
+      </c>
+      <c r="AQ35">
+        <v>0.25</v>
+      </c>
+      <c r="AR35">
+        <v>1.17</v>
+      </c>
+      <c r="AS35">
+        <v>0.98</v>
+      </c>
+      <c r="AT35">
+        <v>2.15</v>
+      </c>
+      <c r="AU35">
+        <v>5</v>
+      </c>
+      <c r="AV35">
+        <v>0</v>
+      </c>
+      <c r="AW35">
+        <v>5</v>
+      </c>
+      <c r="AX35">
+        <v>10</v>
+      </c>
+      <c r="AY35">
+        <v>11</v>
+      </c>
+      <c r="AZ35">
+        <v>14</v>
+      </c>
+      <c r="BA35">
+        <v>4</v>
+      </c>
+      <c r="BB35">
+        <v>6</v>
+      </c>
+      <c r="BC35">
+        <v>10</v>
+      </c>
+      <c r="BD35">
+        <v>1.82</v>
+      </c>
+      <c r="BE35">
+        <v>6.4</v>
+      </c>
+      <c r="BF35">
+        <v>2.18</v>
+      </c>
+      <c r="BG35">
+        <v>1.47</v>
+      </c>
+      <c r="BH35">
+        <v>2.48</v>
+      </c>
+      <c r="BI35">
+        <v>1.77</v>
+      </c>
+      <c r="BJ35">
+        <v>1.92</v>
+      </c>
+      <c r="BK35">
+        <v>2.23</v>
+      </c>
+      <c r="BL35">
+        <v>1.56</v>
+      </c>
+      <c r="BM35">
+        <v>2.9</v>
+      </c>
+      <c r="BN35">
+        <v>1.34</v>
+      </c>
+      <c r="BO35">
+        <v>3.9</v>
+      </c>
+      <c r="BP35">
+        <v>1.21</v>
+      </c>
+    </row>
+    <row r="36" spans="1:68">
+      <c r="A36" s="1">
+        <v>35</v>
+      </c>
+      <c r="B36">
+        <v>7806792</v>
+      </c>
+      <c r="C36" t="s">
+        <v>68</v>
+      </c>
+      <c r="D36" t="s">
+        <v>69</v>
+      </c>
+      <c r="E36" s="2">
+        <v>45746.1875</v>
+      </c>
+      <c r="F36">
+        <v>6</v>
+      </c>
+      <c r="G36" t="s">
+        <v>81</v>
+      </c>
+      <c r="H36" t="s">
+        <v>78</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>0</v>
+      </c>
+      <c r="K36">
+        <v>0</v>
+      </c>
+      <c r="L36">
+        <v>1</v>
+      </c>
+      <c r="M36">
+        <v>0</v>
+      </c>
+      <c r="N36">
+        <v>1</v>
+      </c>
+      <c r="O36" t="s">
+        <v>105</v>
+      </c>
+      <c r="P36" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q36">
+        <v>2.63</v>
+      </c>
+      <c r="R36">
+        <v>2.05</v>
+      </c>
+      <c r="S36">
+        <v>4.5</v>
+      </c>
+      <c r="T36">
+        <v>1.44</v>
+      </c>
+      <c r="U36">
+        <v>2.63</v>
+      </c>
+      <c r="V36">
+        <v>3.25</v>
+      </c>
+      <c r="W36">
+        <v>1.33</v>
+      </c>
+      <c r="X36">
+        <v>10</v>
+      </c>
+      <c r="Y36">
+        <v>1.06</v>
+      </c>
+      <c r="Z36">
+        <v>1.93</v>
+      </c>
+      <c r="AA36">
+        <v>3.35</v>
+      </c>
+      <c r="AB36">
+        <v>3.96</v>
+      </c>
+      <c r="AC36">
+        <v>1.07</v>
+      </c>
+      <c r="AD36">
+        <v>8</v>
+      </c>
+      <c r="AE36">
+        <v>1.38</v>
+      </c>
+      <c r="AF36">
+        <v>3</v>
+      </c>
+      <c r="AG36">
+        <v>2</v>
+      </c>
+      <c r="AH36">
+        <v>1.65</v>
+      </c>
+      <c r="AI36">
+        <v>1.91</v>
+      </c>
+      <c r="AJ36">
+        <v>1.8</v>
+      </c>
+      <c r="AK36">
+        <v>1.25</v>
+      </c>
+      <c r="AL36">
+        <v>1.25</v>
+      </c>
+      <c r="AM36">
+        <v>1.77</v>
+      </c>
+      <c r="AN36">
+        <v>1</v>
+      </c>
+      <c r="AO36">
+        <v>1.5</v>
+      </c>
+      <c r="AP36">
+        <v>2</v>
+      </c>
+      <c r="AQ36">
+        <v>1</v>
+      </c>
+      <c r="AR36">
+        <v>1.94</v>
+      </c>
+      <c r="AS36">
+        <v>0.92</v>
+      </c>
+      <c r="AT36">
+        <v>2.86</v>
+      </c>
+      <c r="AU36">
+        <v>6</v>
+      </c>
+      <c r="AV36">
+        <v>0</v>
+      </c>
+      <c r="AW36">
+        <v>9</v>
+      </c>
+      <c r="AX36">
+        <v>4</v>
+      </c>
+      <c r="AY36">
+        <v>18</v>
+      </c>
+      <c r="AZ36">
+        <v>7</v>
+      </c>
+      <c r="BA36">
+        <v>4</v>
+      </c>
+      <c r="BB36">
+        <v>5</v>
+      </c>
+      <c r="BC36">
+        <v>9</v>
+      </c>
+      <c r="BD36">
+        <v>1.68</v>
+      </c>
+      <c r="BE36">
+        <v>6.25</v>
+      </c>
+      <c r="BF36">
+        <v>2.48</v>
+      </c>
+      <c r="BG36">
+        <v>1.55</v>
+      </c>
+      <c r="BH36">
+        <v>2.28</v>
+      </c>
+      <c r="BI36">
+        <v>1.91</v>
+      </c>
+      <c r="BJ36">
+        <v>1.78</v>
+      </c>
+      <c r="BK36">
+        <v>2.45</v>
+      </c>
+      <c r="BL36">
+        <v>1.48</v>
+      </c>
+      <c r="BM36">
+        <v>3.3</v>
+      </c>
+      <c r="BN36">
+        <v>1.28</v>
+      </c>
+      <c r="BO36">
+        <v>4.35</v>
+      </c>
+      <c r="BP36">
+        <v>1.17</v>
+      </c>
+    </row>
+    <row r="37" spans="1:68">
+      <c r="A37" s="1">
+        <v>36</v>
+      </c>
+      <c r="B37">
+        <v>7806793</v>
+      </c>
+      <c r="C37" t="s">
+        <v>68</v>
+      </c>
+      <c r="D37" t="s">
+        <v>69</v>
+      </c>
+      <c r="E37" s="2">
+        <v>45746.1875</v>
+      </c>
+      <c r="F37">
+        <v>6</v>
+      </c>
+      <c r="G37" t="s">
+        <v>80</v>
+      </c>
+      <c r="H37" t="s">
+        <v>74</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>0</v>
+      </c>
+      <c r="K37">
+        <v>0</v>
+      </c>
+      <c r="L37">
+        <v>0</v>
+      </c>
+      <c r="M37">
+        <v>1</v>
+      </c>
+      <c r="N37">
+        <v>1</v>
+      </c>
+      <c r="O37" t="s">
+        <v>82</v>
+      </c>
+      <c r="P37" t="s">
+        <v>127</v>
+      </c>
+      <c r="Q37">
+        <v>4</v>
+      </c>
+      <c r="R37">
+        <v>2.05</v>
+      </c>
+      <c r="S37">
+        <v>2.88</v>
+      </c>
+      <c r="T37">
+        <v>1.44</v>
+      </c>
+      <c r="U37">
+        <v>2.63</v>
+      </c>
+      <c r="V37">
+        <v>3.25</v>
+      </c>
+      <c r="W37">
+        <v>1.33</v>
+      </c>
+      <c r="X37">
+        <v>9</v>
+      </c>
+      <c r="Y37">
+        <v>1.07</v>
+      </c>
+      <c r="Z37">
+        <v>3.13</v>
+      </c>
+      <c r="AA37">
+        <v>3.45</v>
+      </c>
+      <c r="AB37">
+        <v>2.18</v>
+      </c>
+      <c r="AC37">
+        <v>1.06</v>
+      </c>
+      <c r="AD37">
+        <v>8.5</v>
+      </c>
+      <c r="AE37">
+        <v>1.35</v>
+      </c>
+      <c r="AF37">
+        <v>3.1</v>
+      </c>
+      <c r="AG37">
+        <v>1.95</v>
+      </c>
+      <c r="AH37">
+        <v>1.7</v>
+      </c>
+      <c r="AI37">
+        <v>1.83</v>
+      </c>
+      <c r="AJ37">
+        <v>1.83</v>
+      </c>
+      <c r="AK37">
+        <v>1.67</v>
+      </c>
+      <c r="AL37">
+        <v>1.25</v>
+      </c>
+      <c r="AM37">
+        <v>1.33</v>
+      </c>
+      <c r="AN37">
+        <v>0</v>
+      </c>
+      <c r="AO37">
+        <v>0</v>
+      </c>
+      <c r="AP37">
+        <v>0</v>
+      </c>
+      <c r="AQ37">
+        <v>1.5</v>
+      </c>
+      <c r="AR37">
+        <v>1.26</v>
+      </c>
+      <c r="AS37">
+        <v>1.32</v>
+      </c>
+      <c r="AT37">
+        <v>2.58</v>
+      </c>
+      <c r="AU37">
+        <v>2</v>
+      </c>
+      <c r="AV37">
+        <v>3</v>
+      </c>
+      <c r="AW37">
+        <v>5</v>
+      </c>
+      <c r="AX37">
+        <v>3</v>
+      </c>
+      <c r="AY37">
+        <v>13</v>
+      </c>
+      <c r="AZ37">
+        <v>11</v>
+      </c>
+      <c r="BA37">
+        <v>7</v>
+      </c>
+      <c r="BB37">
+        <v>5</v>
+      </c>
+      <c r="BC37">
+        <v>12</v>
+      </c>
+      <c r="BD37">
+        <v>2.38</v>
+      </c>
+      <c r="BE37">
+        <v>6.25</v>
+      </c>
+      <c r="BF37">
+        <v>1.74</v>
+      </c>
+      <c r="BG37">
+        <v>1.55</v>
+      </c>
+      <c r="BH37">
+        <v>2.28</v>
+      </c>
+      <c r="BI37">
+        <v>1.93</v>
+      </c>
+      <c r="BJ37">
+        <v>1.77</v>
+      </c>
+      <c r="BK37">
+        <v>2.45</v>
+      </c>
+      <c r="BL37">
+        <v>1.48</v>
+      </c>
+      <c r="BM37">
+        <v>3.3</v>
+      </c>
+      <c r="BN37">
+        <v>1.28</v>
+      </c>
+      <c r="BO37">
+        <v>4.4</v>
+      </c>
+      <c r="BP37">
+        <v>1.16</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/South Korea K League 1_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/South Korea K League 1_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="130">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -334,6 +334,9 @@
     <t>['76']</t>
   </si>
   <si>
+    <t>['42', '45+4']</t>
+  </si>
+  <si>
     <t>['32', '87', '90']</t>
   </si>
   <si>
@@ -398,6 +401,9 @@
   </si>
   <si>
     <t>['53']</t>
+  </si>
+  <si>
+    <t>['4', '13', '64']</t>
   </si>
 </sst>
 </file>
@@ -759,7 +765,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP37"/>
+  <dimension ref="A1:BP38"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1015,7 +1021,7 @@
         <v>82</v>
       </c>
       <c r="P2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="Q2">
         <v>2.75</v>
@@ -1633,7 +1639,7 @@
         <v>82</v>
       </c>
       <c r="P5" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="Q5">
         <v>2.1</v>
@@ -1711,7 +1717,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AQ5">
         <v>1.5</v>
@@ -1839,7 +1845,7 @@
         <v>84</v>
       </c>
       <c r="P6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="Q6">
         <v>3.1</v>
@@ -2045,7 +2051,7 @@
         <v>85</v>
       </c>
       <c r="P7" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="Q7">
         <v>3.5</v>
@@ -2251,7 +2257,7 @@
         <v>86</v>
       </c>
       <c r="P8" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Q8">
         <v>3.4</v>
@@ -2457,7 +2463,7 @@
         <v>87</v>
       </c>
       <c r="P9" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="Q9">
         <v>3.35</v>
@@ -2663,7 +2669,7 @@
         <v>88</v>
       </c>
       <c r="P10" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="Q10">
         <v>2.45</v>
@@ -2869,7 +2875,7 @@
         <v>82</v>
       </c>
       <c r="P11" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="Q11">
         <v>3.45</v>
@@ -3075,7 +3081,7 @@
         <v>89</v>
       </c>
       <c r="P12" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="Q12">
         <v>2.75</v>
@@ -3281,7 +3287,7 @@
         <v>90</v>
       </c>
       <c r="P13" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="Q13">
         <v>2.95</v>
@@ -3565,7 +3571,7 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AQ14">
         <v>1.5</v>
@@ -3899,7 +3905,7 @@
         <v>92</v>
       </c>
       <c r="P16" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="Q16">
         <v>2.75</v>
@@ -4929,7 +4935,7 @@
         <v>94</v>
       </c>
       <c r="P21" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="Q21">
         <v>3.1</v>
@@ -5135,7 +5141,7 @@
         <v>95</v>
       </c>
       <c r="P22" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="Q22">
         <v>3.6</v>
@@ -5419,7 +5425,7 @@
         <v>1</v>
       </c>
       <c r="AP23">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AQ23">
         <v>0.5</v>
@@ -5547,7 +5553,7 @@
         <v>82</v>
       </c>
       <c r="P24" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="Q24">
         <v>2.75</v>
@@ -5753,7 +5759,7 @@
         <v>97</v>
       </c>
       <c r="P25" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="Q25">
         <v>4</v>
@@ -5959,7 +5965,7 @@
         <v>82</v>
       </c>
       <c r="P26" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="Q26">
         <v>3.6</v>
@@ -6165,7 +6171,7 @@
         <v>82</v>
       </c>
       <c r="P27" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="Q27">
         <v>2.75</v>
@@ -6371,7 +6377,7 @@
         <v>98</v>
       </c>
       <c r="P28" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="Q28">
         <v>3.75</v>
@@ -6783,7 +6789,7 @@
         <v>99</v>
       </c>
       <c r="P30" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="Q30">
         <v>2.63</v>
@@ -6989,7 +6995,7 @@
         <v>100</v>
       </c>
       <c r="P31" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="Q31">
         <v>3.1</v>
@@ -7195,7 +7201,7 @@
         <v>101</v>
       </c>
       <c r="P32" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="Q32">
         <v>2.5</v>
@@ -7607,7 +7613,7 @@
         <v>103</v>
       </c>
       <c r="P34" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="Q34">
         <v>3.2</v>
@@ -8225,7 +8231,7 @@
         <v>82</v>
       </c>
       <c r="P37" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="Q37">
         <v>4</v>
@@ -8382,6 +8388,212 @@
       </c>
       <c r="BP37">
         <v>1.16</v>
+      </c>
+    </row>
+    <row r="38" spans="1:68">
+      <c r="A38" s="1">
+        <v>37</v>
+      </c>
+      <c r="B38">
+        <v>7806865</v>
+      </c>
+      <c r="C38" t="s">
+        <v>68</v>
+      </c>
+      <c r="D38" t="s">
+        <v>69</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45748.3125</v>
+      </c>
+      <c r="F38">
+        <v>18</v>
+      </c>
+      <c r="G38" t="s">
+        <v>73</v>
+      </c>
+      <c r="H38" t="s">
+        <v>77</v>
+      </c>
+      <c r="I38">
+        <v>2</v>
+      </c>
+      <c r="J38">
+        <v>2</v>
+      </c>
+      <c r="K38">
+        <v>4</v>
+      </c>
+      <c r="L38">
+        <v>2</v>
+      </c>
+      <c r="M38">
+        <v>3</v>
+      </c>
+      <c r="N38">
+        <v>5</v>
+      </c>
+      <c r="O38" t="s">
+        <v>106</v>
+      </c>
+      <c r="P38" t="s">
+        <v>129</v>
+      </c>
+      <c r="Q38">
+        <v>2.45</v>
+      </c>
+      <c r="R38">
+        <v>2.1</v>
+      </c>
+      <c r="S38">
+        <v>4.1</v>
+      </c>
+      <c r="T38">
+        <v>1.38</v>
+      </c>
+      <c r="U38">
+        <v>2.8</v>
+      </c>
+      <c r="V38">
+        <v>2.7</v>
+      </c>
+      <c r="W38">
+        <v>1.4</v>
+      </c>
+      <c r="X38">
+        <v>6.75</v>
+      </c>
+      <c r="Y38">
+        <v>1.09</v>
+      </c>
+      <c r="Z38">
+        <v>1.9</v>
+      </c>
+      <c r="AA38">
+        <v>3.47</v>
+      </c>
+      <c r="AB38">
+        <v>3.89</v>
+      </c>
+      <c r="AC38">
+        <v>1.05</v>
+      </c>
+      <c r="AD38">
+        <v>9</v>
+      </c>
+      <c r="AE38">
+        <v>1.29</v>
+      </c>
+      <c r="AF38">
+        <v>3.3</v>
+      </c>
+      <c r="AG38">
+        <v>1.98</v>
+      </c>
+      <c r="AH38">
+        <v>1.77</v>
+      </c>
+      <c r="AI38">
+        <v>1.78</v>
+      </c>
+      <c r="AJ38">
+        <v>1.9</v>
+      </c>
+      <c r="AK38">
+        <v>1.25</v>
+      </c>
+      <c r="AL38">
+        <v>1.28</v>
+      </c>
+      <c r="AM38">
+        <v>1.85</v>
+      </c>
+      <c r="AN38">
+        <v>2</v>
+      </c>
+      <c r="AO38">
+        <v>3</v>
+      </c>
+      <c r="AP38">
+        <v>1.5</v>
+      </c>
+      <c r="AQ38">
+        <v>3</v>
+      </c>
+      <c r="AR38">
+        <v>2.21</v>
+      </c>
+      <c r="AS38">
+        <v>1.32</v>
+      </c>
+      <c r="AT38">
+        <v>3.53</v>
+      </c>
+      <c r="AU38">
+        <v>7</v>
+      </c>
+      <c r="AV38">
+        <v>5</v>
+      </c>
+      <c r="AW38">
+        <v>8</v>
+      </c>
+      <c r="AX38">
+        <v>2</v>
+      </c>
+      <c r="AY38">
+        <v>17</v>
+      </c>
+      <c r="AZ38">
+        <v>7</v>
+      </c>
+      <c r="BA38">
+        <v>5</v>
+      </c>
+      <c r="BB38">
+        <v>0</v>
+      </c>
+      <c r="BC38">
+        <v>5</v>
+      </c>
+      <c r="BD38">
+        <v>1.71</v>
+      </c>
+      <c r="BE38">
+        <v>6.4</v>
+      </c>
+      <c r="BF38">
+        <v>2.4</v>
+      </c>
+      <c r="BG38">
+        <v>1.49</v>
+      </c>
+      <c r="BH38">
+        <v>2.4</v>
+      </c>
+      <c r="BI38">
+        <v>1.85</v>
+      </c>
+      <c r="BJ38">
+        <v>1.85</v>
+      </c>
+      <c r="BK38">
+        <v>2.28</v>
+      </c>
+      <c r="BL38">
+        <v>1.55</v>
+      </c>
+      <c r="BM38">
+        <v>2.95</v>
+      </c>
+      <c r="BN38">
+        <v>1.33</v>
+      </c>
+      <c r="BO38">
+        <v>3.95</v>
+      </c>
+      <c r="BP38">
+        <v>1.2</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/South Korea K League 1_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/South Korea K League 1_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="133">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -337,6 +337,9 @@
     <t>['42', '45+4']</t>
   </si>
   <si>
+    <t>['33', '45']</t>
+  </si>
+  <si>
     <t>['32', '87', '90']</t>
   </si>
   <si>
@@ -404,6 +407,12 @@
   </si>
   <si>
     <t>['4', '13', '64']</t>
+  </si>
+  <si>
+    <t>['46', '90']</t>
+  </si>
+  <si>
+    <t>['50']</t>
   </si>
 </sst>
 </file>
@@ -765,7 +774,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP38"/>
+  <dimension ref="A1:BP42"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1021,7 +1030,7 @@
         <v>82</v>
       </c>
       <c r="P2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="Q2">
         <v>2.75</v>
@@ -1308,7 +1317,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ3">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -1639,7 +1648,7 @@
         <v>82</v>
       </c>
       <c r="P5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="Q5">
         <v>2.1</v>
@@ -1717,7 +1726,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ5">
         <v>1.5</v>
@@ -1845,7 +1854,7 @@
         <v>84</v>
       </c>
       <c r="P6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="Q6">
         <v>3.1</v>
@@ -2051,7 +2060,7 @@
         <v>85</v>
       </c>
       <c r="P7" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Q7">
         <v>3.5</v>
@@ -2257,7 +2266,7 @@
         <v>86</v>
       </c>
       <c r="P8" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="Q8">
         <v>3.4</v>
@@ -2463,7 +2472,7 @@
         <v>87</v>
       </c>
       <c r="P9" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="Q9">
         <v>3.35</v>
@@ -2669,7 +2678,7 @@
         <v>88</v>
       </c>
       <c r="P10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="Q10">
         <v>2.45</v>
@@ -2875,7 +2884,7 @@
         <v>82</v>
       </c>
       <c r="P11" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="Q11">
         <v>3.45</v>
@@ -2953,7 +2962,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AQ11">
         <v>1.33</v>
@@ -3081,7 +3090,7 @@
         <v>89</v>
       </c>
       <c r="P12" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="Q12">
         <v>2.75</v>
@@ -3287,7 +3296,7 @@
         <v>90</v>
       </c>
       <c r="P13" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Q13">
         <v>2.95</v>
@@ -3368,7 +3377,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ13">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -3571,10 +3580,10 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ14">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AR14">
         <v>2.51</v>
@@ -3780,7 +3789,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ15">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="AR15">
         <v>1.87</v>
@@ -3905,7 +3914,7 @@
         <v>92</v>
       </c>
       <c r="P16" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="Q16">
         <v>2.75</v>
@@ -4189,7 +4198,7 @@
         <v>0.5</v>
       </c>
       <c r="AP17">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AQ17">
         <v>0.25</v>
@@ -4810,7 +4819,7 @@
         <v>1</v>
       </c>
       <c r="AQ20">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AR20">
         <v>0</v>
@@ -4935,7 +4944,7 @@
         <v>94</v>
       </c>
       <c r="P21" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="Q21">
         <v>3.1</v>
@@ -5141,7 +5150,7 @@
         <v>95</v>
       </c>
       <c r="P22" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="Q22">
         <v>3.6</v>
@@ -5425,7 +5434,7 @@
         <v>1</v>
       </c>
       <c r="AP23">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ23">
         <v>0.5</v>
@@ -5553,7 +5562,7 @@
         <v>82</v>
       </c>
       <c r="P24" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="Q24">
         <v>2.75</v>
@@ -5759,7 +5768,7 @@
         <v>97</v>
       </c>
       <c r="P25" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="Q25">
         <v>4</v>
@@ -5965,7 +5974,7 @@
         <v>82</v>
       </c>
       <c r="P26" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="Q26">
         <v>3.6</v>
@@ -6046,7 +6055,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ26">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AR26">
         <v>1.64</v>
@@ -6171,7 +6180,7 @@
         <v>82</v>
       </c>
       <c r="P27" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="Q27">
         <v>2.75</v>
@@ -6377,7 +6386,7 @@
         <v>98</v>
       </c>
       <c r="P28" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="Q28">
         <v>3.75</v>
@@ -6661,7 +6670,7 @@
         <v>1</v>
       </c>
       <c r="AP29">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AQ29">
         <v>1</v>
@@ -6789,7 +6798,7 @@
         <v>99</v>
       </c>
       <c r="P30" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="Q30">
         <v>2.63</v>
@@ -6870,7 +6879,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ30">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AR30">
         <v>1.76</v>
@@ -6995,7 +7004,7 @@
         <v>100</v>
       </c>
       <c r="P31" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="Q31">
         <v>3.1</v>
@@ -7076,7 +7085,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ31">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AR31">
         <v>1.73</v>
@@ -7201,7 +7210,7 @@
         <v>101</v>
       </c>
       <c r="P32" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="Q32">
         <v>2.5</v>
@@ -7282,7 +7291,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ32">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="AR32">
         <v>0.86</v>
@@ -7613,7 +7622,7 @@
         <v>103</v>
       </c>
       <c r="P34" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="Q34">
         <v>3.2</v>
@@ -7691,7 +7700,7 @@
         <v>1</v>
       </c>
       <c r="AP34">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AQ34">
         <v>1</v>
@@ -8103,7 +8112,7 @@
         <v>1.5</v>
       </c>
       <c r="AP36">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AQ36">
         <v>1</v>
@@ -8231,7 +8240,7 @@
         <v>82</v>
       </c>
       <c r="P37" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="Q37">
         <v>4</v>
@@ -8312,7 +8321,7 @@
         <v>0</v>
       </c>
       <c r="AQ37">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AR37">
         <v>1.26</v>
@@ -8437,7 +8446,7 @@
         <v>106</v>
       </c>
       <c r="P38" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="Q38">
         <v>2.45</v>
@@ -8515,7 +8524,7 @@
         <v>3</v>
       </c>
       <c r="AP38">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ38">
         <v>3</v>
@@ -8594,6 +8603,830 @@
       </c>
       <c r="BP38">
         <v>1.2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:68">
+      <c r="A39" s="1">
+        <v>38</v>
+      </c>
+      <c r="B39">
+        <v>7806794</v>
+      </c>
+      <c r="C39" t="s">
+        <v>68</v>
+      </c>
+      <c r="D39" t="s">
+        <v>69</v>
+      </c>
+      <c r="E39" s="2">
+        <v>45752.08333333334</v>
+      </c>
+      <c r="F39">
+        <v>7</v>
+      </c>
+      <c r="G39" t="s">
+        <v>73</v>
+      </c>
+      <c r="H39" t="s">
+        <v>76</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>0</v>
+      </c>
+      <c r="K39">
+        <v>0</v>
+      </c>
+      <c r="L39">
+        <v>0</v>
+      </c>
+      <c r="M39">
+        <v>0</v>
+      </c>
+      <c r="N39">
+        <v>0</v>
+      </c>
+      <c r="O39" t="s">
+        <v>82</v>
+      </c>
+      <c r="P39" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q39">
+        <v>2.6</v>
+      </c>
+      <c r="R39">
+        <v>2.2</v>
+      </c>
+      <c r="S39">
+        <v>4.33</v>
+      </c>
+      <c r="T39">
+        <v>1.4</v>
+      </c>
+      <c r="U39">
+        <v>2.75</v>
+      </c>
+      <c r="V39">
+        <v>2.75</v>
+      </c>
+      <c r="W39">
+        <v>1.4</v>
+      </c>
+      <c r="X39">
+        <v>8</v>
+      </c>
+      <c r="Y39">
+        <v>1.08</v>
+      </c>
+      <c r="Z39">
+        <v>1.95</v>
+      </c>
+      <c r="AA39">
+        <v>3.53</v>
+      </c>
+      <c r="AB39">
+        <v>3.64</v>
+      </c>
+      <c r="AC39">
+        <v>2.3</v>
+      </c>
+      <c r="AD39">
+        <v>1.63</v>
+      </c>
+      <c r="AE39">
+        <v>0</v>
+      </c>
+      <c r="AF39">
+        <v>0</v>
+      </c>
+      <c r="AG39">
+        <v>1.91</v>
+      </c>
+      <c r="AH39">
+        <v>1.83</v>
+      </c>
+      <c r="AI39">
+        <v>1.8</v>
+      </c>
+      <c r="AJ39">
+        <v>1.91</v>
+      </c>
+      <c r="AK39">
+        <v>0</v>
+      </c>
+      <c r="AL39">
+        <v>0</v>
+      </c>
+      <c r="AM39">
+        <v>0</v>
+      </c>
+      <c r="AN39">
+        <v>1.5</v>
+      </c>
+      <c r="AO39">
+        <v>1.33</v>
+      </c>
+      <c r="AP39">
+        <v>1.4</v>
+      </c>
+      <c r="AQ39">
+        <v>1.25</v>
+      </c>
+      <c r="AR39">
+        <v>2.14</v>
+      </c>
+      <c r="AS39">
+        <v>1.62</v>
+      </c>
+      <c r="AT39">
+        <v>3.76</v>
+      </c>
+      <c r="AU39">
+        <v>4</v>
+      </c>
+      <c r="AV39">
+        <v>3</v>
+      </c>
+      <c r="AW39">
+        <v>8</v>
+      </c>
+      <c r="AX39">
+        <v>10</v>
+      </c>
+      <c r="AY39">
+        <v>14</v>
+      </c>
+      <c r="AZ39">
+        <v>18</v>
+      </c>
+      <c r="BA39">
+        <v>2</v>
+      </c>
+      <c r="BB39">
+        <v>6</v>
+      </c>
+      <c r="BC39">
+        <v>8</v>
+      </c>
+      <c r="BD39">
+        <v>0</v>
+      </c>
+      <c r="BE39">
+        <v>0</v>
+      </c>
+      <c r="BF39">
+        <v>0</v>
+      </c>
+      <c r="BG39">
+        <v>0</v>
+      </c>
+      <c r="BH39">
+        <v>0</v>
+      </c>
+      <c r="BI39">
+        <v>0</v>
+      </c>
+      <c r="BJ39">
+        <v>0</v>
+      </c>
+      <c r="BK39">
+        <v>0</v>
+      </c>
+      <c r="BL39">
+        <v>0</v>
+      </c>
+      <c r="BM39">
+        <v>0</v>
+      </c>
+      <c r="BN39">
+        <v>0</v>
+      </c>
+      <c r="BO39">
+        <v>0</v>
+      </c>
+      <c r="BP39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:68">
+      <c r="A40" s="1">
+        <v>39</v>
+      </c>
+      <c r="B40">
+        <v>7806795</v>
+      </c>
+      <c r="C40" t="s">
+        <v>68</v>
+      </c>
+      <c r="D40" t="s">
+        <v>69</v>
+      </c>
+      <c r="E40" s="2">
+        <v>45752.1875</v>
+      </c>
+      <c r="F40">
+        <v>7</v>
+      </c>
+      <c r="G40" t="s">
+        <v>81</v>
+      </c>
+      <c r="H40" t="s">
+        <v>75</v>
+      </c>
+      <c r="I40">
+        <v>2</v>
+      </c>
+      <c r="J40">
+        <v>0</v>
+      </c>
+      <c r="K40">
+        <v>2</v>
+      </c>
+      <c r="L40">
+        <v>2</v>
+      </c>
+      <c r="M40">
+        <v>0</v>
+      </c>
+      <c r="N40">
+        <v>2</v>
+      </c>
+      <c r="O40" t="s">
+        <v>107</v>
+      </c>
+      <c r="P40" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q40">
+        <v>2.5</v>
+      </c>
+      <c r="R40">
+        <v>2.25</v>
+      </c>
+      <c r="S40">
+        <v>4.33</v>
+      </c>
+      <c r="T40">
+        <v>1.36</v>
+      </c>
+      <c r="U40">
+        <v>3</v>
+      </c>
+      <c r="V40">
+        <v>2.63</v>
+      </c>
+      <c r="W40">
+        <v>1.44</v>
+      </c>
+      <c r="X40">
+        <v>7</v>
+      </c>
+      <c r="Y40">
+        <v>1.1</v>
+      </c>
+      <c r="Z40">
+        <v>1.81</v>
+      </c>
+      <c r="AA40">
+        <v>3.47</v>
+      </c>
+      <c r="AB40">
+        <v>4.33</v>
+      </c>
+      <c r="AC40">
+        <v>0</v>
+      </c>
+      <c r="AD40">
+        <v>0</v>
+      </c>
+      <c r="AE40">
+        <v>1.18</v>
+      </c>
+      <c r="AF40">
+        <v>4.1</v>
+      </c>
+      <c r="AG40">
+        <v>1.91</v>
+      </c>
+      <c r="AH40">
+        <v>1.83</v>
+      </c>
+      <c r="AI40">
+        <v>1.67</v>
+      </c>
+      <c r="AJ40">
+        <v>2.1</v>
+      </c>
+      <c r="AK40">
+        <v>1.25</v>
+      </c>
+      <c r="AL40">
+        <v>1.29</v>
+      </c>
+      <c r="AM40">
+        <v>1.85</v>
+      </c>
+      <c r="AN40">
+        <v>2</v>
+      </c>
+      <c r="AO40">
+        <v>0.5</v>
+      </c>
+      <c r="AP40">
+        <v>2.33</v>
+      </c>
+      <c r="AQ40">
+        <v>0.33</v>
+      </c>
+      <c r="AR40">
+        <v>1.95</v>
+      </c>
+      <c r="AS40">
+        <v>0.95</v>
+      </c>
+      <c r="AT40">
+        <v>2.9</v>
+      </c>
+      <c r="AU40">
+        <v>6</v>
+      </c>
+      <c r="AV40">
+        <v>5</v>
+      </c>
+      <c r="AW40">
+        <v>8</v>
+      </c>
+      <c r="AX40">
+        <v>6</v>
+      </c>
+      <c r="AY40">
+        <v>16</v>
+      </c>
+      <c r="AZ40">
+        <v>13</v>
+      </c>
+      <c r="BA40">
+        <v>6</v>
+      </c>
+      <c r="BB40">
+        <v>3</v>
+      </c>
+      <c r="BC40">
+        <v>9</v>
+      </c>
+      <c r="BD40">
+        <v>1.44</v>
+      </c>
+      <c r="BE40">
+        <v>9</v>
+      </c>
+      <c r="BF40">
+        <v>3.1</v>
+      </c>
+      <c r="BG40">
+        <v>1.4</v>
+      </c>
+      <c r="BH40">
+        <v>2.64</v>
+      </c>
+      <c r="BI40">
+        <v>1.74</v>
+      </c>
+      <c r="BJ40">
+        <v>1.98</v>
+      </c>
+      <c r="BK40">
+        <v>2.21</v>
+      </c>
+      <c r="BL40">
+        <v>1.56</v>
+      </c>
+      <c r="BM40">
+        <v>2.97</v>
+      </c>
+      <c r="BN40">
+        <v>1.3</v>
+      </c>
+      <c r="BO40">
+        <v>4.25</v>
+      </c>
+      <c r="BP40">
+        <v>1.15</v>
+      </c>
+    </row>
+    <row r="41" spans="1:68">
+      <c r="A41" s="1">
+        <v>40</v>
+      </c>
+      <c r="B41">
+        <v>7806796</v>
+      </c>
+      <c r="C41" t="s">
+        <v>68</v>
+      </c>
+      <c r="D41" t="s">
+        <v>69</v>
+      </c>
+      <c r="E41" s="2">
+        <v>45752.1875</v>
+      </c>
+      <c r="F41">
+        <v>7</v>
+      </c>
+      <c r="G41" t="s">
+        <v>77</v>
+      </c>
+      <c r="H41" t="s">
+        <v>74</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>0</v>
+      </c>
+      <c r="K41">
+        <v>0</v>
+      </c>
+      <c r="L41">
+        <v>0</v>
+      </c>
+      <c r="M41">
+        <v>2</v>
+      </c>
+      <c r="N41">
+        <v>2</v>
+      </c>
+      <c r="O41" t="s">
+        <v>82</v>
+      </c>
+      <c r="P41" t="s">
+        <v>131</v>
+      </c>
+      <c r="Q41">
+        <v>3.25</v>
+      </c>
+      <c r="R41">
+        <v>2.1</v>
+      </c>
+      <c r="S41">
+        <v>3.4</v>
+      </c>
+      <c r="T41">
+        <v>1.4</v>
+      </c>
+      <c r="U41">
+        <v>2.75</v>
+      </c>
+      <c r="V41">
+        <v>3</v>
+      </c>
+      <c r="W41">
+        <v>1.36</v>
+      </c>
+      <c r="X41">
+        <v>9</v>
+      </c>
+      <c r="Y41">
+        <v>1.07</v>
+      </c>
+      <c r="Z41">
+        <v>2.62</v>
+      </c>
+      <c r="AA41">
+        <v>3.16</v>
+      </c>
+      <c r="AB41">
+        <v>2.7</v>
+      </c>
+      <c r="AC41">
+        <v>1.01</v>
+      </c>
+      <c r="AD41">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="AE41">
+        <v>1.85</v>
+      </c>
+      <c r="AF41">
+        <v>2</v>
+      </c>
+      <c r="AG41">
+        <v>1.98</v>
+      </c>
+      <c r="AH41">
+        <v>1.77</v>
+      </c>
+      <c r="AI41">
+        <v>1.73</v>
+      </c>
+      <c r="AJ41">
+        <v>2</v>
+      </c>
+      <c r="AK41">
+        <v>1.44</v>
+      </c>
+      <c r="AL41">
+        <v>1.3</v>
+      </c>
+      <c r="AM41">
+        <v>1.5</v>
+      </c>
+      <c r="AN41">
+        <v>1.33</v>
+      </c>
+      <c r="AO41">
+        <v>1.5</v>
+      </c>
+      <c r="AP41">
+        <v>1</v>
+      </c>
+      <c r="AQ41">
+        <v>2</v>
+      </c>
+      <c r="AR41">
+        <v>1.54</v>
+      </c>
+      <c r="AS41">
+        <v>1.18</v>
+      </c>
+      <c r="AT41">
+        <v>2.72</v>
+      </c>
+      <c r="AU41">
+        <v>2</v>
+      </c>
+      <c r="AV41">
+        <v>4</v>
+      </c>
+      <c r="AW41">
+        <v>4</v>
+      </c>
+      <c r="AX41">
+        <v>3</v>
+      </c>
+      <c r="AY41">
+        <v>10</v>
+      </c>
+      <c r="AZ41">
+        <v>11</v>
+      </c>
+      <c r="BA41">
+        <v>5</v>
+      </c>
+      <c r="BB41">
+        <v>4</v>
+      </c>
+      <c r="BC41">
+        <v>9</v>
+      </c>
+      <c r="BD41">
+        <v>2.05</v>
+      </c>
+      <c r="BE41">
+        <v>8</v>
+      </c>
+      <c r="BF41">
+        <v>1.95</v>
+      </c>
+      <c r="BG41">
+        <v>1.46</v>
+      </c>
+      <c r="BH41">
+        <v>2.45</v>
+      </c>
+      <c r="BI41">
+        <v>1.85</v>
+      </c>
+      <c r="BJ41">
+        <v>1.85</v>
+      </c>
+      <c r="BK41">
+        <v>2.42</v>
+      </c>
+      <c r="BL41">
+        <v>1.47</v>
+      </c>
+      <c r="BM41">
+        <v>3.28</v>
+      </c>
+      <c r="BN41">
+        <v>1.25</v>
+      </c>
+      <c r="BO41">
+        <v>4.75</v>
+      </c>
+      <c r="BP41">
+        <v>1.12</v>
+      </c>
+    </row>
+    <row r="42" spans="1:68">
+      <c r="A42" s="1">
+        <v>41</v>
+      </c>
+      <c r="B42">
+        <v>7806797</v>
+      </c>
+      <c r="C42" t="s">
+        <v>68</v>
+      </c>
+      <c r="D42" t="s">
+        <v>69</v>
+      </c>
+      <c r="E42" s="2">
+        <v>45752.29166666666</v>
+      </c>
+      <c r="F42">
+        <v>7</v>
+      </c>
+      <c r="G42" t="s">
+        <v>79</v>
+      </c>
+      <c r="H42" t="s">
+        <v>70</v>
+      </c>
+      <c r="I42">
+        <v>1</v>
+      </c>
+      <c r="J42">
+        <v>0</v>
+      </c>
+      <c r="K42">
+        <v>1</v>
+      </c>
+      <c r="L42">
+        <v>1</v>
+      </c>
+      <c r="M42">
+        <v>1</v>
+      </c>
+      <c r="N42">
+        <v>2</v>
+      </c>
+      <c r="O42" t="s">
+        <v>98</v>
+      </c>
+      <c r="P42" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q42">
+        <v>3.4</v>
+      </c>
+      <c r="R42">
+        <v>2.1</v>
+      </c>
+      <c r="S42">
+        <v>3.1</v>
+      </c>
+      <c r="T42">
+        <v>1.4</v>
+      </c>
+      <c r="U42">
+        <v>2.75</v>
+      </c>
+      <c r="V42">
+        <v>3</v>
+      </c>
+      <c r="W42">
+        <v>1.36</v>
+      </c>
+      <c r="X42">
+        <v>8</v>
+      </c>
+      <c r="Y42">
+        <v>1.08</v>
+      </c>
+      <c r="Z42">
+        <v>2.8</v>
+      </c>
+      <c r="AA42">
+        <v>3.23</v>
+      </c>
+      <c r="AB42">
+        <v>2.48</v>
+      </c>
+      <c r="AC42">
+        <v>1.03</v>
+      </c>
+      <c r="AD42">
+        <v>7.7</v>
+      </c>
+      <c r="AE42">
+        <v>1.35</v>
+      </c>
+      <c r="AF42">
+        <v>3.34</v>
+      </c>
+      <c r="AG42">
+        <v>1.94</v>
+      </c>
+      <c r="AH42">
+        <v>1.8</v>
+      </c>
+      <c r="AI42">
+        <v>1.73</v>
+      </c>
+      <c r="AJ42">
+        <v>2</v>
+      </c>
+      <c r="AK42">
+        <v>1.6</v>
+      </c>
+      <c r="AL42">
+        <v>1.35</v>
+      </c>
+      <c r="AM42">
+        <v>1.3</v>
+      </c>
+      <c r="AN42">
+        <v>1</v>
+      </c>
+      <c r="AO42">
+        <v>1.33</v>
+      </c>
+      <c r="AP42">
+        <v>1</v>
+      </c>
+      <c r="AQ42">
+        <v>1.25</v>
+      </c>
+      <c r="AR42">
+        <v>1.2</v>
+      </c>
+      <c r="AS42">
+        <v>1.51</v>
+      </c>
+      <c r="AT42">
+        <v>2.71</v>
+      </c>
+      <c r="AU42">
+        <v>8</v>
+      </c>
+      <c r="AV42">
+        <v>4</v>
+      </c>
+      <c r="AW42">
+        <v>7</v>
+      </c>
+      <c r="AX42">
+        <v>11</v>
+      </c>
+      <c r="AY42">
+        <v>16</v>
+      </c>
+      <c r="AZ42">
+        <v>20</v>
+      </c>
+      <c r="BA42">
+        <v>1</v>
+      </c>
+      <c r="BB42">
+        <v>8</v>
+      </c>
+      <c r="BC42">
+        <v>9</v>
+      </c>
+      <c r="BD42">
+        <v>2.2</v>
+      </c>
+      <c r="BE42">
+        <v>8</v>
+      </c>
+      <c r="BF42">
+        <v>1.83</v>
+      </c>
+      <c r="BG42">
+        <v>1.43</v>
+      </c>
+      <c r="BH42">
+        <v>2.54</v>
+      </c>
+      <c r="BI42">
+        <v>1.79</v>
+      </c>
+      <c r="BJ42">
+        <v>1.92</v>
+      </c>
+      <c r="BK42">
+        <v>2.3</v>
+      </c>
+      <c r="BL42">
+        <v>1.52</v>
+      </c>
+      <c r="BM42">
+        <v>3.08</v>
+      </c>
+      <c r="BN42">
+        <v>1.28</v>
+      </c>
+      <c r="BO42">
+        <v>4.45</v>
+      </c>
+      <c r="BP42">
+        <v>1.14</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/South Korea K League 1_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/South Korea K League 1_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="134">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -338,6 +338,9 @@
   </si>
   <si>
     <t>['33', '45']</t>
+  </si>
+  <si>
+    <t>['84', '90+3']</t>
   </si>
   <si>
     <t>['32', '87', '90']</t>
@@ -774,7 +777,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP42"/>
+  <dimension ref="A1:BP43"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1030,7 +1033,7 @@
         <v>82</v>
       </c>
       <c r="P2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="Q2">
         <v>2.75</v>
@@ -1648,7 +1651,7 @@
         <v>82</v>
       </c>
       <c r="P5" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="Q5">
         <v>2.1</v>
@@ -1854,7 +1857,7 @@
         <v>84</v>
       </c>
       <c r="P6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Q6">
         <v>3.1</v>
@@ -2060,7 +2063,7 @@
         <v>85</v>
       </c>
       <c r="P7" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="Q7">
         <v>3.5</v>
@@ -2141,7 +2144,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ7">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2266,7 +2269,7 @@
         <v>86</v>
       </c>
       <c r="P8" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="Q8">
         <v>3.4</v>
@@ -2472,7 +2475,7 @@
         <v>87</v>
       </c>
       <c r="P9" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="Q9">
         <v>3.35</v>
@@ -2678,7 +2681,7 @@
         <v>88</v>
       </c>
       <c r="P10" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="Q10">
         <v>2.45</v>
@@ -2884,7 +2887,7 @@
         <v>82</v>
       </c>
       <c r="P11" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="Q11">
         <v>3.45</v>
@@ -3090,7 +3093,7 @@
         <v>89</v>
       </c>
       <c r="P12" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="Q12">
         <v>2.75</v>
@@ -3296,7 +3299,7 @@
         <v>90</v>
       </c>
       <c r="P13" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="Q13">
         <v>2.95</v>
@@ -3914,7 +3917,7 @@
         <v>92</v>
       </c>
       <c r="P16" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="Q16">
         <v>2.75</v>
@@ -4944,7 +4947,7 @@
         <v>94</v>
       </c>
       <c r="P21" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="Q21">
         <v>3.1</v>
@@ -5150,7 +5153,7 @@
         <v>95</v>
       </c>
       <c r="P22" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="Q22">
         <v>3.6</v>
@@ -5228,7 +5231,7 @@
         <v>1.33</v>
       </c>
       <c r="AP22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ22">
         <v>1.75</v>
@@ -5562,7 +5565,7 @@
         <v>82</v>
       </c>
       <c r="P24" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="Q24">
         <v>2.75</v>
@@ -5643,7 +5646,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ24">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="AR24">
         <v>1.82</v>
@@ -5768,7 +5771,7 @@
         <v>97</v>
       </c>
       <c r="P25" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="Q25">
         <v>4</v>
@@ -5974,7 +5977,7 @@
         <v>82</v>
       </c>
       <c r="P26" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="Q26">
         <v>3.6</v>
@@ -6180,7 +6183,7 @@
         <v>82</v>
       </c>
       <c r="P27" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="Q27">
         <v>2.75</v>
@@ -6386,7 +6389,7 @@
         <v>98</v>
       </c>
       <c r="P28" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="Q28">
         <v>3.75</v>
@@ -6798,7 +6801,7 @@
         <v>99</v>
       </c>
       <c r="P30" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="Q30">
         <v>2.63</v>
@@ -7004,7 +7007,7 @@
         <v>100</v>
       </c>
       <c r="P31" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="Q31">
         <v>3.1</v>
@@ -7210,7 +7213,7 @@
         <v>101</v>
       </c>
       <c r="P32" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="Q32">
         <v>2.5</v>
@@ -7622,7 +7625,7 @@
         <v>103</v>
       </c>
       <c r="P34" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="Q34">
         <v>3.2</v>
@@ -8115,7 +8118,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ36">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="AR36">
         <v>1.94</v>
@@ -8240,7 +8243,7 @@
         <v>82</v>
       </c>
       <c r="P37" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="Q37">
         <v>4</v>
@@ -8318,7 +8321,7 @@
         <v>0</v>
       </c>
       <c r="AP37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ37">
         <v>2</v>
@@ -8446,7 +8449,7 @@
         <v>106</v>
       </c>
       <c r="P38" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="Q38">
         <v>2.45</v>
@@ -9064,7 +9067,7 @@
         <v>82</v>
       </c>
       <c r="P41" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="Q41">
         <v>3.25</v>
@@ -9270,7 +9273,7 @@
         <v>98</v>
       </c>
       <c r="P42" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="Q42">
         <v>3.4</v>
@@ -9427,6 +9430,212 @@
       </c>
       <c r="BP42">
         <v>1.14</v>
+      </c>
+    </row>
+    <row r="43" spans="1:68">
+      <c r="A43" s="1">
+        <v>42</v>
+      </c>
+      <c r="B43">
+        <v>7806798</v>
+      </c>
+      <c r="C43" t="s">
+        <v>68</v>
+      </c>
+      <c r="D43" t="s">
+        <v>69</v>
+      </c>
+      <c r="E43" s="2">
+        <v>45753.1875</v>
+      </c>
+      <c r="F43">
+        <v>7</v>
+      </c>
+      <c r="G43" t="s">
+        <v>80</v>
+      </c>
+      <c r="H43" t="s">
+        <v>78</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>0</v>
+      </c>
+      <c r="K43">
+        <v>0</v>
+      </c>
+      <c r="L43">
+        <v>2</v>
+      </c>
+      <c r="M43">
+        <v>0</v>
+      </c>
+      <c r="N43">
+        <v>2</v>
+      </c>
+      <c r="O43" t="s">
+        <v>108</v>
+      </c>
+      <c r="P43" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q43">
+        <v>3.5</v>
+      </c>
+      <c r="R43">
+        <v>2</v>
+      </c>
+      <c r="S43">
+        <v>3.4</v>
+      </c>
+      <c r="T43">
+        <v>1.5</v>
+      </c>
+      <c r="U43">
+        <v>2.5</v>
+      </c>
+      <c r="V43">
+        <v>3.5</v>
+      </c>
+      <c r="W43">
+        <v>1.29</v>
+      </c>
+      <c r="X43">
+        <v>10</v>
+      </c>
+      <c r="Y43">
+        <v>1.06</v>
+      </c>
+      <c r="Z43">
+        <v>2.8</v>
+      </c>
+      <c r="AA43">
+        <v>3</v>
+      </c>
+      <c r="AB43">
+        <v>2.64</v>
+      </c>
+      <c r="AC43">
+        <v>1.09</v>
+      </c>
+      <c r="AD43">
+        <v>7</v>
+      </c>
+      <c r="AE43">
+        <v>1.42</v>
+      </c>
+      <c r="AF43">
+        <v>2.8</v>
+      </c>
+      <c r="AG43">
+        <v>2.15</v>
+      </c>
+      <c r="AH43">
+        <v>1.57</v>
+      </c>
+      <c r="AI43">
+        <v>1.91</v>
+      </c>
+      <c r="AJ43">
+        <v>1.8</v>
+      </c>
+      <c r="AK43">
+        <v>1.45</v>
+      </c>
+      <c r="AL43">
+        <v>1.3</v>
+      </c>
+      <c r="AM43">
+        <v>1.42</v>
+      </c>
+      <c r="AN43">
+        <v>0</v>
+      </c>
+      <c r="AO43">
+        <v>1</v>
+      </c>
+      <c r="AP43">
+        <v>1</v>
+      </c>
+      <c r="AQ43">
+        <v>0.75</v>
+      </c>
+      <c r="AR43">
+        <v>1.25</v>
+      </c>
+      <c r="AS43">
+        <v>0.86</v>
+      </c>
+      <c r="AT43">
+        <v>2.11</v>
+      </c>
+      <c r="AU43">
+        <v>9</v>
+      </c>
+      <c r="AV43">
+        <v>4</v>
+      </c>
+      <c r="AW43">
+        <v>8</v>
+      </c>
+      <c r="AX43">
+        <v>7</v>
+      </c>
+      <c r="AY43">
+        <v>20</v>
+      </c>
+      <c r="AZ43">
+        <v>13</v>
+      </c>
+      <c r="BA43">
+        <v>5</v>
+      </c>
+      <c r="BB43">
+        <v>6</v>
+      </c>
+      <c r="BC43">
+        <v>11</v>
+      </c>
+      <c r="BD43">
+        <v>2.02</v>
+      </c>
+      <c r="BE43">
+        <v>5.8</v>
+      </c>
+      <c r="BF43">
+        <v>1.98</v>
+      </c>
+      <c r="BG43">
+        <v>1.7</v>
+      </c>
+      <c r="BH43">
+        <v>2.02</v>
+      </c>
+      <c r="BI43">
+        <v>2.15</v>
+      </c>
+      <c r="BJ43">
+        <v>1.61</v>
+      </c>
+      <c r="BK43">
+        <v>2.8</v>
+      </c>
+      <c r="BL43">
+        <v>1.36</v>
+      </c>
+      <c r="BM43">
+        <v>3.9</v>
+      </c>
+      <c r="BN43">
+        <v>1.21</v>
+      </c>
+      <c r="BO43">
+        <v>5.3</v>
+      </c>
+      <c r="BP43">
+        <v>1.11</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/South Korea K League 1_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/South Korea K League 1_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="134">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -343,6 +343,9 @@
     <t>['84', '90+3']</t>
   </si>
   <si>
+    <t>['90']</t>
+  </si>
+  <si>
     <t>['32', '87', '90']</t>
   </si>
   <si>
@@ -377,9 +380,6 @@
   </si>
   <si>
     <t>['20', '36', '38']</t>
-  </si>
-  <si>
-    <t>['90']</t>
   </si>
   <si>
     <t>['50', '90+1', '90+4']</t>
@@ -777,7 +777,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP43"/>
+  <dimension ref="A1:BP44"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1033,7 +1033,7 @@
         <v>82</v>
       </c>
       <c r="P2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="Q2">
         <v>2.75</v>
@@ -1523,7 +1523,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="AQ4">
         <v>0.25</v>
@@ -1651,7 +1651,7 @@
         <v>82</v>
       </c>
       <c r="P5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Q5">
         <v>2.1</v>
@@ -1857,7 +1857,7 @@
         <v>84</v>
       </c>
       <c r="P6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="Q6">
         <v>3.1</v>
@@ -2063,7 +2063,7 @@
         <v>85</v>
       </c>
       <c r="P7" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="Q7">
         <v>3.5</v>
@@ -2269,7 +2269,7 @@
         <v>86</v>
       </c>
       <c r="P8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="Q8">
         <v>3.4</v>
@@ -2475,7 +2475,7 @@
         <v>87</v>
       </c>
       <c r="P9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="Q9">
         <v>3.35</v>
@@ -2681,7 +2681,7 @@
         <v>88</v>
       </c>
       <c r="P10" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="Q10">
         <v>2.45</v>
@@ -2887,7 +2887,7 @@
         <v>82</v>
       </c>
       <c r="P11" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="Q11">
         <v>3.45</v>
@@ -3093,7 +3093,7 @@
         <v>89</v>
       </c>
       <c r="P12" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="Q12">
         <v>2.75</v>
@@ -3299,7 +3299,7 @@
         <v>90</v>
       </c>
       <c r="P13" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="Q13">
         <v>2.95</v>
@@ -3917,7 +3917,7 @@
         <v>92</v>
       </c>
       <c r="P16" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="Q16">
         <v>2.75</v>
@@ -3995,7 +3995,7 @@
         <v>1.5</v>
       </c>
       <c r="AP16">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="AQ16">
         <v>1.5</v>
@@ -4410,7 +4410,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ18">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="AR18">
         <v>2.13</v>
@@ -4947,7 +4947,7 @@
         <v>94</v>
       </c>
       <c r="P21" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="Q21">
         <v>3.1</v>
@@ -5153,7 +5153,7 @@
         <v>95</v>
       </c>
       <c r="P22" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="Q22">
         <v>3.6</v>
@@ -5440,7 +5440,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ23">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="AR23">
         <v>2.19</v>
@@ -5565,7 +5565,7 @@
         <v>82</v>
       </c>
       <c r="P24" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="Q24">
         <v>2.75</v>
@@ -7085,7 +7085,7 @@
         <v>0.5</v>
       </c>
       <c r="AP31">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="AQ31">
         <v>1.25</v>
@@ -9636,6 +9636,212 @@
       </c>
       <c r="BP43">
         <v>1.11</v>
+      </c>
+    </row>
+    <row r="44" spans="1:68">
+      <c r="A44" s="1">
+        <v>43</v>
+      </c>
+      <c r="B44">
+        <v>7806799</v>
+      </c>
+      <c r="C44" t="s">
+        <v>68</v>
+      </c>
+      <c r="D44" t="s">
+        <v>69</v>
+      </c>
+      <c r="E44" s="2">
+        <v>45753.1875</v>
+      </c>
+      <c r="F44">
+        <v>7</v>
+      </c>
+      <c r="G44" t="s">
+        <v>72</v>
+      </c>
+      <c r="H44" t="s">
+        <v>71</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>0</v>
+      </c>
+      <c r="K44">
+        <v>0</v>
+      </c>
+      <c r="L44">
+        <v>1</v>
+      </c>
+      <c r="M44">
+        <v>0</v>
+      </c>
+      <c r="N44">
+        <v>1</v>
+      </c>
+      <c r="O44" t="s">
+        <v>109</v>
+      </c>
+      <c r="P44" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q44">
+        <v>2.63</v>
+      </c>
+      <c r="R44">
+        <v>2.05</v>
+      </c>
+      <c r="S44">
+        <v>4.5</v>
+      </c>
+      <c r="T44">
+        <v>1.5</v>
+      </c>
+      <c r="U44">
+        <v>2.5</v>
+      </c>
+      <c r="V44">
+        <v>3.4</v>
+      </c>
+      <c r="W44">
+        <v>1.3</v>
+      </c>
+      <c r="X44">
+        <v>10</v>
+      </c>
+      <c r="Y44">
+        <v>1.06</v>
+      </c>
+      <c r="Z44">
+        <v>1.95</v>
+      </c>
+      <c r="AA44">
+        <v>3.29</v>
+      </c>
+      <c r="AB44">
+        <v>3.95</v>
+      </c>
+      <c r="AC44">
+        <v>1.07</v>
+      </c>
+      <c r="AD44">
+        <v>8</v>
+      </c>
+      <c r="AE44">
+        <v>1.38</v>
+      </c>
+      <c r="AF44">
+        <v>2.95</v>
+      </c>
+      <c r="AG44">
+        <v>2.1</v>
+      </c>
+      <c r="AH44">
+        <v>1.61</v>
+      </c>
+      <c r="AI44">
+        <v>1.91</v>
+      </c>
+      <c r="AJ44">
+        <v>1.8</v>
+      </c>
+      <c r="AK44">
+        <v>1.25</v>
+      </c>
+      <c r="AL44">
+        <v>1.28</v>
+      </c>
+      <c r="AM44">
+        <v>1.77</v>
+      </c>
+      <c r="AN44">
+        <v>1.33</v>
+      </c>
+      <c r="AO44">
+        <v>0.5</v>
+      </c>
+      <c r="AP44">
+        <v>1.75</v>
+      </c>
+      <c r="AQ44">
+        <v>0.33</v>
+      </c>
+      <c r="AR44">
+        <v>1.71</v>
+      </c>
+      <c r="AS44">
+        <v>1.6</v>
+      </c>
+      <c r="AT44">
+        <v>3.31</v>
+      </c>
+      <c r="AU44">
+        <v>6</v>
+      </c>
+      <c r="AV44">
+        <v>3</v>
+      </c>
+      <c r="AW44">
+        <v>3</v>
+      </c>
+      <c r="AX44">
+        <v>3</v>
+      </c>
+      <c r="AY44">
+        <v>9</v>
+      </c>
+      <c r="AZ44">
+        <v>8</v>
+      </c>
+      <c r="BA44">
+        <v>7</v>
+      </c>
+      <c r="BB44">
+        <v>1</v>
+      </c>
+      <c r="BC44">
+        <v>8</v>
+      </c>
+      <c r="BD44">
+        <v>1.61</v>
+      </c>
+      <c r="BE44">
+        <v>6.4</v>
+      </c>
+      <c r="BF44">
+        <v>2.55</v>
+      </c>
+      <c r="BG44">
+        <v>1.46</v>
+      </c>
+      <c r="BH44">
+        <v>2.5</v>
+      </c>
+      <c r="BI44">
+        <v>1.75</v>
+      </c>
+      <c r="BJ44">
+        <v>1.95</v>
+      </c>
+      <c r="BK44">
+        <v>2.2</v>
+      </c>
+      <c r="BL44">
+        <v>1.58</v>
+      </c>
+      <c r="BM44">
+        <v>2.9</v>
+      </c>
+      <c r="BN44">
+        <v>1.35</v>
+      </c>
+      <c r="BO44">
+        <v>3.8</v>
+      </c>
+      <c r="BP44">
+        <v>1.22</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/South Korea K League 1_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/South Korea K League 1_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="135">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -344,6 +344,9 @@
   </si>
   <si>
     <t>['90']</t>
+  </si>
+  <si>
+    <t>['12', '45+2']</t>
   </si>
   <si>
     <t>['32', '87', '90']</t>
@@ -777,7 +780,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP44"/>
+  <dimension ref="A1:BP45"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1033,7 +1036,7 @@
         <v>82</v>
       </c>
       <c r="P2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Q2">
         <v>2.75</v>
@@ -1523,7 +1526,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AQ4">
         <v>0.25</v>
@@ -1651,7 +1654,7 @@
         <v>82</v>
       </c>
       <c r="P5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="Q5">
         <v>2.1</v>
@@ -1857,7 +1860,7 @@
         <v>84</v>
       </c>
       <c r="P6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="Q6">
         <v>3.1</v>
@@ -2063,7 +2066,7 @@
         <v>85</v>
       </c>
       <c r="P7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="Q7">
         <v>3.5</v>
@@ -2269,7 +2272,7 @@
         <v>86</v>
       </c>
       <c r="P8" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="Q8">
         <v>3.4</v>
@@ -2475,7 +2478,7 @@
         <v>87</v>
       </c>
       <c r="P9" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="Q9">
         <v>3.35</v>
@@ -2681,7 +2684,7 @@
         <v>88</v>
       </c>
       <c r="P10" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="Q10">
         <v>2.45</v>
@@ -2887,7 +2890,7 @@
         <v>82</v>
       </c>
       <c r="P11" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="Q11">
         <v>3.45</v>
@@ -3093,7 +3096,7 @@
         <v>89</v>
       </c>
       <c r="P12" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="Q12">
         <v>2.75</v>
@@ -3299,7 +3302,7 @@
         <v>90</v>
       </c>
       <c r="P13" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="Q13">
         <v>2.95</v>
@@ -3792,7 +3795,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ15">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AR15">
         <v>1.87</v>
@@ -3917,7 +3920,7 @@
         <v>92</v>
       </c>
       <c r="P16" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="Q16">
         <v>2.75</v>
@@ -3995,7 +3998,7 @@
         <v>1.5</v>
       </c>
       <c r="AP16">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AQ16">
         <v>1.5</v>
@@ -4947,7 +4950,7 @@
         <v>94</v>
       </c>
       <c r="P21" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="Q21">
         <v>3.1</v>
@@ -5153,7 +5156,7 @@
         <v>95</v>
       </c>
       <c r="P22" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="Q22">
         <v>3.6</v>
@@ -5771,7 +5774,7 @@
         <v>97</v>
       </c>
       <c r="P25" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="Q25">
         <v>4</v>
@@ -5977,7 +5980,7 @@
         <v>82</v>
       </c>
       <c r="P26" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="Q26">
         <v>3.6</v>
@@ -6183,7 +6186,7 @@
         <v>82</v>
       </c>
       <c r="P27" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="Q27">
         <v>2.75</v>
@@ -6389,7 +6392,7 @@
         <v>98</v>
       </c>
       <c r="P28" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="Q28">
         <v>3.75</v>
@@ -6801,7 +6804,7 @@
         <v>99</v>
       </c>
       <c r="P30" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="Q30">
         <v>2.63</v>
@@ -7007,7 +7010,7 @@
         <v>100</v>
       </c>
       <c r="P31" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="Q31">
         <v>3.1</v>
@@ -7085,7 +7088,7 @@
         <v>0.5</v>
       </c>
       <c r="AP31">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AQ31">
         <v>1.25</v>
@@ -7213,7 +7216,7 @@
         <v>101</v>
       </c>
       <c r="P32" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="Q32">
         <v>2.5</v>
@@ -7294,7 +7297,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ32">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AR32">
         <v>0.86</v>
@@ -7625,7 +7628,7 @@
         <v>103</v>
       </c>
       <c r="P34" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="Q34">
         <v>3.2</v>
@@ -8243,7 +8246,7 @@
         <v>82</v>
       </c>
       <c r="P37" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="Q37">
         <v>4</v>
@@ -8449,7 +8452,7 @@
         <v>106</v>
       </c>
       <c r="P38" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="Q38">
         <v>2.45</v>
@@ -8942,7 +8945,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ40">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AR40">
         <v>1.95</v>
@@ -9067,7 +9070,7 @@
         <v>82</v>
       </c>
       <c r="P41" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="Q41">
         <v>3.25</v>
@@ -9273,7 +9276,7 @@
         <v>98</v>
       </c>
       <c r="P42" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="Q42">
         <v>3.4</v>
@@ -9763,7 +9766,7 @@
         <v>0.5</v>
       </c>
       <c r="AP44">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AQ44">
         <v>0.33</v>
@@ -9841,6 +9844,212 @@
         <v>3.8</v>
       </c>
       <c r="BP44">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="45" spans="1:68">
+      <c r="A45" s="1">
+        <v>44</v>
+      </c>
+      <c r="B45">
+        <v>7806813</v>
+      </c>
+      <c r="C45" t="s">
+        <v>68</v>
+      </c>
+      <c r="D45" t="s">
+        <v>69</v>
+      </c>
+      <c r="E45" s="2">
+        <v>45756.3125</v>
+      </c>
+      <c r="F45">
+        <v>10</v>
+      </c>
+      <c r="G45" t="s">
+        <v>72</v>
+      </c>
+      <c r="H45" t="s">
+        <v>75</v>
+      </c>
+      <c r="I45">
+        <v>2</v>
+      </c>
+      <c r="J45">
+        <v>0</v>
+      </c>
+      <c r="K45">
+        <v>2</v>
+      </c>
+      <c r="L45">
+        <v>2</v>
+      </c>
+      <c r="M45">
+        <v>1</v>
+      </c>
+      <c r="N45">
+        <v>3</v>
+      </c>
+      <c r="O45" t="s">
+        <v>110</v>
+      </c>
+      <c r="P45" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q45">
+        <v>2.75</v>
+      </c>
+      <c r="R45">
+        <v>2.05</v>
+      </c>
+      <c r="S45">
+        <v>4.33</v>
+      </c>
+      <c r="T45">
+        <v>1.44</v>
+      </c>
+      <c r="U45">
+        <v>2.63</v>
+      </c>
+      <c r="V45">
+        <v>3.25</v>
+      </c>
+      <c r="W45">
+        <v>1.33</v>
+      </c>
+      <c r="X45">
+        <v>10</v>
+      </c>
+      <c r="Y45">
+        <v>1.06</v>
+      </c>
+      <c r="Z45">
+        <v>1.98</v>
+      </c>
+      <c r="AA45">
+        <v>3.26</v>
+      </c>
+      <c r="AB45">
+        <v>3.85</v>
+      </c>
+      <c r="AC45">
+        <v>1.07</v>
+      </c>
+      <c r="AD45">
+        <v>8</v>
+      </c>
+      <c r="AE45">
+        <v>1.38</v>
+      </c>
+      <c r="AF45">
+        <v>3</v>
+      </c>
+      <c r="AG45">
+        <v>2</v>
+      </c>
+      <c r="AH45">
+        <v>1.67</v>
+      </c>
+      <c r="AI45">
+        <v>1.83</v>
+      </c>
+      <c r="AJ45">
+        <v>1.83</v>
+      </c>
+      <c r="AK45">
+        <v>1.25</v>
+      </c>
+      <c r="AL45">
+        <v>1.28</v>
+      </c>
+      <c r="AM45">
+        <v>1.77</v>
+      </c>
+      <c r="AN45">
+        <v>1.75</v>
+      </c>
+      <c r="AO45">
+        <v>0.33</v>
+      </c>
+      <c r="AP45">
+        <v>2</v>
+      </c>
+      <c r="AQ45">
+        <v>0.25</v>
+      </c>
+      <c r="AR45">
+        <v>1.77</v>
+      </c>
+      <c r="AS45">
+        <v>1.18</v>
+      </c>
+      <c r="AT45">
+        <v>2.95</v>
+      </c>
+      <c r="AU45">
+        <v>5</v>
+      </c>
+      <c r="AV45">
+        <v>3</v>
+      </c>
+      <c r="AW45">
+        <v>1</v>
+      </c>
+      <c r="AX45">
+        <v>8</v>
+      </c>
+      <c r="AY45">
+        <v>7</v>
+      </c>
+      <c r="AZ45">
+        <v>13</v>
+      </c>
+      <c r="BA45">
+        <v>4</v>
+      </c>
+      <c r="BB45">
+        <v>5</v>
+      </c>
+      <c r="BC45">
+        <v>9</v>
+      </c>
+      <c r="BD45">
+        <v>1.7</v>
+      </c>
+      <c r="BE45">
+        <v>6.4</v>
+      </c>
+      <c r="BF45">
+        <v>2.4</v>
+      </c>
+      <c r="BG45">
+        <v>1.45</v>
+      </c>
+      <c r="BH45">
+        <v>2.55</v>
+      </c>
+      <c r="BI45">
+        <v>1.75</v>
+      </c>
+      <c r="BJ45">
+        <v>1.95</v>
+      </c>
+      <c r="BK45">
+        <v>2.2</v>
+      </c>
+      <c r="BL45">
+        <v>1.58</v>
+      </c>
+      <c r="BM45">
+        <v>2.88</v>
+      </c>
+      <c r="BN45">
+        <v>1.35</v>
+      </c>
+      <c r="BO45">
+        <v>3.8</v>
+      </c>
+      <c r="BP45">
         <v>1.22</v>
       </c>
     </row>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/South Korea K League 1_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/South Korea K League 1_2025.xlsx
@@ -8661,46 +8661,46 @@
         <v>82</v>
       </c>
       <c r="Q39">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="R39">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S39">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="T39">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="U39">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="V39">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="W39">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="X39">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Y39">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Z39">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AA39">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="AB39">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="AC39">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD39">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AE39">
         <v>0</v>
@@ -8709,16 +8709,16 @@
         <v>0</v>
       </c>
       <c r="AG39">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AH39">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AI39">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AJ39">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AK39">
         <v>0</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/South Korea K League 1_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/South Korea K League 1_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="692" uniqueCount="202">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="722" uniqueCount="209">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -463,6 +463,18 @@
     <t>['67']</t>
   </si>
   <si>
+    <t>['9005']</t>
+  </si>
+  <si>
+    <t>['29']</t>
+  </si>
+  <si>
+    <t>['42']</t>
+  </si>
+  <si>
+    <t>['67', '81']</t>
+  </si>
+  <si>
     <t>['32', '87', '90']</t>
   </si>
   <si>
@@ -527,9 +539,6 @@
   </si>
   <si>
     <t>['43', '45+2']</t>
-  </si>
-  <si>
-    <t>['42']</t>
   </si>
   <si>
     <t>['17', '47']</t>
@@ -620,6 +629,18 @@
   </si>
   <si>
     <t>['23', '50', '68']</t>
+  </si>
+  <si>
+    <t>['6', '32', '79']</t>
+  </si>
+  <si>
+    <t>['10', '55', '69']</t>
+  </si>
+  <si>
+    <t>['65', '75']</t>
+  </si>
+  <si>
+    <t>['41']</t>
   </si>
 </sst>
 </file>
@@ -981,7 +1002,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP105"/>
+  <dimension ref="A1:BP110"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1237,7 +1258,7 @@
         <v>82</v>
       </c>
       <c r="P2" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="Q2">
         <v>2.75</v>
@@ -1521,10 +1542,10 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AQ3">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -1727,7 +1748,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AQ4">
         <v>0.44</v>
@@ -1855,7 +1876,7 @@
         <v>82</v>
       </c>
       <c r="P5" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="Q5">
         <v>2.1</v>
@@ -1936,7 +1957,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ5">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2267,7 +2288,7 @@
         <v>85</v>
       </c>
       <c r="P7" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="Q7">
         <v>3.5</v>
@@ -2473,7 +2494,7 @@
         <v>86</v>
       </c>
       <c r="P8" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="Q8">
         <v>3.4</v>
@@ -2551,7 +2572,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AQ8">
         <v>1.44</v>
@@ -2679,7 +2700,7 @@
         <v>87</v>
       </c>
       <c r="P9" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="Q9">
         <v>3.35</v>
@@ -2966,7 +2987,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ10">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3091,7 +3112,7 @@
         <v>82</v>
       </c>
       <c r="P11" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="Q11">
         <v>3.45</v>
@@ -3297,7 +3318,7 @@
         <v>89</v>
       </c>
       <c r="P12" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="Q12">
         <v>2.75</v>
@@ -3503,7 +3524,7 @@
         <v>90</v>
       </c>
       <c r="P13" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="Q13">
         <v>2.95</v>
@@ -3581,10 +3602,10 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AQ13">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -3790,7 +3811,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ14">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="AR14">
         <v>2.51</v>
@@ -3996,7 +4017,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ15">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AR15">
         <v>1.87</v>
@@ -4199,10 +4220,10 @@
         <v>1.5</v>
       </c>
       <c r="AP16">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AQ16">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AR16">
         <v>1.8</v>
@@ -4611,7 +4632,7 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AQ18">
         <v>1</v>
@@ -5023,10 +5044,10 @@
         <v>0</v>
       </c>
       <c r="AP20">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AQ20">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AR20">
         <v>0</v>
@@ -5151,7 +5172,7 @@
         <v>94</v>
       </c>
       <c r="P21" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="Q21">
         <v>3.1</v>
@@ -5357,7 +5378,7 @@
         <v>95</v>
       </c>
       <c r="P22" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="Q22">
         <v>3.6</v>
@@ -5975,7 +5996,7 @@
         <v>97</v>
       </c>
       <c r="P25" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="Q25">
         <v>4</v>
@@ -6053,7 +6074,7 @@
         <v>3</v>
       </c>
       <c r="AP25">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AQ25">
         <v>2</v>
@@ -6181,7 +6202,7 @@
         <v>82</v>
       </c>
       <c r="P26" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="Q26">
         <v>3.6</v>
@@ -6259,10 +6280,10 @@
         <v>0.5</v>
       </c>
       <c r="AP26">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AQ26">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AR26">
         <v>1.64</v>
@@ -6387,7 +6408,7 @@
         <v>82</v>
       </c>
       <c r="P27" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="Q27">
         <v>2.75</v>
@@ -6468,7 +6489,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ27">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AR27">
         <v>2.02</v>
@@ -6593,7 +6614,7 @@
         <v>98</v>
       </c>
       <c r="P28" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="Q28">
         <v>3.75</v>
@@ -6671,7 +6692,7 @@
         <v>3</v>
       </c>
       <c r="AP28">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AQ28">
         <v>1.5</v>
@@ -6877,7 +6898,7 @@
         <v>1</v>
       </c>
       <c r="AP29">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AQ29">
         <v>1.25</v>
@@ -7005,7 +7026,7 @@
         <v>99</v>
       </c>
       <c r="P30" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="Q30">
         <v>2.63</v>
@@ -7086,7 +7107,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ30">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AR30">
         <v>1.76</v>
@@ -7211,7 +7232,7 @@
         <v>100</v>
       </c>
       <c r="P31" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="Q31">
         <v>3.1</v>
@@ -7289,10 +7310,10 @@
         <v>0.5</v>
       </c>
       <c r="AP31">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AQ31">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AR31">
         <v>1.73</v>
@@ -7417,7 +7438,7 @@
         <v>101</v>
       </c>
       <c r="P32" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="Q32">
         <v>2.5</v>
@@ -7498,7 +7519,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ32">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AR32">
         <v>0.86</v>
@@ -7829,7 +7850,7 @@
         <v>103</v>
       </c>
       <c r="P34" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="Q34">
         <v>3.2</v>
@@ -8113,7 +8134,7 @@
         <v>0.33</v>
       </c>
       <c r="AP35">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AQ35">
         <v>0.44</v>
@@ -8319,7 +8340,7 @@
         <v>1.5</v>
       </c>
       <c r="AP36">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AQ36">
         <v>1.33</v>
@@ -8528,7 +8549,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ37">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="AR37">
         <v>1.26</v>
@@ -8653,7 +8674,7 @@
         <v>106</v>
       </c>
       <c r="P38" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="Q38">
         <v>2.45</v>
@@ -8940,7 +8961,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ39">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AR39">
         <v>2.14</v>
@@ -9143,10 +9164,10 @@
         <v>0.5</v>
       </c>
       <c r="AP40">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AQ40">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AR40">
         <v>1.95</v>
@@ -9271,7 +9292,7 @@
         <v>82</v>
       </c>
       <c r="P41" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="Q41">
         <v>3.25</v>
@@ -9352,7 +9373,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ41">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="AR41">
         <v>1.54</v>
@@ -9477,7 +9498,7 @@
         <v>98</v>
       </c>
       <c r="P42" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="Q42">
         <v>3.4</v>
@@ -9555,10 +9576,10 @@
         <v>1.33</v>
       </c>
       <c r="AP42">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AQ42">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AR42">
         <v>1.2</v>
@@ -9967,7 +9988,7 @@
         <v>0.5</v>
       </c>
       <c r="AP44">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AQ44">
         <v>1</v>
@@ -10173,10 +10194,10 @@
         <v>0.33</v>
       </c>
       <c r="AP45">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AQ45">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AR45">
         <v>1.77</v>
@@ -10301,7 +10322,7 @@
         <v>111</v>
       </c>
       <c r="P46" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="Q46">
         <v>4.33</v>
@@ -10379,7 +10400,7 @@
         <v>1.75</v>
       </c>
       <c r="AP46">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AQ46">
         <v>1.44</v>
@@ -10507,7 +10528,7 @@
         <v>112</v>
       </c>
       <c r="P47" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="Q47">
         <v>2.6</v>
@@ -10794,7 +10815,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ48">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AR48">
         <v>1.68</v>
@@ -10997,7 +11018,7 @@
         <v>1</v>
       </c>
       <c r="AP49">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AQ49">
         <v>1.25</v>
@@ -11125,7 +11146,7 @@
         <v>115</v>
       </c>
       <c r="P50" t="s">
-        <v>171</v>
+        <v>151</v>
       </c>
       <c r="Q50">
         <v>2.3</v>
@@ -11537,7 +11558,7 @@
         <v>116</v>
       </c>
       <c r="P52" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="Q52">
         <v>2.38</v>
@@ -11743,7 +11764,7 @@
         <v>117</v>
       </c>
       <c r="P53" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="Q53">
         <v>3.1</v>
@@ -11949,7 +11970,7 @@
         <v>82</v>
       </c>
       <c r="P54" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="Q54">
         <v>2.75</v>
@@ -12027,7 +12048,7 @@
         <v>2.6</v>
       </c>
       <c r="AP54">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AQ54">
         <v>2</v>
@@ -12155,7 +12176,7 @@
         <v>118</v>
       </c>
       <c r="P55" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="Q55">
         <v>2.75</v>
@@ -12439,10 +12460,10 @@
         <v>1.25</v>
       </c>
       <c r="AP56">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AQ56">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AR56">
         <v>1.24</v>
@@ -12567,7 +12588,7 @@
         <v>120</v>
       </c>
       <c r="P57" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="Q57">
         <v>2.3</v>
@@ -12648,7 +12669,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ57">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AR57">
         <v>1.63</v>
@@ -12773,7 +12794,7 @@
         <v>82</v>
       </c>
       <c r="P58" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="Q58">
         <v>4.5</v>
@@ -12979,7 +13000,7 @@
         <v>121</v>
       </c>
       <c r="P59" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="Q59">
         <v>4</v>
@@ -13057,10 +13078,10 @@
         <v>2</v>
       </c>
       <c r="AP59">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AQ59">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="AR59">
         <v>1.49</v>
@@ -13185,7 +13206,7 @@
         <v>122</v>
       </c>
       <c r="P60" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="Q60">
         <v>2.7</v>
@@ -13472,7 +13493,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ61">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AR61">
         <v>1.8</v>
@@ -13675,7 +13696,7 @@
         <v>2</v>
       </c>
       <c r="AP62">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AQ62">
         <v>1.5</v>
@@ -14215,7 +14236,7 @@
         <v>105</v>
       </c>
       <c r="P65" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="Q65">
         <v>3.4</v>
@@ -14421,7 +14442,7 @@
         <v>127</v>
       </c>
       <c r="P66" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="Q66">
         <v>2.5</v>
@@ -14502,7 +14523,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ66">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AR66">
         <v>1.46</v>
@@ -14833,7 +14854,7 @@
         <v>82</v>
       </c>
       <c r="P68" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="Q68">
         <v>3</v>
@@ -14914,7 +14935,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ68">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="AR68">
         <v>1.47</v>
@@ -15117,7 +15138,7 @@
         <v>0.2</v>
       </c>
       <c r="AP69">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AQ69">
         <v>0.44</v>
@@ -15245,7 +15266,7 @@
         <v>116</v>
       </c>
       <c r="P70" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="Q70">
         <v>2.38</v>
@@ -15326,7 +15347,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ70">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AR70">
         <v>2.06</v>
@@ -15529,7 +15550,7 @@
         <v>1.67</v>
       </c>
       <c r="AP71">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AQ71">
         <v>1.44</v>
@@ -15863,7 +15884,7 @@
         <v>82</v>
       </c>
       <c r="P73" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="Q73">
         <v>3</v>
@@ -15941,7 +15962,7 @@
         <v>1</v>
       </c>
       <c r="AP73">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AQ73">
         <v>1.33</v>
@@ -16069,7 +16090,7 @@
         <v>130</v>
       </c>
       <c r="P74" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="Q74">
         <v>5</v>
@@ -16150,7 +16171,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ74">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AR74">
         <v>1.59</v>
@@ -16275,7 +16296,7 @@
         <v>131</v>
       </c>
       <c r="P75" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="Q75">
         <v>2.88</v>
@@ -16353,10 +16374,10 @@
         <v>0.2</v>
       </c>
       <c r="AP75">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AQ75">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AR75">
         <v>1.55</v>
@@ -16687,7 +16708,7 @@
         <v>133</v>
       </c>
       <c r="P77" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="Q77">
         <v>3</v>
@@ -16768,7 +16789,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ77">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AR77">
         <v>1.51</v>
@@ -16974,7 +16995,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ78">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AR78">
         <v>1.46</v>
@@ -17099,7 +17120,7 @@
         <v>134</v>
       </c>
       <c r="P79" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="Q79">
         <v>4.33</v>
@@ -17177,7 +17198,7 @@
         <v>1.67</v>
       </c>
       <c r="AP79">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AQ79">
         <v>1.5</v>
@@ -17305,7 +17326,7 @@
         <v>82</v>
       </c>
       <c r="P80" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="Q80">
         <v>3.6</v>
@@ -17383,7 +17404,7 @@
         <v>1.43</v>
       </c>
       <c r="AP80">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AQ80">
         <v>1.44</v>
@@ -17511,7 +17532,7 @@
         <v>82</v>
       </c>
       <c r="P81" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="Q81">
         <v>3.5</v>
@@ -17589,10 +17610,10 @@
         <v>2.4</v>
       </c>
       <c r="AP81">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AQ81">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="AR81">
         <v>1.49</v>
@@ -17798,7 +17819,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ82">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AR82">
         <v>1.65</v>
@@ -17923,7 +17944,7 @@
         <v>136</v>
       </c>
       <c r="P83" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="Q83">
         <v>4.33</v>
@@ -18001,7 +18022,7 @@
         <v>1.86</v>
       </c>
       <c r="AP83">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AQ83">
         <v>1.5</v>
@@ -18129,7 +18150,7 @@
         <v>137</v>
       </c>
       <c r="P84" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="Q84">
         <v>2.4</v>
@@ -18207,7 +18228,7 @@
         <v>0.33</v>
       </c>
       <c r="AP84">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AQ84">
         <v>1</v>
@@ -18541,7 +18562,7 @@
         <v>82</v>
       </c>
       <c r="P86" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="Q86">
         <v>5</v>
@@ -18622,7 +18643,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ86">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AR86">
         <v>1.94</v>
@@ -18825,7 +18846,7 @@
         <v>2.43</v>
       </c>
       <c r="AP87">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AQ87">
         <v>2</v>
@@ -19031,10 +19052,10 @@
         <v>2.5</v>
       </c>
       <c r="AP88">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AQ88">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="AR88">
         <v>1.52</v>
@@ -19159,7 +19180,7 @@
         <v>82</v>
       </c>
       <c r="P89" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="Q89">
         <v>3.4</v>
@@ -19240,7 +19261,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ89">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AR89">
         <v>1.57</v>
@@ -19365,7 +19386,7 @@
         <v>139</v>
       </c>
       <c r="P90" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="Q90">
         <v>2.3</v>
@@ -19571,7 +19592,7 @@
         <v>140</v>
       </c>
       <c r="P91" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="Q91">
         <v>2.55</v>
@@ -19858,7 +19879,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ92">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AR92">
         <v>1.34</v>
@@ -19983,7 +20004,7 @@
         <v>82</v>
       </c>
       <c r="P93" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="Q93">
         <v>2.88</v>
@@ -20061,7 +20082,7 @@
         <v>1.29</v>
       </c>
       <c r="AP93">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AQ93">
         <v>1.33</v>
@@ -20189,7 +20210,7 @@
         <v>82</v>
       </c>
       <c r="P94" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="Q94">
         <v>2.8</v>
@@ -20267,7 +20288,7 @@
         <v>0.43</v>
       </c>
       <c r="AP94">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AQ94">
         <v>1</v>
@@ -20395,7 +20416,7 @@
         <v>142</v>
       </c>
       <c r="P95" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="Q95">
         <v>2.62</v>
@@ -20476,7 +20497,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ95">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AR95">
         <v>1.37</v>
@@ -20601,7 +20622,7 @@
         <v>82</v>
       </c>
       <c r="P96" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="Q96">
         <v>4</v>
@@ -20682,7 +20703,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ96">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="AR96">
         <v>1.86</v>
@@ -20807,7 +20828,7 @@
         <v>82</v>
       </c>
       <c r="P97" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="Q97">
         <v>3.1</v>
@@ -20885,10 +20906,10 @@
         <v>1.25</v>
       </c>
       <c r="AP97">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AQ97">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AR97">
         <v>1.74</v>
@@ -21013,7 +21034,7 @@
         <v>125</v>
       </c>
       <c r="P98" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="Q98">
         <v>2.75</v>
@@ -21091,10 +21112,10 @@
         <v>0.86</v>
       </c>
       <c r="AP98">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AQ98">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AR98">
         <v>1.5</v>
@@ -21219,7 +21240,7 @@
         <v>143</v>
       </c>
       <c r="P99" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="Q99">
         <v>3.4</v>
@@ -21297,7 +21318,7 @@
         <v>1.75</v>
       </c>
       <c r="AP99">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AQ99">
         <v>1.5</v>
@@ -21425,7 +21446,7 @@
         <v>134</v>
       </c>
       <c r="P100" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="Q100">
         <v>3.3</v>
@@ -21631,7 +21652,7 @@
         <v>144</v>
       </c>
       <c r="P101" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="Q101">
         <v>3</v>
@@ -21837,7 +21858,7 @@
         <v>145</v>
       </c>
       <c r="P102" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="Q102">
         <v>2.3</v>
@@ -22043,7 +22064,7 @@
         <v>146</v>
       </c>
       <c r="P103" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="Q103">
         <v>2.1</v>
@@ -22121,7 +22142,7 @@
         <v>0.38</v>
       </c>
       <c r="AP103">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AQ103">
         <v>0.44</v>
@@ -22249,7 +22270,7 @@
         <v>147</v>
       </c>
       <c r="P104" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="Q104">
         <v>2.55</v>
@@ -22612,6 +22633,1036 @@
       </c>
       <c r="BP105">
         <v>1.24</v>
+      </c>
+    </row>
+    <row r="106" spans="1:68">
+      <c r="A106" s="1">
+        <v>105</v>
+      </c>
+      <c r="B106">
+        <v>7806860</v>
+      </c>
+      <c r="C106" t="s">
+        <v>68</v>
+      </c>
+      <c r="D106" t="s">
+        <v>69</v>
+      </c>
+      <c r="E106" s="2">
+        <v>45821.3125</v>
+      </c>
+      <c r="F106">
+        <v>18</v>
+      </c>
+      <c r="G106" t="s">
+        <v>78</v>
+      </c>
+      <c r="H106" t="s">
+        <v>74</v>
+      </c>
+      <c r="I106">
+        <v>0</v>
+      </c>
+      <c r="J106">
+        <v>2</v>
+      </c>
+      <c r="K106">
+        <v>2</v>
+      </c>
+      <c r="L106">
+        <v>0</v>
+      </c>
+      <c r="M106">
+        <v>3</v>
+      </c>
+      <c r="N106">
+        <v>3</v>
+      </c>
+      <c r="O106" t="s">
+        <v>82</v>
+      </c>
+      <c r="P106" t="s">
+        <v>205</v>
+      </c>
+      <c r="Q106">
+        <v>4.5</v>
+      </c>
+      <c r="R106">
+        <v>2.05</v>
+      </c>
+      <c r="S106">
+        <v>2.63</v>
+      </c>
+      <c r="T106">
+        <v>1.44</v>
+      </c>
+      <c r="U106">
+        <v>2.63</v>
+      </c>
+      <c r="V106">
+        <v>3.25</v>
+      </c>
+      <c r="W106">
+        <v>1.33</v>
+      </c>
+      <c r="X106">
+        <v>10</v>
+      </c>
+      <c r="Y106">
+        <v>1.06</v>
+      </c>
+      <c r="Z106">
+        <v>3.62</v>
+      </c>
+      <c r="AA106">
+        <v>3.11</v>
+      </c>
+      <c r="AB106">
+        <v>1.92</v>
+      </c>
+      <c r="AC106">
+        <v>1.09</v>
+      </c>
+      <c r="AD106">
+        <v>7</v>
+      </c>
+      <c r="AE106">
+        <v>1.42</v>
+      </c>
+      <c r="AF106">
+        <v>2.8</v>
+      </c>
+      <c r="AG106">
+        <v>2.05</v>
+      </c>
+      <c r="AH106">
+        <v>1.68</v>
+      </c>
+      <c r="AI106">
+        <v>1.91</v>
+      </c>
+      <c r="AJ106">
+        <v>1.8</v>
+      </c>
+      <c r="AK106">
+        <v>1.75</v>
+      </c>
+      <c r="AL106">
+        <v>1.3</v>
+      </c>
+      <c r="AM106">
+        <v>1.25</v>
+      </c>
+      <c r="AN106">
+        <v>1.13</v>
+      </c>
+      <c r="AO106">
+        <v>2.38</v>
+      </c>
+      <c r="AP106">
+        <v>1</v>
+      </c>
+      <c r="AQ106">
+        <v>2.44</v>
+      </c>
+      <c r="AR106">
+        <v>1.5</v>
+      </c>
+      <c r="AS106">
+        <v>1.27</v>
+      </c>
+      <c r="AT106">
+        <v>2.77</v>
+      </c>
+      <c r="AU106">
+        <v>4</v>
+      </c>
+      <c r="AV106">
+        <v>8</v>
+      </c>
+      <c r="AW106">
+        <v>13</v>
+      </c>
+      <c r="AX106">
+        <v>7</v>
+      </c>
+      <c r="AY106">
+        <v>17</v>
+      </c>
+      <c r="AZ106">
+        <v>15</v>
+      </c>
+      <c r="BA106">
+        <v>5</v>
+      </c>
+      <c r="BB106">
+        <v>5</v>
+      </c>
+      <c r="BC106">
+        <v>10</v>
+      </c>
+      <c r="BD106">
+        <v>2.25</v>
+      </c>
+      <c r="BE106">
+        <v>6.25</v>
+      </c>
+      <c r="BF106">
+        <v>1.79</v>
+      </c>
+      <c r="BG106">
+        <v>1.52</v>
+      </c>
+      <c r="BH106">
+        <v>2.33</v>
+      </c>
+      <c r="BI106">
+        <v>1.86</v>
+      </c>
+      <c r="BJ106">
+        <v>1.82</v>
+      </c>
+      <c r="BK106">
+        <v>2.4</v>
+      </c>
+      <c r="BL106">
+        <v>1.5</v>
+      </c>
+      <c r="BM106">
+        <v>3.15</v>
+      </c>
+      <c r="BN106">
+        <v>1.3</v>
+      </c>
+      <c r="BO106">
+        <v>4.3</v>
+      </c>
+      <c r="BP106">
+        <v>1.18</v>
+      </c>
+    </row>
+    <row r="107" spans="1:68">
+      <c r="A107" s="1">
+        <v>106</v>
+      </c>
+      <c r="B107">
+        <v>7806861</v>
+      </c>
+      <c r="C107" t="s">
+        <v>68</v>
+      </c>
+      <c r="D107" t="s">
+        <v>69</v>
+      </c>
+      <c r="E107" s="2">
+        <v>45821.3125</v>
+      </c>
+      <c r="F107">
+        <v>18</v>
+      </c>
+      <c r="G107" t="s">
+        <v>72</v>
+      </c>
+      <c r="H107" t="s">
+        <v>76</v>
+      </c>
+      <c r="I107">
+        <v>0</v>
+      </c>
+      <c r="J107">
+        <v>1</v>
+      </c>
+      <c r="K107">
+        <v>1</v>
+      </c>
+      <c r="L107">
+        <v>1</v>
+      </c>
+      <c r="M107">
+        <v>3</v>
+      </c>
+      <c r="N107">
+        <v>4</v>
+      </c>
+      <c r="O107" t="s">
+        <v>149</v>
+      </c>
+      <c r="P107" t="s">
+        <v>206</v>
+      </c>
+      <c r="Q107">
+        <v>4.33</v>
+      </c>
+      <c r="R107">
+        <v>1.95</v>
+      </c>
+      <c r="S107">
+        <v>3</v>
+      </c>
+      <c r="T107">
+        <v>1.53</v>
+      </c>
+      <c r="U107">
+        <v>2.38</v>
+      </c>
+      <c r="V107">
+        <v>3.5</v>
+      </c>
+      <c r="W107">
+        <v>1.29</v>
+      </c>
+      <c r="X107">
+        <v>11</v>
+      </c>
+      <c r="Y107">
+        <v>1.05</v>
+      </c>
+      <c r="Z107">
+        <v>3.25</v>
+      </c>
+      <c r="AA107">
+        <v>2.9</v>
+      </c>
+      <c r="AB107">
+        <v>2.14</v>
+      </c>
+      <c r="AC107">
+        <v>1.11</v>
+      </c>
+      <c r="AD107">
+        <v>6.25</v>
+      </c>
+      <c r="AE107">
+        <v>1.48</v>
+      </c>
+      <c r="AF107">
+        <v>2.37</v>
+      </c>
+      <c r="AG107">
+        <v>2.43</v>
+      </c>
+      <c r="AH107">
+        <v>1.49</v>
+      </c>
+      <c r="AI107">
+        <v>2.1</v>
+      </c>
+      <c r="AJ107">
+        <v>1.67</v>
+      </c>
+      <c r="AK107">
+        <v>1.6</v>
+      </c>
+      <c r="AL107">
+        <v>1.33</v>
+      </c>
+      <c r="AM107">
+        <v>1.3</v>
+      </c>
+      <c r="AN107">
+        <v>1.56</v>
+      </c>
+      <c r="AO107">
+        <v>1.44</v>
+      </c>
+      <c r="AP107">
+        <v>1.4</v>
+      </c>
+      <c r="AQ107">
+        <v>1.6</v>
+      </c>
+      <c r="AR107">
+        <v>1.53</v>
+      </c>
+      <c r="AS107">
+        <v>1.79</v>
+      </c>
+      <c r="AT107">
+        <v>3.32</v>
+      </c>
+      <c r="AU107">
+        <v>2</v>
+      </c>
+      <c r="AV107">
+        <v>6</v>
+      </c>
+      <c r="AW107">
+        <v>9</v>
+      </c>
+      <c r="AX107">
+        <v>5</v>
+      </c>
+      <c r="AY107">
+        <v>11</v>
+      </c>
+      <c r="AZ107">
+        <v>11</v>
+      </c>
+      <c r="BA107">
+        <v>5</v>
+      </c>
+      <c r="BB107">
+        <v>5</v>
+      </c>
+      <c r="BC107">
+        <v>10</v>
+      </c>
+      <c r="BD107">
+        <v>2.17</v>
+      </c>
+      <c r="BE107">
+        <v>6.25</v>
+      </c>
+      <c r="BF107">
+        <v>1.86</v>
+      </c>
+      <c r="BG107">
+        <v>1.47</v>
+      </c>
+      <c r="BH107">
+        <v>2.48</v>
+      </c>
+      <c r="BI107">
+        <v>1.78</v>
+      </c>
+      <c r="BJ107">
+        <v>1.92</v>
+      </c>
+      <c r="BK107">
+        <v>2.25</v>
+      </c>
+      <c r="BL107">
+        <v>1.55</v>
+      </c>
+      <c r="BM107">
+        <v>2.95</v>
+      </c>
+      <c r="BN107">
+        <v>1.33</v>
+      </c>
+      <c r="BO107">
+        <v>3.95</v>
+      </c>
+      <c r="BP107">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="108" spans="1:68">
+      <c r="A108" s="1">
+        <v>107</v>
+      </c>
+      <c r="B108">
+        <v>7806862</v>
+      </c>
+      <c r="C108" t="s">
+        <v>68</v>
+      </c>
+      <c r="D108" t="s">
+        <v>69</v>
+      </c>
+      <c r="E108" s="2">
+        <v>45822.29166666666</v>
+      </c>
+      <c r="F108">
+        <v>18</v>
+      </c>
+      <c r="G108" t="s">
+        <v>81</v>
+      </c>
+      <c r="H108" t="s">
+        <v>70</v>
+      </c>
+      <c r="I108">
+        <v>1</v>
+      </c>
+      <c r="J108">
+        <v>0</v>
+      </c>
+      <c r="K108">
+        <v>1</v>
+      </c>
+      <c r="L108">
+        <v>1</v>
+      </c>
+      <c r="M108">
+        <v>0</v>
+      </c>
+      <c r="N108">
+        <v>1</v>
+      </c>
+      <c r="O108" t="s">
+        <v>150</v>
+      </c>
+      <c r="P108" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q108">
+        <v>2.75</v>
+      </c>
+      <c r="R108">
+        <v>2.2</v>
+      </c>
+      <c r="S108">
+        <v>3.75</v>
+      </c>
+      <c r="T108">
+        <v>1.36</v>
+      </c>
+      <c r="U108">
+        <v>3</v>
+      </c>
+      <c r="V108">
+        <v>2.75</v>
+      </c>
+      <c r="W108">
+        <v>1.4</v>
+      </c>
+      <c r="X108">
+        <v>7</v>
+      </c>
+      <c r="Y108">
+        <v>1.1</v>
+      </c>
+      <c r="Z108">
+        <v>2.07</v>
+      </c>
+      <c r="AA108">
+        <v>3.21</v>
+      </c>
+      <c r="AB108">
+        <v>3.08</v>
+      </c>
+      <c r="AC108">
+        <v>1.06</v>
+      </c>
+      <c r="AD108">
+        <v>8.5</v>
+      </c>
+      <c r="AE108">
+        <v>1.3</v>
+      </c>
+      <c r="AF108">
+        <v>3.45</v>
+      </c>
+      <c r="AG108">
+        <v>1.84</v>
+      </c>
+      <c r="AH108">
+        <v>1.86</v>
+      </c>
+      <c r="AI108">
+        <v>1.67</v>
+      </c>
+      <c r="AJ108">
+        <v>2.1</v>
+      </c>
+      <c r="AK108">
+        <v>1.3</v>
+      </c>
+      <c r="AL108">
+        <v>1.25</v>
+      </c>
+      <c r="AM108">
+        <v>1.7</v>
+      </c>
+      <c r="AN108">
+        <v>1.5</v>
+      </c>
+      <c r="AO108">
+        <v>1.5</v>
+      </c>
+      <c r="AP108">
+        <v>1.67</v>
+      </c>
+      <c r="AQ108">
+        <v>1.33</v>
+      </c>
+      <c r="AR108">
+        <v>1.74</v>
+      </c>
+      <c r="AS108">
+        <v>1.52</v>
+      </c>
+      <c r="AT108">
+        <v>3.26</v>
+      </c>
+      <c r="AU108">
+        <v>4</v>
+      </c>
+      <c r="AV108">
+        <v>2</v>
+      </c>
+      <c r="AW108">
+        <v>6</v>
+      </c>
+      <c r="AX108">
+        <v>4</v>
+      </c>
+      <c r="AY108">
+        <v>10</v>
+      </c>
+      <c r="AZ108">
+        <v>6</v>
+      </c>
+      <c r="BA108">
+        <v>3</v>
+      </c>
+      <c r="BB108">
+        <v>3</v>
+      </c>
+      <c r="BC108">
+        <v>6</v>
+      </c>
+      <c r="BD108">
+        <v>1.73</v>
+      </c>
+      <c r="BE108">
+        <v>6.25</v>
+      </c>
+      <c r="BF108">
+        <v>2.35</v>
+      </c>
+      <c r="BG108">
+        <v>1.49</v>
+      </c>
+      <c r="BH108">
+        <v>2.4</v>
+      </c>
+      <c r="BI108">
+        <v>1.83</v>
+      </c>
+      <c r="BJ108">
+        <v>1.85</v>
+      </c>
+      <c r="BK108">
+        <v>2.33</v>
+      </c>
+      <c r="BL108">
+        <v>1.52</v>
+      </c>
+      <c r="BM108">
+        <v>3.05</v>
+      </c>
+      <c r="BN108">
+        <v>1.32</v>
+      </c>
+      <c r="BO108">
+        <v>4.1</v>
+      </c>
+      <c r="BP108">
+        <v>1.19</v>
+      </c>
+    </row>
+    <row r="109" spans="1:68">
+      <c r="A109" s="1">
+        <v>108</v>
+      </c>
+      <c r="B109">
+        <v>7806863</v>
+      </c>
+      <c r="C109" t="s">
+        <v>68</v>
+      </c>
+      <c r="D109" t="s">
+        <v>69</v>
+      </c>
+      <c r="E109" s="2">
+        <v>45822.29166666666</v>
+      </c>
+      <c r="F109">
+        <v>18</v>
+      </c>
+      <c r="G109" t="s">
+        <v>79</v>
+      </c>
+      <c r="H109" t="s">
+        <v>80</v>
+      </c>
+      <c r="I109">
+        <v>1</v>
+      </c>
+      <c r="J109">
+        <v>0</v>
+      </c>
+      <c r="K109">
+        <v>1</v>
+      </c>
+      <c r="L109">
+        <v>1</v>
+      </c>
+      <c r="M109">
+        <v>2</v>
+      </c>
+      <c r="N109">
+        <v>3</v>
+      </c>
+      <c r="O109" t="s">
+        <v>151</v>
+      </c>
+      <c r="P109" t="s">
+        <v>207</v>
+      </c>
+      <c r="Q109">
+        <v>3</v>
+      </c>
+      <c r="R109">
+        <v>2.1</v>
+      </c>
+      <c r="S109">
+        <v>3.6</v>
+      </c>
+      <c r="T109">
+        <v>1.4</v>
+      </c>
+      <c r="U109">
+        <v>2.75</v>
+      </c>
+      <c r="V109">
+        <v>3</v>
+      </c>
+      <c r="W109">
+        <v>1.36</v>
+      </c>
+      <c r="X109">
+        <v>8</v>
+      </c>
+      <c r="Y109">
+        <v>1.08</v>
+      </c>
+      <c r="Z109">
+        <v>2.23</v>
+      </c>
+      <c r="AA109">
+        <v>3.15</v>
+      </c>
+      <c r="AB109">
+        <v>2.83</v>
+      </c>
+      <c r="AC109">
+        <v>1.06</v>
+      </c>
+      <c r="AD109">
+        <v>8.5</v>
+      </c>
+      <c r="AE109">
+        <v>1.33</v>
+      </c>
+      <c r="AF109">
+        <v>3.2</v>
+      </c>
+      <c r="AG109">
+        <v>1.95</v>
+      </c>
+      <c r="AH109">
+        <v>1.75</v>
+      </c>
+      <c r="AI109">
+        <v>1.73</v>
+      </c>
+      <c r="AJ109">
+        <v>2</v>
+      </c>
+      <c r="AK109">
+        <v>1.36</v>
+      </c>
+      <c r="AL109">
+        <v>1.28</v>
+      </c>
+      <c r="AM109">
+        <v>1.57</v>
+      </c>
+      <c r="AN109">
+        <v>1.5</v>
+      </c>
+      <c r="AO109">
+        <v>1.13</v>
+      </c>
+      <c r="AP109">
+        <v>1.33</v>
+      </c>
+      <c r="AQ109">
+        <v>1.33</v>
+      </c>
+      <c r="AR109">
+        <v>1.77</v>
+      </c>
+      <c r="AS109">
+        <v>1.44</v>
+      </c>
+      <c r="AT109">
+        <v>3.21</v>
+      </c>
+      <c r="AU109">
+        <v>2</v>
+      </c>
+      <c r="AV109">
+        <v>3</v>
+      </c>
+      <c r="AW109">
+        <v>5</v>
+      </c>
+      <c r="AX109">
+        <v>8</v>
+      </c>
+      <c r="AY109">
+        <v>7</v>
+      </c>
+      <c r="AZ109">
+        <v>11</v>
+      </c>
+      <c r="BA109">
+        <v>0</v>
+      </c>
+      <c r="BB109">
+        <v>4</v>
+      </c>
+      <c r="BC109">
+        <v>4</v>
+      </c>
+      <c r="BD109">
+        <v>1.84</v>
+      </c>
+      <c r="BE109">
+        <v>6.1</v>
+      </c>
+      <c r="BF109">
+        <v>2.18</v>
+      </c>
+      <c r="BG109">
+        <v>1.55</v>
+      </c>
+      <c r="BH109">
+        <v>2.28</v>
+      </c>
+      <c r="BI109">
+        <v>1.91</v>
+      </c>
+      <c r="BJ109">
+        <v>1.78</v>
+      </c>
+      <c r="BK109">
+        <v>2.43</v>
+      </c>
+      <c r="BL109">
+        <v>1.49</v>
+      </c>
+      <c r="BM109">
+        <v>3.2</v>
+      </c>
+      <c r="BN109">
+        <v>1.29</v>
+      </c>
+      <c r="BO109">
+        <v>4.35</v>
+      </c>
+      <c r="BP109">
+        <v>1.17</v>
+      </c>
+    </row>
+    <row r="110" spans="1:68">
+      <c r="A110" s="1">
+        <v>109</v>
+      </c>
+      <c r="B110">
+        <v>7806864</v>
+      </c>
+      <c r="C110" t="s">
+        <v>68</v>
+      </c>
+      <c r="D110" t="s">
+        <v>69</v>
+      </c>
+      <c r="E110" s="2">
+        <v>45822.29166666666</v>
+      </c>
+      <c r="F110">
+        <v>18</v>
+      </c>
+      <c r="G110" t="s">
+        <v>71</v>
+      </c>
+      <c r="H110" t="s">
+        <v>75</v>
+      </c>
+      <c r="I110">
+        <v>0</v>
+      </c>
+      <c r="J110">
+        <v>1</v>
+      </c>
+      <c r="K110">
+        <v>1</v>
+      </c>
+      <c r="L110">
+        <v>2</v>
+      </c>
+      <c r="M110">
+        <v>1</v>
+      </c>
+      <c r="N110">
+        <v>3</v>
+      </c>
+      <c r="O110" t="s">
+        <v>152</v>
+      </c>
+      <c r="P110" t="s">
+        <v>208</v>
+      </c>
+      <c r="Q110">
+        <v>2.5</v>
+      </c>
+      <c r="R110">
+        <v>2.25</v>
+      </c>
+      <c r="S110">
+        <v>4.33</v>
+      </c>
+      <c r="T110">
+        <v>1.36</v>
+      </c>
+      <c r="U110">
+        <v>3</v>
+      </c>
+      <c r="V110">
+        <v>2.63</v>
+      </c>
+      <c r="W110">
+        <v>1.44</v>
+      </c>
+      <c r="X110">
+        <v>7</v>
+      </c>
+      <c r="Y110">
+        <v>1.1</v>
+      </c>
+      <c r="Z110">
+        <v>1.9</v>
+      </c>
+      <c r="AA110">
+        <v>3.34</v>
+      </c>
+      <c r="AB110">
+        <v>3.39</v>
+      </c>
+      <c r="AC110">
+        <v>1.05</v>
+      </c>
+      <c r="AD110">
+        <v>9</v>
+      </c>
+      <c r="AE110">
+        <v>1.28</v>
+      </c>
+      <c r="AF110">
+        <v>3.55</v>
+      </c>
+      <c r="AG110">
+        <v>1.83</v>
+      </c>
+      <c r="AH110">
+        <v>1.87</v>
+      </c>
+      <c r="AI110">
+        <v>1.73</v>
+      </c>
+      <c r="AJ110">
+        <v>2</v>
+      </c>
+      <c r="AK110">
+        <v>1.25</v>
+      </c>
+      <c r="AL110">
+        <v>1.25</v>
+      </c>
+      <c r="AM110">
+        <v>1.83</v>
+      </c>
+      <c r="AN110">
+        <v>1.25</v>
+      </c>
+      <c r="AO110">
+        <v>0.25</v>
+      </c>
+      <c r="AP110">
+        <v>1.44</v>
+      </c>
+      <c r="AQ110">
+        <v>0.22</v>
+      </c>
+      <c r="AR110">
+        <v>1.5</v>
+      </c>
+      <c r="AS110">
+        <v>1.33</v>
+      </c>
+      <c r="AT110">
+        <v>2.83</v>
+      </c>
+      <c r="AU110">
+        <v>4</v>
+      </c>
+      <c r="AV110">
+        <v>5</v>
+      </c>
+      <c r="AW110">
+        <v>7</v>
+      </c>
+      <c r="AX110">
+        <v>3</v>
+      </c>
+      <c r="AY110">
+        <v>11</v>
+      </c>
+      <c r="AZ110">
+        <v>8</v>
+      </c>
+      <c r="BA110">
+        <v>7</v>
+      </c>
+      <c r="BB110">
+        <v>1</v>
+      </c>
+      <c r="BC110">
+        <v>8</v>
+      </c>
+      <c r="BD110">
+        <v>1.75</v>
+      </c>
+      <c r="BE110">
+        <v>6.4</v>
+      </c>
+      <c r="BF110">
+        <v>2.3</v>
+      </c>
+      <c r="BG110">
+        <v>1.35</v>
+      </c>
+      <c r="BH110">
+        <v>2.9</v>
+      </c>
+      <c r="BI110">
+        <v>1.6</v>
+      </c>
+      <c r="BJ110">
+        <v>2.17</v>
+      </c>
+      <c r="BK110">
+        <v>1.98</v>
+      </c>
+      <c r="BL110">
+        <v>1.74</v>
+      </c>
+      <c r="BM110">
+        <v>2.5</v>
+      </c>
+      <c r="BN110">
+        <v>1.46</v>
+      </c>
+      <c r="BO110">
+        <v>3.3</v>
+      </c>
+      <c r="BP110">
+        <v>1.28</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/South Korea K League 1_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/South Korea K League 1_2025.xlsx
@@ -23187,19 +23187,19 @@
         <v>3.26</v>
       </c>
       <c r="AU108">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AV108">
         <v>2</v>
       </c>
       <c r="AW108">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AX108">
         <v>4</v>
       </c>
       <c r="AY108">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AZ108">
         <v>6</v>
@@ -23393,22 +23393,22 @@
         <v>3.21</v>
       </c>
       <c r="AU109">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AV109">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AW109">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AX109">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AY109">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AZ109">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BA109">
         <v>0</v>
@@ -23599,22 +23599,22 @@
         <v>2.83</v>
       </c>
       <c r="AU110">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AV110">
         <v>5</v>
       </c>
       <c r="AW110">
+        <v>5</v>
+      </c>
+      <c r="AX110">
+        <v>2</v>
+      </c>
+      <c r="AY110">
+        <v>10</v>
+      </c>
+      <c r="AZ110">
         <v>7</v>
-      </c>
-      <c r="AX110">
-        <v>3</v>
-      </c>
-      <c r="AY110">
-        <v>11</v>
-      </c>
-      <c r="AZ110">
-        <v>8</v>
       </c>
       <c r="BA110">
         <v>7</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/South Korea K League 1_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/South Korea K League 1_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="722" uniqueCount="209">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="740" uniqueCount="215">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -475,6 +475,15 @@
     <t>['67', '81']</t>
   </si>
   <si>
+    <t>['83']</t>
+  </si>
+  <si>
+    <t>['72']</t>
+  </si>
+  <si>
+    <t>['52', '72']</t>
+  </si>
+  <si>
     <t>['32', '87', '90']</t>
   </si>
   <si>
@@ -641,6 +650,15 @@
   </si>
   <si>
     <t>['41']</t>
+  </si>
+  <si>
+    <t>['32']</t>
+  </si>
+  <si>
+    <t>['25']</t>
+  </si>
+  <si>
+    <t>['5', '31']</t>
   </si>
 </sst>
 </file>
@@ -1002,7 +1020,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP110"/>
+  <dimension ref="A1:BP113"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1258,7 +1276,7 @@
         <v>82</v>
       </c>
       <c r="P2" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="Q2">
         <v>2.75</v>
@@ -1751,7 +1769,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ4">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -1876,7 +1894,7 @@
         <v>82</v>
       </c>
       <c r="P5" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="Q5">
         <v>2.1</v>
@@ -2160,7 +2178,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AQ6">
         <v>1.44</v>
@@ -2288,7 +2306,7 @@
         <v>85</v>
       </c>
       <c r="P7" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="Q7">
         <v>3.5</v>
@@ -2366,10 +2384,10 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AQ7">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2494,7 +2512,7 @@
         <v>86</v>
       </c>
       <c r="P8" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="Q8">
         <v>3.4</v>
@@ -2700,7 +2718,7 @@
         <v>87</v>
       </c>
       <c r="P9" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="Q9">
         <v>3.35</v>
@@ -2778,10 +2796,10 @@
         <v>1</v>
       </c>
       <c r="AP9">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AQ9">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="AR9">
         <v>1.95</v>
@@ -2984,7 +3002,7 @@
         <v>3</v>
       </c>
       <c r="AP10">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AQ10">
         <v>1.33</v>
@@ -3112,7 +3130,7 @@
         <v>82</v>
       </c>
       <c r="P11" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="Q11">
         <v>3.45</v>
@@ -3318,7 +3336,7 @@
         <v>89</v>
       </c>
       <c r="P12" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="Q12">
         <v>2.75</v>
@@ -3396,7 +3414,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AQ12">
         <v>1.25</v>
@@ -3524,7 +3542,7 @@
         <v>90</v>
       </c>
       <c r="P13" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="Q13">
         <v>2.95</v>
@@ -3605,7 +3623,7 @@
         <v>1</v>
       </c>
       <c r="AQ13">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -4429,7 +4447,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ17">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="AR17">
         <v>1.3</v>
@@ -4838,7 +4856,7 @@
         <v>1.5</v>
       </c>
       <c r="AP19">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AQ19">
         <v>1.44</v>
@@ -5172,7 +5190,7 @@
         <v>94</v>
       </c>
       <c r="P21" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="Q21">
         <v>3.1</v>
@@ -5250,7 +5268,7 @@
         <v>3</v>
       </c>
       <c r="AP21">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AQ21">
         <v>2</v>
@@ -5378,7 +5396,7 @@
         <v>95</v>
       </c>
       <c r="P22" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="Q22">
         <v>3.6</v>
@@ -5868,10 +5886,10 @@
         <v>0</v>
       </c>
       <c r="AP24">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AQ24">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AR24">
         <v>1.82</v>
@@ -5996,7 +6014,7 @@
         <v>97</v>
       </c>
       <c r="P25" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="Q25">
         <v>4</v>
@@ -6202,7 +6220,7 @@
         <v>82</v>
       </c>
       <c r="P26" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="Q26">
         <v>3.6</v>
@@ -6408,7 +6426,7 @@
         <v>82</v>
       </c>
       <c r="P27" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="Q27">
         <v>2.75</v>
@@ -6486,7 +6504,7 @@
         <v>1</v>
       </c>
       <c r="AP27">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AQ27">
         <v>1.33</v>
@@ -6614,7 +6632,7 @@
         <v>98</v>
       </c>
       <c r="P28" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="Q28">
         <v>3.75</v>
@@ -7026,7 +7044,7 @@
         <v>99</v>
       </c>
       <c r="P30" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="Q30">
         <v>2.63</v>
@@ -7104,10 +7122,10 @@
         <v>0</v>
       </c>
       <c r="AP30">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AQ30">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AR30">
         <v>1.76</v>
@@ -7232,7 +7250,7 @@
         <v>100</v>
       </c>
       <c r="P31" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="Q31">
         <v>3.1</v>
@@ -7313,7 +7331,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ31">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AR31">
         <v>1.73</v>
@@ -7438,7 +7456,7 @@
         <v>101</v>
       </c>
       <c r="P32" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="Q32">
         <v>2.5</v>
@@ -7516,7 +7534,7 @@
         <v>1</v>
       </c>
       <c r="AP32">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AQ32">
         <v>0.22</v>
@@ -7850,7 +7868,7 @@
         <v>103</v>
       </c>
       <c r="P34" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="Q34">
         <v>3.2</v>
@@ -8137,7 +8155,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ35">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="AR35">
         <v>1.17</v>
@@ -8343,7 +8361,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ36">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AR36">
         <v>1.94</v>
@@ -8674,7 +8692,7 @@
         <v>106</v>
       </c>
       <c r="P38" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="Q38">
         <v>2.45</v>
@@ -9292,7 +9310,7 @@
         <v>82</v>
       </c>
       <c r="P41" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="Q41">
         <v>3.25</v>
@@ -9498,7 +9516,7 @@
         <v>98</v>
       </c>
       <c r="P42" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="Q42">
         <v>3.4</v>
@@ -9579,7 +9597,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ42">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AR42">
         <v>1.2</v>
@@ -9785,7 +9803,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ43">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AR43">
         <v>1.25</v>
@@ -10322,7 +10340,7 @@
         <v>111</v>
       </c>
       <c r="P46" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="Q46">
         <v>4.33</v>
@@ -10528,7 +10546,7 @@
         <v>112</v>
       </c>
       <c r="P47" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="Q47">
         <v>2.6</v>
@@ -10606,7 +10624,7 @@
         <v>3</v>
       </c>
       <c r="AP47">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AQ47">
         <v>2</v>
@@ -11224,7 +11242,7 @@
         <v>0.33</v>
       </c>
       <c r="AP50">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AQ50">
         <v>1</v>
@@ -11430,7 +11448,7 @@
         <v>1.33</v>
       </c>
       <c r="AP51">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AQ51">
         <v>1.5</v>
@@ -11558,7 +11576,7 @@
         <v>116</v>
       </c>
       <c r="P52" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="Q52">
         <v>2.38</v>
@@ -11639,7 +11657,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ52">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AR52">
         <v>2.04</v>
@@ -11764,7 +11782,7 @@
         <v>117</v>
       </c>
       <c r="P53" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="Q53">
         <v>3.1</v>
@@ -11845,7 +11863,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ53">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="AR53">
         <v>1.51</v>
@@ -11970,7 +11988,7 @@
         <v>82</v>
       </c>
       <c r="P54" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="Q54">
         <v>2.75</v>
@@ -12176,7 +12194,7 @@
         <v>118</v>
       </c>
       <c r="P55" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="Q55">
         <v>2.75</v>
@@ -12254,7 +12272,7 @@
         <v>0.75</v>
       </c>
       <c r="AP55">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AQ55">
         <v>1.25</v>
@@ -12463,7 +12481,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ56">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AR56">
         <v>1.24</v>
@@ -12588,7 +12606,7 @@
         <v>120</v>
       </c>
       <c r="P57" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="Q57">
         <v>2.3</v>
@@ -12666,7 +12684,7 @@
         <v>0.25</v>
       </c>
       <c r="AP57">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AQ57">
         <v>0.22</v>
@@ -12794,7 +12812,7 @@
         <v>82</v>
       </c>
       <c r="P58" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="Q58">
         <v>4.5</v>
@@ -13000,7 +13018,7 @@
         <v>121</v>
       </c>
       <c r="P59" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="Q59">
         <v>4</v>
@@ -13206,7 +13224,7 @@
         <v>122</v>
       </c>
       <c r="P60" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="Q60">
         <v>2.7</v>
@@ -13905,7 +13923,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ63">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AR63">
         <v>1.45</v>
@@ -14236,7 +14254,7 @@
         <v>105</v>
       </c>
       <c r="P65" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="Q65">
         <v>3.4</v>
@@ -14442,7 +14460,7 @@
         <v>127</v>
       </c>
       <c r="P66" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="Q66">
         <v>2.5</v>
@@ -14726,7 +14744,7 @@
         <v>0.4</v>
       </c>
       <c r="AP67">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AQ67">
         <v>1</v>
@@ -14854,7 +14872,7 @@
         <v>82</v>
       </c>
       <c r="P68" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="Q68">
         <v>3</v>
@@ -14932,7 +14950,7 @@
         <v>2.25</v>
       </c>
       <c r="AP68">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AQ68">
         <v>2.44</v>
@@ -15141,7 +15159,7 @@
         <v>1</v>
       </c>
       <c r="AQ69">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="AR69">
         <v>1.43</v>
@@ -15266,7 +15284,7 @@
         <v>116</v>
       </c>
       <c r="P70" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="Q70">
         <v>2.38</v>
@@ -15347,7 +15365,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ70">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AR70">
         <v>2.06</v>
@@ -15756,7 +15774,7 @@
         <v>2.67</v>
       </c>
       <c r="AP72">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AQ72">
         <v>2</v>
@@ -15884,7 +15902,7 @@
         <v>82</v>
       </c>
       <c r="P73" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="Q73">
         <v>3</v>
@@ -15965,7 +15983,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ73">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AR73">
         <v>1.33</v>
@@ -16090,7 +16108,7 @@
         <v>130</v>
       </c>
       <c r="P74" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="Q74">
         <v>5</v>
@@ -16296,7 +16314,7 @@
         <v>131</v>
       </c>
       <c r="P75" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="Q75">
         <v>2.88</v>
@@ -16583,7 +16601,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ76">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="AR76">
         <v>1.63</v>
@@ -16708,7 +16726,7 @@
         <v>133</v>
       </c>
       <c r="P77" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="Q77">
         <v>3</v>
@@ -17120,7 +17138,7 @@
         <v>134</v>
       </c>
       <c r="P79" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="Q79">
         <v>4.33</v>
@@ -17326,7 +17344,7 @@
         <v>82</v>
       </c>
       <c r="P80" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="Q80">
         <v>3.6</v>
@@ -17532,7 +17550,7 @@
         <v>82</v>
       </c>
       <c r="P81" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="Q81">
         <v>3.5</v>
@@ -17816,7 +17834,7 @@
         <v>1</v>
       </c>
       <c r="AP82">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AQ82">
         <v>1.33</v>
@@ -17944,7 +17962,7 @@
         <v>136</v>
       </c>
       <c r="P83" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="Q83">
         <v>4.33</v>
@@ -18150,7 +18168,7 @@
         <v>137</v>
       </c>
       <c r="P84" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="Q84">
         <v>2.4</v>
@@ -18562,7 +18580,7 @@
         <v>82</v>
       </c>
       <c r="P86" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="Q86">
         <v>5</v>
@@ -18640,7 +18658,7 @@
         <v>1</v>
       </c>
       <c r="AP86">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AQ86">
         <v>1.6</v>
@@ -19180,7 +19198,7 @@
         <v>82</v>
       </c>
       <c r="P89" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="Q89">
         <v>3.4</v>
@@ -19261,7 +19279,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ89">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AR89">
         <v>1.57</v>
@@ -19386,7 +19404,7 @@
         <v>139</v>
       </c>
       <c r="P90" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="Q90">
         <v>2.3</v>
@@ -19464,10 +19482,10 @@
         <v>0.29</v>
       </c>
       <c r="AP90">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AQ90">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="AR90">
         <v>1.6</v>
@@ -19592,7 +19610,7 @@
         <v>140</v>
       </c>
       <c r="P91" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="Q91">
         <v>2.55</v>
@@ -20004,7 +20022,7 @@
         <v>82</v>
       </c>
       <c r="P93" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="Q93">
         <v>2.88</v>
@@ -20085,7 +20103,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ93">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AR93">
         <v>1.57</v>
@@ -20210,7 +20228,7 @@
         <v>82</v>
       </c>
       <c r="P94" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="Q94">
         <v>2.8</v>
@@ -20416,7 +20434,7 @@
         <v>142</v>
       </c>
       <c r="P95" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="Q95">
         <v>2.62</v>
@@ -20497,7 +20515,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ95">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AR95">
         <v>1.37</v>
@@ -20622,7 +20640,7 @@
         <v>82</v>
       </c>
       <c r="P96" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="Q96">
         <v>4</v>
@@ -20700,7 +20718,7 @@
         <v>2.29</v>
       </c>
       <c r="AP96">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AQ96">
         <v>2.44</v>
@@ -20828,7 +20846,7 @@
         <v>82</v>
       </c>
       <c r="P97" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="Q97">
         <v>3.1</v>
@@ -21034,7 +21052,7 @@
         <v>125</v>
       </c>
       <c r="P98" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="Q98">
         <v>2.75</v>
@@ -21240,7 +21258,7 @@
         <v>143</v>
       </c>
       <c r="P99" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="Q99">
         <v>3.4</v>
@@ -21446,7 +21464,7 @@
         <v>134</v>
       </c>
       <c r="P100" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="Q100">
         <v>3.3</v>
@@ -21652,7 +21670,7 @@
         <v>144</v>
       </c>
       <c r="P101" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="Q101">
         <v>3</v>
@@ -21730,7 +21748,7 @@
         <v>1.67</v>
       </c>
       <c r="AP101">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AQ101">
         <v>1.5</v>
@@ -21858,7 +21876,7 @@
         <v>145</v>
       </c>
       <c r="P102" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="Q102">
         <v>2.3</v>
@@ -21936,7 +21954,7 @@
         <v>0.75</v>
       </c>
       <c r="AP102">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AQ102">
         <v>1</v>
@@ -22064,7 +22082,7 @@
         <v>146</v>
       </c>
       <c r="P103" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="Q103">
         <v>2.1</v>
@@ -22145,7 +22163,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ103">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="AR103">
         <v>1.74</v>
@@ -22270,7 +22288,7 @@
         <v>147</v>
       </c>
       <c r="P104" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="Q104">
         <v>2.55</v>
@@ -22351,7 +22369,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ104">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AR104">
         <v>1.62</v>
@@ -22554,7 +22572,7 @@
         <v>1.29</v>
       </c>
       <c r="AP105">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AQ105">
         <v>1.25</v>
@@ -22682,7 +22700,7 @@
         <v>82</v>
       </c>
       <c r="P106" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="Q106">
         <v>4.5</v>
@@ -22888,7 +22906,7 @@
         <v>149</v>
       </c>
       <c r="P107" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="Q107">
         <v>4.33</v>
@@ -23175,7 +23193,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ108">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AR108">
         <v>1.74</v>
@@ -23300,7 +23318,7 @@
         <v>151</v>
       </c>
       <c r="P109" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="Q109">
         <v>3</v>
@@ -23506,7 +23524,7 @@
         <v>152</v>
       </c>
       <c r="P110" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="Q110">
         <v>2.5</v>
@@ -23663,6 +23681,624 @@
       </c>
       <c r="BP110">
         <v>1.28</v>
+      </c>
+    </row>
+    <row r="111" spans="1:68">
+      <c r="A111" s="1">
+        <v>110</v>
+      </c>
+      <c r="B111">
+        <v>7806868</v>
+      </c>
+      <c r="C111" t="s">
+        <v>68</v>
+      </c>
+      <c r="D111" t="s">
+        <v>69</v>
+      </c>
+      <c r="E111" s="2">
+        <v>45825.3125</v>
+      </c>
+      <c r="F111">
+        <v>19</v>
+      </c>
+      <c r="G111" t="s">
+        <v>75</v>
+      </c>
+      <c r="H111" t="s">
+        <v>70</v>
+      </c>
+      <c r="I111">
+        <v>0</v>
+      </c>
+      <c r="J111">
+        <v>1</v>
+      </c>
+      <c r="K111">
+        <v>1</v>
+      </c>
+      <c r="L111">
+        <v>1</v>
+      </c>
+      <c r="M111">
+        <v>1</v>
+      </c>
+      <c r="N111">
+        <v>2</v>
+      </c>
+      <c r="O111" t="s">
+        <v>153</v>
+      </c>
+      <c r="P111" t="s">
+        <v>212</v>
+      </c>
+      <c r="Q111">
+        <v>4.33</v>
+      </c>
+      <c r="R111">
+        <v>2.25</v>
+      </c>
+      <c r="S111">
+        <v>2.5</v>
+      </c>
+      <c r="T111">
+        <v>1.36</v>
+      </c>
+      <c r="U111">
+        <v>3</v>
+      </c>
+      <c r="V111">
+        <v>2.63</v>
+      </c>
+      <c r="W111">
+        <v>1.44</v>
+      </c>
+      <c r="X111">
+        <v>7</v>
+      </c>
+      <c r="Y111">
+        <v>1.1</v>
+      </c>
+      <c r="Z111">
+        <v>3.53</v>
+      </c>
+      <c r="AA111">
+        <v>3.25</v>
+      </c>
+      <c r="AB111">
+        <v>1.89</v>
+      </c>
+      <c r="AC111">
+        <v>1.05</v>
+      </c>
+      <c r="AD111">
+        <v>9.5</v>
+      </c>
+      <c r="AE111">
+        <v>1.28</v>
+      </c>
+      <c r="AF111">
+        <v>3.55</v>
+      </c>
+      <c r="AG111">
+        <v>1.86</v>
+      </c>
+      <c r="AH111">
+        <v>1.84</v>
+      </c>
+      <c r="AI111">
+        <v>1.73</v>
+      </c>
+      <c r="AJ111">
+        <v>2</v>
+      </c>
+      <c r="AK111">
+        <v>1.77</v>
+      </c>
+      <c r="AL111">
+        <v>1.25</v>
+      </c>
+      <c r="AM111">
+        <v>1.28</v>
+      </c>
+      <c r="AN111">
+        <v>1.11</v>
+      </c>
+      <c r="AO111">
+        <v>1.33</v>
+      </c>
+      <c r="AP111">
+        <v>1.1</v>
+      </c>
+      <c r="AQ111">
+        <v>1.3</v>
+      </c>
+      <c r="AR111">
+        <v>1.83</v>
+      </c>
+      <c r="AS111">
+        <v>1.48</v>
+      </c>
+      <c r="AT111">
+        <v>3.31</v>
+      </c>
+      <c r="AU111">
+        <v>5</v>
+      </c>
+      <c r="AV111">
+        <v>6</v>
+      </c>
+      <c r="AW111">
+        <v>9</v>
+      </c>
+      <c r="AX111">
+        <v>2</v>
+      </c>
+      <c r="AY111">
+        <v>14</v>
+      </c>
+      <c r="AZ111">
+        <v>8</v>
+      </c>
+      <c r="BA111">
+        <v>2</v>
+      </c>
+      <c r="BB111">
+        <v>4</v>
+      </c>
+      <c r="BC111">
+        <v>6</v>
+      </c>
+      <c r="BD111">
+        <v>2.18</v>
+      </c>
+      <c r="BE111">
+        <v>6.4</v>
+      </c>
+      <c r="BF111">
+        <v>1.84</v>
+      </c>
+      <c r="BG111">
+        <v>1.4</v>
+      </c>
+      <c r="BH111">
+        <v>2.7</v>
+      </c>
+      <c r="BI111">
+        <v>1.67</v>
+      </c>
+      <c r="BJ111">
+        <v>2.07</v>
+      </c>
+      <c r="BK111">
+        <v>2.07</v>
+      </c>
+      <c r="BL111">
+        <v>1.68</v>
+      </c>
+      <c r="BM111">
+        <v>2.65</v>
+      </c>
+      <c r="BN111">
+        <v>1.42</v>
+      </c>
+      <c r="BO111">
+        <v>3.45</v>
+      </c>
+      <c r="BP111">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="112" spans="1:68">
+      <c r="A112" s="1">
+        <v>111</v>
+      </c>
+      <c r="B112">
+        <v>7806866</v>
+      </c>
+      <c r="C112" t="s">
+        <v>68</v>
+      </c>
+      <c r="D112" t="s">
+        <v>69</v>
+      </c>
+      <c r="E112" s="2">
+        <v>45825.3125</v>
+      </c>
+      <c r="F112">
+        <v>19</v>
+      </c>
+      <c r="G112" t="s">
+        <v>76</v>
+      </c>
+      <c r="H112" t="s">
+        <v>78</v>
+      </c>
+      <c r="I112">
+        <v>0</v>
+      </c>
+      <c r="J112">
+        <v>1</v>
+      </c>
+      <c r="K112">
+        <v>1</v>
+      </c>
+      <c r="L112">
+        <v>1</v>
+      </c>
+      <c r="M112">
+        <v>1</v>
+      </c>
+      <c r="N112">
+        <v>2</v>
+      </c>
+      <c r="O112" t="s">
+        <v>154</v>
+      </c>
+      <c r="P112" t="s">
+        <v>213</v>
+      </c>
+      <c r="Q112">
+        <v>2.25</v>
+      </c>
+      <c r="R112">
+        <v>2.05</v>
+      </c>
+      <c r="S112">
+        <v>5.25</v>
+      </c>
+      <c r="T112">
+        <v>1.48</v>
+      </c>
+      <c r="U112">
+        <v>2.5</v>
+      </c>
+      <c r="V112">
+        <v>3.2</v>
+      </c>
+      <c r="W112">
+        <v>1.3</v>
+      </c>
+      <c r="X112">
+        <v>7.8</v>
+      </c>
+      <c r="Y112">
+        <v>1.02</v>
+      </c>
+      <c r="Z112">
+        <v>1.6</v>
+      </c>
+      <c r="AA112">
+        <v>3.32</v>
+      </c>
+      <c r="AB112">
+        <v>5.2</v>
+      </c>
+      <c r="AC112">
+        <v>1.08</v>
+      </c>
+      <c r="AD112">
+        <v>7.5</v>
+      </c>
+      <c r="AE112">
+        <v>1.42</v>
+      </c>
+      <c r="AF112">
+        <v>2.8</v>
+      </c>
+      <c r="AG112">
+        <v>2</v>
+      </c>
+      <c r="AH112">
+        <v>1.72</v>
+      </c>
+      <c r="AI112">
+        <v>2.1</v>
+      </c>
+      <c r="AJ112">
+        <v>1.62</v>
+      </c>
+      <c r="AK112">
+        <v>1.14</v>
+      </c>
+      <c r="AL112">
+        <v>1.25</v>
+      </c>
+      <c r="AM112">
+        <v>2.15</v>
+      </c>
+      <c r="AN112">
+        <v>1.13</v>
+      </c>
+      <c r="AO112">
+        <v>1.33</v>
+      </c>
+      <c r="AP112">
+        <v>1.11</v>
+      </c>
+      <c r="AQ112">
+        <v>1.3</v>
+      </c>
+      <c r="AR112">
+        <v>1.66</v>
+      </c>
+      <c r="AS112">
+        <v>0.92</v>
+      </c>
+      <c r="AT112">
+        <v>2.58</v>
+      </c>
+      <c r="AU112">
+        <v>4</v>
+      </c>
+      <c r="AV112">
+        <v>6</v>
+      </c>
+      <c r="AW112">
+        <v>10</v>
+      </c>
+      <c r="AX112">
+        <v>6</v>
+      </c>
+      <c r="AY112">
+        <v>14</v>
+      </c>
+      <c r="AZ112">
+        <v>12</v>
+      </c>
+      <c r="BA112">
+        <v>5</v>
+      </c>
+      <c r="BB112">
+        <v>3</v>
+      </c>
+      <c r="BC112">
+        <v>8</v>
+      </c>
+      <c r="BD112">
+        <v>1.54</v>
+      </c>
+      <c r="BE112">
+        <v>6.5</v>
+      </c>
+      <c r="BF112">
+        <v>2.8</v>
+      </c>
+      <c r="BG112">
+        <v>1.47</v>
+      </c>
+      <c r="BH112">
+        <v>2.48</v>
+      </c>
+      <c r="BI112">
+        <v>1.78</v>
+      </c>
+      <c r="BJ112">
+        <v>1.91</v>
+      </c>
+      <c r="BK112">
+        <v>2.23</v>
+      </c>
+      <c r="BL112">
+        <v>1.56</v>
+      </c>
+      <c r="BM112">
+        <v>2.9</v>
+      </c>
+      <c r="BN112">
+        <v>1.34</v>
+      </c>
+      <c r="BO112">
+        <v>3.9</v>
+      </c>
+      <c r="BP112">
+        <v>1.21</v>
+      </c>
+    </row>
+    <row r="113" spans="1:68">
+      <c r="A113" s="1">
+        <v>112</v>
+      </c>
+      <c r="B113">
+        <v>7806867</v>
+      </c>
+      <c r="C113" t="s">
+        <v>68</v>
+      </c>
+      <c r="D113" t="s">
+        <v>69</v>
+      </c>
+      <c r="E113" s="2">
+        <v>45825.3125</v>
+      </c>
+      <c r="F113">
+        <v>19</v>
+      </c>
+      <c r="G113" t="s">
+        <v>74</v>
+      </c>
+      <c r="H113" t="s">
+        <v>79</v>
+      </c>
+      <c r="I113">
+        <v>0</v>
+      </c>
+      <c r="J113">
+        <v>2</v>
+      </c>
+      <c r="K113">
+        <v>2</v>
+      </c>
+      <c r="L113">
+        <v>2</v>
+      </c>
+      <c r="M113">
+        <v>2</v>
+      </c>
+      <c r="N113">
+        <v>4</v>
+      </c>
+      <c r="O113" t="s">
+        <v>155</v>
+      </c>
+      <c r="P113" t="s">
+        <v>214</v>
+      </c>
+      <c r="Q113">
+        <v>2.2</v>
+      </c>
+      <c r="R113">
+        <v>2.25</v>
+      </c>
+      <c r="S113">
+        <v>5.5</v>
+      </c>
+      <c r="T113">
+        <v>1.36</v>
+      </c>
+      <c r="U113">
+        <v>3</v>
+      </c>
+      <c r="V113">
+        <v>2.75</v>
+      </c>
+      <c r="W113">
+        <v>1.4</v>
+      </c>
+      <c r="X113">
+        <v>7</v>
+      </c>
+      <c r="Y113">
+        <v>1.1</v>
+      </c>
+      <c r="Z113">
+        <v>1.6</v>
+      </c>
+      <c r="AA113">
+        <v>3.55</v>
+      </c>
+      <c r="AB113">
+        <v>4.7</v>
+      </c>
+      <c r="AC113">
+        <v>1.05</v>
+      </c>
+      <c r="AD113">
+        <v>9</v>
+      </c>
+      <c r="AE113">
+        <v>1.3</v>
+      </c>
+      <c r="AF113">
+        <v>3.45</v>
+      </c>
+      <c r="AG113">
+        <v>1.87</v>
+      </c>
+      <c r="AH113">
+        <v>1.83</v>
+      </c>
+      <c r="AI113">
+        <v>1.83</v>
+      </c>
+      <c r="AJ113">
+        <v>1.83</v>
+      </c>
+      <c r="AK113">
+        <v>1.15</v>
+      </c>
+      <c r="AL113">
+        <v>1.2</v>
+      </c>
+      <c r="AM113">
+        <v>2.2</v>
+      </c>
+      <c r="AN113">
+        <v>1.78</v>
+      </c>
+      <c r="AO113">
+        <v>0.44</v>
+      </c>
+      <c r="AP113">
+        <v>1.7</v>
+      </c>
+      <c r="AQ113">
+        <v>0.5</v>
+      </c>
+      <c r="AR113">
+        <v>1.6</v>
+      </c>
+      <c r="AS113">
+        <v>1.27</v>
+      </c>
+      <c r="AT113">
+        <v>2.87</v>
+      </c>
+      <c r="AU113">
+        <v>6</v>
+      </c>
+      <c r="AV113">
+        <v>6</v>
+      </c>
+      <c r="AW113">
+        <v>5</v>
+      </c>
+      <c r="AX113">
+        <v>5</v>
+      </c>
+      <c r="AY113">
+        <v>11</v>
+      </c>
+      <c r="AZ113">
+        <v>11</v>
+      </c>
+      <c r="BA113">
+        <v>8</v>
+      </c>
+      <c r="BB113">
+        <v>1</v>
+      </c>
+      <c r="BC113">
+        <v>9</v>
+      </c>
+      <c r="BD113">
+        <v>1.49</v>
+      </c>
+      <c r="BE113">
+        <v>6.75</v>
+      </c>
+      <c r="BF113">
+        <v>2.95</v>
+      </c>
+      <c r="BG113">
+        <v>1.45</v>
+      </c>
+      <c r="BH113">
+        <v>2.55</v>
+      </c>
+      <c r="BI113">
+        <v>1.74</v>
+      </c>
+      <c r="BJ113">
+        <v>1.95</v>
+      </c>
+      <c r="BK113">
+        <v>2.18</v>
+      </c>
+      <c r="BL113">
+        <v>1.58</v>
+      </c>
+      <c r="BM113">
+        <v>2.8</v>
+      </c>
+      <c r="BN113">
+        <v>1.36</v>
+      </c>
+      <c r="BO113">
+        <v>3.8</v>
+      </c>
+      <c r="BP113">
+        <v>1.22</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/South Korea K League 1_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/South Korea K League 1_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="740" uniqueCount="215">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="752" uniqueCount="216">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -660,6 +660,9 @@
   <si>
     <t>['5', '31']</t>
   </si>
+  <si>
+    <t>['46']</t>
+  </si>
 </sst>
 </file>
 
@@ -1020,7 +1023,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP113"/>
+  <dimension ref="A1:BP115"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1560,7 +1563,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AQ3">
         <v>1.6</v>
@@ -2181,7 +2184,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ6">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2590,10 +2593,10 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AQ8">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AR8">
         <v>1.38</v>
@@ -3208,7 +3211,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AQ11">
         <v>1.5</v>
@@ -3417,7 +3420,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ12">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AR12">
         <v>1.8</v>
@@ -4444,7 +4447,7 @@
         <v>0.5</v>
       </c>
       <c r="AP17">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AQ17">
         <v>0.5</v>
@@ -4859,7 +4862,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ19">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AR19">
         <v>1.46</v>
@@ -5477,7 +5480,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ22">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AR22">
         <v>0</v>
@@ -6092,7 +6095,7 @@
         <v>3</v>
       </c>
       <c r="AP25">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AQ25">
         <v>2</v>
@@ -6919,7 +6922,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ29">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AR29">
         <v>0</v>
@@ -7946,10 +7949,10 @@
         <v>1</v>
       </c>
       <c r="AP34">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AQ34">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AR34">
         <v>1.58</v>
@@ -8152,7 +8155,7 @@
         <v>0.33</v>
       </c>
       <c r="AP35">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AQ35">
         <v>0.5</v>
@@ -9388,7 +9391,7 @@
         <v>1.5</v>
       </c>
       <c r="AP41">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AQ41">
         <v>2.44</v>
@@ -10421,7 +10424,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ46">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AR46">
         <v>1.44</v>
@@ -11039,7 +11042,7 @@
         <v>1</v>
       </c>
       <c r="AQ49">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AR49">
         <v>1.43</v>
@@ -12275,7 +12278,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ55">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AR55">
         <v>1.28</v>
@@ -12478,7 +12481,7 @@
         <v>1.25</v>
       </c>
       <c r="AP56">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AQ56">
         <v>1.3</v>
@@ -13920,7 +13923,7 @@
         <v>1.2</v>
       </c>
       <c r="AP63">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AQ63">
         <v>1.3</v>
@@ -14129,7 +14132,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ64">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AR64">
         <v>2.07</v>
@@ -14335,7 +14338,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ65">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AR65">
         <v>1.65</v>
@@ -14538,7 +14541,7 @@
         <v>1.2</v>
       </c>
       <c r="AP66">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AQ66">
         <v>1.33</v>
@@ -15571,7 +15574,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ71">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AR71">
         <v>1.66</v>
@@ -15980,7 +15983,7 @@
         <v>1</v>
       </c>
       <c r="AP73">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AQ73">
         <v>1.3</v>
@@ -17010,7 +17013,7 @@
         <v>1</v>
       </c>
       <c r="AP78">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AQ78">
         <v>1.6</v>
@@ -17216,7 +17219,7 @@
         <v>1.67</v>
       </c>
       <c r="AP79">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AQ79">
         <v>1.5</v>
@@ -17425,7 +17428,7 @@
         <v>1</v>
       </c>
       <c r="AQ80">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AR80">
         <v>1.51</v>
@@ -18455,7 +18458,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ85">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AR85">
         <v>1.61</v>
@@ -19070,7 +19073,7 @@
         <v>2.5</v>
       </c>
       <c r="AP88">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AQ88">
         <v>2.44</v>
@@ -19691,7 +19694,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ91">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AR91">
         <v>2.04</v>
@@ -19894,7 +19897,7 @@
         <v>0.29</v>
       </c>
       <c r="AP92">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AQ92">
         <v>0.22</v>
@@ -20512,7 +20515,7 @@
         <v>1.29</v>
       </c>
       <c r="AP95">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AQ95">
         <v>1.3</v>
@@ -22575,7 +22578,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ105">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AR105">
         <v>1.83</v>
@@ -23602,7 +23605,7 @@
         <v>0.25</v>
       </c>
       <c r="AP110">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AQ110">
         <v>0.22</v>
@@ -24299,6 +24302,418 @@
       </c>
       <c r="BP113">
         <v>1.22</v>
+      </c>
+    </row>
+    <row r="114" spans="1:68">
+      <c r="A114" s="1">
+        <v>113</v>
+      </c>
+      <c r="B114">
+        <v>7806869</v>
+      </c>
+      <c r="C114" t="s">
+        <v>68</v>
+      </c>
+      <c r="D114" t="s">
+        <v>69</v>
+      </c>
+      <c r="E114" s="2">
+        <v>45826.3125</v>
+      </c>
+      <c r="F114">
+        <v>19</v>
+      </c>
+      <c r="G114" t="s">
+        <v>71</v>
+      </c>
+      <c r="H114" t="s">
+        <v>72</v>
+      </c>
+      <c r="I114">
+        <v>0</v>
+      </c>
+      <c r="J114">
+        <v>0</v>
+      </c>
+      <c r="K114">
+        <v>0</v>
+      </c>
+      <c r="L114">
+        <v>0</v>
+      </c>
+      <c r="M114">
+        <v>1</v>
+      </c>
+      <c r="N114">
+        <v>1</v>
+      </c>
+      <c r="O114" t="s">
+        <v>82</v>
+      </c>
+      <c r="P114" t="s">
+        <v>215</v>
+      </c>
+      <c r="Q114">
+        <v>3.4</v>
+      </c>
+      <c r="R114">
+        <v>2</v>
+      </c>
+      <c r="S114">
+        <v>3.5</v>
+      </c>
+      <c r="T114">
+        <v>1.5</v>
+      </c>
+      <c r="U114">
+        <v>2.5</v>
+      </c>
+      <c r="V114">
+        <v>3.4</v>
+      </c>
+      <c r="W114">
+        <v>1.3</v>
+      </c>
+      <c r="X114">
+        <v>10</v>
+      </c>
+      <c r="Y114">
+        <v>1.06</v>
+      </c>
+      <c r="Z114">
+        <v>2.71</v>
+      </c>
+      <c r="AA114">
+        <v>2.82</v>
+      </c>
+      <c r="AB114">
+        <v>2.52</v>
+      </c>
+      <c r="AC114">
+        <v>1.09</v>
+      </c>
+      <c r="AD114">
+        <v>7</v>
+      </c>
+      <c r="AE114">
+        <v>1.48</v>
+      </c>
+      <c r="AF114">
+        <v>2.65</v>
+      </c>
+      <c r="AG114">
+        <v>2.29</v>
+      </c>
+      <c r="AH114">
+        <v>1.55</v>
+      </c>
+      <c r="AI114">
+        <v>2</v>
+      </c>
+      <c r="AJ114">
+        <v>1.73</v>
+      </c>
+      <c r="AK114">
+        <v>1.42</v>
+      </c>
+      <c r="AL114">
+        <v>1.3</v>
+      </c>
+      <c r="AM114">
+        <v>1.45</v>
+      </c>
+      <c r="AN114">
+        <v>1.44</v>
+      </c>
+      <c r="AO114">
+        <v>1.25</v>
+      </c>
+      <c r="AP114">
+        <v>1.3</v>
+      </c>
+      <c r="AQ114">
+        <v>1.44</v>
+      </c>
+      <c r="AR114">
+        <v>1.5</v>
+      </c>
+      <c r="AS114">
+        <v>1.07</v>
+      </c>
+      <c r="AT114">
+        <v>2.57</v>
+      </c>
+      <c r="AU114">
+        <v>5</v>
+      </c>
+      <c r="AV114">
+        <v>5</v>
+      </c>
+      <c r="AW114">
+        <v>7</v>
+      </c>
+      <c r="AX114">
+        <v>5</v>
+      </c>
+      <c r="AY114">
+        <v>12</v>
+      </c>
+      <c r="AZ114">
+        <v>10</v>
+      </c>
+      <c r="BA114">
+        <v>2</v>
+      </c>
+      <c r="BB114">
+        <v>5</v>
+      </c>
+      <c r="BC114">
+        <v>7</v>
+      </c>
+      <c r="BD114">
+        <v>2.26</v>
+      </c>
+      <c r="BE114">
+        <v>6.2</v>
+      </c>
+      <c r="BF114">
+        <v>2.04</v>
+      </c>
+      <c r="BG114">
+        <v>1.41</v>
+      </c>
+      <c r="BH114">
+        <v>2.6</v>
+      </c>
+      <c r="BI114">
+        <v>1.76</v>
+      </c>
+      <c r="BJ114">
+        <v>1.95</v>
+      </c>
+      <c r="BK114">
+        <v>2.27</v>
+      </c>
+      <c r="BL114">
+        <v>1.53</v>
+      </c>
+      <c r="BM114">
+        <v>3.05</v>
+      </c>
+      <c r="BN114">
+        <v>1.28</v>
+      </c>
+      <c r="BO114">
+        <v>4.35</v>
+      </c>
+      <c r="BP114">
+        <v>1.14</v>
+      </c>
+    </row>
+    <row r="115" spans="1:68">
+      <c r="A115" s="1">
+        <v>114</v>
+      </c>
+      <c r="B115">
+        <v>7806870</v>
+      </c>
+      <c r="C115" t="s">
+        <v>68</v>
+      </c>
+      <c r="D115" t="s">
+        <v>69</v>
+      </c>
+      <c r="E115" s="2">
+        <v>45826.3125</v>
+      </c>
+      <c r="F115">
+        <v>19</v>
+      </c>
+      <c r="G115" t="s">
+        <v>77</v>
+      </c>
+      <c r="H115" t="s">
+        <v>81</v>
+      </c>
+      <c r="I115">
+        <v>0</v>
+      </c>
+      <c r="J115">
+        <v>0</v>
+      </c>
+      <c r="K115">
+        <v>0</v>
+      </c>
+      <c r="L115">
+        <v>0</v>
+      </c>
+      <c r="M115">
+        <v>0</v>
+      </c>
+      <c r="N115">
+        <v>0</v>
+      </c>
+      <c r="O115" t="s">
+        <v>82</v>
+      </c>
+      <c r="P115" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q115">
+        <v>3.6</v>
+      </c>
+      <c r="R115">
+        <v>2.3</v>
+      </c>
+      <c r="S115">
+        <v>2.75</v>
+      </c>
+      <c r="T115">
+        <v>1.33</v>
+      </c>
+      <c r="U115">
+        <v>3.25</v>
+      </c>
+      <c r="V115">
+        <v>2.5</v>
+      </c>
+      <c r="W115">
+        <v>1.5</v>
+      </c>
+      <c r="X115">
+        <v>6</v>
+      </c>
+      <c r="Y115">
+        <v>1.13</v>
+      </c>
+      <c r="Z115">
+        <v>3.06</v>
+      </c>
+      <c r="AA115">
+        <v>3.31</v>
+      </c>
+      <c r="AB115">
+        <v>2.04</v>
+      </c>
+      <c r="AC115">
+        <v>1.04</v>
+      </c>
+      <c r="AD115">
+        <v>10</v>
+      </c>
+      <c r="AE115">
+        <v>1.25</v>
+      </c>
+      <c r="AF115">
+        <v>3.95</v>
+      </c>
+      <c r="AG115">
+        <v>1.87</v>
+      </c>
+      <c r="AH115">
+        <v>1.83</v>
+      </c>
+      <c r="AI115">
+        <v>1.62</v>
+      </c>
+      <c r="AJ115">
+        <v>2.2</v>
+      </c>
+      <c r="AK115">
+        <v>1.67</v>
+      </c>
+      <c r="AL115">
+        <v>1.22</v>
+      </c>
+      <c r="AM115">
+        <v>1.33</v>
+      </c>
+      <c r="AN115">
+        <v>1.56</v>
+      </c>
+      <c r="AO115">
+        <v>1.44</v>
+      </c>
+      <c r="AP115">
+        <v>1.5</v>
+      </c>
+      <c r="AQ115">
+        <v>1.4</v>
+      </c>
+      <c r="AR115">
+        <v>1.43</v>
+      </c>
+      <c r="AS115">
+        <v>1.7</v>
+      </c>
+      <c r="AT115">
+        <v>3.13</v>
+      </c>
+      <c r="AU115">
+        <v>2</v>
+      </c>
+      <c r="AV115">
+        <v>6</v>
+      </c>
+      <c r="AW115">
+        <v>8</v>
+      </c>
+      <c r="AX115">
+        <v>8</v>
+      </c>
+      <c r="AY115">
+        <v>10</v>
+      </c>
+      <c r="AZ115">
+        <v>14</v>
+      </c>
+      <c r="BA115">
+        <v>7</v>
+      </c>
+      <c r="BB115">
+        <v>5</v>
+      </c>
+      <c r="BC115">
+        <v>12</v>
+      </c>
+      <c r="BD115">
+        <v>2.86</v>
+      </c>
+      <c r="BE115">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BF115">
+        <v>1.61</v>
+      </c>
+      <c r="BG115">
+        <v>1.48</v>
+      </c>
+      <c r="BH115">
+        <v>2.4</v>
+      </c>
+      <c r="BI115">
+        <v>1.87</v>
+      </c>
+      <c r="BJ115">
+        <v>1.83</v>
+      </c>
+      <c r="BK115">
+        <v>2.45</v>
+      </c>
+      <c r="BL115">
+        <v>1.46</v>
+      </c>
+      <c r="BM115">
+        <v>3.34</v>
+      </c>
+      <c r="BN115">
+        <v>1.24</v>
+      </c>
+      <c r="BO115">
+        <v>4.85</v>
+      </c>
+      <c r="BP115">
+        <v>1.11</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/South Korea K League 1_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/South Korea K League 1_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="752" uniqueCount="216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="770" uniqueCount="220">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -484,6 +484,15 @@
     <t>['52', '72']</t>
   </si>
   <si>
+    <t>['45', '74', '78']</t>
+  </si>
+  <si>
+    <t>['63', '9001']</t>
+  </si>
+  <si>
+    <t>['4502']</t>
+  </si>
+  <si>
     <t>['32', '87', '90']</t>
   </si>
   <si>
@@ -662,6 +671,9 @@
   </si>
   <si>
     <t>['46']</t>
+  </si>
+  <si>
+    <t>['9008']</t>
   </si>
 </sst>
 </file>
@@ -1023,7 +1035,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP115"/>
+  <dimension ref="A1:BP118"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1279,7 +1291,7 @@
         <v>82</v>
       </c>
       <c r="P2" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="Q2">
         <v>2.75</v>
@@ -1357,7 +1369,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AQ2">
         <v>2</v>
@@ -1566,7 +1578,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ3">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -1897,7 +1909,7 @@
         <v>82</v>
       </c>
       <c r="P5" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="Q5">
         <v>2.1</v>
@@ -2181,7 +2193,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AQ6">
         <v>1.4</v>
@@ -2309,7 +2321,7 @@
         <v>85</v>
       </c>
       <c r="P7" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="Q7">
         <v>3.5</v>
@@ -2515,7 +2527,7 @@
         <v>86</v>
       </c>
       <c r="P8" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="Q8">
         <v>3.4</v>
@@ -2721,7 +2733,7 @@
         <v>87</v>
       </c>
       <c r="P9" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="Q9">
         <v>3.35</v>
@@ -3133,7 +3145,7 @@
         <v>82</v>
       </c>
       <c r="P11" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="Q11">
         <v>3.45</v>
@@ -3339,7 +3351,7 @@
         <v>89</v>
       </c>
       <c r="P12" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="Q12">
         <v>2.75</v>
@@ -3417,7 +3429,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AQ12">
         <v>1.44</v>
@@ -3545,7 +3557,7 @@
         <v>90</v>
       </c>
       <c r="P13" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="Q13">
         <v>2.95</v>
@@ -3623,7 +3635,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AQ13">
         <v>1.3</v>
@@ -4035,10 +4047,10 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AQ15">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AR15">
         <v>1.87</v>
@@ -4653,10 +4665,10 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AQ18">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AR18">
         <v>2.13</v>
@@ -5068,7 +5080,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ20">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AR20">
         <v>0</v>
@@ -5193,7 +5205,7 @@
         <v>94</v>
       </c>
       <c r="P21" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="Q21">
         <v>3.1</v>
@@ -5399,7 +5411,7 @@
         <v>95</v>
       </c>
       <c r="P22" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="Q22">
         <v>3.6</v>
@@ -5686,7 +5698,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ23">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AR23">
         <v>2.19</v>
@@ -5889,7 +5901,7 @@
         <v>0</v>
       </c>
       <c r="AP24">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AQ24">
         <v>1.3</v>
@@ -6017,7 +6029,7 @@
         <v>97</v>
       </c>
       <c r="P25" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="Q25">
         <v>4</v>
@@ -6223,7 +6235,7 @@
         <v>82</v>
       </c>
       <c r="P26" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="Q26">
         <v>3.6</v>
@@ -6301,10 +6313,10 @@
         <v>0.5</v>
       </c>
       <c r="AP26">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AQ26">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AR26">
         <v>1.64</v>
@@ -6429,7 +6441,7 @@
         <v>82</v>
       </c>
       <c r="P27" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="Q27">
         <v>2.75</v>
@@ -6635,7 +6647,7 @@
         <v>98</v>
       </c>
       <c r="P28" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="Q28">
         <v>3.75</v>
@@ -7047,7 +7059,7 @@
         <v>99</v>
       </c>
       <c r="P30" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="Q30">
         <v>2.63</v>
@@ -7125,7 +7137,7 @@
         <v>0</v>
       </c>
       <c r="AP30">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AQ30">
         <v>1.3</v>
@@ -7253,7 +7265,7 @@
         <v>100</v>
       </c>
       <c r="P31" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="Q31">
         <v>3.1</v>
@@ -7459,7 +7471,7 @@
         <v>101</v>
       </c>
       <c r="P32" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="Q32">
         <v>2.5</v>
@@ -7540,7 +7552,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ32">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AR32">
         <v>0.86</v>
@@ -7743,7 +7755,7 @@
         <v>2</v>
       </c>
       <c r="AP33">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AQ33">
         <v>1.5</v>
@@ -7871,7 +7883,7 @@
         <v>103</v>
       </c>
       <c r="P34" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="Q34">
         <v>3.2</v>
@@ -8695,7 +8707,7 @@
         <v>106</v>
       </c>
       <c r="P38" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="Q38">
         <v>2.45</v>
@@ -8982,7 +8994,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ39">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AR39">
         <v>2.14</v>
@@ -9188,7 +9200,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ40">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AR40">
         <v>1.95</v>
@@ -9313,7 +9325,7 @@
         <v>82</v>
       </c>
       <c r="P41" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="Q41">
         <v>3.25</v>
@@ -9519,7 +9531,7 @@
         <v>98</v>
       </c>
       <c r="P42" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="Q42">
         <v>3.4</v>
@@ -10012,7 +10024,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ44">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AR44">
         <v>1.71</v>
@@ -10218,7 +10230,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ45">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AR45">
         <v>1.77</v>
@@ -10343,7 +10355,7 @@
         <v>111</v>
       </c>
       <c r="P46" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="Q46">
         <v>4.33</v>
@@ -10549,7 +10561,7 @@
         <v>112</v>
       </c>
       <c r="P47" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="Q47">
         <v>2.6</v>
@@ -10833,7 +10845,7 @@
         <v>1.5</v>
       </c>
       <c r="AP48">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AQ48">
         <v>1.33</v>
@@ -11039,7 +11051,7 @@
         <v>1</v>
       </c>
       <c r="AP49">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AQ49">
         <v>1.44</v>
@@ -11245,10 +11257,10 @@
         <v>0.33</v>
       </c>
       <c r="AP50">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AQ50">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AR50">
         <v>1.68</v>
@@ -11579,7 +11591,7 @@
         <v>116</v>
       </c>
       <c r="P52" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="Q52">
         <v>2.38</v>
@@ -11785,7 +11797,7 @@
         <v>117</v>
       </c>
       <c r="P53" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="Q53">
         <v>3.1</v>
@@ -11991,7 +12003,7 @@
         <v>82</v>
       </c>
       <c r="P54" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="Q54">
         <v>2.75</v>
@@ -12197,7 +12209,7 @@
         <v>118</v>
       </c>
       <c r="P55" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="Q55">
         <v>2.75</v>
@@ -12609,7 +12621,7 @@
         <v>120</v>
       </c>
       <c r="P57" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="Q57">
         <v>2.3</v>
@@ -12687,10 +12699,10 @@
         <v>0.25</v>
       </c>
       <c r="AP57">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AQ57">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AR57">
         <v>1.63</v>
@@ -12815,7 +12827,7 @@
         <v>82</v>
       </c>
       <c r="P58" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="Q58">
         <v>4.5</v>
@@ -13021,7 +13033,7 @@
         <v>121</v>
       </c>
       <c r="P59" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="Q59">
         <v>4</v>
@@ -13227,7 +13239,7 @@
         <v>122</v>
       </c>
       <c r="P60" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="Q60">
         <v>2.7</v>
@@ -13308,7 +13320,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ60">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AR60">
         <v>1.61</v>
@@ -13511,10 +13523,10 @@
         <v>1.25</v>
       </c>
       <c r="AP61">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AQ61">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AR61">
         <v>1.8</v>
@@ -14257,7 +14269,7 @@
         <v>105</v>
       </c>
       <c r="P65" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="Q65">
         <v>3.4</v>
@@ -14335,7 +14347,7 @@
         <v>1.4</v>
       </c>
       <c r="AP65">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AQ65">
         <v>1.4</v>
@@ -14463,7 +14475,7 @@
         <v>127</v>
       </c>
       <c r="P66" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="Q66">
         <v>2.5</v>
@@ -14750,7 +14762,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ67">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AR67">
         <v>2.01</v>
@@ -14875,7 +14887,7 @@
         <v>82</v>
       </c>
       <c r="P68" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="Q68">
         <v>3</v>
@@ -15159,7 +15171,7 @@
         <v>0.2</v>
       </c>
       <c r="AP69">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AQ69">
         <v>0.5</v>
@@ -15287,7 +15299,7 @@
         <v>116</v>
       </c>
       <c r="P70" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="Q70">
         <v>2.38</v>
@@ -15777,7 +15789,7 @@
         <v>2.67</v>
       </c>
       <c r="AP72">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AQ72">
         <v>2</v>
@@ -15905,7 +15917,7 @@
         <v>82</v>
       </c>
       <c r="P73" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="Q73">
         <v>3</v>
@@ -16111,7 +16123,7 @@
         <v>130</v>
       </c>
       <c r="P74" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="Q74">
         <v>5</v>
@@ -16192,7 +16204,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ74">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AR74">
         <v>1.59</v>
@@ -16317,7 +16329,7 @@
         <v>131</v>
       </c>
       <c r="P75" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="Q75">
         <v>2.88</v>
@@ -16398,7 +16410,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ75">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AR75">
         <v>1.55</v>
@@ -16601,7 +16613,7 @@
         <v>0.33</v>
       </c>
       <c r="AP76">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AQ76">
         <v>0.5</v>
@@ -16729,7 +16741,7 @@
         <v>133</v>
       </c>
       <c r="P77" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="Q77">
         <v>3</v>
@@ -16810,7 +16822,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ77">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AR77">
         <v>1.51</v>
@@ -17016,7 +17028,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ78">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AR78">
         <v>1.46</v>
@@ -17141,7 +17153,7 @@
         <v>134</v>
       </c>
       <c r="P79" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="Q79">
         <v>4.33</v>
@@ -17347,7 +17359,7 @@
         <v>82</v>
       </c>
       <c r="P80" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="Q80">
         <v>3.6</v>
@@ -17425,7 +17437,7 @@
         <v>1.43</v>
       </c>
       <c r="AP80">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AQ80">
         <v>1.4</v>
@@ -17553,7 +17565,7 @@
         <v>82</v>
       </c>
       <c r="P81" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="Q81">
         <v>3.5</v>
@@ -17837,7 +17849,7 @@
         <v>1</v>
       </c>
       <c r="AP82">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AQ82">
         <v>1.33</v>
@@ -17965,7 +17977,7 @@
         <v>136</v>
       </c>
       <c r="P83" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="Q83">
         <v>4.33</v>
@@ -18043,7 +18055,7 @@
         <v>1.86</v>
       </c>
       <c r="AP83">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AQ83">
         <v>1.5</v>
@@ -18171,7 +18183,7 @@
         <v>137</v>
       </c>
       <c r="P84" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="Q84">
         <v>2.4</v>
@@ -18252,7 +18264,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ84">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AR84">
         <v>1.76</v>
@@ -18455,7 +18467,7 @@
         <v>1</v>
       </c>
       <c r="AP85">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AQ85">
         <v>1.44</v>
@@ -18583,7 +18595,7 @@
         <v>82</v>
       </c>
       <c r="P86" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="Q86">
         <v>5</v>
@@ -18664,7 +18676,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ86">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AR86">
         <v>1.94</v>
@@ -19201,7 +19213,7 @@
         <v>82</v>
       </c>
       <c r="P89" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="Q89">
         <v>3.4</v>
@@ -19407,7 +19419,7 @@
         <v>139</v>
       </c>
       <c r="P90" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="Q90">
         <v>2.3</v>
@@ -19613,7 +19625,7 @@
         <v>140</v>
       </c>
       <c r="P91" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="Q91">
         <v>2.55</v>
@@ -19900,7 +19912,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ92">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AR92">
         <v>1.34</v>
@@ -20025,7 +20037,7 @@
         <v>82</v>
       </c>
       <c r="P93" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="Q93">
         <v>2.88</v>
@@ -20231,7 +20243,7 @@
         <v>82</v>
       </c>
       <c r="P94" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="Q94">
         <v>2.8</v>
@@ -20312,7 +20324,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ94">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AR94">
         <v>1.88</v>
@@ -20437,7 +20449,7 @@
         <v>142</v>
       </c>
       <c r="P95" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="Q95">
         <v>2.62</v>
@@ -20643,7 +20655,7 @@
         <v>82</v>
       </c>
       <c r="P96" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="Q96">
         <v>4</v>
@@ -20849,7 +20861,7 @@
         <v>82</v>
       </c>
       <c r="P97" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="Q97">
         <v>3.1</v>
@@ -20930,7 +20942,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ97">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AR97">
         <v>1.74</v>
@@ -21055,7 +21067,7 @@
         <v>125</v>
       </c>
       <c r="P98" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="Q98">
         <v>2.75</v>
@@ -21133,7 +21145,7 @@
         <v>0.86</v>
       </c>
       <c r="AP98">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AQ98">
         <v>1.33</v>
@@ -21261,7 +21273,7 @@
         <v>143</v>
       </c>
       <c r="P99" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="Q99">
         <v>3.4</v>
@@ -21467,7 +21479,7 @@
         <v>134</v>
       </c>
       <c r="P100" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="Q100">
         <v>3.3</v>
@@ -21673,7 +21685,7 @@
         <v>144</v>
       </c>
       <c r="P101" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="Q101">
         <v>3</v>
@@ -21751,7 +21763,7 @@
         <v>1.67</v>
       </c>
       <c r="AP101">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AQ101">
         <v>1.5</v>
@@ -21879,7 +21891,7 @@
         <v>145</v>
       </c>
       <c r="P102" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="Q102">
         <v>2.3</v>
@@ -21960,7 +21972,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ102">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AR102">
         <v>1.66</v>
@@ -22085,7 +22097,7 @@
         <v>146</v>
       </c>
       <c r="P103" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="Q103">
         <v>2.1</v>
@@ -22291,7 +22303,7 @@
         <v>147</v>
       </c>
       <c r="P104" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="Q104">
         <v>2.55</v>
@@ -22369,7 +22381,7 @@
         <v>1.5</v>
       </c>
       <c r="AP104">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AQ104">
         <v>1.3</v>
@@ -22703,7 +22715,7 @@
         <v>82</v>
       </c>
       <c r="P106" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="Q106">
         <v>4.5</v>
@@ -22781,7 +22793,7 @@
         <v>2.38</v>
       </c>
       <c r="AP106">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AQ106">
         <v>2.44</v>
@@ -22909,7 +22921,7 @@
         <v>149</v>
       </c>
       <c r="P107" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="Q107">
         <v>4.33</v>
@@ -22990,7 +23002,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ107">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AR107">
         <v>1.53</v>
@@ -23321,7 +23333,7 @@
         <v>151</v>
       </c>
       <c r="P109" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="Q109">
         <v>3</v>
@@ -23527,7 +23539,7 @@
         <v>152</v>
       </c>
       <c r="P110" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="Q110">
         <v>2.5</v>
@@ -23608,7 +23620,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ110">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AR110">
         <v>1.5</v>
@@ -23733,7 +23745,7 @@
         <v>153</v>
       </c>
       <c r="P111" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="Q111">
         <v>4.33</v>
@@ -23939,7 +23951,7 @@
         <v>154</v>
       </c>
       <c r="P112" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="Q112">
         <v>2.25</v>
@@ -24145,7 +24157,7 @@
         <v>155</v>
       </c>
       <c r="P113" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="Q113">
         <v>2.2</v>
@@ -24223,7 +24235,7 @@
         <v>0.44</v>
       </c>
       <c r="AP113">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AQ113">
         <v>0.5</v>
@@ -24351,7 +24363,7 @@
         <v>82</v>
       </c>
       <c r="P114" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="Q114">
         <v>3.4</v>
@@ -24714,6 +24726,624 @@
       </c>
       <c r="BP115">
         <v>1.11</v>
+      </c>
+    </row>
+    <row r="116" spans="1:68">
+      <c r="A116" s="1">
+        <v>115</v>
+      </c>
+      <c r="B116">
+        <v>7806872</v>
+      </c>
+      <c r="C116" t="s">
+        <v>68</v>
+      </c>
+      <c r="D116" t="s">
+        <v>69</v>
+      </c>
+      <c r="E116" s="2">
+        <v>45829.29166666666</v>
+      </c>
+      <c r="F116">
+        <v>20</v>
+      </c>
+      <c r="G116" t="s">
+        <v>78</v>
+      </c>
+      <c r="H116" t="s">
+        <v>75</v>
+      </c>
+      <c r="I116">
+        <v>1</v>
+      </c>
+      <c r="J116">
+        <v>0</v>
+      </c>
+      <c r="K116">
+        <v>1</v>
+      </c>
+      <c r="L116">
+        <v>3</v>
+      </c>
+      <c r="M116">
+        <v>0</v>
+      </c>
+      <c r="N116">
+        <v>3</v>
+      </c>
+      <c r="O116" t="s">
+        <v>156</v>
+      </c>
+      <c r="P116" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q116">
+        <v>2.45</v>
+      </c>
+      <c r="R116">
+        <v>2.05</v>
+      </c>
+      <c r="S116">
+        <v>4.33</v>
+      </c>
+      <c r="T116">
+        <v>1.41</v>
+      </c>
+      <c r="U116">
+        <v>2.65</v>
+      </c>
+      <c r="V116">
+        <v>2.85</v>
+      </c>
+      <c r="W116">
+        <v>1.37</v>
+      </c>
+      <c r="X116">
+        <v>7.5</v>
+      </c>
+      <c r="Y116">
+        <v>1.08</v>
+      </c>
+      <c r="Z116">
+        <v>1.84</v>
+      </c>
+      <c r="AA116">
+        <v>3.25</v>
+      </c>
+      <c r="AB116">
+        <v>3.72</v>
+      </c>
+      <c r="AC116">
+        <v>1.07</v>
+      </c>
+      <c r="AD116">
+        <v>8</v>
+      </c>
+      <c r="AE116">
+        <v>1.35</v>
+      </c>
+      <c r="AF116">
+        <v>3.1</v>
+      </c>
+      <c r="AG116">
+        <v>1.96</v>
+      </c>
+      <c r="AH116">
+        <v>1.74</v>
+      </c>
+      <c r="AI116">
+        <v>1.87</v>
+      </c>
+      <c r="AJ116">
+        <v>1.8</v>
+      </c>
+      <c r="AK116">
+        <v>1.23</v>
+      </c>
+      <c r="AL116">
+        <v>1.29</v>
+      </c>
+      <c r="AM116">
+        <v>1.85</v>
+      </c>
+      <c r="AN116">
+        <v>1</v>
+      </c>
+      <c r="AO116">
+        <v>0.22</v>
+      </c>
+      <c r="AP116">
+        <v>1.2</v>
+      </c>
+      <c r="AQ116">
+        <v>0.2</v>
+      </c>
+      <c r="AR116">
+        <v>1.56</v>
+      </c>
+      <c r="AS116">
+        <v>1.31</v>
+      </c>
+      <c r="AT116">
+        <v>2.87</v>
+      </c>
+      <c r="AU116">
+        <v>10</v>
+      </c>
+      <c r="AV116">
+        <v>4</v>
+      </c>
+      <c r="AW116">
+        <v>7</v>
+      </c>
+      <c r="AX116">
+        <v>6</v>
+      </c>
+      <c r="AY116">
+        <v>17</v>
+      </c>
+      <c r="AZ116">
+        <v>10</v>
+      </c>
+      <c r="BA116">
+        <v>7</v>
+      </c>
+      <c r="BB116">
+        <v>2</v>
+      </c>
+      <c r="BC116">
+        <v>9</v>
+      </c>
+      <c r="BD116">
+        <v>1.78</v>
+      </c>
+      <c r="BE116">
+        <v>6.25</v>
+      </c>
+      <c r="BF116">
+        <v>2.28</v>
+      </c>
+      <c r="BG116">
+        <v>1.44</v>
+      </c>
+      <c r="BH116">
+        <v>2.55</v>
+      </c>
+      <c r="BI116">
+        <v>1.74</v>
+      </c>
+      <c r="BJ116">
+        <v>1.98</v>
+      </c>
+      <c r="BK116">
+        <v>2.17</v>
+      </c>
+      <c r="BL116">
+        <v>1.6</v>
+      </c>
+      <c r="BM116">
+        <v>2.8</v>
+      </c>
+      <c r="BN116">
+        <v>1.38</v>
+      </c>
+      <c r="BO116">
+        <v>3.7</v>
+      </c>
+      <c r="BP116">
+        <v>1.23</v>
+      </c>
+    </row>
+    <row r="117" spans="1:68">
+      <c r="A117" s="1">
+        <v>116</v>
+      </c>
+      <c r="B117">
+        <v>7806873</v>
+      </c>
+      <c r="C117" t="s">
+        <v>68</v>
+      </c>
+      <c r="D117" t="s">
+        <v>69</v>
+      </c>
+      <c r="E117" s="2">
+        <v>45829.29166666666</v>
+      </c>
+      <c r="F117">
+        <v>20</v>
+      </c>
+      <c r="G117" t="s">
+        <v>70</v>
+      </c>
+      <c r="H117" t="s">
+        <v>71</v>
+      </c>
+      <c r="I117">
+        <v>0</v>
+      </c>
+      <c r="J117">
+        <v>0</v>
+      </c>
+      <c r="K117">
+        <v>0</v>
+      </c>
+      <c r="L117">
+        <v>2</v>
+      </c>
+      <c r="M117">
+        <v>1</v>
+      </c>
+      <c r="N117">
+        <v>3</v>
+      </c>
+      <c r="O117" t="s">
+        <v>157</v>
+      </c>
+      <c r="P117" t="s">
+        <v>219</v>
+      </c>
+      <c r="Q117">
+        <v>2.5</v>
+      </c>
+      <c r="R117">
+        <v>2.1</v>
+      </c>
+      <c r="S117">
+        <v>5</v>
+      </c>
+      <c r="T117">
+        <v>1.44</v>
+      </c>
+      <c r="U117">
+        <v>2.63</v>
+      </c>
+      <c r="V117">
+        <v>3.25</v>
+      </c>
+      <c r="W117">
+        <v>1.33</v>
+      </c>
+      <c r="X117">
+        <v>10</v>
+      </c>
+      <c r="Y117">
+        <v>1.06</v>
+      </c>
+      <c r="Z117">
+        <v>1.8</v>
+      </c>
+      <c r="AA117">
+        <v>3.12</v>
+      </c>
+      <c r="AB117">
+        <v>4.1</v>
+      </c>
+      <c r="AC117">
+        <v>1.03</v>
+      </c>
+      <c r="AD117">
+        <v>7.2</v>
+      </c>
+      <c r="AE117">
+        <v>1.35</v>
+      </c>
+      <c r="AF117">
+        <v>2.83</v>
+      </c>
+      <c r="AG117">
+        <v>2.05</v>
+      </c>
+      <c r="AH117">
+        <v>1.68</v>
+      </c>
+      <c r="AI117">
+        <v>2</v>
+      </c>
+      <c r="AJ117">
+        <v>1.73</v>
+      </c>
+      <c r="AK117">
+        <v>1.21</v>
+      </c>
+      <c r="AL117">
+        <v>1.32</v>
+      </c>
+      <c r="AM117">
+        <v>1.87</v>
+      </c>
+      <c r="AN117">
+        <v>1.78</v>
+      </c>
+      <c r="AO117">
+        <v>1</v>
+      </c>
+      <c r="AP117">
+        <v>1.9</v>
+      </c>
+      <c r="AQ117">
+        <v>0.9</v>
+      </c>
+      <c r="AR117">
+        <v>1.62</v>
+      </c>
+      <c r="AS117">
+        <v>1.53</v>
+      </c>
+      <c r="AT117">
+        <v>3.15</v>
+      </c>
+      <c r="AU117">
+        <v>11</v>
+      </c>
+      <c r="AV117">
+        <v>6</v>
+      </c>
+      <c r="AW117">
+        <v>10</v>
+      </c>
+      <c r="AX117">
+        <v>5</v>
+      </c>
+      <c r="AY117">
+        <v>21</v>
+      </c>
+      <c r="AZ117">
+        <v>11</v>
+      </c>
+      <c r="BA117">
+        <v>4</v>
+      </c>
+      <c r="BB117">
+        <v>2</v>
+      </c>
+      <c r="BC117">
+        <v>6</v>
+      </c>
+      <c r="BD117">
+        <v>1.61</v>
+      </c>
+      <c r="BE117">
+        <v>6.5</v>
+      </c>
+      <c r="BF117">
+        <v>2.55</v>
+      </c>
+      <c r="BG117">
+        <v>1.45</v>
+      </c>
+      <c r="BH117">
+        <v>2.55</v>
+      </c>
+      <c r="BI117">
+        <v>1.75</v>
+      </c>
+      <c r="BJ117">
+        <v>1.95</v>
+      </c>
+      <c r="BK117">
+        <v>2.18</v>
+      </c>
+      <c r="BL117">
+        <v>1.58</v>
+      </c>
+      <c r="BM117">
+        <v>2.8</v>
+      </c>
+      <c r="BN117">
+        <v>1.37</v>
+      </c>
+      <c r="BO117">
+        <v>3.7</v>
+      </c>
+      <c r="BP117">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="118" spans="1:68">
+      <c r="A118" s="1">
+        <v>117</v>
+      </c>
+      <c r="B118">
+        <v>7806874</v>
+      </c>
+      <c r="C118" t="s">
+        <v>68</v>
+      </c>
+      <c r="D118" t="s">
+        <v>69</v>
+      </c>
+      <c r="E118" s="2">
+        <v>45829.29166666666</v>
+      </c>
+      <c r="F118">
+        <v>20</v>
+      </c>
+      <c r="G118" t="s">
+        <v>74</v>
+      </c>
+      <c r="H118" t="s">
+        <v>76</v>
+      </c>
+      <c r="I118">
+        <v>1</v>
+      </c>
+      <c r="J118">
+        <v>1</v>
+      </c>
+      <c r="K118">
+        <v>2</v>
+      </c>
+      <c r="L118">
+        <v>1</v>
+      </c>
+      <c r="M118">
+        <v>1</v>
+      </c>
+      <c r="N118">
+        <v>2</v>
+      </c>
+      <c r="O118" t="s">
+        <v>158</v>
+      </c>
+      <c r="P118" t="s">
+        <v>216</v>
+      </c>
+      <c r="Q118">
+        <v>3.4</v>
+      </c>
+      <c r="R118">
+        <v>1.95</v>
+      </c>
+      <c r="S118">
+        <v>3.2</v>
+      </c>
+      <c r="T118">
+        <v>1.47</v>
+      </c>
+      <c r="U118">
+        <v>2.5</v>
+      </c>
+      <c r="V118">
+        <v>3.1</v>
+      </c>
+      <c r="W118">
+        <v>1.32</v>
+      </c>
+      <c r="X118">
+        <v>8.25</v>
+      </c>
+      <c r="Y118">
+        <v>1.06</v>
+      </c>
+      <c r="Z118">
+        <v>2.67</v>
+      </c>
+      <c r="AA118">
+        <v>2.92</v>
+      </c>
+      <c r="AB118">
+        <v>2.48</v>
+      </c>
+      <c r="AC118">
+        <v>1.08</v>
+      </c>
+      <c r="AD118">
+        <v>7.5</v>
+      </c>
+      <c r="AE118">
+        <v>1.42</v>
+      </c>
+      <c r="AF118">
+        <v>2.85</v>
+      </c>
+      <c r="AG118">
+        <v>1.95</v>
+      </c>
+      <c r="AH118">
+        <v>1.75</v>
+      </c>
+      <c r="AI118">
+        <v>1.88</v>
+      </c>
+      <c r="AJ118">
+        <v>1.8</v>
+      </c>
+      <c r="AK118">
+        <v>1.47</v>
+      </c>
+      <c r="AL118">
+        <v>1.35</v>
+      </c>
+      <c r="AM118">
+        <v>1.42</v>
+      </c>
+      <c r="AN118">
+        <v>1.7</v>
+      </c>
+      <c r="AO118">
+        <v>1.6</v>
+      </c>
+      <c r="AP118">
+        <v>1.64</v>
+      </c>
+      <c r="AQ118">
+        <v>1.55</v>
+      </c>
+      <c r="AR118">
+        <v>1.62</v>
+      </c>
+      <c r="AS118">
+        <v>1.76</v>
+      </c>
+      <c r="AT118">
+        <v>3.38</v>
+      </c>
+      <c r="AU118">
+        <v>4</v>
+      </c>
+      <c r="AV118">
+        <v>2</v>
+      </c>
+      <c r="AW118">
+        <v>3</v>
+      </c>
+      <c r="AX118">
+        <v>4</v>
+      </c>
+      <c r="AY118">
+        <v>7</v>
+      </c>
+      <c r="AZ118">
+        <v>6</v>
+      </c>
+      <c r="BA118">
+        <v>3</v>
+      </c>
+      <c r="BB118">
+        <v>1</v>
+      </c>
+      <c r="BC118">
+        <v>4</v>
+      </c>
+      <c r="BD118">
+        <v>1.86</v>
+      </c>
+      <c r="BE118">
+        <v>6.4</v>
+      </c>
+      <c r="BF118">
+        <v>2.15</v>
+      </c>
+      <c r="BG118">
+        <v>1.42</v>
+      </c>
+      <c r="BH118">
+        <v>2.65</v>
+      </c>
+      <c r="BI118">
+        <v>1.71</v>
+      </c>
+      <c r="BJ118">
+        <v>2</v>
+      </c>
+      <c r="BK118">
+        <v>2.12</v>
+      </c>
+      <c r="BL118">
+        <v>1.63</v>
+      </c>
+      <c r="BM118">
+        <v>2.7</v>
+      </c>
+      <c r="BN118">
+        <v>1.38</v>
+      </c>
+      <c r="BO118">
+        <v>3.65</v>
+      </c>
+      <c r="BP118">
+        <v>1.24</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/South Korea K League 1_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/South Korea K League 1_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="770" uniqueCount="220">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="782" uniqueCount="223">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -493,6 +493,12 @@
     <t>['4502']</t>
   </si>
   <si>
+    <t>['84']</t>
+  </si>
+  <si>
+    <t>['56', '72']</t>
+  </si>
+  <si>
     <t>['32', '87', '90']</t>
   </si>
   <si>
@@ -674,6 +680,9 @@
   </si>
   <si>
     <t>['9008']</t>
+  </si>
+  <si>
+    <t>['69', '78']</t>
   </si>
 </sst>
 </file>
@@ -1035,7 +1044,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP118"/>
+  <dimension ref="A1:BP120"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1291,7 +1300,7 @@
         <v>82</v>
       </c>
       <c r="P2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="Q2">
         <v>2.75</v>
@@ -1372,7 +1381,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ2">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1781,7 +1790,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AQ4">
         <v>0.5</v>
@@ -1909,7 +1918,7 @@
         <v>82</v>
       </c>
       <c r="P5" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="Q5">
         <v>2.1</v>
@@ -1990,7 +1999,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ5">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2321,7 +2330,7 @@
         <v>85</v>
       </c>
       <c r="P7" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="Q7">
         <v>3.5</v>
@@ -2527,7 +2536,7 @@
         <v>86</v>
       </c>
       <c r="P8" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="Q8">
         <v>3.4</v>
@@ -2733,7 +2742,7 @@
         <v>87</v>
       </c>
       <c r="P9" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="Q9">
         <v>3.35</v>
@@ -3020,7 +3029,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ10">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3145,7 +3154,7 @@
         <v>82</v>
       </c>
       <c r="P11" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="Q11">
         <v>3.45</v>
@@ -3351,7 +3360,7 @@
         <v>89</v>
       </c>
       <c r="P12" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="Q12">
         <v>2.75</v>
@@ -3557,7 +3566,7 @@
         <v>90</v>
       </c>
       <c r="P13" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="Q13">
         <v>2.95</v>
@@ -4253,10 +4262,10 @@
         <v>1.5</v>
       </c>
       <c r="AP16">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AQ16">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR16">
         <v>1.8</v>
@@ -5205,7 +5214,7 @@
         <v>94</v>
       </c>
       <c r="P21" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="Q21">
         <v>3.1</v>
@@ -5286,7 +5295,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ21">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AR21">
         <v>1.94</v>
@@ -5411,7 +5420,7 @@
         <v>95</v>
       </c>
       <c r="P22" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q22">
         <v>3.6</v>
@@ -6029,7 +6038,7 @@
         <v>97</v>
       </c>
       <c r="P25" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="Q25">
         <v>4</v>
@@ -6110,7 +6119,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ25">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AR25">
         <v>1.2</v>
@@ -6235,7 +6244,7 @@
         <v>82</v>
       </c>
       <c r="P26" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="Q26">
         <v>3.6</v>
@@ -6441,7 +6450,7 @@
         <v>82</v>
       </c>
       <c r="P27" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="Q27">
         <v>2.75</v>
@@ -6522,7 +6531,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ27">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR27">
         <v>2.02</v>
@@ -6647,7 +6656,7 @@
         <v>98</v>
       </c>
       <c r="P28" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="Q28">
         <v>3.75</v>
@@ -6931,7 +6940,7 @@
         <v>1</v>
       </c>
       <c r="AP29">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ29">
         <v>1.44</v>
@@ -7059,7 +7068,7 @@
         <v>99</v>
       </c>
       <c r="P30" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="Q30">
         <v>2.63</v>
@@ -7265,7 +7274,7 @@
         <v>100</v>
       </c>
       <c r="P31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="Q31">
         <v>3.1</v>
@@ -7343,7 +7352,7 @@
         <v>0.5</v>
       </c>
       <c r="AP31">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AQ31">
         <v>1.3</v>
@@ -7471,7 +7480,7 @@
         <v>101</v>
       </c>
       <c r="P32" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="Q32">
         <v>2.5</v>
@@ -7883,7 +7892,7 @@
         <v>103</v>
       </c>
       <c r="P34" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="Q34">
         <v>3.2</v>
@@ -8373,7 +8382,7 @@
         <v>1.5</v>
       </c>
       <c r="AP36">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ36">
         <v>1.3</v>
@@ -8707,7 +8716,7 @@
         <v>106</v>
       </c>
       <c r="P38" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="Q38">
         <v>2.45</v>
@@ -8788,7 +8797,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ38">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AR38">
         <v>2.21</v>
@@ -9197,7 +9206,7 @@
         <v>0.5</v>
       </c>
       <c r="AP40">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ40">
         <v>0.2</v>
@@ -9325,7 +9334,7 @@
         <v>82</v>
       </c>
       <c r="P41" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="Q41">
         <v>3.25</v>
@@ -9531,7 +9540,7 @@
         <v>98</v>
       </c>
       <c r="P42" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="Q42">
         <v>3.4</v>
@@ -10021,7 +10030,7 @@
         <v>0.5</v>
       </c>
       <c r="AP44">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AQ44">
         <v>0.9</v>
@@ -10227,7 +10236,7 @@
         <v>0.33</v>
       </c>
       <c r="AP45">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AQ45">
         <v>0.2</v>
@@ -10355,7 +10364,7 @@
         <v>111</v>
       </c>
       <c r="P46" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="Q46">
         <v>4.33</v>
@@ -10561,7 +10570,7 @@
         <v>112</v>
       </c>
       <c r="P47" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="Q47">
         <v>2.6</v>
@@ -10642,7 +10651,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ47">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AR47">
         <v>0.99</v>
@@ -10848,7 +10857,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ48">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR48">
         <v>1.68</v>
@@ -11591,7 +11600,7 @@
         <v>116</v>
       </c>
       <c r="P52" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="Q52">
         <v>2.38</v>
@@ -11797,7 +11806,7 @@
         <v>117</v>
       </c>
       <c r="P53" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="Q53">
         <v>3.1</v>
@@ -12003,7 +12012,7 @@
         <v>82</v>
       </c>
       <c r="P54" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="Q54">
         <v>2.75</v>
@@ -12081,10 +12090,10 @@
         <v>2.6</v>
       </c>
       <c r="AP54">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ54">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AR54">
         <v>1.88</v>
@@ -12209,7 +12218,7 @@
         <v>118</v>
       </c>
       <c r="P55" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="Q55">
         <v>2.75</v>
@@ -12621,7 +12630,7 @@
         <v>120</v>
       </c>
       <c r="P57" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="Q57">
         <v>2.3</v>
@@ -12827,7 +12836,7 @@
         <v>82</v>
       </c>
       <c r="P58" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="Q58">
         <v>4.5</v>
@@ -13033,7 +13042,7 @@
         <v>121</v>
       </c>
       <c r="P59" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="Q59">
         <v>4</v>
@@ -13239,7 +13248,7 @@
         <v>122</v>
       </c>
       <c r="P60" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="Q60">
         <v>2.7</v>
@@ -13729,7 +13738,7 @@
         <v>2</v>
       </c>
       <c r="AP62">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ62">
         <v>1.5</v>
@@ -14269,7 +14278,7 @@
         <v>105</v>
       </c>
       <c r="P65" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="Q65">
         <v>3.4</v>
@@ -14475,7 +14484,7 @@
         <v>127</v>
       </c>
       <c r="P66" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="Q66">
         <v>2.5</v>
@@ -14556,7 +14565,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ66">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR66">
         <v>1.46</v>
@@ -14887,7 +14896,7 @@
         <v>82</v>
       </c>
       <c r="P68" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="Q68">
         <v>3</v>
@@ -15299,7 +15308,7 @@
         <v>116</v>
       </c>
       <c r="P70" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="Q70">
         <v>2.38</v>
@@ -15583,7 +15592,7 @@
         <v>1.67</v>
       </c>
       <c r="AP71">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AQ71">
         <v>1.4</v>
@@ -15792,7 +15801,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ72">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AR72">
         <v>1.66</v>
@@ -15917,7 +15926,7 @@
         <v>82</v>
       </c>
       <c r="P73" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="Q73">
         <v>3</v>
@@ -16123,7 +16132,7 @@
         <v>130</v>
       </c>
       <c r="P74" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="Q74">
         <v>5</v>
@@ -16329,7 +16338,7 @@
         <v>131</v>
       </c>
       <c r="P75" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q75">
         <v>2.88</v>
@@ -16741,7 +16750,7 @@
         <v>133</v>
       </c>
       <c r="P77" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="Q77">
         <v>3</v>
@@ -17153,7 +17162,7 @@
         <v>134</v>
       </c>
       <c r="P79" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q79">
         <v>4.33</v>
@@ -17359,7 +17368,7 @@
         <v>82</v>
       </c>
       <c r="P80" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="Q80">
         <v>3.6</v>
@@ -17565,7 +17574,7 @@
         <v>82</v>
       </c>
       <c r="P81" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Q81">
         <v>3.5</v>
@@ -17643,7 +17652,7 @@
         <v>2.4</v>
       </c>
       <c r="AP81">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AQ81">
         <v>2.44</v>
@@ -17852,7 +17861,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ82">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR82">
         <v>1.65</v>
@@ -17977,7 +17986,7 @@
         <v>136</v>
       </c>
       <c r="P83" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="Q83">
         <v>4.33</v>
@@ -18183,7 +18192,7 @@
         <v>137</v>
       </c>
       <c r="P84" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="Q84">
         <v>2.4</v>
@@ -18261,7 +18270,7 @@
         <v>0.33</v>
       </c>
       <c r="AP84">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ84">
         <v>0.9</v>
@@ -18595,7 +18604,7 @@
         <v>82</v>
       </c>
       <c r="P86" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q86">
         <v>5</v>
@@ -18882,7 +18891,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ87">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AR87">
         <v>1.6</v>
@@ -19213,7 +19222,7 @@
         <v>82</v>
       </c>
       <c r="P89" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="Q89">
         <v>3.4</v>
@@ -19419,7 +19428,7 @@
         <v>139</v>
       </c>
       <c r="P90" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="Q90">
         <v>2.3</v>
@@ -19625,7 +19634,7 @@
         <v>140</v>
       </c>
       <c r="P91" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="Q91">
         <v>2.55</v>
@@ -20037,7 +20046,7 @@
         <v>82</v>
       </c>
       <c r="P93" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="Q93">
         <v>2.88</v>
@@ -20115,7 +20124,7 @@
         <v>1.29</v>
       </c>
       <c r="AP93">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AQ93">
         <v>1.3</v>
@@ -20243,7 +20252,7 @@
         <v>82</v>
       </c>
       <c r="P94" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="Q94">
         <v>2.8</v>
@@ -20449,7 +20458,7 @@
         <v>142</v>
       </c>
       <c r="P95" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="Q95">
         <v>2.62</v>
@@ -20655,7 +20664,7 @@
         <v>82</v>
       </c>
       <c r="P96" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Q96">
         <v>4</v>
@@ -20861,7 +20870,7 @@
         <v>82</v>
       </c>
       <c r="P97" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="Q97">
         <v>3.1</v>
@@ -20939,7 +20948,7 @@
         <v>1.25</v>
       </c>
       <c r="AP97">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ97">
         <v>1.55</v>
@@ -21067,7 +21076,7 @@
         <v>125</v>
       </c>
       <c r="P98" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Q98">
         <v>2.75</v>
@@ -21148,7 +21157,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ98">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR98">
         <v>1.5</v>
@@ -21273,7 +21282,7 @@
         <v>143</v>
       </c>
       <c r="P99" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q99">
         <v>3.4</v>
@@ -21351,7 +21360,7 @@
         <v>1.75</v>
       </c>
       <c r="AP99">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AQ99">
         <v>1.5</v>
@@ -21479,7 +21488,7 @@
         <v>134</v>
       </c>
       <c r="P100" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Q100">
         <v>3.3</v>
@@ -21560,7 +21569,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ100">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AR100">
         <v>1.51</v>
@@ -21685,7 +21694,7 @@
         <v>144</v>
       </c>
       <c r="P101" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Q101">
         <v>3</v>
@@ -21891,7 +21900,7 @@
         <v>145</v>
       </c>
       <c r="P102" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="Q102">
         <v>2.3</v>
@@ -22097,7 +22106,7 @@
         <v>146</v>
       </c>
       <c r="P103" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="Q103">
         <v>2.1</v>
@@ -22175,7 +22184,7 @@
         <v>0.38</v>
       </c>
       <c r="AP103">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ103">
         <v>0.5</v>
@@ -22303,7 +22312,7 @@
         <v>147</v>
       </c>
       <c r="P104" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Q104">
         <v>2.55</v>
@@ -22715,7 +22724,7 @@
         <v>82</v>
       </c>
       <c r="P106" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q106">
         <v>4.5</v>
@@ -22921,7 +22930,7 @@
         <v>149</v>
       </c>
       <c r="P107" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="Q107">
         <v>4.33</v>
@@ -22999,7 +23008,7 @@
         <v>1.44</v>
       </c>
       <c r="AP107">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AQ107">
         <v>1.55</v>
@@ -23205,7 +23214,7 @@
         <v>1.5</v>
       </c>
       <c r="AP108">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ108">
         <v>1.3</v>
@@ -23333,7 +23342,7 @@
         <v>151</v>
       </c>
       <c r="P109" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="Q109">
         <v>3</v>
@@ -23414,7 +23423,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ109">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR109">
         <v>1.77</v>
@@ -23539,7 +23548,7 @@
         <v>152</v>
       </c>
       <c r="P110" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="Q110">
         <v>2.5</v>
@@ -23745,7 +23754,7 @@
         <v>153</v>
       </c>
       <c r="P111" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="Q111">
         <v>4.33</v>
@@ -23951,7 +23960,7 @@
         <v>154</v>
       </c>
       <c r="P112" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Q112">
         <v>2.25</v>
@@ -24157,7 +24166,7 @@
         <v>155</v>
       </c>
       <c r="P113" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Q113">
         <v>2.2</v>
@@ -24363,7 +24372,7 @@
         <v>82</v>
       </c>
       <c r="P114" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Q114">
         <v>3.4</v>
@@ -24981,7 +24990,7 @@
         <v>157</v>
       </c>
       <c r="P117" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="Q117">
         <v>2.5</v>
@@ -25187,7 +25196,7 @@
         <v>158</v>
       </c>
       <c r="P118" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Q118">
         <v>3.4</v>
@@ -25344,6 +25353,418 @@
       </c>
       <c r="BP118">
         <v>1.24</v>
+      </c>
+    </row>
+    <row r="119" spans="1:68">
+      <c r="A119" s="1">
+        <v>118</v>
+      </c>
+      <c r="B119">
+        <v>7806875</v>
+      </c>
+      <c r="C119" t="s">
+        <v>68</v>
+      </c>
+      <c r="D119" t="s">
+        <v>69</v>
+      </c>
+      <c r="E119" s="2">
+        <v>45830.29166666666</v>
+      </c>
+      <c r="F119">
+        <v>20</v>
+      </c>
+      <c r="G119" t="s">
+        <v>81</v>
+      </c>
+      <c r="H119" t="s">
+        <v>80</v>
+      </c>
+      <c r="I119">
+        <v>0</v>
+      </c>
+      <c r="J119">
+        <v>0</v>
+      </c>
+      <c r="K119">
+        <v>0</v>
+      </c>
+      <c r="L119">
+        <v>1</v>
+      </c>
+      <c r="M119">
+        <v>0</v>
+      </c>
+      <c r="N119">
+        <v>1</v>
+      </c>
+      <c r="O119" t="s">
+        <v>159</v>
+      </c>
+      <c r="P119" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q119">
+        <v>2.2</v>
+      </c>
+      <c r="R119">
+        <v>2.3</v>
+      </c>
+      <c r="S119">
+        <v>4.33</v>
+      </c>
+      <c r="T119">
+        <v>1.3</v>
+      </c>
+      <c r="U119">
+        <v>3.2</v>
+      </c>
+      <c r="V119">
+        <v>2.4</v>
+      </c>
+      <c r="W119">
+        <v>1.5</v>
+      </c>
+      <c r="X119">
+        <v>6.8</v>
+      </c>
+      <c r="Y119">
+        <v>1.04</v>
+      </c>
+      <c r="Z119">
+        <v>1.67</v>
+      </c>
+      <c r="AA119">
+        <v>3.63</v>
+      </c>
+      <c r="AB119">
+        <v>4.1</v>
+      </c>
+      <c r="AC119">
+        <v>1.04</v>
+      </c>
+      <c r="AD119">
+        <v>10</v>
+      </c>
+      <c r="AE119">
+        <v>1.22</v>
+      </c>
+      <c r="AF119">
+        <v>4.2</v>
+      </c>
+      <c r="AG119">
+        <v>1.78</v>
+      </c>
+      <c r="AH119">
+        <v>1.92</v>
+      </c>
+      <c r="AI119">
+        <v>1.62</v>
+      </c>
+      <c r="AJ119">
+        <v>2.1</v>
+      </c>
+      <c r="AK119">
+        <v>1.2</v>
+      </c>
+      <c r="AL119">
+        <v>1.2</v>
+      </c>
+      <c r="AM119">
+        <v>2.05</v>
+      </c>
+      <c r="AN119">
+        <v>1.67</v>
+      </c>
+      <c r="AO119">
+        <v>1.33</v>
+      </c>
+      <c r="AP119">
+        <v>1.8</v>
+      </c>
+      <c r="AQ119">
+        <v>1.2</v>
+      </c>
+      <c r="AR119">
+        <v>1.75</v>
+      </c>
+      <c r="AS119">
+        <v>1.48</v>
+      </c>
+      <c r="AT119">
+        <v>3.23</v>
+      </c>
+      <c r="AU119">
+        <v>3</v>
+      </c>
+      <c r="AV119">
+        <v>0</v>
+      </c>
+      <c r="AW119">
+        <v>16</v>
+      </c>
+      <c r="AX119">
+        <v>8</v>
+      </c>
+      <c r="AY119">
+        <v>19</v>
+      </c>
+      <c r="AZ119">
+        <v>8</v>
+      </c>
+      <c r="BA119">
+        <v>8</v>
+      </c>
+      <c r="BB119">
+        <v>4</v>
+      </c>
+      <c r="BC119">
+        <v>12</v>
+      </c>
+      <c r="BD119">
+        <v>1.55</v>
+      </c>
+      <c r="BE119">
+        <v>6.4</v>
+      </c>
+      <c r="BF119">
+        <v>2.75</v>
+      </c>
+      <c r="BG119">
+        <v>1.47</v>
+      </c>
+      <c r="BH119">
+        <v>2.48</v>
+      </c>
+      <c r="BI119">
+        <v>1.78</v>
+      </c>
+      <c r="BJ119">
+        <v>1.92</v>
+      </c>
+      <c r="BK119">
+        <v>2.23</v>
+      </c>
+      <c r="BL119">
+        <v>1.56</v>
+      </c>
+      <c r="BM119">
+        <v>2.9</v>
+      </c>
+      <c r="BN119">
+        <v>1.34</v>
+      </c>
+      <c r="BO119">
+        <v>3.9</v>
+      </c>
+      <c r="BP119">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="120" spans="1:68">
+      <c r="A120" s="1">
+        <v>119</v>
+      </c>
+      <c r="B120">
+        <v>7806877</v>
+      </c>
+      <c r="C120" t="s">
+        <v>68</v>
+      </c>
+      <c r="D120" t="s">
+        <v>69</v>
+      </c>
+      <c r="E120" s="2">
+        <v>45830.29166666666</v>
+      </c>
+      <c r="F120">
+        <v>20</v>
+      </c>
+      <c r="G120" t="s">
+        <v>72</v>
+      </c>
+      <c r="H120" t="s">
+        <v>77</v>
+      </c>
+      <c r="I120">
+        <v>0</v>
+      </c>
+      <c r="J120">
+        <v>0</v>
+      </c>
+      <c r="K120">
+        <v>0</v>
+      </c>
+      <c r="L120">
+        <v>2</v>
+      </c>
+      <c r="M120">
+        <v>2</v>
+      </c>
+      <c r="N120">
+        <v>4</v>
+      </c>
+      <c r="O120" t="s">
+        <v>160</v>
+      </c>
+      <c r="P120" t="s">
+        <v>222</v>
+      </c>
+      <c r="Q120">
+        <v>2.7</v>
+      </c>
+      <c r="R120">
+        <v>2</v>
+      </c>
+      <c r="S120">
+        <v>3.95</v>
+      </c>
+      <c r="T120">
+        <v>1.44</v>
+      </c>
+      <c r="U120">
+        <v>2.6</v>
+      </c>
+      <c r="V120">
+        <v>3</v>
+      </c>
+      <c r="W120">
+        <v>1.33</v>
+      </c>
+      <c r="X120">
+        <v>7.7</v>
+      </c>
+      <c r="Y120">
+        <v>1.03</v>
+      </c>
+      <c r="Z120">
+        <v>2.06</v>
+      </c>
+      <c r="AA120">
+        <v>3.11</v>
+      </c>
+      <c r="AB120">
+        <v>3.21</v>
+      </c>
+      <c r="AC120">
+        <v>1.07</v>
+      </c>
+      <c r="AD120">
+        <v>8</v>
+      </c>
+      <c r="AE120">
+        <v>1.38</v>
+      </c>
+      <c r="AF120">
+        <v>3</v>
+      </c>
+      <c r="AG120">
+        <v>2.25</v>
+      </c>
+      <c r="AH120">
+        <v>1.57</v>
+      </c>
+      <c r="AI120">
+        <v>1.83</v>
+      </c>
+      <c r="AJ120">
+        <v>1.83</v>
+      </c>
+      <c r="AK120">
+        <v>1.28</v>
+      </c>
+      <c r="AL120">
+        <v>1.28</v>
+      </c>
+      <c r="AM120">
+        <v>1.7</v>
+      </c>
+      <c r="AN120">
+        <v>1.4</v>
+      </c>
+      <c r="AO120">
+        <v>2</v>
+      </c>
+      <c r="AP120">
+        <v>1.36</v>
+      </c>
+      <c r="AQ120">
+        <v>1.9</v>
+      </c>
+      <c r="AR120">
+        <v>1.52</v>
+      </c>
+      <c r="AS120">
+        <v>1.25</v>
+      </c>
+      <c r="AT120">
+        <v>2.77</v>
+      </c>
+      <c r="AU120">
+        <v>4</v>
+      </c>
+      <c r="AV120">
+        <v>6</v>
+      </c>
+      <c r="AW120">
+        <v>5</v>
+      </c>
+      <c r="AX120">
+        <v>9</v>
+      </c>
+      <c r="AY120">
+        <v>9</v>
+      </c>
+      <c r="AZ120">
+        <v>15</v>
+      </c>
+      <c r="BA120">
+        <v>4</v>
+      </c>
+      <c r="BB120">
+        <v>8</v>
+      </c>
+      <c r="BC120">
+        <v>12</v>
+      </c>
+      <c r="BD120">
+        <v>1.75</v>
+      </c>
+      <c r="BE120">
+        <v>6.25</v>
+      </c>
+      <c r="BF120">
+        <v>2.32</v>
+      </c>
+      <c r="BG120">
+        <v>1.5</v>
+      </c>
+      <c r="BH120">
+        <v>2.35</v>
+      </c>
+      <c r="BI120">
+        <v>1.85</v>
+      </c>
+      <c r="BJ120">
+        <v>1.83</v>
+      </c>
+      <c r="BK120">
+        <v>2.35</v>
+      </c>
+      <c r="BL120">
+        <v>1.5</v>
+      </c>
+      <c r="BM120">
+        <v>3.1</v>
+      </c>
+      <c r="BN120">
+        <v>1.3</v>
+      </c>
+      <c r="BO120">
+        <v>4.1</v>
+      </c>
+      <c r="BP120">
+        <v>1.18</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/South Korea K League 1_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/South Korea K League 1_2025.xlsx
@@ -24877,22 +24877,22 @@
         <v>2.87</v>
       </c>
       <c r="AU116">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AV116">
         <v>4</v>
       </c>
       <c r="AW116">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AX116">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AY116">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="AZ116">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BA116">
         <v>7</v>
@@ -25083,22 +25083,22 @@
         <v>3.15</v>
       </c>
       <c r="AU117">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AV117">
         <v>6</v>
       </c>
       <c r="AW117">
+        <v>3</v>
+      </c>
+      <c r="AX117">
+        <v>4</v>
+      </c>
+      <c r="AY117">
+        <v>15</v>
+      </c>
+      <c r="AZ117">
         <v>10</v>
-      </c>
-      <c r="AX117">
-        <v>5</v>
-      </c>
-      <c r="AY117">
-        <v>21</v>
-      </c>
-      <c r="AZ117">
-        <v>11</v>
       </c>
       <c r="BA117">
         <v>4</v>
@@ -25292,19 +25292,19 @@
         <v>4</v>
       </c>
       <c r="AV118">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AW118">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AX118">
         <v>4</v>
       </c>
       <c r="AY118">
+        <v>8</v>
+      </c>
+      <c r="AZ118">
         <v>7</v>
-      </c>
-      <c r="AZ118">
-        <v>6</v>
       </c>
       <c r="BA118">
         <v>3</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/South Korea K League 1_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/South Korea K League 1_2025.xlsx
@@ -25196,7 +25196,7 @@
         <v>158</v>
       </c>
       <c r="P118" t="s">
-        <v>218</v>
+        <v>191</v>
       </c>
       <c r="Q118">
         <v>3.4</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/South Korea K League 1_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/South Korea K League 1_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="782" uniqueCount="223">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="794" uniqueCount="226">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -499,6 +499,9 @@
     <t>['56', '72']</t>
   </si>
   <si>
+    <t>['78']</t>
+  </si>
+  <si>
     <t>['32', '87', '90']</t>
   </si>
   <si>
@@ -683,6 +686,12 @@
   </si>
   <si>
     <t>['69', '78']</t>
+  </si>
+  <si>
+    <t>['37', '53']</t>
+  </si>
+  <si>
+    <t>['9007']</t>
   </si>
 </sst>
 </file>
@@ -1044,7 +1053,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP120"/>
+  <dimension ref="A1:BP122"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1300,7 +1309,7 @@
         <v>82</v>
       </c>
       <c r="P2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Q2">
         <v>2.75</v>
@@ -1918,7 +1927,7 @@
         <v>82</v>
       </c>
       <c r="P5" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Q5">
         <v>2.1</v>
@@ -2330,7 +2339,7 @@
         <v>85</v>
       </c>
       <c r="P7" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Q7">
         <v>3.5</v>
@@ -2536,7 +2545,7 @@
         <v>86</v>
       </c>
       <c r="P8" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Q8">
         <v>3.4</v>
@@ -2742,7 +2751,7 @@
         <v>87</v>
       </c>
       <c r="P9" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q9">
         <v>3.35</v>
@@ -3154,7 +3163,7 @@
         <v>82</v>
       </c>
       <c r="P11" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q11">
         <v>3.45</v>
@@ -3232,7 +3241,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AQ11">
         <v>1.5</v>
@@ -3360,7 +3369,7 @@
         <v>89</v>
       </c>
       <c r="P12" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q12">
         <v>2.75</v>
@@ -3566,7 +3575,7 @@
         <v>90</v>
       </c>
       <c r="P13" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Q13">
         <v>2.95</v>
@@ -3853,7 +3862,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ14">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="AR14">
         <v>2.51</v>
@@ -4468,7 +4477,7 @@
         <v>0.5</v>
       </c>
       <c r="AP17">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AQ17">
         <v>0.5</v>
@@ -4677,7 +4686,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ18">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AR18">
         <v>2.13</v>
@@ -5214,7 +5223,7 @@
         <v>94</v>
       </c>
       <c r="P21" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q21">
         <v>3.1</v>
@@ -5420,7 +5429,7 @@
         <v>95</v>
       </c>
       <c r="P22" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q22">
         <v>3.6</v>
@@ -5707,7 +5716,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ23">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AR23">
         <v>2.19</v>
@@ -6038,7 +6047,7 @@
         <v>97</v>
       </c>
       <c r="P25" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q25">
         <v>4</v>
@@ -6244,7 +6253,7 @@
         <v>82</v>
       </c>
       <c r="P26" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q26">
         <v>3.6</v>
@@ -6450,7 +6459,7 @@
         <v>82</v>
       </c>
       <c r="P27" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q27">
         <v>2.75</v>
@@ -6656,7 +6665,7 @@
         <v>98</v>
       </c>
       <c r="P28" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q28">
         <v>3.75</v>
@@ -6940,7 +6949,7 @@
         <v>1</v>
       </c>
       <c r="AP29">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AQ29">
         <v>1.44</v>
@@ -7068,7 +7077,7 @@
         <v>99</v>
       </c>
       <c r="P30" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q30">
         <v>2.63</v>
@@ -7274,7 +7283,7 @@
         <v>100</v>
       </c>
       <c r="P31" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q31">
         <v>3.1</v>
@@ -7480,7 +7489,7 @@
         <v>101</v>
       </c>
       <c r="P32" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q32">
         <v>2.5</v>
@@ -7892,7 +7901,7 @@
         <v>103</v>
       </c>
       <c r="P34" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q34">
         <v>3.2</v>
@@ -7970,7 +7979,7 @@
         <v>1</v>
       </c>
       <c r="AP34">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AQ34">
         <v>1.44</v>
@@ -8382,7 +8391,7 @@
         <v>1.5</v>
       </c>
       <c r="AP36">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AQ36">
         <v>1.3</v>
@@ -8591,7 +8600,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ37">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="AR37">
         <v>1.26</v>
@@ -8716,7 +8725,7 @@
         <v>106</v>
       </c>
       <c r="P38" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q38">
         <v>2.45</v>
@@ -9206,7 +9215,7 @@
         <v>0.5</v>
       </c>
       <c r="AP40">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AQ40">
         <v>0.2</v>
@@ -9334,7 +9343,7 @@
         <v>82</v>
       </c>
       <c r="P41" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q41">
         <v>3.25</v>
@@ -9412,10 +9421,10 @@
         <v>1.5</v>
       </c>
       <c r="AP41">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AQ41">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="AR41">
         <v>1.54</v>
@@ -9540,7 +9549,7 @@
         <v>98</v>
       </c>
       <c r="P42" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q42">
         <v>3.4</v>
@@ -10033,7 +10042,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ44">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AR44">
         <v>1.71</v>
@@ -10364,7 +10373,7 @@
         <v>111</v>
       </c>
       <c r="P46" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q46">
         <v>4.33</v>
@@ -10570,7 +10579,7 @@
         <v>112</v>
       </c>
       <c r="P47" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q47">
         <v>2.6</v>
@@ -11269,7 +11278,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ50">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AR50">
         <v>1.68</v>
@@ -11600,7 +11609,7 @@
         <v>116</v>
       </c>
       <c r="P52" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q52">
         <v>2.38</v>
@@ -11806,7 +11815,7 @@
         <v>117</v>
       </c>
       <c r="P53" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q53">
         <v>3.1</v>
@@ -12012,7 +12021,7 @@
         <v>82</v>
       </c>
       <c r="P54" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q54">
         <v>2.75</v>
@@ -12090,7 +12099,7 @@
         <v>2.6</v>
       </c>
       <c r="AP54">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AQ54">
         <v>1.9</v>
@@ -12218,7 +12227,7 @@
         <v>118</v>
       </c>
       <c r="P55" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q55">
         <v>2.75</v>
@@ -12630,7 +12639,7 @@
         <v>120</v>
       </c>
       <c r="P57" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q57">
         <v>2.3</v>
@@ -12836,7 +12845,7 @@
         <v>82</v>
       </c>
       <c r="P58" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q58">
         <v>4.5</v>
@@ -13042,7 +13051,7 @@
         <v>121</v>
       </c>
       <c r="P59" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q59">
         <v>4</v>
@@ -13123,7 +13132,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ59">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="AR59">
         <v>1.49</v>
@@ -13248,7 +13257,7 @@
         <v>122</v>
       </c>
       <c r="P60" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q60">
         <v>2.7</v>
@@ -13329,7 +13338,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ60">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AR60">
         <v>1.61</v>
@@ -13738,7 +13747,7 @@
         <v>2</v>
       </c>
       <c r="AP62">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AQ62">
         <v>1.5</v>
@@ -13944,7 +13953,7 @@
         <v>1.2</v>
       </c>
       <c r="AP63">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AQ63">
         <v>1.3</v>
@@ -14278,7 +14287,7 @@
         <v>105</v>
       </c>
       <c r="P65" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q65">
         <v>3.4</v>
@@ -14484,7 +14493,7 @@
         <v>127</v>
       </c>
       <c r="P66" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Q66">
         <v>2.5</v>
@@ -14562,7 +14571,7 @@
         <v>1.2</v>
       </c>
       <c r="AP66">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AQ66">
         <v>1.2</v>
@@ -14771,7 +14780,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ67">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AR67">
         <v>2.01</v>
@@ -14896,7 +14905,7 @@
         <v>82</v>
       </c>
       <c r="P68" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q68">
         <v>3</v>
@@ -14977,7 +14986,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ68">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="AR68">
         <v>1.47</v>
@@ -15308,7 +15317,7 @@
         <v>116</v>
       </c>
       <c r="P70" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q70">
         <v>2.38</v>
@@ -15926,7 +15935,7 @@
         <v>82</v>
       </c>
       <c r="P73" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q73">
         <v>3</v>
@@ -16132,7 +16141,7 @@
         <v>130</v>
       </c>
       <c r="P74" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q74">
         <v>5</v>
@@ -16338,7 +16347,7 @@
         <v>131</v>
       </c>
       <c r="P75" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q75">
         <v>2.88</v>
@@ -16750,7 +16759,7 @@
         <v>133</v>
       </c>
       <c r="P77" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q77">
         <v>3</v>
@@ -17034,7 +17043,7 @@
         <v>1</v>
       </c>
       <c r="AP78">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AQ78">
         <v>1.55</v>
@@ -17162,7 +17171,7 @@
         <v>134</v>
       </c>
       <c r="P79" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q79">
         <v>4.33</v>
@@ -17368,7 +17377,7 @@
         <v>82</v>
       </c>
       <c r="P80" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q80">
         <v>3.6</v>
@@ -17574,7 +17583,7 @@
         <v>82</v>
       </c>
       <c r="P81" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q81">
         <v>3.5</v>
@@ -17655,7 +17664,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ81">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="AR81">
         <v>1.49</v>
@@ -17986,7 +17995,7 @@
         <v>136</v>
       </c>
       <c r="P83" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q83">
         <v>4.33</v>
@@ -18192,7 +18201,7 @@
         <v>137</v>
       </c>
       <c r="P84" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q84">
         <v>2.4</v>
@@ -18270,10 +18279,10 @@
         <v>0.33</v>
       </c>
       <c r="AP84">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AQ84">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AR84">
         <v>1.76</v>
@@ -18604,7 +18613,7 @@
         <v>82</v>
       </c>
       <c r="P86" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q86">
         <v>5</v>
@@ -19097,7 +19106,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ88">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="AR88">
         <v>1.52</v>
@@ -19222,7 +19231,7 @@
         <v>82</v>
       </c>
       <c r="P89" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q89">
         <v>3.4</v>
@@ -19428,7 +19437,7 @@
         <v>139</v>
       </c>
       <c r="P90" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q90">
         <v>2.3</v>
@@ -19634,7 +19643,7 @@
         <v>140</v>
       </c>
       <c r="P91" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q91">
         <v>2.55</v>
@@ -19918,7 +19927,7 @@
         <v>0.29</v>
       </c>
       <c r="AP92">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AQ92">
         <v>0.2</v>
@@ -20046,7 +20055,7 @@
         <v>82</v>
       </c>
       <c r="P93" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q93">
         <v>2.88</v>
@@ -20252,7 +20261,7 @@
         <v>82</v>
       </c>
       <c r="P94" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q94">
         <v>2.8</v>
@@ -20333,7 +20342,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ94">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AR94">
         <v>1.88</v>
@@ -20458,7 +20467,7 @@
         <v>142</v>
       </c>
       <c r="P95" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q95">
         <v>2.62</v>
@@ -20536,7 +20545,7 @@
         <v>1.29</v>
       </c>
       <c r="AP95">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AQ95">
         <v>1.3</v>
@@ -20664,7 +20673,7 @@
         <v>82</v>
       </c>
       <c r="P96" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q96">
         <v>4</v>
@@ -20745,7 +20754,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ96">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="AR96">
         <v>1.86</v>
@@ -20870,7 +20879,7 @@
         <v>82</v>
       </c>
       <c r="P97" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q97">
         <v>3.1</v>
@@ -20948,7 +20957,7 @@
         <v>1.25</v>
       </c>
       <c r="AP97">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AQ97">
         <v>1.55</v>
@@ -21076,7 +21085,7 @@
         <v>125</v>
       </c>
       <c r="P98" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q98">
         <v>2.75</v>
@@ -21282,7 +21291,7 @@
         <v>143</v>
       </c>
       <c r="P99" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q99">
         <v>3.4</v>
@@ -21488,7 +21497,7 @@
         <v>134</v>
       </c>
       <c r="P100" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q100">
         <v>3.3</v>
@@ -21694,7 +21703,7 @@
         <v>144</v>
       </c>
       <c r="P101" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q101">
         <v>3</v>
@@ -21900,7 +21909,7 @@
         <v>145</v>
       </c>
       <c r="P102" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q102">
         <v>2.3</v>
@@ -21981,7 +21990,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ102">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AR102">
         <v>1.66</v>
@@ -22106,7 +22115,7 @@
         <v>146</v>
       </c>
       <c r="P103" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q103">
         <v>2.1</v>
@@ -22184,7 +22193,7 @@
         <v>0.38</v>
       </c>
       <c r="AP103">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AQ103">
         <v>0.5</v>
@@ -22312,7 +22321,7 @@
         <v>147</v>
       </c>
       <c r="P104" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q104">
         <v>2.55</v>
@@ -22724,7 +22733,7 @@
         <v>82</v>
       </c>
       <c r="P106" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q106">
         <v>4.5</v>
@@ -22805,7 +22814,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ106">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="AR106">
         <v>1.5</v>
@@ -22930,7 +22939,7 @@
         <v>149</v>
       </c>
       <c r="P107" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q107">
         <v>4.33</v>
@@ -23214,7 +23223,7 @@
         <v>1.5</v>
       </c>
       <c r="AP108">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AQ108">
         <v>1.3</v>
@@ -23342,7 +23351,7 @@
         <v>151</v>
       </c>
       <c r="P109" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q109">
         <v>3</v>
@@ -23548,7 +23557,7 @@
         <v>152</v>
       </c>
       <c r="P110" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q110">
         <v>2.5</v>
@@ -23754,7 +23763,7 @@
         <v>153</v>
       </c>
       <c r="P111" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q111">
         <v>4.33</v>
@@ -23960,7 +23969,7 @@
         <v>154</v>
       </c>
       <c r="P112" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q112">
         <v>2.25</v>
@@ -24166,7 +24175,7 @@
         <v>155</v>
       </c>
       <c r="P113" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q113">
         <v>2.2</v>
@@ -24372,7 +24381,7 @@
         <v>82</v>
       </c>
       <c r="P114" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q114">
         <v>3.4</v>
@@ -24656,7 +24665,7 @@
         <v>1.44</v>
       </c>
       <c r="AP115">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AQ115">
         <v>1.4</v>
@@ -24990,7 +24999,7 @@
         <v>157</v>
       </c>
       <c r="P117" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q117">
         <v>2.5</v>
@@ -25071,7 +25080,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ117">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AR117">
         <v>1.62</v>
@@ -25196,7 +25205,7 @@
         <v>158</v>
       </c>
       <c r="P118" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q118">
         <v>3.4</v>
@@ -25480,7 +25489,7 @@
         <v>1.33</v>
       </c>
       <c r="AP119">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AQ119">
         <v>1.2</v>
@@ -25608,7 +25617,7 @@
         <v>160</v>
       </c>
       <c r="P120" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q120">
         <v>2.7</v>
@@ -25765,6 +25774,418 @@
       </c>
       <c r="BP120">
         <v>1.18</v>
+      </c>
+    </row>
+    <row r="121" spans="1:68">
+      <c r="A121" s="1">
+        <v>120</v>
+      </c>
+      <c r="B121">
+        <v>7806878</v>
+      </c>
+      <c r="C121" t="s">
+        <v>68</v>
+      </c>
+      <c r="D121" t="s">
+        <v>69</v>
+      </c>
+      <c r="E121" s="2">
+        <v>45835.3125</v>
+      </c>
+      <c r="F121">
+        <v>21</v>
+      </c>
+      <c r="G121" t="s">
+        <v>81</v>
+      </c>
+      <c r="H121" t="s">
+        <v>74</v>
+      </c>
+      <c r="I121">
+        <v>0</v>
+      </c>
+      <c r="J121">
+        <v>1</v>
+      </c>
+      <c r="K121">
+        <v>1</v>
+      </c>
+      <c r="L121">
+        <v>1</v>
+      </c>
+      <c r="M121">
+        <v>2</v>
+      </c>
+      <c r="N121">
+        <v>3</v>
+      </c>
+      <c r="O121" t="s">
+        <v>118</v>
+      </c>
+      <c r="P121" t="s">
+        <v>224</v>
+      </c>
+      <c r="Q121">
+        <v>3.2</v>
+      </c>
+      <c r="R121">
+        <v>2.1</v>
+      </c>
+      <c r="S121">
+        <v>3</v>
+      </c>
+      <c r="T121">
+        <v>1.36</v>
+      </c>
+      <c r="U121">
+        <v>2.88</v>
+      </c>
+      <c r="V121">
+        <v>2.6</v>
+      </c>
+      <c r="W121">
+        <v>1.44</v>
+      </c>
+      <c r="X121">
+        <v>6.7</v>
+      </c>
+      <c r="Y121">
+        <v>1.05</v>
+      </c>
+      <c r="Z121">
+        <v>2.52</v>
+      </c>
+      <c r="AA121">
+        <v>3.06</v>
+      </c>
+      <c r="AB121">
+        <v>2.52</v>
+      </c>
+      <c r="AC121">
+        <v>1.05</v>
+      </c>
+      <c r="AD121">
+        <v>9</v>
+      </c>
+      <c r="AE121">
+        <v>1.28</v>
+      </c>
+      <c r="AF121">
+        <v>3.65</v>
+      </c>
+      <c r="AG121">
+        <v>1.88</v>
+      </c>
+      <c r="AH121">
+        <v>1.82</v>
+      </c>
+      <c r="AI121">
+        <v>1.6</v>
+      </c>
+      <c r="AJ121">
+        <v>2.15</v>
+      </c>
+      <c r="AK121">
+        <v>1.5</v>
+      </c>
+      <c r="AL121">
+        <v>1.28</v>
+      </c>
+      <c r="AM121">
+        <v>1.42</v>
+      </c>
+      <c r="AN121">
+        <v>1.8</v>
+      </c>
+      <c r="AO121">
+        <v>2.44</v>
+      </c>
+      <c r="AP121">
+        <v>1.64</v>
+      </c>
+      <c r="AQ121">
+        <v>2.5</v>
+      </c>
+      <c r="AR121">
+        <v>1.78</v>
+      </c>
+      <c r="AS121">
+        <v>1.35</v>
+      </c>
+      <c r="AT121">
+        <v>3.13</v>
+      </c>
+      <c r="AU121">
+        <v>3</v>
+      </c>
+      <c r="AV121">
+        <v>4</v>
+      </c>
+      <c r="AW121">
+        <v>11</v>
+      </c>
+      <c r="AX121">
+        <v>5</v>
+      </c>
+      <c r="AY121">
+        <v>14</v>
+      </c>
+      <c r="AZ121">
+        <v>9</v>
+      </c>
+      <c r="BA121">
+        <v>7</v>
+      </c>
+      <c r="BB121">
+        <v>6</v>
+      </c>
+      <c r="BC121">
+        <v>13</v>
+      </c>
+      <c r="BD121">
+        <v>1.93</v>
+      </c>
+      <c r="BE121">
+        <v>6.25</v>
+      </c>
+      <c r="BF121">
+        <v>2.08</v>
+      </c>
+      <c r="BG121">
+        <v>1.41</v>
+      </c>
+      <c r="BH121">
+        <v>2.65</v>
+      </c>
+      <c r="BI121">
+        <v>1.68</v>
+      </c>
+      <c r="BJ121">
+        <v>2.05</v>
+      </c>
+      <c r="BK121">
+        <v>2.07</v>
+      </c>
+      <c r="BL121">
+        <v>1.66</v>
+      </c>
+      <c r="BM121">
+        <v>2.65</v>
+      </c>
+      <c r="BN121">
+        <v>1.41</v>
+      </c>
+      <c r="BO121">
+        <v>3.55</v>
+      </c>
+      <c r="BP121">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="122" spans="1:68">
+      <c r="A122" s="1">
+        <v>121</v>
+      </c>
+      <c r="B122">
+        <v>7806879</v>
+      </c>
+      <c r="C122" t="s">
+        <v>68</v>
+      </c>
+      <c r="D122" t="s">
+        <v>69</v>
+      </c>
+      <c r="E122" s="2">
+        <v>45835.3125</v>
+      </c>
+      <c r="F122">
+        <v>21</v>
+      </c>
+      <c r="G122" t="s">
+        <v>77</v>
+      </c>
+      <c r="H122" t="s">
+        <v>71</v>
+      </c>
+      <c r="I122">
+        <v>0</v>
+      </c>
+      <c r="J122">
+        <v>0</v>
+      </c>
+      <c r="K122">
+        <v>0</v>
+      </c>
+      <c r="L122">
+        <v>1</v>
+      </c>
+      <c r="M122">
+        <v>1</v>
+      </c>
+      <c r="N122">
+        <v>2</v>
+      </c>
+      <c r="O122" t="s">
+        <v>161</v>
+      </c>
+      <c r="P122" t="s">
+        <v>225</v>
+      </c>
+      <c r="Q122">
+        <v>2.9</v>
+      </c>
+      <c r="R122">
+        <v>2</v>
+      </c>
+      <c r="S122">
+        <v>3.6</v>
+      </c>
+      <c r="T122">
+        <v>1.42</v>
+      </c>
+      <c r="U122">
+        <v>2.65</v>
+      </c>
+      <c r="V122">
+        <v>2.9</v>
+      </c>
+      <c r="W122">
+        <v>1.36</v>
+      </c>
+      <c r="X122">
+        <v>8</v>
+      </c>
+      <c r="Y122">
+        <v>1.02</v>
+      </c>
+      <c r="Z122">
+        <v>2.21</v>
+      </c>
+      <c r="AA122">
+        <v>3.03</v>
+      </c>
+      <c r="AB122">
+        <v>2.97</v>
+      </c>
+      <c r="AC122">
+        <v>1.07</v>
+      </c>
+      <c r="AD122">
+        <v>8</v>
+      </c>
+      <c r="AE122">
+        <v>1.38</v>
+      </c>
+      <c r="AF122">
+        <v>3</v>
+      </c>
+      <c r="AG122">
+        <v>2.08</v>
+      </c>
+      <c r="AH122">
+        <v>1.66</v>
+      </c>
+      <c r="AI122">
+        <v>1.77</v>
+      </c>
+      <c r="AJ122">
+        <v>1.9</v>
+      </c>
+      <c r="AK122">
+        <v>1.36</v>
+      </c>
+      <c r="AL122">
+        <v>1.28</v>
+      </c>
+      <c r="AM122">
+        <v>1.57</v>
+      </c>
+      <c r="AN122">
+        <v>1.5</v>
+      </c>
+      <c r="AO122">
+        <v>0.9</v>
+      </c>
+      <c r="AP122">
+        <v>1.45</v>
+      </c>
+      <c r="AQ122">
+        <v>0.91</v>
+      </c>
+      <c r="AR122">
+        <v>1.4</v>
+      </c>
+      <c r="AS122">
+        <v>1.52</v>
+      </c>
+      <c r="AT122">
+        <v>2.92</v>
+      </c>
+      <c r="AU122">
+        <v>5</v>
+      </c>
+      <c r="AV122">
+        <v>11</v>
+      </c>
+      <c r="AW122">
+        <v>9</v>
+      </c>
+      <c r="AX122">
+        <v>9</v>
+      </c>
+      <c r="AY122">
+        <v>14</v>
+      </c>
+      <c r="AZ122">
+        <v>20</v>
+      </c>
+      <c r="BA122">
+        <v>5</v>
+      </c>
+      <c r="BB122">
+        <v>3</v>
+      </c>
+      <c r="BC122">
+        <v>8</v>
+      </c>
+      <c r="BD122">
+        <v>2.1</v>
+      </c>
+      <c r="BE122">
+        <v>7.5</v>
+      </c>
+      <c r="BF122">
+        <v>2</v>
+      </c>
+      <c r="BG122">
+        <v>1.44</v>
+      </c>
+      <c r="BH122">
+        <v>2.6</v>
+      </c>
+      <c r="BI122">
+        <v>1.75</v>
+      </c>
+      <c r="BJ122">
+        <v>2.01</v>
+      </c>
+      <c r="BK122">
+        <v>2.21</v>
+      </c>
+      <c r="BL122">
+        <v>1.62</v>
+      </c>
+      <c r="BM122">
+        <v>2.82</v>
+      </c>
+      <c r="BN122">
+        <v>1.38</v>
+      </c>
+      <c r="BO122">
+        <v>3.82</v>
+      </c>
+      <c r="BP122">
+        <v>1.2</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/South Korea K League 1_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/South Korea K League 1_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="794" uniqueCount="226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="806" uniqueCount="228">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -502,6 +502,9 @@
     <t>['78']</t>
   </si>
   <si>
+    <t>['46']</t>
+  </si>
+  <si>
     <t>['32', '87', '90']</t>
   </si>
   <si>
@@ -679,9 +682,6 @@
     <t>['5', '31']</t>
   </si>
   <si>
-    <t>['46']</t>
-  </si>
-  <si>
     <t>['9008']</t>
   </si>
   <si>
@@ -692,6 +692,12 @@
   </si>
   <si>
     <t>['9007']</t>
+  </si>
+  <si>
+    <t>['38', '9001']</t>
+  </si>
+  <si>
+    <t>['12', '38']</t>
   </si>
 </sst>
 </file>
@@ -1053,7 +1059,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP122"/>
+  <dimension ref="A1:BP124"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1309,7 +1315,7 @@
         <v>82</v>
       </c>
       <c r="P2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Q2">
         <v>2.75</v>
@@ -1927,7 +1933,7 @@
         <v>82</v>
       </c>
       <c r="P5" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Q5">
         <v>2.1</v>
@@ -2339,7 +2345,7 @@
         <v>85</v>
       </c>
       <c r="P7" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Q7">
         <v>3.5</v>
@@ -2420,7 +2426,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ7">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2545,7 +2551,7 @@
         <v>86</v>
       </c>
       <c r="P8" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q8">
         <v>3.4</v>
@@ -2751,7 +2757,7 @@
         <v>87</v>
       </c>
       <c r="P9" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q9">
         <v>3.35</v>
@@ -3163,7 +3169,7 @@
         <v>82</v>
       </c>
       <c r="P11" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q11">
         <v>3.45</v>
@@ -3369,7 +3375,7 @@
         <v>89</v>
       </c>
       <c r="P12" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q12">
         <v>2.75</v>
@@ -3450,7 +3456,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ12">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AR12">
         <v>1.8</v>
@@ -3575,7 +3581,7 @@
         <v>90</v>
       </c>
       <c r="P13" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Q13">
         <v>2.95</v>
@@ -5095,7 +5101,7 @@
         <v>0</v>
       </c>
       <c r="AP20">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AQ20">
         <v>1.55</v>
@@ -5223,7 +5229,7 @@
         <v>94</v>
       </c>
       <c r="P21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q21">
         <v>3.1</v>
@@ -5429,7 +5435,7 @@
         <v>95</v>
       </c>
       <c r="P22" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q22">
         <v>3.6</v>
@@ -5507,7 +5513,7 @@
         <v>1.33</v>
       </c>
       <c r="AP22">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AQ22">
         <v>1.4</v>
@@ -5922,7 +5928,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ24">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AR24">
         <v>1.82</v>
@@ -6047,7 +6053,7 @@
         <v>97</v>
       </c>
       <c r="P25" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q25">
         <v>4</v>
@@ -6253,7 +6259,7 @@
         <v>82</v>
       </c>
       <c r="P26" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q26">
         <v>3.6</v>
@@ -6459,7 +6465,7 @@
         <v>82</v>
       </c>
       <c r="P27" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q27">
         <v>2.75</v>
@@ -6665,7 +6671,7 @@
         <v>98</v>
       </c>
       <c r="P28" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q28">
         <v>3.75</v>
@@ -6743,7 +6749,7 @@
         <v>3</v>
       </c>
       <c r="AP28">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AQ28">
         <v>1.5</v>
@@ -6952,7 +6958,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ29">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AR29">
         <v>0</v>
@@ -7077,7 +7083,7 @@
         <v>99</v>
       </c>
       <c r="P30" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q30">
         <v>2.63</v>
@@ -7283,7 +7289,7 @@
         <v>100</v>
       </c>
       <c r="P31" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q31">
         <v>3.1</v>
@@ -7489,7 +7495,7 @@
         <v>101</v>
       </c>
       <c r="P32" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q32">
         <v>2.5</v>
@@ -7901,7 +7907,7 @@
         <v>103</v>
       </c>
       <c r="P34" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q34">
         <v>3.2</v>
@@ -7982,7 +7988,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ34">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AR34">
         <v>1.58</v>
@@ -8394,7 +8400,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ36">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AR36">
         <v>1.94</v>
@@ -8597,7 +8603,7 @@
         <v>0</v>
       </c>
       <c r="AP37">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AQ37">
         <v>2.5</v>
@@ -8725,7 +8731,7 @@
         <v>106</v>
       </c>
       <c r="P38" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q38">
         <v>2.45</v>
@@ -9343,7 +9349,7 @@
         <v>82</v>
       </c>
       <c r="P41" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q41">
         <v>3.25</v>
@@ -9549,7 +9555,7 @@
         <v>98</v>
       </c>
       <c r="P42" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q42">
         <v>3.4</v>
@@ -9627,7 +9633,7 @@
         <v>1.33</v>
       </c>
       <c r="AP42">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AQ42">
         <v>1.3</v>
@@ -9833,10 +9839,10 @@
         <v>1</v>
       </c>
       <c r="AP43">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AQ43">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AR43">
         <v>1.25</v>
@@ -10373,7 +10379,7 @@
         <v>111</v>
       </c>
       <c r="P46" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q46">
         <v>4.33</v>
@@ -10451,7 +10457,7 @@
         <v>1.75</v>
       </c>
       <c r="AP46">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AQ46">
         <v>1.4</v>
@@ -10579,7 +10585,7 @@
         <v>112</v>
       </c>
       <c r="P47" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q47">
         <v>2.6</v>
@@ -11072,7 +11078,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ49">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AR49">
         <v>1.43</v>
@@ -11609,7 +11615,7 @@
         <v>116</v>
       </c>
       <c r="P52" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q52">
         <v>2.38</v>
@@ -11690,7 +11696,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ52">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AR52">
         <v>2.04</v>
@@ -11815,7 +11821,7 @@
         <v>117</v>
       </c>
       <c r="P53" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q53">
         <v>3.1</v>
@@ -11893,7 +11899,7 @@
         <v>0.25</v>
       </c>
       <c r="AP53">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AQ53">
         <v>0.5</v>
@@ -12021,7 +12027,7 @@
         <v>82</v>
       </c>
       <c r="P54" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q54">
         <v>2.75</v>
@@ -12227,7 +12233,7 @@
         <v>118</v>
       </c>
       <c r="P55" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q55">
         <v>2.75</v>
@@ -12308,7 +12314,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ55">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AR55">
         <v>1.28</v>
@@ -12639,7 +12645,7 @@
         <v>120</v>
       </c>
       <c r="P57" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q57">
         <v>2.3</v>
@@ -12845,7 +12851,7 @@
         <v>82</v>
       </c>
       <c r="P58" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q58">
         <v>4.5</v>
@@ -12923,7 +12929,7 @@
         <v>1.75</v>
       </c>
       <c r="AP58">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AQ58">
         <v>1.5</v>
@@ -13051,7 +13057,7 @@
         <v>121</v>
       </c>
       <c r="P59" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q59">
         <v>4</v>
@@ -13129,7 +13135,7 @@
         <v>2</v>
       </c>
       <c r="AP59">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AQ59">
         <v>2.5</v>
@@ -13257,7 +13263,7 @@
         <v>122</v>
       </c>
       <c r="P60" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q60">
         <v>2.7</v>
@@ -13335,7 +13341,7 @@
         <v>0.5</v>
       </c>
       <c r="AP60">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AQ60">
         <v>0.91</v>
@@ -13956,7 +13962,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ63">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AR63">
         <v>1.45</v>
@@ -14162,7 +14168,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ64">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AR64">
         <v>2.07</v>
@@ -14287,7 +14293,7 @@
         <v>105</v>
       </c>
       <c r="P65" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q65">
         <v>3.4</v>
@@ -14493,7 +14499,7 @@
         <v>127</v>
       </c>
       <c r="P66" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Q66">
         <v>2.5</v>
@@ -14905,7 +14911,7 @@
         <v>82</v>
       </c>
       <c r="P68" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q68">
         <v>3</v>
@@ -15317,7 +15323,7 @@
         <v>116</v>
       </c>
       <c r="P70" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q70">
         <v>2.38</v>
@@ -15935,7 +15941,7 @@
         <v>82</v>
       </c>
       <c r="P73" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q73">
         <v>3</v>
@@ -16016,7 +16022,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ73">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AR73">
         <v>1.33</v>
@@ -16141,7 +16147,7 @@
         <v>130</v>
       </c>
       <c r="P74" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q74">
         <v>5</v>
@@ -16219,7 +16225,7 @@
         <v>1</v>
       </c>
       <c r="AP74">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AQ74">
         <v>1.55</v>
@@ -16347,7 +16353,7 @@
         <v>131</v>
       </c>
       <c r="P75" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q75">
         <v>2.88</v>
@@ -16425,7 +16431,7 @@
         <v>0.2</v>
       </c>
       <c r="AP75">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AQ75">
         <v>0.2</v>
@@ -16759,7 +16765,7 @@
         <v>133</v>
       </c>
       <c r="P77" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q77">
         <v>3</v>
@@ -16837,7 +16843,7 @@
         <v>0.17</v>
       </c>
       <c r="AP77">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AQ77">
         <v>0.2</v>
@@ -17171,7 +17177,7 @@
         <v>134</v>
       </c>
       <c r="P79" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q79">
         <v>4.33</v>
@@ -17377,7 +17383,7 @@
         <v>82</v>
       </c>
       <c r="P80" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q80">
         <v>3.6</v>
@@ -17583,7 +17589,7 @@
         <v>82</v>
       </c>
       <c r="P81" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q81">
         <v>3.5</v>
@@ -17995,7 +18001,7 @@
         <v>136</v>
       </c>
       <c r="P83" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q83">
         <v>4.33</v>
@@ -18201,7 +18207,7 @@
         <v>137</v>
       </c>
       <c r="P84" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q84">
         <v>2.4</v>
@@ -18488,7 +18494,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ85">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AR85">
         <v>1.61</v>
@@ -18613,7 +18619,7 @@
         <v>82</v>
       </c>
       <c r="P86" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q86">
         <v>5</v>
@@ -18897,7 +18903,7 @@
         <v>2.43</v>
       </c>
       <c r="AP87">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AQ87">
         <v>1.9</v>
@@ -19231,7 +19237,7 @@
         <v>82</v>
       </c>
       <c r="P89" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q89">
         <v>3.4</v>
@@ -19309,7 +19315,7 @@
         <v>1</v>
       </c>
       <c r="AP89">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AQ89">
         <v>1.3</v>
@@ -19437,7 +19443,7 @@
         <v>139</v>
       </c>
       <c r="P90" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q90">
         <v>2.3</v>
@@ -19643,7 +19649,7 @@
         <v>140</v>
       </c>
       <c r="P91" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q91">
         <v>2.55</v>
@@ -20055,7 +20061,7 @@
         <v>82</v>
       </c>
       <c r="P93" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q93">
         <v>2.88</v>
@@ -20136,7 +20142,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ93">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AR93">
         <v>1.57</v>
@@ -20261,7 +20267,7 @@
         <v>82</v>
       </c>
       <c r="P94" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q94">
         <v>2.8</v>
@@ -20339,7 +20345,7 @@
         <v>0.43</v>
       </c>
       <c r="AP94">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AQ94">
         <v>0.91</v>
@@ -20467,7 +20473,7 @@
         <v>142</v>
       </c>
       <c r="P95" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q95">
         <v>2.62</v>
@@ -20673,7 +20679,7 @@
         <v>82</v>
       </c>
       <c r="P96" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q96">
         <v>4</v>
@@ -20879,7 +20885,7 @@
         <v>82</v>
       </c>
       <c r="P97" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q97">
         <v>3.1</v>
@@ -21085,7 +21091,7 @@
         <v>125</v>
       </c>
       <c r="P98" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q98">
         <v>2.75</v>
@@ -21291,7 +21297,7 @@
         <v>143</v>
       </c>
       <c r="P99" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q99">
         <v>3.4</v>
@@ -21497,7 +21503,7 @@
         <v>134</v>
       </c>
       <c r="P100" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q100">
         <v>3.3</v>
@@ -21575,7 +21581,7 @@
         <v>2.13</v>
       </c>
       <c r="AP100">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AQ100">
         <v>1.9</v>
@@ -21703,7 +21709,7 @@
         <v>144</v>
       </c>
       <c r="P101" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q101">
         <v>3</v>
@@ -21909,7 +21915,7 @@
         <v>145</v>
       </c>
       <c r="P102" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q102">
         <v>2.3</v>
@@ -22115,7 +22121,7 @@
         <v>146</v>
       </c>
       <c r="P103" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q103">
         <v>2.1</v>
@@ -22321,7 +22327,7 @@
         <v>147</v>
       </c>
       <c r="P104" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q104">
         <v>2.55</v>
@@ -22402,7 +22408,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ104">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AR104">
         <v>1.62</v>
@@ -22608,7 +22614,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ105">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AR105">
         <v>1.83</v>
@@ -22733,7 +22739,7 @@
         <v>82</v>
       </c>
       <c r="P106" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q106">
         <v>4.5</v>
@@ -22939,7 +22945,7 @@
         <v>149</v>
       </c>
       <c r="P107" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q107">
         <v>4.33</v>
@@ -23351,7 +23357,7 @@
         <v>151</v>
       </c>
       <c r="P109" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q109">
         <v>3</v>
@@ -23429,7 +23435,7 @@
         <v>1.13</v>
       </c>
       <c r="AP109">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AQ109">
         <v>1.2</v>
@@ -23557,7 +23563,7 @@
         <v>152</v>
       </c>
       <c r="P110" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q110">
         <v>2.5</v>
@@ -23763,7 +23769,7 @@
         <v>153</v>
       </c>
       <c r="P111" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q111">
         <v>4.33</v>
@@ -23969,7 +23975,7 @@
         <v>154</v>
       </c>
       <c r="P112" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q112">
         <v>2.25</v>
@@ -24050,7 +24056,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ112">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AR112">
         <v>1.66</v>
@@ -24175,7 +24181,7 @@
         <v>155</v>
       </c>
       <c r="P113" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q113">
         <v>2.2</v>
@@ -24381,7 +24387,7 @@
         <v>82</v>
       </c>
       <c r="P114" t="s">
-        <v>221</v>
+        <v>162</v>
       </c>
       <c r="Q114">
         <v>3.4</v>
@@ -24462,7 +24468,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ114">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AR114">
         <v>1.5</v>
@@ -25205,7 +25211,7 @@
         <v>158</v>
       </c>
       <c r="P118" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q118">
         <v>3.4</v>
@@ -26186,6 +26192,418 @@
       </c>
       <c r="BP122">
         <v>1.2</v>
+      </c>
+    </row>
+    <row r="123" spans="1:68">
+      <c r="A123" s="1">
+        <v>122</v>
+      </c>
+      <c r="B123">
+        <v>7806880</v>
+      </c>
+      <c r="C123" t="s">
+        <v>68</v>
+      </c>
+      <c r="D123" t="s">
+        <v>69</v>
+      </c>
+      <c r="E123" s="2">
+        <v>45836.29166666666</v>
+      </c>
+      <c r="F123">
+        <v>21</v>
+      </c>
+      <c r="G123" t="s">
+        <v>79</v>
+      </c>
+      <c r="H123" t="s">
+        <v>78</v>
+      </c>
+      <c r="I123">
+        <v>0</v>
+      </c>
+      <c r="J123">
+        <v>1</v>
+      </c>
+      <c r="K123">
+        <v>1</v>
+      </c>
+      <c r="L123">
+        <v>1</v>
+      </c>
+      <c r="M123">
+        <v>2</v>
+      </c>
+      <c r="N123">
+        <v>3</v>
+      </c>
+      <c r="O123" t="s">
+        <v>162</v>
+      </c>
+      <c r="P123" t="s">
+        <v>226</v>
+      </c>
+      <c r="Q123">
+        <v>3.1</v>
+      </c>
+      <c r="R123">
+        <v>2</v>
+      </c>
+      <c r="S123">
+        <v>3.4</v>
+      </c>
+      <c r="T123">
+        <v>1.42</v>
+      </c>
+      <c r="U123">
+        <v>2.65</v>
+      </c>
+      <c r="V123">
+        <v>2.9</v>
+      </c>
+      <c r="W123">
+        <v>1.36</v>
+      </c>
+      <c r="X123">
+        <v>8.6</v>
+      </c>
+      <c r="Y123">
+        <v>1.01</v>
+      </c>
+      <c r="Z123">
+        <v>2.39</v>
+      </c>
+      <c r="AA123">
+        <v>2.97</v>
+      </c>
+      <c r="AB123">
+        <v>2.74</v>
+      </c>
+      <c r="AC123">
+        <v>1.07</v>
+      </c>
+      <c r="AD123">
+        <v>8</v>
+      </c>
+      <c r="AE123">
+        <v>1.36</v>
+      </c>
+      <c r="AF123">
+        <v>3.1</v>
+      </c>
+      <c r="AG123">
+        <v>2.02</v>
+      </c>
+      <c r="AH123">
+        <v>1.7</v>
+      </c>
+      <c r="AI123">
+        <v>1.77</v>
+      </c>
+      <c r="AJ123">
+        <v>1.9</v>
+      </c>
+      <c r="AK123">
+        <v>1.4</v>
+      </c>
+      <c r="AL123">
+        <v>1.28</v>
+      </c>
+      <c r="AM123">
+        <v>1.5</v>
+      </c>
+      <c r="AN123">
+        <v>1.33</v>
+      </c>
+      <c r="AO123">
+        <v>1.3</v>
+      </c>
+      <c r="AP123">
+        <v>1.2</v>
+      </c>
+      <c r="AQ123">
+        <v>1.45</v>
+      </c>
+      <c r="AR123">
+        <v>1.75</v>
+      </c>
+      <c r="AS123">
+        <v>0.97</v>
+      </c>
+      <c r="AT123">
+        <v>2.72</v>
+      </c>
+      <c r="AU123">
+        <v>6</v>
+      </c>
+      <c r="AV123">
+        <v>4</v>
+      </c>
+      <c r="AW123">
+        <v>16</v>
+      </c>
+      <c r="AX123">
+        <v>6</v>
+      </c>
+      <c r="AY123">
+        <v>22</v>
+      </c>
+      <c r="AZ123">
+        <v>10</v>
+      </c>
+      <c r="BA123">
+        <v>6</v>
+      </c>
+      <c r="BB123">
+        <v>4</v>
+      </c>
+      <c r="BC123">
+        <v>10</v>
+      </c>
+      <c r="BD123">
+        <v>1.9</v>
+      </c>
+      <c r="BE123">
+        <v>6.25</v>
+      </c>
+      <c r="BF123">
+        <v>2.1</v>
+      </c>
+      <c r="BG123">
+        <v>1.49</v>
+      </c>
+      <c r="BH123">
+        <v>2.4</v>
+      </c>
+      <c r="BI123">
+        <v>1.88</v>
+      </c>
+      <c r="BJ123">
+        <v>1.92</v>
+      </c>
+      <c r="BK123">
+        <v>2.32</v>
+      </c>
+      <c r="BL123">
+        <v>1.53</v>
+      </c>
+      <c r="BM123">
+        <v>3.05</v>
+      </c>
+      <c r="BN123">
+        <v>1.32</v>
+      </c>
+      <c r="BO123">
+        <v>4.1</v>
+      </c>
+      <c r="BP123">
+        <v>1.19</v>
+      </c>
+    </row>
+    <row r="124" spans="1:68">
+      <c r="A124" s="1">
+        <v>123</v>
+      </c>
+      <c r="B124">
+        <v>7806881</v>
+      </c>
+      <c r="C124" t="s">
+        <v>68</v>
+      </c>
+      <c r="D124" t="s">
+        <v>69</v>
+      </c>
+      <c r="E124" s="2">
+        <v>45836.29166666666</v>
+      </c>
+      <c r="F124">
+        <v>21</v>
+      </c>
+      <c r="G124" t="s">
+        <v>80</v>
+      </c>
+      <c r="H124" t="s">
+        <v>72</v>
+      </c>
+      <c r="I124">
+        <v>1</v>
+      </c>
+      <c r="J124">
+        <v>2</v>
+      </c>
+      <c r="K124">
+        <v>3</v>
+      </c>
+      <c r="L124">
+        <v>1</v>
+      </c>
+      <c r="M124">
+        <v>2</v>
+      </c>
+      <c r="N124">
+        <v>3</v>
+      </c>
+      <c r="O124" t="s">
+        <v>151</v>
+      </c>
+      <c r="P124" t="s">
+        <v>227</v>
+      </c>
+      <c r="Q124">
+        <v>3.7</v>
+      </c>
+      <c r="R124">
+        <v>1.93</v>
+      </c>
+      <c r="S124">
+        <v>3</v>
+      </c>
+      <c r="T124">
+        <v>1.5</v>
+      </c>
+      <c r="U124">
+        <v>2.4</v>
+      </c>
+      <c r="V124">
+        <v>3.3</v>
+      </c>
+      <c r="W124">
+        <v>1.28</v>
+      </c>
+      <c r="X124">
+        <v>9.6</v>
+      </c>
+      <c r="Y124">
+        <v>1.04</v>
+      </c>
+      <c r="Z124">
+        <v>3</v>
+      </c>
+      <c r="AA124">
+        <v>2.87</v>
+      </c>
+      <c r="AB124">
+        <v>2.28</v>
+      </c>
+      <c r="AC124">
+        <v>1.09</v>
+      </c>
+      <c r="AD124">
+        <v>7</v>
+      </c>
+      <c r="AE124">
+        <v>1.48</v>
+      </c>
+      <c r="AF124">
+        <v>2.65</v>
+      </c>
+      <c r="AG124">
+        <v>2.35</v>
+      </c>
+      <c r="AH124">
+        <v>1.52</v>
+      </c>
+      <c r="AI124">
+        <v>1.95</v>
+      </c>
+      <c r="AJ124">
+        <v>1.73</v>
+      </c>
+      <c r="AK124">
+        <v>1.55</v>
+      </c>
+      <c r="AL124">
+        <v>1.3</v>
+      </c>
+      <c r="AM124">
+        <v>1.36</v>
+      </c>
+      <c r="AN124">
+        <v>1.2</v>
+      </c>
+      <c r="AO124">
+        <v>1.44</v>
+      </c>
+      <c r="AP124">
+        <v>1.09</v>
+      </c>
+      <c r="AQ124">
+        <v>1.6</v>
+      </c>
+      <c r="AR124">
+        <v>1.51</v>
+      </c>
+      <c r="AS124">
+        <v>1.13</v>
+      </c>
+      <c r="AT124">
+        <v>2.64</v>
+      </c>
+      <c r="AU124">
+        <v>3</v>
+      </c>
+      <c r="AV124">
+        <v>7</v>
+      </c>
+      <c r="AW124">
+        <v>4</v>
+      </c>
+      <c r="AX124">
+        <v>8</v>
+      </c>
+      <c r="AY124">
+        <v>7</v>
+      </c>
+      <c r="AZ124">
+        <v>15</v>
+      </c>
+      <c r="BA124">
+        <v>2</v>
+      </c>
+      <c r="BB124">
+        <v>4</v>
+      </c>
+      <c r="BC124">
+        <v>6</v>
+      </c>
+      <c r="BD124">
+        <v>2.07</v>
+      </c>
+      <c r="BE124">
+        <v>6.1</v>
+      </c>
+      <c r="BF124">
+        <v>1.95</v>
+      </c>
+      <c r="BG124">
+        <v>1.61</v>
+      </c>
+      <c r="BH124">
+        <v>2.15</v>
+      </c>
+      <c r="BI124">
+        <v>2</v>
+      </c>
+      <c r="BJ124">
+        <v>1.7</v>
+      </c>
+      <c r="BK124">
+        <v>2.6</v>
+      </c>
+      <c r="BL124">
+        <v>1.43</v>
+      </c>
+      <c r="BM124">
+        <v>3.45</v>
+      </c>
+      <c r="BN124">
+        <v>1.25</v>
+      </c>
+      <c r="BO124">
+        <v>4.8</v>
+      </c>
+      <c r="BP124">
+        <v>1.15</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/South Korea K League 1_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/South Korea K League 1_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="806" uniqueCount="228">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="812" uniqueCount="230">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -505,6 +505,9 @@
     <t>['46']</t>
   </si>
   <si>
+    <t>['17', '33', '4504', '85']</t>
+  </si>
+  <si>
     <t>['32', '87', '90']</t>
   </si>
   <si>
@@ -698,6 +701,9 @@
   </si>
   <si>
     <t>['12', '38']</t>
+  </si>
+  <si>
+    <t>['75']</t>
   </si>
 </sst>
 </file>
@@ -1059,7 +1065,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP124"/>
+  <dimension ref="A1:BP125"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1315,7 +1321,7 @@
         <v>82</v>
       </c>
       <c r="P2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Q2">
         <v>2.75</v>
@@ -1933,7 +1939,7 @@
         <v>82</v>
       </c>
       <c r="P5" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Q5">
         <v>2.1</v>
@@ -2345,7 +2351,7 @@
         <v>85</v>
       </c>
       <c r="P7" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q7">
         <v>3.5</v>
@@ -2551,7 +2557,7 @@
         <v>86</v>
       </c>
       <c r="P8" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q8">
         <v>3.4</v>
@@ -2757,7 +2763,7 @@
         <v>87</v>
       </c>
       <c r="P9" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q9">
         <v>3.35</v>
@@ -3041,7 +3047,7 @@
         <v>3</v>
       </c>
       <c r="AP10">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AQ10">
         <v>1.2</v>
@@ -3169,7 +3175,7 @@
         <v>82</v>
       </c>
       <c r="P11" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q11">
         <v>3.45</v>
@@ -3375,7 +3381,7 @@
         <v>89</v>
       </c>
       <c r="P12" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q12">
         <v>2.75</v>
@@ -3581,7 +3587,7 @@
         <v>90</v>
       </c>
       <c r="P13" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q13">
         <v>2.95</v>
@@ -3662,7 +3668,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ13">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -4895,7 +4901,7 @@
         <v>1.5</v>
       </c>
       <c r="AP19">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AQ19">
         <v>1.4</v>
@@ -5229,7 +5235,7 @@
         <v>94</v>
       </c>
       <c r="P21" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q21">
         <v>3.1</v>
@@ -5435,7 +5441,7 @@
         <v>95</v>
       </c>
       <c r="P22" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q22">
         <v>3.6</v>
@@ -6053,7 +6059,7 @@
         <v>97</v>
       </c>
       <c r="P25" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q25">
         <v>4</v>
@@ -6259,7 +6265,7 @@
         <v>82</v>
       </c>
       <c r="P26" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q26">
         <v>3.6</v>
@@ -6465,7 +6471,7 @@
         <v>82</v>
       </c>
       <c r="P27" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q27">
         <v>2.75</v>
@@ -6671,7 +6677,7 @@
         <v>98</v>
       </c>
       <c r="P28" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q28">
         <v>3.75</v>
@@ -7083,7 +7089,7 @@
         <v>99</v>
       </c>
       <c r="P30" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q30">
         <v>2.63</v>
@@ -7164,7 +7170,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ30">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR30">
         <v>1.76</v>
@@ -7289,7 +7295,7 @@
         <v>100</v>
       </c>
       <c r="P31" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q31">
         <v>3.1</v>
@@ -7370,7 +7376,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ31">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR31">
         <v>1.73</v>
@@ -7495,7 +7501,7 @@
         <v>101</v>
       </c>
       <c r="P32" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q32">
         <v>2.5</v>
@@ -7573,7 +7579,7 @@
         <v>1</v>
       </c>
       <c r="AP32">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AQ32">
         <v>0.2</v>
@@ -7907,7 +7913,7 @@
         <v>103</v>
       </c>
       <c r="P34" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q34">
         <v>3.2</v>
@@ -8731,7 +8737,7 @@
         <v>106</v>
       </c>
       <c r="P38" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q38">
         <v>2.45</v>
@@ -9349,7 +9355,7 @@
         <v>82</v>
       </c>
       <c r="P41" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q41">
         <v>3.25</v>
@@ -9555,7 +9561,7 @@
         <v>98</v>
       </c>
       <c r="P42" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q42">
         <v>3.4</v>
@@ -9636,7 +9642,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ42">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR42">
         <v>1.2</v>
@@ -10379,7 +10385,7 @@
         <v>111</v>
       </c>
       <c r="P46" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q46">
         <v>4.33</v>
@@ -10585,7 +10591,7 @@
         <v>112</v>
       </c>
       <c r="P47" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q47">
         <v>2.6</v>
@@ -10663,7 +10669,7 @@
         <v>3</v>
       </c>
       <c r="AP47">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AQ47">
         <v>1.9</v>
@@ -11615,7 +11621,7 @@
         <v>116</v>
       </c>
       <c r="P52" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q52">
         <v>2.38</v>
@@ -11821,7 +11827,7 @@
         <v>117</v>
       </c>
       <c r="P53" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q53">
         <v>3.1</v>
@@ -12027,7 +12033,7 @@
         <v>82</v>
       </c>
       <c r="P54" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q54">
         <v>2.75</v>
@@ -12233,7 +12239,7 @@
         <v>118</v>
       </c>
       <c r="P55" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q55">
         <v>2.75</v>
@@ -12311,7 +12317,7 @@
         <v>0.75</v>
       </c>
       <c r="AP55">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AQ55">
         <v>1.6</v>
@@ -12520,7 +12526,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ56">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR56">
         <v>1.24</v>
@@ -12645,7 +12651,7 @@
         <v>120</v>
       </c>
       <c r="P57" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q57">
         <v>2.3</v>
@@ -12851,7 +12857,7 @@
         <v>82</v>
       </c>
       <c r="P58" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q58">
         <v>4.5</v>
@@ -13057,7 +13063,7 @@
         <v>121</v>
       </c>
       <c r="P59" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q59">
         <v>4</v>
@@ -13263,7 +13269,7 @@
         <v>122</v>
       </c>
       <c r="P60" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q60">
         <v>2.7</v>
@@ -14293,7 +14299,7 @@
         <v>105</v>
       </c>
       <c r="P65" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q65">
         <v>3.4</v>
@@ -14499,7 +14505,7 @@
         <v>127</v>
       </c>
       <c r="P66" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Q66">
         <v>2.5</v>
@@ -14911,7 +14917,7 @@
         <v>82</v>
       </c>
       <c r="P68" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q68">
         <v>3</v>
@@ -14989,7 +14995,7 @@
         <v>2.25</v>
       </c>
       <c r="AP68">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AQ68">
         <v>2.5</v>
@@ -15323,7 +15329,7 @@
         <v>116</v>
       </c>
       <c r="P70" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q70">
         <v>2.38</v>
@@ -15404,7 +15410,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ70">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR70">
         <v>2.06</v>
@@ -15941,7 +15947,7 @@
         <v>82</v>
       </c>
       <c r="P73" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q73">
         <v>3</v>
@@ -16147,7 +16153,7 @@
         <v>130</v>
       </c>
       <c r="P74" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q74">
         <v>5</v>
@@ -16353,7 +16359,7 @@
         <v>131</v>
       </c>
       <c r="P75" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q75">
         <v>2.88</v>
@@ -16765,7 +16771,7 @@
         <v>133</v>
       </c>
       <c r="P77" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q77">
         <v>3</v>
@@ -17177,7 +17183,7 @@
         <v>134</v>
       </c>
       <c r="P79" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q79">
         <v>4.33</v>
@@ -17383,7 +17389,7 @@
         <v>82</v>
       </c>
       <c r="P80" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q80">
         <v>3.6</v>
@@ -17589,7 +17595,7 @@
         <v>82</v>
       </c>
       <c r="P81" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q81">
         <v>3.5</v>
@@ -18001,7 +18007,7 @@
         <v>136</v>
       </c>
       <c r="P83" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q83">
         <v>4.33</v>
@@ -18207,7 +18213,7 @@
         <v>137</v>
       </c>
       <c r="P84" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q84">
         <v>2.4</v>
@@ -18619,7 +18625,7 @@
         <v>82</v>
       </c>
       <c r="P86" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q86">
         <v>5</v>
@@ -19237,7 +19243,7 @@
         <v>82</v>
       </c>
       <c r="P89" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q89">
         <v>3.4</v>
@@ -19318,7 +19324,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ89">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR89">
         <v>1.57</v>
@@ -19443,7 +19449,7 @@
         <v>139</v>
       </c>
       <c r="P90" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q90">
         <v>2.3</v>
@@ -19521,7 +19527,7 @@
         <v>0.29</v>
       </c>
       <c r="AP90">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AQ90">
         <v>0.5</v>
@@ -19649,7 +19655,7 @@
         <v>140</v>
       </c>
       <c r="P91" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q91">
         <v>2.55</v>
@@ -20061,7 +20067,7 @@
         <v>82</v>
       </c>
       <c r="P93" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q93">
         <v>2.88</v>
@@ -20267,7 +20273,7 @@
         <v>82</v>
       </c>
       <c r="P94" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q94">
         <v>2.8</v>
@@ -20473,7 +20479,7 @@
         <v>142</v>
       </c>
       <c r="P95" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q95">
         <v>2.62</v>
@@ -20554,7 +20560,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ95">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR95">
         <v>1.37</v>
@@ -20679,7 +20685,7 @@
         <v>82</v>
       </c>
       <c r="P96" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q96">
         <v>4</v>
@@ -20885,7 +20891,7 @@
         <v>82</v>
       </c>
       <c r="P97" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q97">
         <v>3.1</v>
@@ -21091,7 +21097,7 @@
         <v>125</v>
       </c>
       <c r="P98" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q98">
         <v>2.75</v>
@@ -21297,7 +21303,7 @@
         <v>143</v>
       </c>
       <c r="P99" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q99">
         <v>3.4</v>
@@ -21503,7 +21509,7 @@
         <v>134</v>
       </c>
       <c r="P100" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q100">
         <v>3.3</v>
@@ -21709,7 +21715,7 @@
         <v>144</v>
       </c>
       <c r="P101" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q101">
         <v>3</v>
@@ -21915,7 +21921,7 @@
         <v>145</v>
       </c>
       <c r="P102" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q102">
         <v>2.3</v>
@@ -21993,7 +21999,7 @@
         <v>0.75</v>
       </c>
       <c r="AP102">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AQ102">
         <v>0.91</v>
@@ -22121,7 +22127,7 @@
         <v>146</v>
       </c>
       <c r="P103" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q103">
         <v>2.1</v>
@@ -22327,7 +22333,7 @@
         <v>147</v>
       </c>
       <c r="P104" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q104">
         <v>2.55</v>
@@ -22739,7 +22745,7 @@
         <v>82</v>
       </c>
       <c r="P106" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q106">
         <v>4.5</v>
@@ -22945,7 +22951,7 @@
         <v>149</v>
       </c>
       <c r="P107" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q107">
         <v>4.33</v>
@@ -23232,7 +23238,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ108">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR108">
         <v>1.74</v>
@@ -23357,7 +23363,7 @@
         <v>151</v>
       </c>
       <c r="P109" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q109">
         <v>3</v>
@@ -23563,7 +23569,7 @@
         <v>152</v>
       </c>
       <c r="P110" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q110">
         <v>2.5</v>
@@ -23769,7 +23775,7 @@
         <v>153</v>
       </c>
       <c r="P111" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q111">
         <v>4.33</v>
@@ -23850,7 +23856,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ111">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR111">
         <v>1.83</v>
@@ -23975,7 +23981,7 @@
         <v>154</v>
       </c>
       <c r="P112" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q112">
         <v>2.25</v>
@@ -24053,7 +24059,7 @@
         <v>1.33</v>
       </c>
       <c r="AP112">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AQ112">
         <v>1.45</v>
@@ -24181,7 +24187,7 @@
         <v>155</v>
       </c>
       <c r="P113" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q113">
         <v>2.2</v>
@@ -25005,7 +25011,7 @@
         <v>157</v>
       </c>
       <c r="P117" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q117">
         <v>2.5</v>
@@ -25211,7 +25217,7 @@
         <v>158</v>
       </c>
       <c r="P118" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q118">
         <v>3.4</v>
@@ -25623,7 +25629,7 @@
         <v>160</v>
       </c>
       <c r="P120" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q120">
         <v>2.7</v>
@@ -25829,7 +25835,7 @@
         <v>118</v>
       </c>
       <c r="P121" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q121">
         <v>3.2</v>
@@ -26035,7 +26041,7 @@
         <v>161</v>
       </c>
       <c r="P122" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q122">
         <v>2.9</v>
@@ -26241,7 +26247,7 @@
         <v>162</v>
       </c>
       <c r="P123" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q123">
         <v>3.1</v>
@@ -26447,7 +26453,7 @@
         <v>151</v>
       </c>
       <c r="P124" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q124">
         <v>3.7</v>
@@ -26604,6 +26610,212 @@
       </c>
       <c r="BP124">
         <v>1.15</v>
+      </c>
+    </row>
+    <row r="125" spans="1:68">
+      <c r="A125" s="1">
+        <v>124</v>
+      </c>
+      <c r="B125">
+        <v>7806883</v>
+      </c>
+      <c r="C125" t="s">
+        <v>68</v>
+      </c>
+      <c r="D125" t="s">
+        <v>69</v>
+      </c>
+      <c r="E125" s="2">
+        <v>45837.29166666666</v>
+      </c>
+      <c r="F125">
+        <v>21</v>
+      </c>
+      <c r="G125" t="s">
+        <v>76</v>
+      </c>
+      <c r="H125" t="s">
+        <v>70</v>
+      </c>
+      <c r="I125">
+        <v>3</v>
+      </c>
+      <c r="J125">
+        <v>0</v>
+      </c>
+      <c r="K125">
+        <v>3</v>
+      </c>
+      <c r="L125">
+        <v>4</v>
+      </c>
+      <c r="M125">
+        <v>1</v>
+      </c>
+      <c r="N125">
+        <v>5</v>
+      </c>
+      <c r="O125" t="s">
+        <v>163</v>
+      </c>
+      <c r="P125" t="s">
+        <v>229</v>
+      </c>
+      <c r="Q125">
+        <v>2.75</v>
+      </c>
+      <c r="R125">
+        <v>2.05</v>
+      </c>
+      <c r="S125">
+        <v>4.5</v>
+      </c>
+      <c r="T125">
+        <v>1.5</v>
+      </c>
+      <c r="U125">
+        <v>2.5</v>
+      </c>
+      <c r="V125">
+        <v>3.4</v>
+      </c>
+      <c r="W125">
+        <v>1.3</v>
+      </c>
+      <c r="X125">
+        <v>10</v>
+      </c>
+      <c r="Y125">
+        <v>1.06</v>
+      </c>
+      <c r="Z125">
+        <v>1.94</v>
+      </c>
+      <c r="AA125">
+        <v>3.08</v>
+      </c>
+      <c r="AB125">
+        <v>3.58</v>
+      </c>
+      <c r="AC125">
+        <v>1.08</v>
+      </c>
+      <c r="AD125">
+        <v>7.5</v>
+      </c>
+      <c r="AE125">
+        <v>1.42</v>
+      </c>
+      <c r="AF125">
+        <v>2.8</v>
+      </c>
+      <c r="AG125">
+        <v>2.13</v>
+      </c>
+      <c r="AH125">
+        <v>1.63</v>
+      </c>
+      <c r="AI125">
+        <v>2</v>
+      </c>
+      <c r="AJ125">
+        <v>1.73</v>
+      </c>
+      <c r="AK125">
+        <v>1.25</v>
+      </c>
+      <c r="AL125">
+        <v>1.28</v>
+      </c>
+      <c r="AM125">
+        <v>1.75</v>
+      </c>
+      <c r="AN125">
+        <v>1.11</v>
+      </c>
+      <c r="AO125">
+        <v>1.3</v>
+      </c>
+      <c r="AP125">
+        <v>1.3</v>
+      </c>
+      <c r="AQ125">
+        <v>1.18</v>
+      </c>
+      <c r="AR125">
+        <v>1.64</v>
+      </c>
+      <c r="AS125">
+        <v>1.46</v>
+      </c>
+      <c r="AT125">
+        <v>3.1</v>
+      </c>
+      <c r="AU125">
+        <v>5</v>
+      </c>
+      <c r="AV125">
+        <v>2</v>
+      </c>
+      <c r="AW125">
+        <v>10</v>
+      </c>
+      <c r="AX125">
+        <v>3</v>
+      </c>
+      <c r="AY125">
+        <v>15</v>
+      </c>
+      <c r="AZ125">
+        <v>5</v>
+      </c>
+      <c r="BA125">
+        <v>7</v>
+      </c>
+      <c r="BB125">
+        <v>4</v>
+      </c>
+      <c r="BC125">
+        <v>11</v>
+      </c>
+      <c r="BD125">
+        <v>1.7</v>
+      </c>
+      <c r="BE125">
+        <v>6.4</v>
+      </c>
+      <c r="BF125">
+        <v>2.4</v>
+      </c>
+      <c r="BG125">
+        <v>1.45</v>
+      </c>
+      <c r="BH125">
+        <v>2.55</v>
+      </c>
+      <c r="BI125">
+        <v>1.74</v>
+      </c>
+      <c r="BJ125">
+        <v>1.96</v>
+      </c>
+      <c r="BK125">
+        <v>2.18</v>
+      </c>
+      <c r="BL125">
+        <v>1.58</v>
+      </c>
+      <c r="BM125">
+        <v>2.8</v>
+      </c>
+      <c r="BN125">
+        <v>1.36</v>
+      </c>
+      <c r="BO125">
+        <v>3.8</v>
+      </c>
+      <c r="BP125">
+        <v>1.22</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/South Korea K League 1_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/South Korea K League 1_2025.xlsx
@@ -26752,22 +26752,22 @@
         <v>3.1</v>
       </c>
       <c r="AU125">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="AV125">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AW125">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AX125">
         <v>3</v>
       </c>
       <c r="AY125">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="AZ125">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="BA125">
         <v>7</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/South Korea K League 1_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/South Korea K League 1_2025.xlsx
@@ -457,13 +457,13 @@
     <t>['77']</t>
   </si>
   <si>
-    <t>['4502', '69']</t>
+    <t>['45+2', '69']</t>
   </si>
   <si>
     <t>['67']</t>
   </si>
   <si>
-    <t>['9005']</t>
+    <t>['90+5']</t>
   </si>
   <si>
     <t>['29']</t>
@@ -481,16 +481,16 @@
     <t>['72']</t>
   </si>
   <si>
-    <t>['52', '72']</t>
+    <t>['52', '72', '89']</t>
   </si>
   <si>
     <t>['45', '74', '78']</t>
   </si>
   <si>
-    <t>['63', '9001']</t>
+    <t>['63', '90+1']</t>
   </si>
   <si>
-    <t>['4502']</t>
+    <t>['45+2']</t>
   </si>
   <si>
     <t>['84']</t>
@@ -505,7 +505,7 @@
     <t>['46']</t>
   </si>
   <si>
-    <t>['17', '33', '4504', '85']</t>
+    <t>['17', '33', '45+4', '85']</t>
   </si>
   <si>
     <t>['32', '87', '90']</t>
@@ -685,7 +685,7 @@
     <t>['5', '31']</t>
   </si>
   <si>
-    <t>['9008']</t>
+    <t>['90+8']</t>
   </si>
   <si>
     <t>['69', '78']</t>
@@ -694,10 +694,10 @@
     <t>['37', '53']</t>
   </si>
   <si>
-    <t>['9007']</t>
+    <t>['90+6']</t>
   </si>
   <si>
-    <t>['38', '9001']</t>
+    <t>['38', '90+1']</t>
   </si>
   <si>
     <t>['12', '38']</t>
@@ -1814,7 +1814,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ4">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2223,7 +2223,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>1.64</v>
+        <v>1.82</v>
       </c>
       <c r="AQ6">
         <v>1.4</v>
@@ -2844,7 +2844,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ9">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AR9">
         <v>1.95</v>
@@ -3459,7 +3459,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>1.64</v>
+        <v>1.82</v>
       </c>
       <c r="AQ12">
         <v>1.6</v>
@@ -4492,7 +4492,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ17">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AR17">
         <v>1.3</v>
@@ -5931,7 +5931,7 @@
         <v>0</v>
       </c>
       <c r="AP24">
-        <v>1.64</v>
+        <v>1.82</v>
       </c>
       <c r="AQ24">
         <v>1.45</v>
@@ -7167,7 +7167,7 @@
         <v>0</v>
       </c>
       <c r="AP30">
-        <v>1.64</v>
+        <v>1.82</v>
       </c>
       <c r="AQ30">
         <v>1.18</v>
@@ -8200,7 +8200,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ35">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AR35">
         <v>1.17</v>
@@ -11287,7 +11287,7 @@
         <v>0.33</v>
       </c>
       <c r="AP50">
-        <v>1.64</v>
+        <v>1.82</v>
       </c>
       <c r="AQ50">
         <v>0.91</v>
@@ -11908,7 +11908,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ53">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AR53">
         <v>1.51</v>
@@ -12729,7 +12729,7 @@
         <v>0.25</v>
       </c>
       <c r="AP57">
-        <v>1.64</v>
+        <v>1.82</v>
       </c>
       <c r="AQ57">
         <v>0.2</v>
@@ -15204,7 +15204,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ69">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AR69">
         <v>1.43</v>
@@ -15819,7 +15819,7 @@
         <v>2.67</v>
       </c>
       <c r="AP72">
-        <v>1.64</v>
+        <v>1.82</v>
       </c>
       <c r="AQ72">
         <v>1.9</v>
@@ -16646,7 +16646,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ76">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AR76">
         <v>1.63</v>
@@ -17879,7 +17879,7 @@
         <v>1</v>
       </c>
       <c r="AP82">
-        <v>1.64</v>
+        <v>1.82</v>
       </c>
       <c r="AQ82">
         <v>1.2</v>
@@ -19530,7 +19530,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ90">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AR90">
         <v>1.6</v>
@@ -21793,7 +21793,7 @@
         <v>1.67</v>
       </c>
       <c r="AP101">
-        <v>1.64</v>
+        <v>1.82</v>
       </c>
       <c r="AQ101">
         <v>1.5</v>
@@ -22208,7 +22208,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ103">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AR103">
         <v>1.74</v>
@@ -24175,13 +24175,13 @@
         <v>2</v>
       </c>
       <c r="L113">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M113">
         <v>2</v>
       </c>
       <c r="N113">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O113" t="s">
         <v>155</v>
@@ -24265,10 +24265,10 @@
         <v>0.44</v>
       </c>
       <c r="AP113">
-        <v>1.64</v>
+        <v>1.82</v>
       </c>
       <c r="AQ113">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AR113">
         <v>1.6</v>
@@ -25289,13 +25289,13 @@
         <v>1.42</v>
       </c>
       <c r="AN118">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="AO118">
         <v>1.6</v>
       </c>
       <c r="AP118">
-        <v>1.64</v>
+        <v>1.82</v>
       </c>
       <c r="AQ118">
         <v>1.55</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/South Korea K League 1_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/South Korea K League 1_2025.xlsx
@@ -22841,19 +22841,19 @@
         <v>4</v>
       </c>
       <c r="AV106">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AW106">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="AX106">
+        <v>4</v>
+      </c>
+      <c r="AY106">
         <v>7</v>
       </c>
-      <c r="AY106">
-        <v>17</v>
-      </c>
       <c r="AZ106">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="BA106">
         <v>5</v>
@@ -23044,31 +23044,31 @@
         <v>3.32</v>
       </c>
       <c r="AU107">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AV107">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AW107">
         <v>9</v>
       </c>
       <c r="AX107">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AY107">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AZ107">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA107">
         <v>5</v>
       </c>
       <c r="BB107">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BC107">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BD107">
         <v>2.17</v>
@@ -23671,13 +23671,13 @@
         <v>5</v>
       </c>
       <c r="AX110">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AY110">
         <v>10</v>
       </c>
       <c r="AZ110">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BA110">
         <v>7</v>
@@ -23862,37 +23862,37 @@
         <v>1.83</v>
       </c>
       <c r="AS111">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="AT111">
-        <v>3.31</v>
+        <v>3.35</v>
       </c>
       <c r="AU111">
+        <v>6</v>
+      </c>
+      <c r="AV111">
+        <v>7</v>
+      </c>
+      <c r="AW111">
+        <v>7</v>
+      </c>
+      <c r="AX111">
+        <v>3</v>
+      </c>
+      <c r="AY111">
+        <v>13</v>
+      </c>
+      <c r="AZ111">
+        <v>10</v>
+      </c>
+      <c r="BA111">
+        <v>2</v>
+      </c>
+      <c r="BB111">
         <v>5</v>
       </c>
-      <c r="AV111">
-        <v>6</v>
-      </c>
-      <c r="AW111">
-        <v>9</v>
-      </c>
-      <c r="AX111">
-        <v>2</v>
-      </c>
-      <c r="AY111">
-        <v>14</v>
-      </c>
-      <c r="AZ111">
-        <v>8</v>
-      </c>
-      <c r="BA111">
-        <v>2</v>
-      </c>
-      <c r="BB111">
-        <v>4</v>
-      </c>
       <c r="BC111">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BD111">
         <v>2.18</v>
@@ -24074,22 +24074,22 @@
         <v>2.58</v>
       </c>
       <c r="AU112">
+        <v>5</v>
+      </c>
+      <c r="AV112">
+        <v>5</v>
+      </c>
+      <c r="AW112">
         <v>4</v>
       </c>
-      <c r="AV112">
-        <v>6</v>
-      </c>
-      <c r="AW112">
+      <c r="AX112">
+        <v>5</v>
+      </c>
+      <c r="AY112">
+        <v>9</v>
+      </c>
+      <c r="AZ112">
         <v>10</v>
-      </c>
-      <c r="AX112">
-        <v>6</v>
-      </c>
-      <c r="AY112">
-        <v>14</v>
-      </c>
-      <c r="AZ112">
-        <v>12</v>
       </c>
       <c r="BA112">
         <v>5</v>
@@ -24280,13 +24280,13 @@
         <v>2.87</v>
       </c>
       <c r="AU113">
+        <v>5</v>
+      </c>
+      <c r="AV113">
+        <v>7</v>
+      </c>
+      <c r="AW113">
         <v>6</v>
-      </c>
-      <c r="AV113">
-        <v>6</v>
-      </c>
-      <c r="AW113">
-        <v>5</v>
       </c>
       <c r="AX113">
         <v>5</v>
@@ -24295,7 +24295,7 @@
         <v>11</v>
       </c>
       <c r="AZ113">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BA113">
         <v>8</v>
@@ -24492,16 +24492,16 @@
         <v>5</v>
       </c>
       <c r="AW114">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AX114">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AY114">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AZ114">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BA114">
         <v>2</v>
@@ -24692,22 +24692,22 @@
         <v>3.13</v>
       </c>
       <c r="AU115">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AV115">
+        <v>7</v>
+      </c>
+      <c r="AW115">
         <v>6</v>
       </c>
-      <c r="AW115">
-        <v>8</v>
-      </c>
       <c r="AX115">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AY115">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ115">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BA115">
         <v>7</v>
@@ -24889,13 +24889,13 @@
         <v>0.2</v>
       </c>
       <c r="AR116">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AS116">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AT116">
-        <v>2.87</v>
+        <v>2.83</v>
       </c>
       <c r="AU116">
         <v>7</v>
@@ -25301,13 +25301,13 @@
         <v>1.55</v>
       </c>
       <c r="AR118">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AS118">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="AT118">
-        <v>3.38</v>
+        <v>3.39</v>
       </c>
       <c r="AU118">
         <v>4</v>
@@ -25507,31 +25507,31 @@
         <v>1.2</v>
       </c>
       <c r="AR119">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AS119">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AT119">
-        <v>3.23</v>
+        <v>3.18</v>
       </c>
       <c r="AU119">
         <v>3</v>
       </c>
       <c r="AV119">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AW119">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="AX119">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AY119">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="AZ119">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA119">
         <v>8</v>
@@ -25713,31 +25713,31 @@
         <v>1.9</v>
       </c>
       <c r="AR120">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AS120">
         <v>1.25</v>
       </c>
       <c r="AT120">
-        <v>2.77</v>
+        <v>2.78</v>
       </c>
       <c r="AU120">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AV120">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AW120">
         <v>5</v>
       </c>
       <c r="AX120">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AY120">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AZ120">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="BA120">
         <v>4</v>
@@ -25919,22 +25919,22 @@
         <v>2.5</v>
       </c>
       <c r="AR121">
-        <v>1.78</v>
+        <v>1.74</v>
       </c>
       <c r="AS121">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
       <c r="AT121">
-        <v>3.13</v>
+        <v>3.01</v>
       </c>
       <c r="AU121">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AV121">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AW121">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AX121">
         <v>5</v>
@@ -25943,7 +25943,7 @@
         <v>14</v>
       </c>
       <c r="AZ121">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="BA121">
         <v>7</v>
@@ -26125,31 +26125,31 @@
         <v>0.91</v>
       </c>
       <c r="AR122">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="AS122">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AT122">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="AU122">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AV122">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AW122">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="AX122">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AY122">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="AZ122">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="BA122">
         <v>5</v>
@@ -26331,13 +26331,13 @@
         <v>1.45</v>
       </c>
       <c r="AR123">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AS123">
-        <v>0.97</v>
+        <v>0.92</v>
       </c>
       <c r="AT123">
-        <v>2.72</v>
+        <v>2.69</v>
       </c>
       <c r="AU123">
         <v>6</v>
@@ -26346,16 +26346,16 @@
         <v>4</v>
       </c>
       <c r="AW123">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AX123">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AY123">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="AZ123">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA123">
         <v>6</v>
@@ -26540,28 +26540,28 @@
         <v>1.51</v>
       </c>
       <c r="AS124">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="AT124">
-        <v>2.64</v>
+        <v>2.58</v>
       </c>
       <c r="AU124">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AV124">
+        <v>9</v>
+      </c>
+      <c r="AW124">
+        <v>6</v>
+      </c>
+      <c r="AX124">
         <v>7</v>
       </c>
-      <c r="AW124">
-        <v>4</v>
-      </c>
-      <c r="AX124">
-        <v>8</v>
-      </c>
       <c r="AY124">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AZ124">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BA124">
         <v>2</v>
@@ -26743,28 +26743,28 @@
         <v>1.18</v>
       </c>
       <c r="AR125">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="AS125">
-        <v>1.46</v>
+        <v>1.52</v>
       </c>
       <c r="AT125">
-        <v>3.1</v>
+        <v>3.18</v>
       </c>
       <c r="AU125">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AV125">
+        <v>3</v>
+      </c>
+      <c r="AW125">
+        <v>7</v>
+      </c>
+      <c r="AX125">
         <v>4</v>
       </c>
-      <c r="AW125">
-        <v>11</v>
-      </c>
-      <c r="AX125">
-        <v>3</v>
-      </c>
       <c r="AY125">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="AZ125">
         <v>7</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/South Korea K League 1_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/South Korea K League 1_2025.xlsx
@@ -22841,19 +22841,19 @@
         <v>4</v>
       </c>
       <c r="AV106">
+        <v>8</v>
+      </c>
+      <c r="AW106">
+        <v>13</v>
+      </c>
+      <c r="AX106">
         <v>7</v>
       </c>
-      <c r="AW106">
-        <v>3</v>
-      </c>
-      <c r="AX106">
-        <v>4</v>
-      </c>
       <c r="AY106">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="AZ106">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="BA106">
         <v>5</v>
@@ -23044,31 +23044,31 @@
         <v>3.32</v>
       </c>
       <c r="AU107">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV107">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW107">
         <v>9</v>
       </c>
       <c r="AX107">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AY107">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ107">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BA107">
         <v>5</v>
       </c>
       <c r="BB107">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BC107">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BD107">
         <v>2.17</v>
@@ -23671,13 +23671,13 @@
         <v>5</v>
       </c>
       <c r="AX110">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AY110">
         <v>10</v>
       </c>
       <c r="AZ110">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA110">
         <v>7</v>
@@ -23862,37 +23862,37 @@
         <v>1.83</v>
       </c>
       <c r="AS111">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="AT111">
-        <v>3.35</v>
+        <v>3.31</v>
       </c>
       <c r="AU111">
+        <v>5</v>
+      </c>
+      <c r="AV111">
         <v>6</v>
       </c>
-      <c r="AV111">
-        <v>7</v>
-      </c>
       <c r="AW111">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AX111">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AY111">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AZ111">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BA111">
         <v>2</v>
       </c>
       <c r="BB111">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BC111">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BD111">
         <v>2.18</v>
@@ -24074,22 +24074,22 @@
         <v>2.58</v>
       </c>
       <c r="AU112">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV112">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AW112">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="AX112">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AY112">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="AZ112">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BA112">
         <v>5</v>
@@ -24280,13 +24280,13 @@
         <v>2.87</v>
       </c>
       <c r="AU113">
+        <v>6</v>
+      </c>
+      <c r="AV113">
+        <v>6</v>
+      </c>
+      <c r="AW113">
         <v>5</v>
-      </c>
-      <c r="AV113">
-        <v>7</v>
-      </c>
-      <c r="AW113">
-        <v>6</v>
       </c>
       <c r="AX113">
         <v>5</v>
@@ -24295,7 +24295,7 @@
         <v>11</v>
       </c>
       <c r="AZ113">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA113">
         <v>8</v>
@@ -24492,16 +24492,16 @@
         <v>5</v>
       </c>
       <c r="AW114">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AX114">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AY114">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AZ114">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="BA114">
         <v>2</v>
@@ -24692,22 +24692,22 @@
         <v>3.13</v>
       </c>
       <c r="AU115">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV115">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW115">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AX115">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AY115">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AZ115">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BA115">
         <v>7</v>
@@ -24889,13 +24889,13 @@
         <v>0.2</v>
       </c>
       <c r="AR116">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="AS116">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AT116">
-        <v>2.83</v>
+        <v>2.87</v>
       </c>
       <c r="AU116">
         <v>7</v>
@@ -25301,13 +25301,13 @@
         <v>1.55</v>
       </c>
       <c r="AR118">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AS118">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="AT118">
-        <v>3.39</v>
+        <v>3.38</v>
       </c>
       <c r="AU118">
         <v>4</v>
@@ -25507,31 +25507,31 @@
         <v>1.2</v>
       </c>
       <c r="AR119">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AS119">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="AT119">
-        <v>3.18</v>
+        <v>3.23</v>
       </c>
       <c r="AU119">
         <v>3</v>
       </c>
       <c r="AV119">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AW119">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="AX119">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AY119">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="AZ119">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BA119">
         <v>8</v>
@@ -25713,31 +25713,31 @@
         <v>1.9</v>
       </c>
       <c r="AR120">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AS120">
         <v>1.25</v>
       </c>
       <c r="AT120">
-        <v>2.78</v>
+        <v>2.77</v>
       </c>
       <c r="AU120">
+        <v>4</v>
+      </c>
+      <c r="AV120">
         <v>6</v>
-      </c>
-      <c r="AV120">
-        <v>8</v>
       </c>
       <c r="AW120">
         <v>5</v>
       </c>
       <c r="AX120">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AY120">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AZ120">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BA120">
         <v>4</v>
@@ -25919,22 +25919,22 @@
         <v>2.5</v>
       </c>
       <c r="AR121">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="AS121">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
       <c r="AT121">
-        <v>3.01</v>
+        <v>3.13</v>
       </c>
       <c r="AU121">
+        <v>3</v>
+      </c>
+      <c r="AV121">
         <v>4</v>
       </c>
-      <c r="AV121">
-        <v>6</v>
-      </c>
       <c r="AW121">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AX121">
         <v>5</v>
@@ -25943,7 +25943,7 @@
         <v>14</v>
       </c>
       <c r="AZ121">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BA121">
         <v>7</v>
@@ -26125,31 +26125,31 @@
         <v>0.91</v>
       </c>
       <c r="AR122">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AS122">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AT122">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="AU122">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV122">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AW122">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="AX122">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AY122">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="AZ122">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BA122">
         <v>5</v>
@@ -26331,13 +26331,13 @@
         <v>1.45</v>
       </c>
       <c r="AR123">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AS123">
-        <v>0.92</v>
+        <v>0.97</v>
       </c>
       <c r="AT123">
-        <v>2.69</v>
+        <v>2.72</v>
       </c>
       <c r="AU123">
         <v>6</v>
@@ -26346,16 +26346,16 @@
         <v>4</v>
       </c>
       <c r="AW123">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="AX123">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AY123">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="AZ123">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BA123">
         <v>6</v>
@@ -26540,28 +26540,28 @@
         <v>1.51</v>
       </c>
       <c r="AS124">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="AT124">
-        <v>2.58</v>
+        <v>2.64</v>
       </c>
       <c r="AU124">
+        <v>3</v>
+      </c>
+      <c r="AV124">
+        <v>7</v>
+      </c>
+      <c r="AW124">
         <v>4</v>
       </c>
-      <c r="AV124">
-        <v>9</v>
-      </c>
-      <c r="AW124">
-        <v>6</v>
-      </c>
       <c r="AX124">
+        <v>8</v>
+      </c>
+      <c r="AY124">
         <v>7</v>
       </c>
-      <c r="AY124">
-        <v>10</v>
-      </c>
       <c r="AZ124">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BA124">
         <v>2</v>
@@ -26743,28 +26743,28 @@
         <v>1.18</v>
       </c>
       <c r="AR125">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="AS125">
-        <v>1.52</v>
+        <v>1.46</v>
       </c>
       <c r="AT125">
-        <v>3.18</v>
+        <v>3.1</v>
       </c>
       <c r="AU125">
+        <v>14</v>
+      </c>
+      <c r="AV125">
+        <v>4</v>
+      </c>
+      <c r="AW125">
         <v>11</v>
       </c>
-      <c r="AV125">
+      <c r="AX125">
         <v>3</v>
       </c>
-      <c r="AW125">
-        <v>7</v>
-      </c>
-      <c r="AX125">
-        <v>4</v>
-      </c>
       <c r="AY125">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="AZ125">
         <v>7</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/South Korea K League 1_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/South Korea K League 1_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="812" uniqueCount="230">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="818" uniqueCount="232">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -508,6 +508,9 @@
     <t>['17', '33', '45+4', '85']</t>
   </si>
   <si>
+    <t>['64', '79']</t>
+  </si>
+  <si>
     <t>['32', '87', '90']</t>
   </si>
   <si>
@@ -704,6 +707,9 @@
   </si>
   <si>
     <t>['75']</t>
+  </si>
+  <si>
+    <t>['33', '87']</t>
   </si>
 </sst>
 </file>
@@ -1065,7 +1071,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP125"/>
+  <dimension ref="A1:BP126"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1321,7 +1327,7 @@
         <v>82</v>
       </c>
       <c r="P2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Q2">
         <v>2.75</v>
@@ -1939,7 +1945,7 @@
         <v>82</v>
       </c>
       <c r="P5" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q5">
         <v>2.1</v>
@@ -2017,7 +2023,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AQ5">
         <v>1.2</v>
@@ -2351,7 +2357,7 @@
         <v>85</v>
       </c>
       <c r="P7" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q7">
         <v>3.5</v>
@@ -2557,7 +2563,7 @@
         <v>86</v>
       </c>
       <c r="P8" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q8">
         <v>3.4</v>
@@ -2763,7 +2769,7 @@
         <v>87</v>
       </c>
       <c r="P9" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q9">
         <v>3.35</v>
@@ -3175,7 +3181,7 @@
         <v>82</v>
       </c>
       <c r="P11" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q11">
         <v>3.45</v>
@@ -3381,7 +3387,7 @@
         <v>89</v>
       </c>
       <c r="P12" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q12">
         <v>2.75</v>
@@ -3587,7 +3593,7 @@
         <v>90</v>
       </c>
       <c r="P13" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q13">
         <v>2.95</v>
@@ -3871,7 +3877,7 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AQ14">
         <v>2.5</v>
@@ -4080,7 +4086,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ15">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="AR15">
         <v>1.87</v>
@@ -5235,7 +5241,7 @@
         <v>94</v>
       </c>
       <c r="P21" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q21">
         <v>3.1</v>
@@ -5441,7 +5447,7 @@
         <v>95</v>
       </c>
       <c r="P22" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q22">
         <v>3.6</v>
@@ -5725,7 +5731,7 @@
         <v>1</v>
       </c>
       <c r="AP23">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AQ23">
         <v>0.91</v>
@@ -6059,7 +6065,7 @@
         <v>97</v>
       </c>
       <c r="P25" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q25">
         <v>4</v>
@@ -6265,7 +6271,7 @@
         <v>82</v>
       </c>
       <c r="P26" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q26">
         <v>3.6</v>
@@ -6471,7 +6477,7 @@
         <v>82</v>
       </c>
       <c r="P27" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q27">
         <v>2.75</v>
@@ -6677,7 +6683,7 @@
         <v>98</v>
       </c>
       <c r="P28" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q28">
         <v>3.75</v>
@@ -7089,7 +7095,7 @@
         <v>99</v>
       </c>
       <c r="P30" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q30">
         <v>2.63</v>
@@ -7295,7 +7301,7 @@
         <v>100</v>
       </c>
       <c r="P31" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q31">
         <v>3.1</v>
@@ -7501,7 +7507,7 @@
         <v>101</v>
       </c>
       <c r="P32" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q32">
         <v>2.5</v>
@@ -7582,7 +7588,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ32">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="AR32">
         <v>0.86</v>
@@ -7913,7 +7919,7 @@
         <v>103</v>
       </c>
       <c r="P34" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q34">
         <v>3.2</v>
@@ -8737,7 +8743,7 @@
         <v>106</v>
       </c>
       <c r="P38" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q38">
         <v>2.45</v>
@@ -8815,7 +8821,7 @@
         <v>3</v>
       </c>
       <c r="AP38">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AQ38">
         <v>1.9</v>
@@ -9021,7 +9027,7 @@
         <v>1.33</v>
       </c>
       <c r="AP39">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AQ39">
         <v>1.55</v>
@@ -9230,7 +9236,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ40">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="AR40">
         <v>1.95</v>
@@ -9355,7 +9361,7 @@
         <v>82</v>
       </c>
       <c r="P41" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q41">
         <v>3.25</v>
@@ -9561,7 +9567,7 @@
         <v>98</v>
       </c>
       <c r="P42" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q42">
         <v>3.4</v>
@@ -10260,7 +10266,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ45">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="AR45">
         <v>1.77</v>
@@ -10385,7 +10391,7 @@
         <v>111</v>
       </c>
       <c r="P46" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q46">
         <v>4.33</v>
@@ -10591,7 +10597,7 @@
         <v>112</v>
       </c>
       <c r="P47" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q47">
         <v>2.6</v>
@@ -11621,7 +11627,7 @@
         <v>116</v>
       </c>
       <c r="P52" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q52">
         <v>2.38</v>
@@ -11699,7 +11705,7 @@
         <v>0.75</v>
       </c>
       <c r="AP52">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AQ52">
         <v>1.45</v>
@@ -11827,7 +11833,7 @@
         <v>117</v>
       </c>
       <c r="P53" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q53">
         <v>3.1</v>
@@ -12033,7 +12039,7 @@
         <v>82</v>
       </c>
       <c r="P54" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q54">
         <v>2.75</v>
@@ -12239,7 +12245,7 @@
         <v>118</v>
       </c>
       <c r="P55" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q55">
         <v>2.75</v>
@@ -12651,7 +12657,7 @@
         <v>120</v>
       </c>
       <c r="P57" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q57">
         <v>2.3</v>
@@ -12732,7 +12738,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ57">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="AR57">
         <v>1.63</v>
@@ -12857,7 +12863,7 @@
         <v>82</v>
       </c>
       <c r="P58" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q58">
         <v>4.5</v>
@@ -13063,7 +13069,7 @@
         <v>121</v>
       </c>
       <c r="P59" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q59">
         <v>4</v>
@@ -13269,7 +13275,7 @@
         <v>122</v>
       </c>
       <c r="P60" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q60">
         <v>2.7</v>
@@ -14171,7 +14177,7 @@
         <v>1.2</v>
       </c>
       <c r="AP64">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AQ64">
         <v>1.6</v>
@@ -14299,7 +14305,7 @@
         <v>105</v>
       </c>
       <c r="P65" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q65">
         <v>3.4</v>
@@ -14505,7 +14511,7 @@
         <v>127</v>
       </c>
       <c r="P66" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q66">
         <v>2.5</v>
@@ -14917,7 +14923,7 @@
         <v>82</v>
       </c>
       <c r="P68" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q68">
         <v>3</v>
@@ -15329,7 +15335,7 @@
         <v>116</v>
       </c>
       <c r="P70" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q70">
         <v>2.38</v>
@@ -15407,7 +15413,7 @@
         <v>1</v>
       </c>
       <c r="AP70">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AQ70">
         <v>1.18</v>
@@ -15947,7 +15953,7 @@
         <v>82</v>
       </c>
       <c r="P73" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q73">
         <v>3</v>
@@ -16153,7 +16159,7 @@
         <v>130</v>
       </c>
       <c r="P74" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q74">
         <v>5</v>
@@ -16359,7 +16365,7 @@
         <v>131</v>
       </c>
       <c r="P75" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q75">
         <v>2.88</v>
@@ -16440,7 +16446,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ75">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="AR75">
         <v>1.55</v>
@@ -16771,7 +16777,7 @@
         <v>133</v>
       </c>
       <c r="P77" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q77">
         <v>3</v>
@@ -16852,7 +16858,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ77">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="AR77">
         <v>1.51</v>
@@ -17183,7 +17189,7 @@
         <v>134</v>
       </c>
       <c r="P79" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q79">
         <v>4.33</v>
@@ -17389,7 +17395,7 @@
         <v>82</v>
       </c>
       <c r="P80" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q80">
         <v>3.6</v>
@@ -17595,7 +17601,7 @@
         <v>82</v>
       </c>
       <c r="P81" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q81">
         <v>3.5</v>
@@ -18007,7 +18013,7 @@
         <v>136</v>
       </c>
       <c r="P83" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q83">
         <v>4.33</v>
@@ -18213,7 +18219,7 @@
         <v>137</v>
       </c>
       <c r="P84" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q84">
         <v>2.4</v>
@@ -18625,7 +18631,7 @@
         <v>82</v>
       </c>
       <c r="P86" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q86">
         <v>5</v>
@@ -19243,7 +19249,7 @@
         <v>82</v>
       </c>
       <c r="P89" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q89">
         <v>3.4</v>
@@ -19449,7 +19455,7 @@
         <v>139</v>
       </c>
       <c r="P90" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q90">
         <v>2.3</v>
@@ -19655,7 +19661,7 @@
         <v>140</v>
       </c>
       <c r="P91" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q91">
         <v>2.55</v>
@@ -19733,7 +19739,7 @@
         <v>1.63</v>
       </c>
       <c r="AP91">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AQ91">
         <v>1.4</v>
@@ -19942,7 +19948,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ92">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="AR92">
         <v>1.34</v>
@@ -20067,7 +20073,7 @@
         <v>82</v>
       </c>
       <c r="P93" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q93">
         <v>2.88</v>
@@ -20273,7 +20279,7 @@
         <v>82</v>
       </c>
       <c r="P94" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q94">
         <v>2.8</v>
@@ -20479,7 +20485,7 @@
         <v>142</v>
       </c>
       <c r="P95" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q95">
         <v>2.62</v>
@@ -20685,7 +20691,7 @@
         <v>82</v>
       </c>
       <c r="P96" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q96">
         <v>4</v>
@@ -20891,7 +20897,7 @@
         <v>82</v>
       </c>
       <c r="P97" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q97">
         <v>3.1</v>
@@ -21097,7 +21103,7 @@
         <v>125</v>
       </c>
       <c r="P98" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q98">
         <v>2.75</v>
@@ -21303,7 +21309,7 @@
         <v>143</v>
       </c>
       <c r="P99" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q99">
         <v>3.4</v>
@@ -21509,7 +21515,7 @@
         <v>134</v>
       </c>
       <c r="P100" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q100">
         <v>3.3</v>
@@ -21715,7 +21721,7 @@
         <v>144</v>
       </c>
       <c r="P101" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q101">
         <v>3</v>
@@ -21921,7 +21927,7 @@
         <v>145</v>
       </c>
       <c r="P102" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q102">
         <v>2.3</v>
@@ -22127,7 +22133,7 @@
         <v>146</v>
       </c>
       <c r="P103" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q103">
         <v>2.1</v>
@@ -22333,7 +22339,7 @@
         <v>147</v>
       </c>
       <c r="P104" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q104">
         <v>2.55</v>
@@ -22745,7 +22751,7 @@
         <v>82</v>
       </c>
       <c r="P106" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q106">
         <v>4.5</v>
@@ -22951,7 +22957,7 @@
         <v>149</v>
       </c>
       <c r="P107" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q107">
         <v>4.33</v>
@@ -23363,7 +23369,7 @@
         <v>151</v>
       </c>
       <c r="P109" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q109">
         <v>3</v>
@@ -23569,7 +23575,7 @@
         <v>152</v>
       </c>
       <c r="P110" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q110">
         <v>2.5</v>
@@ -23650,7 +23656,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ110">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="AR110">
         <v>1.5</v>
@@ -23775,7 +23781,7 @@
         <v>153</v>
       </c>
       <c r="P111" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q111">
         <v>4.33</v>
@@ -23981,7 +23987,7 @@
         <v>154</v>
       </c>
       <c r="P112" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q112">
         <v>2.25</v>
@@ -24187,7 +24193,7 @@
         <v>155</v>
       </c>
       <c r="P113" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q113">
         <v>2.2</v>
@@ -24886,7 +24892,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ116">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="AR116">
         <v>1.56</v>
@@ -25011,7 +25017,7 @@
         <v>157</v>
       </c>
       <c r="P117" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q117">
         <v>2.5</v>
@@ -25217,7 +25223,7 @@
         <v>158</v>
       </c>
       <c r="P118" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q118">
         <v>3.4</v>
@@ -25629,7 +25635,7 @@
         <v>160</v>
       </c>
       <c r="P120" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q120">
         <v>2.7</v>
@@ -25835,7 +25841,7 @@
         <v>118</v>
       </c>
       <c r="P121" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q121">
         <v>3.2</v>
@@ -26041,7 +26047,7 @@
         <v>161</v>
       </c>
       <c r="P122" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q122">
         <v>2.9</v>
@@ -26247,7 +26253,7 @@
         <v>162</v>
       </c>
       <c r="P123" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q123">
         <v>3.1</v>
@@ -26453,7 +26459,7 @@
         <v>151</v>
       </c>
       <c r="P124" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q124">
         <v>3.7</v>
@@ -26659,7 +26665,7 @@
         <v>163</v>
       </c>
       <c r="P125" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q125">
         <v>2.75</v>
@@ -26816,6 +26822,212 @@
       </c>
       <c r="BP125">
         <v>1.22</v>
+      </c>
+    </row>
+    <row r="126" spans="1:68">
+      <c r="A126" s="1">
+        <v>125</v>
+      </c>
+      <c r="B126">
+        <v>7806882</v>
+      </c>
+      <c r="C126" t="s">
+        <v>68</v>
+      </c>
+      <c r="D126" t="s">
+        <v>69</v>
+      </c>
+      <c r="E126" s="2">
+        <v>45850.29166666666</v>
+      </c>
+      <c r="F126">
+        <v>21</v>
+      </c>
+      <c r="G126" t="s">
+        <v>73</v>
+      </c>
+      <c r="H126" t="s">
+        <v>75</v>
+      </c>
+      <c r="I126">
+        <v>0</v>
+      </c>
+      <c r="J126">
+        <v>1</v>
+      </c>
+      <c r="K126">
+        <v>1</v>
+      </c>
+      <c r="L126">
+        <v>2</v>
+      </c>
+      <c r="M126">
+        <v>2</v>
+      </c>
+      <c r="N126">
+        <v>4</v>
+      </c>
+      <c r="O126" t="s">
+        <v>164</v>
+      </c>
+      <c r="P126" t="s">
+        <v>231</v>
+      </c>
+      <c r="Q126">
+        <v>2</v>
+      </c>
+      <c r="R126">
+        <v>2.5</v>
+      </c>
+      <c r="S126">
+        <v>5.5</v>
+      </c>
+      <c r="T126">
+        <v>1.3</v>
+      </c>
+      <c r="U126">
+        <v>3.4</v>
+      </c>
+      <c r="V126">
+        <v>2.38</v>
+      </c>
+      <c r="W126">
+        <v>1.53</v>
+      </c>
+      <c r="X126">
+        <v>6</v>
+      </c>
+      <c r="Y126">
+        <v>1.13</v>
+      </c>
+      <c r="Z126">
+        <v>1.45</v>
+      </c>
+      <c r="AA126">
+        <v>4.2</v>
+      </c>
+      <c r="AB126">
+        <v>5.2</v>
+      </c>
+      <c r="AC126">
+        <v>1.03</v>
+      </c>
+      <c r="AD126">
+        <v>11</v>
+      </c>
+      <c r="AE126">
+        <v>1.2</v>
+      </c>
+      <c r="AF126">
+        <v>4.5</v>
+      </c>
+      <c r="AG126">
+        <v>1.58</v>
+      </c>
+      <c r="AH126">
+        <v>2.22</v>
+      </c>
+      <c r="AI126">
+        <v>1.73</v>
+      </c>
+      <c r="AJ126">
+        <v>2</v>
+      </c>
+      <c r="AK126">
+        <v>1.13</v>
+      </c>
+      <c r="AL126">
+        <v>1.15</v>
+      </c>
+      <c r="AM126">
+        <v>2.5</v>
+      </c>
+      <c r="AN126">
+        <v>1.56</v>
+      </c>
+      <c r="AO126">
+        <v>0.2</v>
+      </c>
+      <c r="AP126">
+        <v>1.5</v>
+      </c>
+      <c r="AQ126">
+        <v>0.27</v>
+      </c>
+      <c r="AR126">
+        <v>2</v>
+      </c>
+      <c r="AS126">
+        <v>1.27</v>
+      </c>
+      <c r="AT126">
+        <v>3.27</v>
+      </c>
+      <c r="AU126">
+        <v>12</v>
+      </c>
+      <c r="AV126">
+        <v>5</v>
+      </c>
+      <c r="AW126">
+        <v>17</v>
+      </c>
+      <c r="AX126">
+        <v>4</v>
+      </c>
+      <c r="AY126">
+        <v>29</v>
+      </c>
+      <c r="AZ126">
+        <v>9</v>
+      </c>
+      <c r="BA126">
+        <v>10</v>
+      </c>
+      <c r="BB126">
+        <v>1</v>
+      </c>
+      <c r="BC126">
+        <v>11</v>
+      </c>
+      <c r="BD126">
+        <v>1.35</v>
+      </c>
+      <c r="BE126">
+        <v>7</v>
+      </c>
+      <c r="BF126">
+        <v>3.55</v>
+      </c>
+      <c r="BG126">
+        <v>1.34</v>
+      </c>
+      <c r="BH126">
+        <v>2.9</v>
+      </c>
+      <c r="BI126">
+        <v>1.58</v>
+      </c>
+      <c r="BJ126">
+        <v>2.18</v>
+      </c>
+      <c r="BK126">
+        <v>1.95</v>
+      </c>
+      <c r="BL126">
+        <v>1.74</v>
+      </c>
+      <c r="BM126">
+        <v>2.45</v>
+      </c>
+      <c r="BN126">
+        <v>1.48</v>
+      </c>
+      <c r="BO126">
+        <v>3.15</v>
+      </c>
+      <c r="BP126">
+        <v>1.29</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/South Korea K League 1_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/South Korea K League 1_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="818" uniqueCount="232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="830" uniqueCount="235">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -511,6 +511,12 @@
     <t>['64', '79']</t>
   </si>
   <si>
+    <t>['85', '90']</t>
+  </si>
+  <si>
+    <t>['19', '22']</t>
+  </si>
+  <si>
     <t>['32', '87', '90']</t>
   </si>
   <si>
@@ -710,6 +716,9 @@
   </si>
   <si>
     <t>['33', '87']</t>
+  </si>
+  <si>
+    <t>['37', '54', '90+2']</t>
   </si>
 </sst>
 </file>
@@ -1071,7 +1080,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP126"/>
+  <dimension ref="A1:BP128"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1327,7 +1336,7 @@
         <v>82</v>
       </c>
       <c r="P2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="Q2">
         <v>2.75</v>
@@ -1945,7 +1954,7 @@
         <v>82</v>
       </c>
       <c r="P5" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="Q5">
         <v>2.1</v>
@@ -2232,7 +2241,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ6">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2357,7 +2366,7 @@
         <v>85</v>
       </c>
       <c r="P7" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q7">
         <v>3.5</v>
@@ -2435,7 +2444,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AQ7">
         <v>1.45</v>
@@ -2563,7 +2572,7 @@
         <v>86</v>
       </c>
       <c r="P8" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="Q8">
         <v>3.4</v>
@@ -2644,7 +2653,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ8">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AR8">
         <v>1.38</v>
@@ -2769,7 +2778,7 @@
         <v>87</v>
       </c>
       <c r="P9" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="Q9">
         <v>3.35</v>
@@ -2847,7 +2856,7 @@
         <v>1</v>
       </c>
       <c r="AP9">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AQ9">
         <v>0.4</v>
@@ -3181,7 +3190,7 @@
         <v>82</v>
       </c>
       <c r="P11" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="Q11">
         <v>3.45</v>
@@ -3387,7 +3396,7 @@
         <v>89</v>
       </c>
       <c r="P12" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="Q12">
         <v>2.75</v>
@@ -3468,7 +3477,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ12">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AR12">
         <v>1.8</v>
@@ -3593,7 +3602,7 @@
         <v>90</v>
       </c>
       <c r="P13" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q13">
         <v>2.95</v>
@@ -4910,7 +4919,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ19">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AR19">
         <v>1.46</v>
@@ -5113,7 +5122,7 @@
         <v>0</v>
       </c>
       <c r="AP20">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AQ20">
         <v>1.55</v>
@@ -5241,7 +5250,7 @@
         <v>94</v>
       </c>
       <c r="P21" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="Q21">
         <v>3.1</v>
@@ -5319,7 +5328,7 @@
         <v>3</v>
       </c>
       <c r="AP21">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AQ21">
         <v>1.9</v>
@@ -5447,7 +5456,7 @@
         <v>95</v>
       </c>
       <c r="P22" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="Q22">
         <v>3.6</v>
@@ -5528,7 +5537,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ22">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AR22">
         <v>0</v>
@@ -6065,7 +6074,7 @@
         <v>97</v>
       </c>
       <c r="P25" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="Q25">
         <v>4</v>
@@ -6271,7 +6280,7 @@
         <v>82</v>
       </c>
       <c r="P26" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="Q26">
         <v>3.6</v>
@@ -6477,7 +6486,7 @@
         <v>82</v>
       </c>
       <c r="P27" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="Q27">
         <v>2.75</v>
@@ -6555,7 +6564,7 @@
         <v>1</v>
       </c>
       <c r="AP27">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AQ27">
         <v>1.2</v>
@@ -6683,7 +6692,7 @@
         <v>98</v>
       </c>
       <c r="P28" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="Q28">
         <v>3.75</v>
@@ -6761,7 +6770,7 @@
         <v>3</v>
       </c>
       <c r="AP28">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AQ28">
         <v>1.5</v>
@@ -6970,7 +6979,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ29">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AR29">
         <v>0</v>
@@ -7095,7 +7104,7 @@
         <v>99</v>
       </c>
       <c r="P30" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="Q30">
         <v>2.63</v>
@@ -7301,7 +7310,7 @@
         <v>100</v>
       </c>
       <c r="P31" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="Q31">
         <v>3.1</v>
@@ -7507,7 +7516,7 @@
         <v>101</v>
       </c>
       <c r="P32" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="Q32">
         <v>2.5</v>
@@ -7919,7 +7928,7 @@
         <v>103</v>
       </c>
       <c r="P34" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="Q34">
         <v>3.2</v>
@@ -8000,7 +8009,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ34">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AR34">
         <v>1.58</v>
@@ -8743,7 +8752,7 @@
         <v>106</v>
       </c>
       <c r="P38" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="Q38">
         <v>2.45</v>
@@ -9361,7 +9370,7 @@
         <v>82</v>
       </c>
       <c r="P41" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="Q41">
         <v>3.25</v>
@@ -9567,7 +9576,7 @@
         <v>98</v>
       </c>
       <c r="P42" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="Q42">
         <v>3.4</v>
@@ -9645,7 +9654,7 @@
         <v>1.33</v>
       </c>
       <c r="AP42">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AQ42">
         <v>1.18</v>
@@ -10391,7 +10400,7 @@
         <v>111</v>
       </c>
       <c r="P46" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="Q46">
         <v>4.33</v>
@@ -10469,10 +10478,10 @@
         <v>1.75</v>
       </c>
       <c r="AP46">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AQ46">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AR46">
         <v>1.44</v>
@@ -10597,7 +10606,7 @@
         <v>112</v>
       </c>
       <c r="P47" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="Q47">
         <v>2.6</v>
@@ -11090,7 +11099,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ49">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AR49">
         <v>1.43</v>
@@ -11499,7 +11508,7 @@
         <v>1.33</v>
       </c>
       <c r="AP51">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AQ51">
         <v>1.5</v>
@@ -11627,7 +11636,7 @@
         <v>116</v>
       </c>
       <c r="P52" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="Q52">
         <v>2.38</v>
@@ -11833,7 +11842,7 @@
         <v>117</v>
       </c>
       <c r="P53" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="Q53">
         <v>3.1</v>
@@ -12039,7 +12048,7 @@
         <v>82</v>
       </c>
       <c r="P54" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="Q54">
         <v>2.75</v>
@@ -12245,7 +12254,7 @@
         <v>118</v>
       </c>
       <c r="P55" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="Q55">
         <v>2.75</v>
@@ -12326,7 +12335,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ55">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AR55">
         <v>1.28</v>
@@ -12657,7 +12666,7 @@
         <v>120</v>
       </c>
       <c r="P57" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="Q57">
         <v>2.3</v>
@@ -12863,7 +12872,7 @@
         <v>82</v>
       </c>
       <c r="P58" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q58">
         <v>4.5</v>
@@ -13069,7 +13078,7 @@
         <v>121</v>
       </c>
       <c r="P59" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="Q59">
         <v>4</v>
@@ -13147,7 +13156,7 @@
         <v>2</v>
       </c>
       <c r="AP59">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AQ59">
         <v>2.5</v>
@@ -13275,7 +13284,7 @@
         <v>122</v>
       </c>
       <c r="P60" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="Q60">
         <v>2.7</v>
@@ -14180,7 +14189,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ64">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AR64">
         <v>2.07</v>
@@ -14305,7 +14314,7 @@
         <v>105</v>
       </c>
       <c r="P65" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q65">
         <v>3.4</v>
@@ -14386,7 +14395,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ65">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AR65">
         <v>1.65</v>
@@ -14511,7 +14520,7 @@
         <v>127</v>
       </c>
       <c r="P66" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="Q66">
         <v>2.5</v>
@@ -14795,7 +14804,7 @@
         <v>0.4</v>
       </c>
       <c r="AP67">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AQ67">
         <v>0.91</v>
@@ -14923,7 +14932,7 @@
         <v>82</v>
       </c>
       <c r="P68" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="Q68">
         <v>3</v>
@@ -15335,7 +15344,7 @@
         <v>116</v>
       </c>
       <c r="P70" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Q70">
         <v>2.38</v>
@@ -15622,7 +15631,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ71">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AR71">
         <v>1.66</v>
@@ -15953,7 +15962,7 @@
         <v>82</v>
       </c>
       <c r="P73" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="Q73">
         <v>3</v>
@@ -16159,7 +16168,7 @@
         <v>130</v>
       </c>
       <c r="P74" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="Q74">
         <v>5</v>
@@ -16365,7 +16374,7 @@
         <v>131</v>
       </c>
       <c r="P75" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="Q75">
         <v>2.88</v>
@@ -16443,7 +16452,7 @@
         <v>0.2</v>
       </c>
       <c r="AP75">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AQ75">
         <v>0.27</v>
@@ -16777,7 +16786,7 @@
         <v>133</v>
       </c>
       <c r="P77" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q77">
         <v>3</v>
@@ -17189,7 +17198,7 @@
         <v>134</v>
       </c>
       <c r="P79" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="Q79">
         <v>4.33</v>
@@ -17395,7 +17404,7 @@
         <v>82</v>
       </c>
       <c r="P80" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="Q80">
         <v>3.6</v>
@@ -17476,7 +17485,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ80">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AR80">
         <v>1.51</v>
@@ -17601,7 +17610,7 @@
         <v>82</v>
       </c>
       <c r="P81" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="Q81">
         <v>3.5</v>
@@ -18013,7 +18022,7 @@
         <v>136</v>
       </c>
       <c r="P83" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="Q83">
         <v>4.33</v>
@@ -18219,7 +18228,7 @@
         <v>137</v>
       </c>
       <c r="P84" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="Q84">
         <v>2.4</v>
@@ -18506,7 +18515,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ85">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AR85">
         <v>1.61</v>
@@ -18631,7 +18640,7 @@
         <v>82</v>
       </c>
       <c r="P86" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="Q86">
         <v>5</v>
@@ -18709,7 +18718,7 @@
         <v>1</v>
       </c>
       <c r="AP86">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AQ86">
         <v>1.55</v>
@@ -18915,7 +18924,7 @@
         <v>2.43</v>
       </c>
       <c r="AP87">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AQ87">
         <v>1.9</v>
@@ -19249,7 +19258,7 @@
         <v>82</v>
       </c>
       <c r="P89" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Q89">
         <v>3.4</v>
@@ -19455,7 +19464,7 @@
         <v>139</v>
       </c>
       <c r="P90" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Q90">
         <v>2.3</v>
@@ -19661,7 +19670,7 @@
         <v>140</v>
       </c>
       <c r="P91" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Q91">
         <v>2.55</v>
@@ -19742,7 +19751,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ91">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AR91">
         <v>2.04</v>
@@ -20073,7 +20082,7 @@
         <v>82</v>
       </c>
       <c r="P93" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Q93">
         <v>2.88</v>
@@ -20279,7 +20288,7 @@
         <v>82</v>
       </c>
       <c r="P94" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="Q94">
         <v>2.8</v>
@@ -20357,7 +20366,7 @@
         <v>0.43</v>
       </c>
       <c r="AP94">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AQ94">
         <v>0.91</v>
@@ -20485,7 +20494,7 @@
         <v>142</v>
       </c>
       <c r="P95" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q95">
         <v>2.62</v>
@@ -20691,7 +20700,7 @@
         <v>82</v>
       </c>
       <c r="P96" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="Q96">
         <v>4</v>
@@ -20769,7 +20778,7 @@
         <v>2.29</v>
       </c>
       <c r="AP96">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AQ96">
         <v>2.5</v>
@@ -20897,7 +20906,7 @@
         <v>82</v>
       </c>
       <c r="P97" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="Q97">
         <v>3.1</v>
@@ -21103,7 +21112,7 @@
         <v>125</v>
       </c>
       <c r="P98" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="Q98">
         <v>2.75</v>
@@ -21309,7 +21318,7 @@
         <v>143</v>
       </c>
       <c r="P99" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="Q99">
         <v>3.4</v>
@@ -21515,7 +21524,7 @@
         <v>134</v>
       </c>
       <c r="P100" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="Q100">
         <v>3.3</v>
@@ -21721,7 +21730,7 @@
         <v>144</v>
       </c>
       <c r="P101" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="Q101">
         <v>3</v>
@@ -21927,7 +21936,7 @@
         <v>145</v>
       </c>
       <c r="P102" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Q102">
         <v>2.3</v>
@@ -22133,7 +22142,7 @@
         <v>146</v>
       </c>
       <c r="P103" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="Q103">
         <v>2.1</v>
@@ -22339,7 +22348,7 @@
         <v>147</v>
       </c>
       <c r="P104" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="Q104">
         <v>2.55</v>
@@ -22623,10 +22632,10 @@
         <v>1.29</v>
       </c>
       <c r="AP105">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AQ105">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AR105">
         <v>1.83</v>
@@ -22751,7 +22760,7 @@
         <v>82</v>
       </c>
       <c r="P106" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Q106">
         <v>4.5</v>
@@ -22957,7 +22966,7 @@
         <v>149</v>
       </c>
       <c r="P107" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Q107">
         <v>4.33</v>
@@ -23369,7 +23378,7 @@
         <v>151</v>
       </c>
       <c r="P109" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="Q109">
         <v>3</v>
@@ -23447,7 +23456,7 @@
         <v>1.13</v>
       </c>
       <c r="AP109">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AQ109">
         <v>1.2</v>
@@ -23575,7 +23584,7 @@
         <v>152</v>
       </c>
       <c r="P110" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q110">
         <v>2.5</v>
@@ -23781,7 +23790,7 @@
         <v>153</v>
       </c>
       <c r="P111" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="Q111">
         <v>4.33</v>
@@ -23859,7 +23868,7 @@
         <v>1.33</v>
       </c>
       <c r="AP111">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AQ111">
         <v>1.18</v>
@@ -23987,7 +23996,7 @@
         <v>154</v>
       </c>
       <c r="P112" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Q112">
         <v>2.25</v>
@@ -24193,7 +24202,7 @@
         <v>155</v>
       </c>
       <c r="P113" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="Q113">
         <v>2.2</v>
@@ -24480,7 +24489,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ114">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AR114">
         <v>1.5</v>
@@ -24686,7 +24695,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ115">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AR115">
         <v>1.43</v>
@@ -25017,7 +25026,7 @@
         <v>157</v>
       </c>
       <c r="P117" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="Q117">
         <v>2.5</v>
@@ -25223,7 +25232,7 @@
         <v>158</v>
       </c>
       <c r="P118" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="Q118">
         <v>3.4</v>
@@ -25635,7 +25644,7 @@
         <v>160</v>
       </c>
       <c r="P120" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q120">
         <v>2.7</v>
@@ -25841,7 +25850,7 @@
         <v>118</v>
       </c>
       <c r="P121" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="Q121">
         <v>3.2</v>
@@ -26047,7 +26056,7 @@
         <v>161</v>
       </c>
       <c r="P122" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Q122">
         <v>2.9</v>
@@ -26253,7 +26262,7 @@
         <v>162</v>
       </c>
       <c r="P123" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Q123">
         <v>3.1</v>
@@ -26331,7 +26340,7 @@
         <v>1.3</v>
       </c>
       <c r="AP123">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AQ123">
         <v>1.45</v>
@@ -26459,7 +26468,7 @@
         <v>151</v>
       </c>
       <c r="P124" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q124">
         <v>3.7</v>
@@ -26540,7 +26549,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ124">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AR124">
         <v>1.51</v>
@@ -26665,7 +26674,7 @@
         <v>163</v>
       </c>
       <c r="P125" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="Q125">
         <v>2.75</v>
@@ -26871,7 +26880,7 @@
         <v>164</v>
       </c>
       <c r="P126" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="Q126">
         <v>2</v>
@@ -27028,6 +27037,418 @@
       </c>
       <c r="BP126">
         <v>1.29</v>
+      </c>
+    </row>
+    <row r="127" spans="1:68">
+      <c r="A127" s="1">
+        <v>126</v>
+      </c>
+      <c r="B127">
+        <v>7806884</v>
+      </c>
+      <c r="C127" t="s">
+        <v>68</v>
+      </c>
+      <c r="D127" t="s">
+        <v>69</v>
+      </c>
+      <c r="E127" s="2">
+        <v>45856.3125</v>
+      </c>
+      <c r="F127">
+        <v>22</v>
+      </c>
+      <c r="G127" t="s">
+        <v>79</v>
+      </c>
+      <c r="H127" t="s">
+        <v>72</v>
+      </c>
+      <c r="I127">
+        <v>0</v>
+      </c>
+      <c r="J127">
+        <v>0</v>
+      </c>
+      <c r="K127">
+        <v>0</v>
+      </c>
+      <c r="L127">
+        <v>2</v>
+      </c>
+      <c r="M127">
+        <v>1</v>
+      </c>
+      <c r="N127">
+        <v>3</v>
+      </c>
+      <c r="O127" t="s">
+        <v>165</v>
+      </c>
+      <c r="P127" t="s">
+        <v>161</v>
+      </c>
+      <c r="Q127">
+        <v>3.3</v>
+      </c>
+      <c r="R127">
+        <v>2.05</v>
+      </c>
+      <c r="S127">
+        <v>3</v>
+      </c>
+      <c r="T127">
+        <v>1.38</v>
+      </c>
+      <c r="U127">
+        <v>2.8</v>
+      </c>
+      <c r="V127">
+        <v>2.65</v>
+      </c>
+      <c r="W127">
+        <v>1.42</v>
+      </c>
+      <c r="X127">
+        <v>7</v>
+      </c>
+      <c r="Y127">
+        <v>1.08</v>
+      </c>
+      <c r="Z127">
+        <v>2.67</v>
+      </c>
+      <c r="AA127">
+        <v>3.03</v>
+      </c>
+      <c r="AB127">
+        <v>2.41</v>
+      </c>
+      <c r="AC127">
+        <v>1.07</v>
+      </c>
+      <c r="AD127">
+        <v>8</v>
+      </c>
+      <c r="AE127">
+        <v>1.33</v>
+      </c>
+      <c r="AF127">
+        <v>3.25</v>
+      </c>
+      <c r="AG127">
+        <v>1.95</v>
+      </c>
+      <c r="AH127">
+        <v>1.75</v>
+      </c>
+      <c r="AI127">
+        <v>1.7</v>
+      </c>
+      <c r="AJ127">
+        <v>2</v>
+      </c>
+      <c r="AK127">
+        <v>1.5</v>
+      </c>
+      <c r="AL127">
+        <v>1.28</v>
+      </c>
+      <c r="AM127">
+        <v>1.42</v>
+      </c>
+      <c r="AN127">
+        <v>1.2</v>
+      </c>
+      <c r="AO127">
+        <v>1.6</v>
+      </c>
+      <c r="AP127">
+        <v>1.36</v>
+      </c>
+      <c r="AQ127">
+        <v>1.45</v>
+      </c>
+      <c r="AR127">
+        <v>1.81</v>
+      </c>
+      <c r="AS127">
+        <v>1.22</v>
+      </c>
+      <c r="AT127">
+        <v>3.03</v>
+      </c>
+      <c r="AU127">
+        <v>5</v>
+      </c>
+      <c r="AV127">
+        <v>4</v>
+      </c>
+      <c r="AW127">
+        <v>8</v>
+      </c>
+      <c r="AX127">
+        <v>7</v>
+      </c>
+      <c r="AY127">
+        <v>13</v>
+      </c>
+      <c r="AZ127">
+        <v>11</v>
+      </c>
+      <c r="BA127">
+        <v>2</v>
+      </c>
+      <c r="BB127">
+        <v>5</v>
+      </c>
+      <c r="BC127">
+        <v>7</v>
+      </c>
+      <c r="BD127">
+        <v>2.25</v>
+      </c>
+      <c r="BE127">
+        <v>8</v>
+      </c>
+      <c r="BF127">
+        <v>1.96</v>
+      </c>
+      <c r="BG127">
+        <v>1.42</v>
+      </c>
+      <c r="BH127">
+        <v>2.55</v>
+      </c>
+      <c r="BI127">
+        <v>1.8</v>
+      </c>
+      <c r="BJ127">
+        <v>2</v>
+      </c>
+      <c r="BK127">
+        <v>2.25</v>
+      </c>
+      <c r="BL127">
+        <v>1.56</v>
+      </c>
+      <c r="BM127">
+        <v>3.04</v>
+      </c>
+      <c r="BN127">
+        <v>1.29</v>
+      </c>
+      <c r="BO127">
+        <v>4.4</v>
+      </c>
+      <c r="BP127">
+        <v>1.13</v>
+      </c>
+    </row>
+    <row r="128" spans="1:68">
+      <c r="A128" s="1">
+        <v>127</v>
+      </c>
+      <c r="B128">
+        <v>7806885</v>
+      </c>
+      <c r="C128" t="s">
+        <v>68</v>
+      </c>
+      <c r="D128" t="s">
+        <v>69</v>
+      </c>
+      <c r="E128" s="2">
+        <v>45856.3125</v>
+      </c>
+      <c r="F128">
+        <v>22</v>
+      </c>
+      <c r="G128" t="s">
+        <v>75</v>
+      </c>
+      <c r="H128" t="s">
+        <v>81</v>
+      </c>
+      <c r="I128">
+        <v>2</v>
+      </c>
+      <c r="J128">
+        <v>1</v>
+      </c>
+      <c r="K128">
+        <v>3</v>
+      </c>
+      <c r="L128">
+        <v>2</v>
+      </c>
+      <c r="M128">
+        <v>3</v>
+      </c>
+      <c r="N128">
+        <v>5</v>
+      </c>
+      <c r="O128" t="s">
+        <v>166</v>
+      </c>
+      <c r="P128" t="s">
+        <v>234</v>
+      </c>
+      <c r="Q128">
+        <v>3.55</v>
+      </c>
+      <c r="R128">
+        <v>2.2</v>
+      </c>
+      <c r="S128">
+        <v>2.62</v>
+      </c>
+      <c r="T128">
+        <v>1.33</v>
+      </c>
+      <c r="U128">
+        <v>3.1</v>
+      </c>
+      <c r="V128">
+        <v>2.4</v>
+      </c>
+      <c r="W128">
+        <v>1.5</v>
+      </c>
+      <c r="X128">
+        <v>5.65</v>
+      </c>
+      <c r="Y128">
+        <v>1.08</v>
+      </c>
+      <c r="Z128">
+        <v>3.47</v>
+      </c>
+      <c r="AA128">
+        <v>3.45</v>
+      </c>
+      <c r="AB128">
+        <v>1.85</v>
+      </c>
+      <c r="AC128">
+        <v>1.04</v>
+      </c>
+      <c r="AD128">
+        <v>10</v>
+      </c>
+      <c r="AE128">
+        <v>1.22</v>
+      </c>
+      <c r="AF128">
+        <v>4.2</v>
+      </c>
+      <c r="AG128">
+        <v>1.59</v>
+      </c>
+      <c r="AH128">
+        <v>2.2</v>
+      </c>
+      <c r="AI128">
+        <v>1.53</v>
+      </c>
+      <c r="AJ128">
+        <v>2.3</v>
+      </c>
+      <c r="AK128">
+        <v>1.77</v>
+      </c>
+      <c r="AL128">
+        <v>1.22</v>
+      </c>
+      <c r="AM128">
+        <v>1.3</v>
+      </c>
+      <c r="AN128">
+        <v>1.1</v>
+      </c>
+      <c r="AO128">
+        <v>1.4</v>
+      </c>
+      <c r="AP128">
+        <v>1</v>
+      </c>
+      <c r="AQ128">
+        <v>1.55</v>
+      </c>
+      <c r="AR128">
+        <v>1.81</v>
+      </c>
+      <c r="AS128">
+        <v>1.72</v>
+      </c>
+      <c r="AT128">
+        <v>3.53</v>
+      </c>
+      <c r="AU128">
+        <v>5</v>
+      </c>
+      <c r="AV128">
+        <v>7</v>
+      </c>
+      <c r="AW128">
+        <v>6</v>
+      </c>
+      <c r="AX128">
+        <v>8</v>
+      </c>
+      <c r="AY128">
+        <v>11</v>
+      </c>
+      <c r="AZ128">
+        <v>15</v>
+      </c>
+      <c r="BA128">
+        <v>5</v>
+      </c>
+      <c r="BB128">
+        <v>7</v>
+      </c>
+      <c r="BC128">
+        <v>12</v>
+      </c>
+      <c r="BD128">
+        <v>2.28</v>
+      </c>
+      <c r="BE128">
+        <v>8</v>
+      </c>
+      <c r="BF128">
+        <v>1.91</v>
+      </c>
+      <c r="BG128">
+        <v>1.31</v>
+      </c>
+      <c r="BH128">
+        <v>2.97</v>
+      </c>
+      <c r="BI128">
+        <v>1.6</v>
+      </c>
+      <c r="BJ128">
+        <v>2.17</v>
+      </c>
+      <c r="BK128">
+        <v>1.99</v>
+      </c>
+      <c r="BL128">
+        <v>1.72</v>
+      </c>
+      <c r="BM128">
+        <v>2.59</v>
+      </c>
+      <c r="BN128">
+        <v>1.41</v>
+      </c>
+      <c r="BO128">
+        <v>3.58</v>
+      </c>
+      <c r="BP128">
+        <v>1.21</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/South Korea K League 1_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/South Korea K League 1_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="830" uniqueCount="235">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="848" uniqueCount="240">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -517,6 +517,15 @@
     <t>['19', '22']</t>
   </si>
   <si>
+    <t>['90+5', '90+6']</t>
+  </si>
+  <si>
+    <t>['32', '44']</t>
+  </si>
+  <si>
+    <t>['69', '79']</t>
+  </si>
+  <si>
     <t>['32', '87', '90']</t>
   </si>
   <si>
@@ -719,6 +728,12 @@
   </si>
   <si>
     <t>['37', '54', '90+2']</t>
+  </si>
+  <si>
+    <t>['51', '60']</t>
+  </si>
+  <si>
+    <t>['65', '80', '90+5']</t>
   </si>
 </sst>
 </file>
@@ -1080,7 +1095,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP128"/>
+  <dimension ref="A1:BP131"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1336,7 +1351,7 @@
         <v>82</v>
       </c>
       <c r="P2" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="Q2">
         <v>2.75</v>
@@ -1414,10 +1429,10 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AQ2">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1620,7 +1635,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AQ3">
         <v>1.55</v>
@@ -1954,7 +1969,7 @@
         <v>82</v>
       </c>
       <c r="P5" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="Q5">
         <v>2.1</v>
@@ -2035,7 +2050,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ5">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2366,7 +2381,7 @@
         <v>85</v>
       </c>
       <c r="P7" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="Q7">
         <v>3.5</v>
@@ -2572,7 +2587,7 @@
         <v>86</v>
       </c>
       <c r="P8" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="Q8">
         <v>3.4</v>
@@ -2650,7 +2665,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AQ8">
         <v>1.55</v>
@@ -2778,7 +2793,7 @@
         <v>87</v>
       </c>
       <c r="P9" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="Q9">
         <v>3.35</v>
@@ -3065,7 +3080,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ10">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3190,7 +3205,7 @@
         <v>82</v>
       </c>
       <c r="P11" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="Q11">
         <v>3.45</v>
@@ -3396,7 +3411,7 @@
         <v>89</v>
       </c>
       <c r="P12" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="Q12">
         <v>2.75</v>
@@ -3602,7 +3617,7 @@
         <v>90</v>
       </c>
       <c r="P13" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="Q13">
         <v>2.95</v>
@@ -3680,7 +3695,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AQ13">
         <v>1.18</v>
@@ -3889,7 +3904,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ14">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AR14">
         <v>2.51</v>
@@ -4092,7 +4107,7 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AQ15">
         <v>0.27</v>
@@ -4301,7 +4316,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ16">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR16">
         <v>1.8</v>
@@ -4710,7 +4725,7 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AQ18">
         <v>0.91</v>
@@ -5250,7 +5265,7 @@
         <v>94</v>
       </c>
       <c r="P21" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="Q21">
         <v>3.1</v>
@@ -5331,7 +5346,7 @@
         <v>1</v>
       </c>
       <c r="AQ21">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AR21">
         <v>1.94</v>
@@ -5456,7 +5471,7 @@
         <v>95</v>
       </c>
       <c r="P22" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="Q22">
         <v>3.6</v>
@@ -6074,7 +6089,7 @@
         <v>97</v>
       </c>
       <c r="P25" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="Q25">
         <v>4</v>
@@ -6152,10 +6167,10 @@
         <v>3</v>
       </c>
       <c r="AP25">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AQ25">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AR25">
         <v>1.2</v>
@@ -6280,7 +6295,7 @@
         <v>82</v>
       </c>
       <c r="P26" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="Q26">
         <v>3.6</v>
@@ -6358,7 +6373,7 @@
         <v>0.5</v>
       </c>
       <c r="AP26">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AQ26">
         <v>1.55</v>
@@ -6486,7 +6501,7 @@
         <v>82</v>
       </c>
       <c r="P27" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="Q27">
         <v>2.75</v>
@@ -6567,7 +6582,7 @@
         <v>1</v>
       </c>
       <c r="AQ27">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR27">
         <v>2.02</v>
@@ -6692,7 +6707,7 @@
         <v>98</v>
       </c>
       <c r="P28" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="Q28">
         <v>3.75</v>
@@ -7104,7 +7119,7 @@
         <v>99</v>
       </c>
       <c r="P30" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="Q30">
         <v>2.63</v>
@@ -7310,7 +7325,7 @@
         <v>100</v>
       </c>
       <c r="P31" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="Q31">
         <v>3.1</v>
@@ -7516,7 +7531,7 @@
         <v>101</v>
       </c>
       <c r="P32" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="Q32">
         <v>2.5</v>
@@ -7800,7 +7815,7 @@
         <v>2</v>
       </c>
       <c r="AP33">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AQ33">
         <v>1.5</v>
@@ -7928,7 +7943,7 @@
         <v>103</v>
       </c>
       <c r="P34" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="Q34">
         <v>3.2</v>
@@ -8212,7 +8227,7 @@
         <v>0.33</v>
       </c>
       <c r="AP35">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AQ35">
         <v>0.4</v>
@@ -8627,7 +8642,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ37">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AR37">
         <v>1.26</v>
@@ -8752,7 +8767,7 @@
         <v>106</v>
       </c>
       <c r="P38" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="Q38">
         <v>2.45</v>
@@ -8833,7 +8848,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ38">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AR38">
         <v>2.21</v>
@@ -9370,7 +9385,7 @@
         <v>82</v>
       </c>
       <c r="P41" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="Q41">
         <v>3.25</v>
@@ -9451,7 +9466,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ41">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AR41">
         <v>1.54</v>
@@ -9576,7 +9591,7 @@
         <v>98</v>
       </c>
       <c r="P42" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="Q42">
         <v>3.4</v>
@@ -10400,7 +10415,7 @@
         <v>111</v>
       </c>
       <c r="P46" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="Q46">
         <v>4.33</v>
@@ -10606,7 +10621,7 @@
         <v>112</v>
       </c>
       <c r="P47" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="Q47">
         <v>2.6</v>
@@ -10687,7 +10702,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ47">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AR47">
         <v>0.99</v>
@@ -10890,10 +10905,10 @@
         <v>1.5</v>
       </c>
       <c r="AP48">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AQ48">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR48">
         <v>1.68</v>
@@ -11096,7 +11111,7 @@
         <v>1</v>
       </c>
       <c r="AP49">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AQ49">
         <v>1.45</v>
@@ -11636,7 +11651,7 @@
         <v>116</v>
       </c>
       <c r="P52" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="Q52">
         <v>2.38</v>
@@ -11842,7 +11857,7 @@
         <v>117</v>
       </c>
       <c r="P53" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="Q53">
         <v>3.1</v>
@@ -12048,7 +12063,7 @@
         <v>82</v>
       </c>
       <c r="P54" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="Q54">
         <v>2.75</v>
@@ -12129,7 +12144,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ54">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AR54">
         <v>1.88</v>
@@ -12254,7 +12269,7 @@
         <v>118</v>
       </c>
       <c r="P55" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="Q55">
         <v>2.75</v>
@@ -12538,7 +12553,7 @@
         <v>1.25</v>
       </c>
       <c r="AP56">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AQ56">
         <v>1.18</v>
@@ -12666,7 +12681,7 @@
         <v>120</v>
       </c>
       <c r="P57" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="Q57">
         <v>2.3</v>
@@ -12872,7 +12887,7 @@
         <v>82</v>
       </c>
       <c r="P58" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="Q58">
         <v>4.5</v>
@@ -13078,7 +13093,7 @@
         <v>121</v>
       </c>
       <c r="P59" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="Q59">
         <v>4</v>
@@ -13159,7 +13174,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ59">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AR59">
         <v>1.49</v>
@@ -13284,7 +13299,7 @@
         <v>122</v>
       </c>
       <c r="P60" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="Q60">
         <v>2.7</v>
@@ -13568,7 +13583,7 @@
         <v>1.25</v>
       </c>
       <c r="AP61">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AQ61">
         <v>1.55</v>
@@ -14314,7 +14329,7 @@
         <v>105</v>
       </c>
       <c r="P65" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="Q65">
         <v>3.4</v>
@@ -14392,7 +14407,7 @@
         <v>1.4</v>
       </c>
       <c r="AP65">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AQ65">
         <v>1.55</v>
@@ -14520,7 +14535,7 @@
         <v>127</v>
       </c>
       <c r="P66" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="Q66">
         <v>2.5</v>
@@ -14601,7 +14616,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ66">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR66">
         <v>1.46</v>
@@ -14932,7 +14947,7 @@
         <v>82</v>
       </c>
       <c r="P68" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="Q68">
         <v>3</v>
@@ -15013,7 +15028,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ68">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AR68">
         <v>1.47</v>
@@ -15216,7 +15231,7 @@
         <v>0.2</v>
       </c>
       <c r="AP69">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AQ69">
         <v>0.4</v>
@@ -15344,7 +15359,7 @@
         <v>116</v>
       </c>
       <c r="P70" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="Q70">
         <v>2.38</v>
@@ -15837,7 +15852,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ72">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AR72">
         <v>1.66</v>
@@ -15962,7 +15977,7 @@
         <v>82</v>
       </c>
       <c r="P73" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="Q73">
         <v>3</v>
@@ -16040,7 +16055,7 @@
         <v>1</v>
       </c>
       <c r="AP73">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AQ73">
         <v>1.45</v>
@@ -16168,7 +16183,7 @@
         <v>130</v>
       </c>
       <c r="P74" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="Q74">
         <v>5</v>
@@ -16374,7 +16389,7 @@
         <v>131</v>
       </c>
       <c r="P75" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="Q75">
         <v>2.88</v>
@@ -16658,7 +16673,7 @@
         <v>0.33</v>
       </c>
       <c r="AP76">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AQ76">
         <v>0.4</v>
@@ -16786,7 +16801,7 @@
         <v>133</v>
       </c>
       <c r="P77" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="Q77">
         <v>3</v>
@@ -17198,7 +17213,7 @@
         <v>134</v>
       </c>
       <c r="P79" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="Q79">
         <v>4.33</v>
@@ -17276,7 +17291,7 @@
         <v>1.67</v>
       </c>
       <c r="AP79">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AQ79">
         <v>1.5</v>
@@ -17404,7 +17419,7 @@
         <v>82</v>
       </c>
       <c r="P80" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="Q80">
         <v>3.6</v>
@@ -17482,7 +17497,7 @@
         <v>1.43</v>
       </c>
       <c r="AP80">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AQ80">
         <v>1.55</v>
@@ -17610,7 +17625,7 @@
         <v>82</v>
       </c>
       <c r="P81" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="Q81">
         <v>3.5</v>
@@ -17691,7 +17706,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ81">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AR81">
         <v>1.49</v>
@@ -17897,7 +17912,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ82">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR82">
         <v>1.65</v>
@@ -18022,7 +18037,7 @@
         <v>136</v>
       </c>
       <c r="P83" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="Q83">
         <v>4.33</v>
@@ -18100,7 +18115,7 @@
         <v>1.86</v>
       </c>
       <c r="AP83">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AQ83">
         <v>1.5</v>
@@ -18228,7 +18243,7 @@
         <v>137</v>
       </c>
       <c r="P84" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="Q84">
         <v>2.4</v>
@@ -18512,7 +18527,7 @@
         <v>1</v>
       </c>
       <c r="AP85">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AQ85">
         <v>1.45</v>
@@ -18640,7 +18655,7 @@
         <v>82</v>
       </c>
       <c r="P86" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="Q86">
         <v>5</v>
@@ -18927,7 +18942,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ87">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AR87">
         <v>1.6</v>
@@ -19130,10 +19145,10 @@
         <v>2.5</v>
       </c>
       <c r="AP88">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AQ88">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AR88">
         <v>1.52</v>
@@ -19258,7 +19273,7 @@
         <v>82</v>
       </c>
       <c r="P89" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="Q89">
         <v>3.4</v>
@@ -19464,7 +19479,7 @@
         <v>139</v>
       </c>
       <c r="P90" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="Q90">
         <v>2.3</v>
@@ -19670,7 +19685,7 @@
         <v>140</v>
       </c>
       <c r="P91" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="Q91">
         <v>2.55</v>
@@ -20082,7 +20097,7 @@
         <v>82</v>
       </c>
       <c r="P93" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="Q93">
         <v>2.88</v>
@@ -20288,7 +20303,7 @@
         <v>82</v>
       </c>
       <c r="P94" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="Q94">
         <v>2.8</v>
@@ -20494,7 +20509,7 @@
         <v>142</v>
       </c>
       <c r="P95" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="Q95">
         <v>2.62</v>
@@ -20700,7 +20715,7 @@
         <v>82</v>
       </c>
       <c r="P96" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="Q96">
         <v>4</v>
@@ -20781,7 +20796,7 @@
         <v>1</v>
       </c>
       <c r="AQ96">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AR96">
         <v>1.86</v>
@@ -20906,7 +20921,7 @@
         <v>82</v>
       </c>
       <c r="P97" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="Q97">
         <v>3.1</v>
@@ -21112,7 +21127,7 @@
         <v>125</v>
       </c>
       <c r="P98" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="Q98">
         <v>2.75</v>
@@ -21190,10 +21205,10 @@
         <v>0.86</v>
       </c>
       <c r="AP98">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AQ98">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR98">
         <v>1.5</v>
@@ -21318,7 +21333,7 @@
         <v>143</v>
       </c>
       <c r="P99" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="Q99">
         <v>3.4</v>
@@ -21524,7 +21539,7 @@
         <v>134</v>
       </c>
       <c r="P100" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="Q100">
         <v>3.3</v>
@@ -21605,7 +21620,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ100">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AR100">
         <v>1.51</v>
@@ -21730,7 +21745,7 @@
         <v>144</v>
       </c>
       <c r="P101" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="Q101">
         <v>3</v>
@@ -21936,7 +21951,7 @@
         <v>145</v>
       </c>
       <c r="P102" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="Q102">
         <v>2.3</v>
@@ -22142,7 +22157,7 @@
         <v>146</v>
       </c>
       <c r="P103" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="Q103">
         <v>2.1</v>
@@ -22348,7 +22363,7 @@
         <v>147</v>
       </c>
       <c r="P104" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="Q104">
         <v>2.55</v>
@@ -22426,7 +22441,7 @@
         <v>1.5</v>
       </c>
       <c r="AP104">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AQ104">
         <v>1.45</v>
@@ -22760,7 +22775,7 @@
         <v>82</v>
       </c>
       <c r="P106" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="Q106">
         <v>4.5</v>
@@ -22838,10 +22853,10 @@
         <v>2.38</v>
       </c>
       <c r="AP106">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AQ106">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AR106">
         <v>1.5</v>
@@ -22966,7 +22981,7 @@
         <v>149</v>
       </c>
       <c r="P107" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="Q107">
         <v>4.33</v>
@@ -23378,7 +23393,7 @@
         <v>151</v>
       </c>
       <c r="P109" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="Q109">
         <v>3</v>
@@ -23459,7 +23474,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ109">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR109">
         <v>1.77</v>
@@ -23584,7 +23599,7 @@
         <v>152</v>
       </c>
       <c r="P110" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="Q110">
         <v>2.5</v>
@@ -23662,7 +23677,7 @@
         <v>0.25</v>
       </c>
       <c r="AP110">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AQ110">
         <v>0.27</v>
@@ -23790,7 +23805,7 @@
         <v>153</v>
       </c>
       <c r="P111" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="Q111">
         <v>4.33</v>
@@ -23996,7 +24011,7 @@
         <v>154</v>
       </c>
       <c r="P112" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="Q112">
         <v>2.25</v>
@@ -24202,7 +24217,7 @@
         <v>155</v>
       </c>
       <c r="P113" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="Q113">
         <v>2.2</v>
@@ -24486,7 +24501,7 @@
         <v>1.25</v>
       </c>
       <c r="AP114">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AQ114">
         <v>1.45</v>
@@ -24898,7 +24913,7 @@
         <v>0.22</v>
       </c>
       <c r="AP116">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AQ116">
         <v>0.27</v>
@@ -25026,7 +25041,7 @@
         <v>157</v>
       </c>
       <c r="P117" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="Q117">
         <v>2.5</v>
@@ -25104,7 +25119,7 @@
         <v>1</v>
       </c>
       <c r="AP117">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AQ117">
         <v>0.91</v>
@@ -25232,7 +25247,7 @@
         <v>158</v>
       </c>
       <c r="P118" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="Q118">
         <v>3.4</v>
@@ -25519,7 +25534,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ119">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AR119">
         <v>1.75</v>
@@ -25644,7 +25659,7 @@
         <v>160</v>
       </c>
       <c r="P120" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="Q120">
         <v>2.7</v>
@@ -25725,7 +25740,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ120">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AR120">
         <v>1.52</v>
@@ -25850,7 +25865,7 @@
         <v>118</v>
       </c>
       <c r="P121" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="Q121">
         <v>3.2</v>
@@ -25931,7 +25946,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ121">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AR121">
         <v>1.78</v>
@@ -26056,7 +26071,7 @@
         <v>161</v>
       </c>
       <c r="P122" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="Q122">
         <v>2.9</v>
@@ -26262,7 +26277,7 @@
         <v>162</v>
       </c>
       <c r="P123" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="Q123">
         <v>3.1</v>
@@ -26468,7 +26483,7 @@
         <v>151</v>
       </c>
       <c r="P124" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="Q124">
         <v>3.7</v>
@@ -26674,7 +26689,7 @@
         <v>163</v>
       </c>
       <c r="P125" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="Q125">
         <v>2.75</v>
@@ -26880,7 +26895,7 @@
         <v>164</v>
       </c>
       <c r="P126" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="Q126">
         <v>2</v>
@@ -27292,7 +27307,7 @@
         <v>166</v>
       </c>
       <c r="P128" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="Q128">
         <v>3.55</v>
@@ -27449,6 +27464,624 @@
       </c>
       <c r="BP128">
         <v>1.21</v>
+      </c>
+    </row>
+    <row r="129" spans="1:68">
+      <c r="A129" s="1">
+        <v>128</v>
+      </c>
+      <c r="B129">
+        <v>7806886</v>
+      </c>
+      <c r="C129" t="s">
+        <v>68</v>
+      </c>
+      <c r="D129" t="s">
+        <v>69</v>
+      </c>
+      <c r="E129" s="2">
+        <v>45857.29166666666</v>
+      </c>
+      <c r="F129">
+        <v>22</v>
+      </c>
+      <c r="G129" t="s">
+        <v>78</v>
+      </c>
+      <c r="H129" t="s">
+        <v>77</v>
+      </c>
+      <c r="I129">
+        <v>0</v>
+      </c>
+      <c r="J129">
+        <v>0</v>
+      </c>
+      <c r="K129">
+        <v>0</v>
+      </c>
+      <c r="L129">
+        <v>2</v>
+      </c>
+      <c r="M129">
+        <v>2</v>
+      </c>
+      <c r="N129">
+        <v>4</v>
+      </c>
+      <c r="O129" t="s">
+        <v>167</v>
+      </c>
+      <c r="P129" t="s">
+        <v>238</v>
+      </c>
+      <c r="Q129">
+        <v>3.1</v>
+      </c>
+      <c r="R129">
+        <v>2</v>
+      </c>
+      <c r="S129">
+        <v>3.4</v>
+      </c>
+      <c r="T129">
+        <v>1.42</v>
+      </c>
+      <c r="U129">
+        <v>2.65</v>
+      </c>
+      <c r="V129">
+        <v>2.88</v>
+      </c>
+      <c r="W129">
+        <v>1.36</v>
+      </c>
+      <c r="X129">
+        <v>7</v>
+      </c>
+      <c r="Y129">
+        <v>1.08</v>
+      </c>
+      <c r="Z129">
+        <v>2.29</v>
+      </c>
+      <c r="AA129">
+        <v>3.12</v>
+      </c>
+      <c r="AB129">
+        <v>2.75</v>
+      </c>
+      <c r="AC129">
+        <v>1.07</v>
+      </c>
+      <c r="AD129">
+        <v>8</v>
+      </c>
+      <c r="AE129">
+        <v>1.33</v>
+      </c>
+      <c r="AF129">
+        <v>3.25</v>
+      </c>
+      <c r="AG129">
+        <v>1.93</v>
+      </c>
+      <c r="AH129">
+        <v>1.77</v>
+      </c>
+      <c r="AI129">
+        <v>1.7</v>
+      </c>
+      <c r="AJ129">
+        <v>2</v>
+      </c>
+      <c r="AK129">
+        <v>1.42</v>
+      </c>
+      <c r="AL129">
+        <v>1.28</v>
+      </c>
+      <c r="AM129">
+        <v>1.5</v>
+      </c>
+      <c r="AN129">
+        <v>1.2</v>
+      </c>
+      <c r="AO129">
+        <v>1.9</v>
+      </c>
+      <c r="AP129">
+        <v>1.18</v>
+      </c>
+      <c r="AQ129">
+        <v>1.82</v>
+      </c>
+      <c r="AR129">
+        <v>1.55</v>
+      </c>
+      <c r="AS129">
+        <v>1.34</v>
+      </c>
+      <c r="AT129">
+        <v>2.89</v>
+      </c>
+      <c r="AU129">
+        <v>9</v>
+      </c>
+      <c r="AV129">
+        <v>5</v>
+      </c>
+      <c r="AW129">
+        <v>3</v>
+      </c>
+      <c r="AX129">
+        <v>4</v>
+      </c>
+      <c r="AY129">
+        <v>12</v>
+      </c>
+      <c r="AZ129">
+        <v>9</v>
+      </c>
+      <c r="BA129">
+        <v>6</v>
+      </c>
+      <c r="BB129">
+        <v>7</v>
+      </c>
+      <c r="BC129">
+        <v>13</v>
+      </c>
+      <c r="BD129">
+        <v>1.7</v>
+      </c>
+      <c r="BE129">
+        <v>8</v>
+      </c>
+      <c r="BF129">
+        <v>2.7</v>
+      </c>
+      <c r="BG129">
+        <v>1.48</v>
+      </c>
+      <c r="BH129">
+        <v>2.41</v>
+      </c>
+      <c r="BI129">
+        <v>1.9</v>
+      </c>
+      <c r="BJ129">
+        <v>1.9</v>
+      </c>
+      <c r="BK129">
+        <v>2.38</v>
+      </c>
+      <c r="BL129">
+        <v>1.49</v>
+      </c>
+      <c r="BM129">
+        <v>3.28</v>
+      </c>
+      <c r="BN129">
+        <v>1.25</v>
+      </c>
+      <c r="BO129">
+        <v>4.84</v>
+      </c>
+      <c r="BP129">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="130" spans="1:68">
+      <c r="A130" s="1">
+        <v>129</v>
+      </c>
+      <c r="B130">
+        <v>7806887</v>
+      </c>
+      <c r="C130" t="s">
+        <v>68</v>
+      </c>
+      <c r="D130" t="s">
+        <v>69</v>
+      </c>
+      <c r="E130" s="2">
+        <v>45857.29166666666</v>
+      </c>
+      <c r="F130">
+        <v>22</v>
+      </c>
+      <c r="G130" t="s">
+        <v>70</v>
+      </c>
+      <c r="H130" t="s">
+        <v>74</v>
+      </c>
+      <c r="I130">
+        <v>2</v>
+      </c>
+      <c r="J130">
+        <v>0</v>
+      </c>
+      <c r="K130">
+        <v>2</v>
+      </c>
+      <c r="L130">
+        <v>2</v>
+      </c>
+      <c r="M130">
+        <v>3</v>
+      </c>
+      <c r="N130">
+        <v>5</v>
+      </c>
+      <c r="O130" t="s">
+        <v>168</v>
+      </c>
+      <c r="P130" t="s">
+        <v>239</v>
+      </c>
+      <c r="Q130">
+        <v>3.55</v>
+      </c>
+      <c r="R130">
+        <v>1.95</v>
+      </c>
+      <c r="S130">
+        <v>3.1</v>
+      </c>
+      <c r="T130">
+        <v>1.48</v>
+      </c>
+      <c r="U130">
+        <v>2.45</v>
+      </c>
+      <c r="V130">
+        <v>3.2</v>
+      </c>
+      <c r="W130">
+        <v>1.3</v>
+      </c>
+      <c r="X130">
+        <v>7.5</v>
+      </c>
+      <c r="Y130">
+        <v>1.07</v>
+      </c>
+      <c r="Z130">
+        <v>2.85</v>
+      </c>
+      <c r="AA130">
+        <v>3</v>
+      </c>
+      <c r="AB130">
+        <v>2.3</v>
+      </c>
+      <c r="AC130">
+        <v>1.09</v>
+      </c>
+      <c r="AD130">
+        <v>7</v>
+      </c>
+      <c r="AE130">
+        <v>1.42</v>
+      </c>
+      <c r="AF130">
+        <v>2.8</v>
+      </c>
+      <c r="AG130">
+        <v>1.91</v>
+      </c>
+      <c r="AH130">
+        <v>1.79</v>
+      </c>
+      <c r="AI130">
+        <v>1.85</v>
+      </c>
+      <c r="AJ130">
+        <v>1.8</v>
+      </c>
+      <c r="AK130">
+        <v>1.53</v>
+      </c>
+      <c r="AL130">
+        <v>1.3</v>
+      </c>
+      <c r="AM130">
+        <v>1.38</v>
+      </c>
+      <c r="AN130">
+        <v>1.9</v>
+      </c>
+      <c r="AO130">
+        <v>2.5</v>
+      </c>
+      <c r="AP130">
+        <v>1.73</v>
+      </c>
+      <c r="AQ130">
+        <v>2.55</v>
+      </c>
+      <c r="AR130">
+        <v>1.69</v>
+      </c>
+      <c r="AS130">
+        <v>1.35</v>
+      </c>
+      <c r="AT130">
+        <v>3.04</v>
+      </c>
+      <c r="AU130">
+        <v>8</v>
+      </c>
+      <c r="AV130">
+        <v>8</v>
+      </c>
+      <c r="AW130">
+        <v>13</v>
+      </c>
+      <c r="AX130">
+        <v>6</v>
+      </c>
+      <c r="AY130">
+        <v>21</v>
+      </c>
+      <c r="AZ130">
+        <v>14</v>
+      </c>
+      <c r="BA130">
+        <v>6</v>
+      </c>
+      <c r="BB130">
+        <v>5</v>
+      </c>
+      <c r="BC130">
+        <v>11</v>
+      </c>
+      <c r="BD130">
+        <v>2.18</v>
+      </c>
+      <c r="BE130">
+        <v>8</v>
+      </c>
+      <c r="BF130">
+        <v>2.02</v>
+      </c>
+      <c r="BG130">
+        <v>1.45</v>
+      </c>
+      <c r="BH130">
+        <v>2.48</v>
+      </c>
+      <c r="BI130">
+        <v>1.85</v>
+      </c>
+      <c r="BJ130">
+        <v>1.95</v>
+      </c>
+      <c r="BK130">
+        <v>2.32</v>
+      </c>
+      <c r="BL130">
+        <v>1.52</v>
+      </c>
+      <c r="BM130">
+        <v>3.15</v>
+      </c>
+      <c r="BN130">
+        <v>1.27</v>
+      </c>
+      <c r="BO130">
+        <v>4.62</v>
+      </c>
+      <c r="BP130">
+        <v>1.11</v>
+      </c>
+    </row>
+    <row r="131" spans="1:68">
+      <c r="A131" s="1">
+        <v>130</v>
+      </c>
+      <c r="B131">
+        <v>7806888</v>
+      </c>
+      <c r="C131" t="s">
+        <v>68</v>
+      </c>
+      <c r="D131" t="s">
+        <v>69</v>
+      </c>
+      <c r="E131" s="2">
+        <v>45857.29166666666</v>
+      </c>
+      <c r="F131">
+        <v>22</v>
+      </c>
+      <c r="G131" t="s">
+        <v>71</v>
+      </c>
+      <c r="H131" t="s">
+        <v>80</v>
+      </c>
+      <c r="I131">
+        <v>0</v>
+      </c>
+      <c r="J131">
+        <v>0</v>
+      </c>
+      <c r="K131">
+        <v>0</v>
+      </c>
+      <c r="L131">
+        <v>2</v>
+      </c>
+      <c r="M131">
+        <v>0</v>
+      </c>
+      <c r="N131">
+        <v>2</v>
+      </c>
+      <c r="O131" t="s">
+        <v>169</v>
+      </c>
+      <c r="P131" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q131">
+        <v>2.95</v>
+      </c>
+      <c r="R131">
+        <v>2</v>
+      </c>
+      <c r="S131">
+        <v>3.55</v>
+      </c>
+      <c r="T131">
+        <v>1.42</v>
+      </c>
+      <c r="U131">
+        <v>2.65</v>
+      </c>
+      <c r="V131">
+        <v>2.88</v>
+      </c>
+      <c r="W131">
+        <v>1.36</v>
+      </c>
+      <c r="X131">
+        <v>7</v>
+      </c>
+      <c r="Y131">
+        <v>1.08</v>
+      </c>
+      <c r="Z131">
+        <v>2.32</v>
+      </c>
+      <c r="AA131">
+        <v>3.03</v>
+      </c>
+      <c r="AB131">
+        <v>2.79</v>
+      </c>
+      <c r="AC131">
+        <v>1.07</v>
+      </c>
+      <c r="AD131">
+        <v>8</v>
+      </c>
+      <c r="AE131">
+        <v>1.38</v>
+      </c>
+      <c r="AF131">
+        <v>3</v>
+      </c>
+      <c r="AG131">
+        <v>2.1</v>
+      </c>
+      <c r="AH131">
+        <v>1.65</v>
+      </c>
+      <c r="AI131">
+        <v>1.77</v>
+      </c>
+      <c r="AJ131">
+        <v>1.9</v>
+      </c>
+      <c r="AK131">
+        <v>1.36</v>
+      </c>
+      <c r="AL131">
+        <v>1.3</v>
+      </c>
+      <c r="AM131">
+        <v>1.57</v>
+      </c>
+      <c r="AN131">
+        <v>1.3</v>
+      </c>
+      <c r="AO131">
+        <v>1.2</v>
+      </c>
+      <c r="AP131">
+        <v>1.45</v>
+      </c>
+      <c r="AQ131">
+        <v>1.09</v>
+      </c>
+      <c r="AR131">
+        <v>1.51</v>
+      </c>
+      <c r="AS131">
+        <v>1.41</v>
+      </c>
+      <c r="AT131">
+        <v>2.92</v>
+      </c>
+      <c r="AU131">
+        <v>7</v>
+      </c>
+      <c r="AV131">
+        <v>5</v>
+      </c>
+      <c r="AW131">
+        <v>7</v>
+      </c>
+      <c r="AX131">
+        <v>2</v>
+      </c>
+      <c r="AY131">
+        <v>14</v>
+      </c>
+      <c r="AZ131">
+        <v>7</v>
+      </c>
+      <c r="BA131">
+        <v>3</v>
+      </c>
+      <c r="BB131">
+        <v>4</v>
+      </c>
+      <c r="BC131">
+        <v>7</v>
+      </c>
+      <c r="BD131">
+        <v>1.77</v>
+      </c>
+      <c r="BE131">
+        <v>8</v>
+      </c>
+      <c r="BF131">
+        <v>2.55</v>
+      </c>
+      <c r="BG131">
+        <v>1.42</v>
+      </c>
+      <c r="BH131">
+        <v>2.55</v>
+      </c>
+      <c r="BI131">
+        <v>1.8</v>
+      </c>
+      <c r="BJ131">
+        <v>2</v>
+      </c>
+      <c r="BK131">
+        <v>2.25</v>
+      </c>
+      <c r="BL131">
+        <v>1.56</v>
+      </c>
+      <c r="BM131">
+        <v>3.04</v>
+      </c>
+      <c r="BN131">
+        <v>1.29</v>
+      </c>
+      <c r="BO131">
+        <v>4.4</v>
+      </c>
+      <c r="BP131">
+        <v>1.13</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/South Korea K League 1_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/South Korea K League 1_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="848" uniqueCount="240">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="854" uniqueCount="240">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -1095,7 +1095,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP131"/>
+  <dimension ref="A1:BP132"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -3077,7 +3077,7 @@
         <v>3</v>
       </c>
       <c r="AP10">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AQ10">
         <v>1.09</v>
@@ -3286,7 +3286,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ11">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -4931,7 +4931,7 @@
         <v>1.5</v>
       </c>
       <c r="AP19">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AQ19">
         <v>1.55</v>
@@ -6788,7 +6788,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ28">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AR28">
         <v>1.36</v>
@@ -7609,7 +7609,7 @@
         <v>1</v>
       </c>
       <c r="AP32">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AQ32">
         <v>0.27</v>
@@ -7818,7 +7818,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ33">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AR33">
         <v>1.88</v>
@@ -10699,7 +10699,7 @@
         <v>3</v>
       </c>
       <c r="AP47">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AQ47">
         <v>1.82</v>
@@ -11526,7 +11526,7 @@
         <v>1</v>
       </c>
       <c r="AQ51">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AR51">
         <v>2.12</v>
@@ -12347,7 +12347,7 @@
         <v>0.75</v>
       </c>
       <c r="AP55">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AQ55">
         <v>1.45</v>
@@ -12968,7 +12968,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ58">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AR58">
         <v>1.54</v>
@@ -13792,7 +13792,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ62">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AR62">
         <v>1.73</v>
@@ -15025,7 +15025,7 @@
         <v>2.25</v>
       </c>
       <c r="AP68">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AQ68">
         <v>2.55</v>
@@ -17294,7 +17294,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ79">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AR79">
         <v>1.5</v>
@@ -18118,7 +18118,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ83">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AR83">
         <v>1.46</v>
@@ -19557,7 +19557,7 @@
         <v>0.29</v>
       </c>
       <c r="AP90">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AQ90">
         <v>0.4</v>
@@ -21414,7 +21414,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ99">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AR99">
         <v>1.53</v>
@@ -21826,7 +21826,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ101">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AR101">
         <v>1.6</v>
@@ -22029,7 +22029,7 @@
         <v>0.75</v>
       </c>
       <c r="AP102">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AQ102">
         <v>0.91</v>
@@ -24089,7 +24089,7 @@
         <v>1.33</v>
       </c>
       <c r="AP112">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AQ112">
         <v>1.45</v>
@@ -26767,7 +26767,7 @@
         <v>1.3</v>
       </c>
       <c r="AP125">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AQ125">
         <v>1.18</v>
@@ -28082,6 +28082,212 @@
       </c>
       <c r="BP131">
         <v>1.13</v>
+      </c>
+    </row>
+    <row r="132" spans="1:68">
+      <c r="A132" s="1">
+        <v>131</v>
+      </c>
+      <c r="B132">
+        <v>7806889</v>
+      </c>
+      <c r="C132" t="s">
+        <v>68</v>
+      </c>
+      <c r="D132" t="s">
+        <v>69</v>
+      </c>
+      <c r="E132" s="2">
+        <v>45858.29166666666</v>
+      </c>
+      <c r="F132">
+        <v>22</v>
+      </c>
+      <c r="G132" t="s">
+        <v>76</v>
+      </c>
+      <c r="H132" t="s">
+        <v>73</v>
+      </c>
+      <c r="I132">
+        <v>1</v>
+      </c>
+      <c r="J132">
+        <v>0</v>
+      </c>
+      <c r="K132">
+        <v>1</v>
+      </c>
+      <c r="L132">
+        <v>1</v>
+      </c>
+      <c r="M132">
+        <v>0</v>
+      </c>
+      <c r="N132">
+        <v>1</v>
+      </c>
+      <c r="O132" t="s">
+        <v>151</v>
+      </c>
+      <c r="P132" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q132">
+        <v>3</v>
+      </c>
+      <c r="R132">
+        <v>2.05</v>
+      </c>
+      <c r="S132">
+        <v>4</v>
+      </c>
+      <c r="T132">
+        <v>1.44</v>
+      </c>
+      <c r="U132">
+        <v>2.63</v>
+      </c>
+      <c r="V132">
+        <v>3.25</v>
+      </c>
+      <c r="W132">
+        <v>1.33</v>
+      </c>
+      <c r="X132">
+        <v>9</v>
+      </c>
+      <c r="Y132">
+        <v>1.07</v>
+      </c>
+      <c r="Z132">
+        <v>2.19</v>
+      </c>
+      <c r="AA132">
+        <v>3.13</v>
+      </c>
+      <c r="AB132">
+        <v>2.91</v>
+      </c>
+      <c r="AC132">
+        <v>1.08</v>
+      </c>
+      <c r="AD132">
+        <v>7.5</v>
+      </c>
+      <c r="AE132">
+        <v>1.4</v>
+      </c>
+      <c r="AF132">
+        <v>2.9</v>
+      </c>
+      <c r="AG132">
+        <v>2.02</v>
+      </c>
+      <c r="AH132">
+        <v>1.7</v>
+      </c>
+      <c r="AI132">
+        <v>1.83</v>
+      </c>
+      <c r="AJ132">
+        <v>1.83</v>
+      </c>
+      <c r="AK132">
+        <v>1.34</v>
+      </c>
+      <c r="AL132">
+        <v>1.32</v>
+      </c>
+      <c r="AM132">
+        <v>1.62</v>
+      </c>
+      <c r="AN132">
+        <v>1.3</v>
+      </c>
+      <c r="AO132">
+        <v>1.5</v>
+      </c>
+      <c r="AP132">
+        <v>1.45</v>
+      </c>
+      <c r="AQ132">
+        <v>1.36</v>
+      </c>
+      <c r="AR132">
+        <v>1.82</v>
+      </c>
+      <c r="AS132">
+        <v>1.82</v>
+      </c>
+      <c r="AT132">
+        <v>3.64</v>
+      </c>
+      <c r="AU132">
+        <v>5</v>
+      </c>
+      <c r="AV132">
+        <v>3</v>
+      </c>
+      <c r="AW132">
+        <v>4</v>
+      </c>
+      <c r="AX132">
+        <v>11</v>
+      </c>
+      <c r="AY132">
+        <v>9</v>
+      </c>
+      <c r="AZ132">
+        <v>14</v>
+      </c>
+      <c r="BA132">
+        <v>3</v>
+      </c>
+      <c r="BB132">
+        <v>11</v>
+      </c>
+      <c r="BC132">
+        <v>14</v>
+      </c>
+      <c r="BD132">
+        <v>1.7</v>
+      </c>
+      <c r="BE132">
+        <v>8</v>
+      </c>
+      <c r="BF132">
+        <v>2.7</v>
+      </c>
+      <c r="BG132">
+        <v>1.34</v>
+      </c>
+      <c r="BH132">
+        <v>2.84</v>
+      </c>
+      <c r="BI132">
+        <v>1.65</v>
+      </c>
+      <c r="BJ132">
+        <v>2.1</v>
+      </c>
+      <c r="BK132">
+        <v>2.06</v>
+      </c>
+      <c r="BL132">
+        <v>1.68</v>
+      </c>
+      <c r="BM132">
+        <v>2.7</v>
+      </c>
+      <c r="BN132">
+        <v>1.38</v>
+      </c>
+      <c r="BO132">
+        <v>3.78</v>
+      </c>
+      <c r="BP132">
+        <v>1.18</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/South Korea K League 1_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/South Korea K League 1_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="854" uniqueCount="240">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="872" uniqueCount="243">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -526,6 +526,15 @@
     <t>['69', '79']</t>
   </si>
   <si>
+    <t>['30', '45+4', '82', '90+3']</t>
+  </si>
+  <si>
+    <t>['41']</t>
+  </si>
+  <si>
+    <t>['37']</t>
+  </si>
+  <si>
     <t>['32', '87', '90']</t>
   </si>
   <si>
@@ -691,9 +700,6 @@
     <t>['65', '75']</t>
   </si>
   <si>
-    <t>['41']</t>
-  </si>
-  <si>
     <t>['32']</t>
   </si>
   <si>
@@ -734,6 +740,9 @@
   </si>
   <si>
     <t>['65', '80', '90+5']</t>
+  </si>
+  <si>
+    <t>['19', '38', '65', '79', '83']</t>
   </si>
 </sst>
 </file>
@@ -1095,7 +1104,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP132"/>
+  <dimension ref="A1:BP135"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1351,7 +1360,7 @@
         <v>82</v>
       </c>
       <c r="P2" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="Q2">
         <v>2.75</v>
@@ -1429,7 +1438,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AQ2">
         <v>1.82</v>
@@ -1841,10 +1850,10 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ4">
-        <v>0.4</v>
+        <v>0.64</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -1969,7 +1978,7 @@
         <v>82</v>
       </c>
       <c r="P5" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="Q5">
         <v>2.1</v>
@@ -2256,7 +2265,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ6">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2381,7 +2390,7 @@
         <v>85</v>
       </c>
       <c r="P7" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="Q7">
         <v>3.5</v>
@@ -2587,7 +2596,7 @@
         <v>86</v>
       </c>
       <c r="P8" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="Q8">
         <v>3.4</v>
@@ -2668,7 +2677,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ8">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AR8">
         <v>1.38</v>
@@ -2793,7 +2802,7 @@
         <v>87</v>
       </c>
       <c r="P9" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="Q9">
         <v>3.35</v>
@@ -2874,7 +2883,7 @@
         <v>1</v>
       </c>
       <c r="AQ9">
-        <v>0.4</v>
+        <v>0.64</v>
       </c>
       <c r="AR9">
         <v>1.95</v>
@@ -3205,7 +3214,7 @@
         <v>82</v>
       </c>
       <c r="P11" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="Q11">
         <v>3.45</v>
@@ -3411,7 +3420,7 @@
         <v>89</v>
       </c>
       <c r="P12" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="Q12">
         <v>2.75</v>
@@ -3617,7 +3626,7 @@
         <v>90</v>
       </c>
       <c r="P13" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="Q13">
         <v>2.95</v>
@@ -4107,10 +4116,10 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AQ15">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="AR15">
         <v>1.87</v>
@@ -4313,7 +4322,7 @@
         <v>1.5</v>
       </c>
       <c r="AP16">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ16">
         <v>1.09</v>
@@ -4522,7 +4531,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ17">
-        <v>0.4</v>
+        <v>0.64</v>
       </c>
       <c r="AR17">
         <v>1.3</v>
@@ -4934,7 +4943,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ19">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AR19">
         <v>1.46</v>
@@ -5265,7 +5274,7 @@
         <v>94</v>
       </c>
       <c r="P21" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="Q21">
         <v>3.1</v>
@@ -5471,7 +5480,7 @@
         <v>95</v>
       </c>
       <c r="P22" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="Q22">
         <v>3.6</v>
@@ -5549,10 +5558,10 @@
         <v>1.33</v>
       </c>
       <c r="AP22">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AQ22">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AR22">
         <v>0</v>
@@ -6089,7 +6098,7 @@
         <v>97</v>
       </c>
       <c r="P25" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="Q25">
         <v>4</v>
@@ -6295,7 +6304,7 @@
         <v>82</v>
       </c>
       <c r="P26" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="Q26">
         <v>3.6</v>
@@ -6501,7 +6510,7 @@
         <v>82</v>
       </c>
       <c r="P27" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="Q27">
         <v>2.75</v>
@@ -6707,7 +6716,7 @@
         <v>98</v>
       </c>
       <c r="P28" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="Q28">
         <v>3.75</v>
@@ -7119,7 +7128,7 @@
         <v>99</v>
       </c>
       <c r="P30" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="Q30">
         <v>2.63</v>
@@ -7325,7 +7334,7 @@
         <v>100</v>
       </c>
       <c r="P31" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="Q31">
         <v>3.1</v>
@@ -7403,7 +7412,7 @@
         <v>0.5</v>
       </c>
       <c r="AP31">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ31">
         <v>1.18</v>
@@ -7531,7 +7540,7 @@
         <v>101</v>
       </c>
       <c r="P32" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="Q32">
         <v>2.5</v>
@@ -7612,7 +7621,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ32">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="AR32">
         <v>0.86</v>
@@ -7815,7 +7824,7 @@
         <v>2</v>
       </c>
       <c r="AP33">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AQ33">
         <v>1.36</v>
@@ -7943,7 +7952,7 @@
         <v>103</v>
       </c>
       <c r="P34" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="Q34">
         <v>3.2</v>
@@ -8230,7 +8239,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ35">
-        <v>0.4</v>
+        <v>0.64</v>
       </c>
       <c r="AR35">
         <v>1.17</v>
@@ -8639,7 +8648,7 @@
         <v>0</v>
       </c>
       <c r="AP37">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AQ37">
         <v>2.55</v>
@@ -8767,7 +8776,7 @@
         <v>106</v>
       </c>
       <c r="P38" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="Q38">
         <v>2.45</v>
@@ -9260,7 +9269,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ40">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="AR40">
         <v>1.95</v>
@@ -9385,7 +9394,7 @@
         <v>82</v>
       </c>
       <c r="P41" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="Q41">
         <v>3.25</v>
@@ -9591,7 +9600,7 @@
         <v>98</v>
       </c>
       <c r="P42" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="Q42">
         <v>3.4</v>
@@ -9875,7 +9884,7 @@
         <v>1</v>
       </c>
       <c r="AP43">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AQ43">
         <v>1.45</v>
@@ -10081,7 +10090,7 @@
         <v>0.5</v>
       </c>
       <c r="AP44">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ44">
         <v>0.91</v>
@@ -10287,10 +10296,10 @@
         <v>0.33</v>
       </c>
       <c r="AP45">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ45">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="AR45">
         <v>1.77</v>
@@ -10415,7 +10424,7 @@
         <v>111</v>
       </c>
       <c r="P46" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="Q46">
         <v>4.33</v>
@@ -10496,7 +10505,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ46">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AR46">
         <v>1.44</v>
@@ -10621,7 +10630,7 @@
         <v>112</v>
       </c>
       <c r="P47" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="Q47">
         <v>2.6</v>
@@ -10905,7 +10914,7 @@
         <v>1.5</v>
       </c>
       <c r="AP48">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AQ48">
         <v>1.09</v>
@@ -11651,7 +11660,7 @@
         <v>116</v>
       </c>
       <c r="P52" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="Q52">
         <v>2.38</v>
@@ -11857,7 +11866,7 @@
         <v>117</v>
       </c>
       <c r="P53" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="Q53">
         <v>3.1</v>
@@ -11935,10 +11944,10 @@
         <v>0.25</v>
       </c>
       <c r="AP53">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AQ53">
-        <v>0.4</v>
+        <v>0.64</v>
       </c>
       <c r="AR53">
         <v>1.51</v>
@@ -12063,7 +12072,7 @@
         <v>82</v>
       </c>
       <c r="P54" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="Q54">
         <v>2.75</v>
@@ -12269,7 +12278,7 @@
         <v>118</v>
       </c>
       <c r="P55" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="Q55">
         <v>2.75</v>
@@ -12681,7 +12690,7 @@
         <v>120</v>
       </c>
       <c r="P57" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="Q57">
         <v>2.3</v>
@@ -12762,7 +12771,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ57">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="AR57">
         <v>1.63</v>
@@ -12887,7 +12896,7 @@
         <v>82</v>
       </c>
       <c r="P58" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="Q58">
         <v>4.5</v>
@@ -12965,7 +12974,7 @@
         <v>1.75</v>
       </c>
       <c r="AP58">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AQ58">
         <v>1.36</v>
@@ -13093,7 +13102,7 @@
         <v>121</v>
       </c>
       <c r="P59" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="Q59">
         <v>4</v>
@@ -13299,7 +13308,7 @@
         <v>122</v>
       </c>
       <c r="P60" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="Q60">
         <v>2.7</v>
@@ -13377,7 +13386,7 @@
         <v>0.5</v>
       </c>
       <c r="AP60">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AQ60">
         <v>0.91</v>
@@ -13583,7 +13592,7 @@
         <v>1.25</v>
       </c>
       <c r="AP61">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AQ61">
         <v>1.55</v>
@@ -14329,7 +14338,7 @@
         <v>105</v>
       </c>
       <c r="P65" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="Q65">
         <v>3.4</v>
@@ -14407,10 +14416,10 @@
         <v>1.4</v>
       </c>
       <c r="AP65">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AQ65">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AR65">
         <v>1.65</v>
@@ -14535,7 +14544,7 @@
         <v>127</v>
       </c>
       <c r="P66" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="Q66">
         <v>2.5</v>
@@ -14947,7 +14956,7 @@
         <v>82</v>
       </c>
       <c r="P68" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="Q68">
         <v>3</v>
@@ -15234,7 +15243,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ69">
-        <v>0.4</v>
+        <v>0.64</v>
       </c>
       <c r="AR69">
         <v>1.43</v>
@@ -15359,7 +15368,7 @@
         <v>116</v>
       </c>
       <c r="P70" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="Q70">
         <v>2.38</v>
@@ -15643,10 +15652,10 @@
         <v>1.67</v>
       </c>
       <c r="AP71">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ71">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AR71">
         <v>1.66</v>
@@ -15977,7 +15986,7 @@
         <v>82</v>
       </c>
       <c r="P73" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="Q73">
         <v>3</v>
@@ -16183,7 +16192,7 @@
         <v>130</v>
       </c>
       <c r="P74" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="Q74">
         <v>5</v>
@@ -16261,7 +16270,7 @@
         <v>1</v>
       </c>
       <c r="AP74">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AQ74">
         <v>1.55</v>
@@ -16389,7 +16398,7 @@
         <v>131</v>
       </c>
       <c r="P75" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="Q75">
         <v>2.88</v>
@@ -16470,7 +16479,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ75">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="AR75">
         <v>1.55</v>
@@ -16673,10 +16682,10 @@
         <v>0.33</v>
       </c>
       <c r="AP76">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AQ76">
-        <v>0.4</v>
+        <v>0.64</v>
       </c>
       <c r="AR76">
         <v>1.63</v>
@@ -16801,7 +16810,7 @@
         <v>133</v>
       </c>
       <c r="P77" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="Q77">
         <v>3</v>
@@ -16879,10 +16888,10 @@
         <v>0.17</v>
       </c>
       <c r="AP77">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AQ77">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="AR77">
         <v>1.51</v>
@@ -17213,7 +17222,7 @@
         <v>134</v>
       </c>
       <c r="P79" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="Q79">
         <v>4.33</v>
@@ -17419,7 +17428,7 @@
         <v>82</v>
       </c>
       <c r="P80" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="Q80">
         <v>3.6</v>
@@ -17500,7 +17509,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ80">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AR80">
         <v>1.51</v>
@@ -17625,7 +17634,7 @@
         <v>82</v>
       </c>
       <c r="P81" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="Q81">
         <v>3.5</v>
@@ -17703,7 +17712,7 @@
         <v>2.4</v>
       </c>
       <c r="AP81">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ81">
         <v>2.55</v>
@@ -18037,7 +18046,7 @@
         <v>136</v>
       </c>
       <c r="P83" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="Q83">
         <v>4.33</v>
@@ -18243,7 +18252,7 @@
         <v>137</v>
       </c>
       <c r="P84" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="Q84">
         <v>2.4</v>
@@ -18527,7 +18536,7 @@
         <v>1</v>
       </c>
       <c r="AP85">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AQ85">
         <v>1.45</v>
@@ -18655,7 +18664,7 @@
         <v>82</v>
       </c>
       <c r="P86" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="Q86">
         <v>5</v>
@@ -19273,7 +19282,7 @@
         <v>82</v>
       </c>
       <c r="P89" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="Q89">
         <v>3.4</v>
@@ -19351,7 +19360,7 @@
         <v>1</v>
       </c>
       <c r="AP89">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AQ89">
         <v>1.18</v>
@@ -19479,7 +19488,7 @@
         <v>139</v>
       </c>
       <c r="P90" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="Q90">
         <v>2.3</v>
@@ -19560,7 +19569,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ90">
-        <v>0.4</v>
+        <v>0.64</v>
       </c>
       <c r="AR90">
         <v>1.6</v>
@@ -19685,7 +19694,7 @@
         <v>140</v>
       </c>
       <c r="P91" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="Q91">
         <v>2.55</v>
@@ -19766,7 +19775,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ91">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AR91">
         <v>2.04</v>
@@ -19972,7 +19981,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ92">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="AR92">
         <v>1.34</v>
@@ -20097,7 +20106,7 @@
         <v>82</v>
       </c>
       <c r="P93" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="Q93">
         <v>2.88</v>
@@ -20175,7 +20184,7 @@
         <v>1.29</v>
       </c>
       <c r="AP93">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ93">
         <v>1.45</v>
@@ -20303,7 +20312,7 @@
         <v>82</v>
       </c>
       <c r="P94" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="Q94">
         <v>2.8</v>
@@ -20509,7 +20518,7 @@
         <v>142</v>
       </c>
       <c r="P95" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="Q95">
         <v>2.62</v>
@@ -20715,7 +20724,7 @@
         <v>82</v>
       </c>
       <c r="P96" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="Q96">
         <v>4</v>
@@ -20921,7 +20930,7 @@
         <v>82</v>
       </c>
       <c r="P97" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="Q97">
         <v>3.1</v>
@@ -21127,7 +21136,7 @@
         <v>125</v>
       </c>
       <c r="P98" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="Q98">
         <v>2.75</v>
@@ -21333,7 +21342,7 @@
         <v>143</v>
       </c>
       <c r="P99" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="Q99">
         <v>3.4</v>
@@ -21411,7 +21420,7 @@
         <v>1.75</v>
       </c>
       <c r="AP99">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ99">
         <v>1.36</v>
@@ -21539,7 +21548,7 @@
         <v>134</v>
       </c>
       <c r="P100" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="Q100">
         <v>3.3</v>
@@ -21617,7 +21626,7 @@
         <v>2.13</v>
       </c>
       <c r="AP100">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AQ100">
         <v>1.82</v>
@@ -21745,7 +21754,7 @@
         <v>144</v>
       </c>
       <c r="P101" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="Q101">
         <v>3</v>
@@ -21951,7 +21960,7 @@
         <v>145</v>
       </c>
       <c r="P102" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="Q102">
         <v>2.3</v>
@@ -22157,7 +22166,7 @@
         <v>146</v>
       </c>
       <c r="P103" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="Q103">
         <v>2.1</v>
@@ -22238,7 +22247,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ103">
-        <v>0.4</v>
+        <v>0.64</v>
       </c>
       <c r="AR103">
         <v>1.74</v>
@@ -22363,7 +22372,7 @@
         <v>147</v>
       </c>
       <c r="P104" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="Q104">
         <v>2.55</v>
@@ -22441,7 +22450,7 @@
         <v>1.5</v>
       </c>
       <c r="AP104">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AQ104">
         <v>1.45</v>
@@ -22775,7 +22784,7 @@
         <v>82</v>
       </c>
       <c r="P106" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="Q106">
         <v>4.5</v>
@@ -22981,7 +22990,7 @@
         <v>149</v>
       </c>
       <c r="P107" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="Q107">
         <v>4.33</v>
@@ -23059,7 +23068,7 @@
         <v>1.44</v>
       </c>
       <c r="AP107">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ107">
         <v>1.55</v>
@@ -23393,7 +23402,7 @@
         <v>151</v>
       </c>
       <c r="P109" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="Q109">
         <v>3</v>
@@ -23599,7 +23608,7 @@
         <v>152</v>
       </c>
       <c r="P110" t="s">
-        <v>225</v>
+        <v>171</v>
       </c>
       <c r="Q110">
         <v>2.5</v>
@@ -23680,7 +23689,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ110">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="AR110">
         <v>1.5</v>
@@ -23805,7 +23814,7 @@
         <v>153</v>
       </c>
       <c r="P111" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="Q111">
         <v>4.33</v>
@@ -24011,7 +24020,7 @@
         <v>154</v>
       </c>
       <c r="P112" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Q112">
         <v>2.25</v>
@@ -24217,7 +24226,7 @@
         <v>155</v>
       </c>
       <c r="P113" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Q113">
         <v>2.2</v>
@@ -24298,7 +24307,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ113">
-        <v>0.4</v>
+        <v>0.64</v>
       </c>
       <c r="AR113">
         <v>1.6</v>
@@ -24710,7 +24719,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ115">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AR115">
         <v>1.43</v>
@@ -24916,7 +24925,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ116">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="AR116">
         <v>1.56</v>
@@ -25041,7 +25050,7 @@
         <v>157</v>
       </c>
       <c r="P117" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q117">
         <v>2.5</v>
@@ -25119,7 +25128,7 @@
         <v>1</v>
       </c>
       <c r="AP117">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AQ117">
         <v>0.91</v>
@@ -25247,7 +25256,7 @@
         <v>158</v>
       </c>
       <c r="P118" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="Q118">
         <v>3.4</v>
@@ -25659,7 +25668,7 @@
         <v>160</v>
       </c>
       <c r="P120" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="Q120">
         <v>2.7</v>
@@ -25737,7 +25746,7 @@
         <v>2</v>
       </c>
       <c r="AP120">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AQ120">
         <v>1.82</v>
@@ -25865,7 +25874,7 @@
         <v>118</v>
       </c>
       <c r="P121" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="Q121">
         <v>3.2</v>
@@ -26071,7 +26080,7 @@
         <v>161</v>
       </c>
       <c r="P122" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="Q122">
         <v>2.9</v>
@@ -26277,7 +26286,7 @@
         <v>162</v>
       </c>
       <c r="P123" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Q123">
         <v>3.1</v>
@@ -26483,7 +26492,7 @@
         <v>151</v>
       </c>
       <c r="P124" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="Q124">
         <v>3.7</v>
@@ -26561,7 +26570,7 @@
         <v>1.44</v>
       </c>
       <c r="AP124">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AQ124">
         <v>1.45</v>
@@ -26689,7 +26698,7 @@
         <v>163</v>
       </c>
       <c r="P125" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Q125">
         <v>2.75</v>
@@ -26895,7 +26904,7 @@
         <v>164</v>
       </c>
       <c r="P126" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Q126">
         <v>2</v>
@@ -26976,7 +26985,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ126">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="AR126">
         <v>2</v>
@@ -27307,7 +27316,7 @@
         <v>166</v>
       </c>
       <c r="P128" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q128">
         <v>3.55</v>
@@ -27388,7 +27397,7 @@
         <v>1</v>
       </c>
       <c r="AQ128">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AR128">
         <v>1.81</v>
@@ -27513,7 +27522,7 @@
         <v>167</v>
       </c>
       <c r="P129" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q129">
         <v>3.1</v>
@@ -27609,28 +27618,28 @@
         <v>9</v>
       </c>
       <c r="AV129">
+        <v>8</v>
+      </c>
+      <c r="AW129">
         <v>5</v>
       </c>
-      <c r="AW129">
-        <v>3</v>
-      </c>
       <c r="AX129">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AY129">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AZ129">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BA129">
         <v>6</v>
       </c>
       <c r="BB129">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BC129">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BD129">
         <v>1.7</v>
@@ -27719,7 +27728,7 @@
         <v>168</v>
       </c>
       <c r="P130" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q130">
         <v>3.55</v>
@@ -27797,7 +27806,7 @@
         <v>2.5</v>
       </c>
       <c r="AP130">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AQ130">
         <v>2.55</v>
@@ -27815,16 +27824,16 @@
         <v>8</v>
       </c>
       <c r="AV130">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AW130">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AX130">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AY130">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="AZ130">
         <v>14</v>
@@ -28024,16 +28033,16 @@
         <v>5</v>
       </c>
       <c r="AW131">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AX131">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AY131">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AZ131">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA131">
         <v>3</v>
@@ -28288,6 +28297,624 @@
       </c>
       <c r="BP132">
         <v>1.18</v>
+      </c>
+    </row>
+    <row r="133" spans="1:68">
+      <c r="A133" s="1">
+        <v>132</v>
+      </c>
+      <c r="B133">
+        <v>7806892</v>
+      </c>
+      <c r="C133" t="s">
+        <v>68</v>
+      </c>
+      <c r="D133" t="s">
+        <v>69</v>
+      </c>
+      <c r="E133" s="2">
+        <v>45860.3125</v>
+      </c>
+      <c r="F133">
+        <v>23</v>
+      </c>
+      <c r="G133" t="s">
+        <v>80</v>
+      </c>
+      <c r="H133" t="s">
+        <v>75</v>
+      </c>
+      <c r="I133">
+        <v>2</v>
+      </c>
+      <c r="J133">
+        <v>0</v>
+      </c>
+      <c r="K133">
+        <v>2</v>
+      </c>
+      <c r="L133">
+        <v>4</v>
+      </c>
+      <c r="M133">
+        <v>0</v>
+      </c>
+      <c r="N133">
+        <v>4</v>
+      </c>
+      <c r="O133" t="s">
+        <v>170</v>
+      </c>
+      <c r="P133" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q133">
+        <v>2.55</v>
+      </c>
+      <c r="R133">
+        <v>2.1</v>
+      </c>
+      <c r="S133">
+        <v>3.8</v>
+      </c>
+      <c r="T133">
+        <v>1.36</v>
+      </c>
+      <c r="U133">
+        <v>2.87</v>
+      </c>
+      <c r="V133">
+        <v>2.6</v>
+      </c>
+      <c r="W133">
+        <v>1.44</v>
+      </c>
+      <c r="X133">
+        <v>6.5</v>
+      </c>
+      <c r="Y133">
+        <v>1.1</v>
+      </c>
+      <c r="Z133">
+        <v>1.9</v>
+      </c>
+      <c r="AA133">
+        <v>3.32</v>
+      </c>
+      <c r="AB133">
+        <v>3.45</v>
+      </c>
+      <c r="AC133">
+        <v>1.05</v>
+      </c>
+      <c r="AD133">
+        <v>9</v>
+      </c>
+      <c r="AE133">
+        <v>1.28</v>
+      </c>
+      <c r="AF133">
+        <v>3.6</v>
+      </c>
+      <c r="AG133">
+        <v>1.7</v>
+      </c>
+      <c r="AH133">
+        <v>2.02</v>
+      </c>
+      <c r="AI133">
+        <v>1.7</v>
+      </c>
+      <c r="AJ133">
+        <v>2</v>
+      </c>
+      <c r="AK133">
+        <v>1.28</v>
+      </c>
+      <c r="AL133">
+        <v>1.29</v>
+      </c>
+      <c r="AM133">
+        <v>1.75</v>
+      </c>
+      <c r="AN133">
+        <v>1.09</v>
+      </c>
+      <c r="AO133">
+        <v>0.27</v>
+      </c>
+      <c r="AP133">
+        <v>1.25</v>
+      </c>
+      <c r="AQ133">
+        <v>0.25</v>
+      </c>
+      <c r="AR133">
+        <v>1.48</v>
+      </c>
+      <c r="AS133">
+        <v>1.27</v>
+      </c>
+      <c r="AT133">
+        <v>2.75</v>
+      </c>
+      <c r="AU133">
+        <v>7</v>
+      </c>
+      <c r="AV133">
+        <v>4</v>
+      </c>
+      <c r="AW133">
+        <v>8</v>
+      </c>
+      <c r="AX133">
+        <v>8</v>
+      </c>
+      <c r="AY133">
+        <v>15</v>
+      </c>
+      <c r="AZ133">
+        <v>12</v>
+      </c>
+      <c r="BA133">
+        <v>5</v>
+      </c>
+      <c r="BB133">
+        <v>3</v>
+      </c>
+      <c r="BC133">
+        <v>8</v>
+      </c>
+      <c r="BD133">
+        <v>1.54</v>
+      </c>
+      <c r="BE133">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="BF133">
+        <v>3.04</v>
+      </c>
+      <c r="BG133">
+        <v>1.31</v>
+      </c>
+      <c r="BH133">
+        <v>2.92</v>
+      </c>
+      <c r="BI133">
+        <v>1.59</v>
+      </c>
+      <c r="BJ133">
+        <v>2.16</v>
+      </c>
+      <c r="BK133">
+        <v>2.03</v>
+      </c>
+      <c r="BL133">
+        <v>1.7</v>
+      </c>
+      <c r="BM133">
+        <v>2.67</v>
+      </c>
+      <c r="BN133">
+        <v>1.39</v>
+      </c>
+      <c r="BO133">
+        <v>3.58</v>
+      </c>
+      <c r="BP133">
+        <v>1.21</v>
+      </c>
+    </row>
+    <row r="134" spans="1:68">
+      <c r="A134" s="1">
+        <v>133</v>
+      </c>
+      <c r="B134">
+        <v>7806890</v>
+      </c>
+      <c r="C134" t="s">
+        <v>68</v>
+      </c>
+      <c r="D134" t="s">
+        <v>69</v>
+      </c>
+      <c r="E134" s="2">
+        <v>45860.3125</v>
+      </c>
+      <c r="F134">
+        <v>23</v>
+      </c>
+      <c r="G134" t="s">
+        <v>70</v>
+      </c>
+      <c r="H134" t="s">
+        <v>79</v>
+      </c>
+      <c r="I134">
+        <v>1</v>
+      </c>
+      <c r="J134">
+        <v>2</v>
+      </c>
+      <c r="K134">
+        <v>3</v>
+      </c>
+      <c r="L134">
+        <v>1</v>
+      </c>
+      <c r="M134">
+        <v>5</v>
+      </c>
+      <c r="N134">
+        <v>6</v>
+      </c>
+      <c r="O134" t="s">
+        <v>171</v>
+      </c>
+      <c r="P134" t="s">
+        <v>242</v>
+      </c>
+      <c r="Q134">
+        <v>2.55</v>
+      </c>
+      <c r="R134">
+        <v>2.05</v>
+      </c>
+      <c r="S134">
+        <v>4</v>
+      </c>
+      <c r="T134">
+        <v>1.4</v>
+      </c>
+      <c r="U134">
+        <v>2.7</v>
+      </c>
+      <c r="V134">
+        <v>2.85</v>
+      </c>
+      <c r="W134">
+        <v>1.37</v>
+      </c>
+      <c r="X134">
+        <v>7.5</v>
+      </c>
+      <c r="Y134">
+        <v>1.08</v>
+      </c>
+      <c r="Z134">
+        <v>1.9</v>
+      </c>
+      <c r="AA134">
+        <v>3.29</v>
+      </c>
+      <c r="AB134">
+        <v>3.45</v>
+      </c>
+      <c r="AC134">
+        <v>1.06</v>
+      </c>
+      <c r="AD134">
+        <v>8.5</v>
+      </c>
+      <c r="AE134">
+        <v>1.33</v>
+      </c>
+      <c r="AF134">
+        <v>3.25</v>
+      </c>
+      <c r="AG134">
+        <v>1.96</v>
+      </c>
+      <c r="AH134">
+        <v>1.74</v>
+      </c>
+      <c r="AI134">
+        <v>1.83</v>
+      </c>
+      <c r="AJ134">
+        <v>1.85</v>
+      </c>
+      <c r="AK134">
+        <v>1.26</v>
+      </c>
+      <c r="AL134">
+        <v>1.3</v>
+      </c>
+      <c r="AM134">
+        <v>1.78</v>
+      </c>
+      <c r="AN134">
+        <v>1.73</v>
+      </c>
+      <c r="AO134">
+        <v>0.4</v>
+      </c>
+      <c r="AP134">
+        <v>1.58</v>
+      </c>
+      <c r="AQ134">
+        <v>0.64</v>
+      </c>
+      <c r="AR134">
+        <v>1.73</v>
+      </c>
+      <c r="AS134">
+        <v>1.3</v>
+      </c>
+      <c r="AT134">
+        <v>3.03</v>
+      </c>
+      <c r="AU134">
+        <v>7</v>
+      </c>
+      <c r="AV134">
+        <v>9</v>
+      </c>
+      <c r="AW134">
+        <v>8</v>
+      </c>
+      <c r="AX134">
+        <v>8</v>
+      </c>
+      <c r="AY134">
+        <v>15</v>
+      </c>
+      <c r="AZ134">
+        <v>17</v>
+      </c>
+      <c r="BA134">
+        <v>7</v>
+      </c>
+      <c r="BB134">
+        <v>3</v>
+      </c>
+      <c r="BC134">
+        <v>10</v>
+      </c>
+      <c r="BD134">
+        <v>1.49</v>
+      </c>
+      <c r="BE134">
+        <v>7.75</v>
+      </c>
+      <c r="BF134">
+        <v>3.62</v>
+      </c>
+      <c r="BG134">
+        <v>1.33</v>
+      </c>
+      <c r="BH134">
+        <v>2.88</v>
+      </c>
+      <c r="BI134">
+        <v>1.75</v>
+      </c>
+      <c r="BJ134">
+        <v>2.04</v>
+      </c>
+      <c r="BK134">
+        <v>2.22</v>
+      </c>
+      <c r="BL134">
+        <v>1.62</v>
+      </c>
+      <c r="BM134">
+        <v>2.66</v>
+      </c>
+      <c r="BN134">
+        <v>1.39</v>
+      </c>
+      <c r="BO134">
+        <v>3.72</v>
+      </c>
+      <c r="BP134">
+        <v>1.19</v>
+      </c>
+    </row>
+    <row r="135" spans="1:68">
+      <c r="A135" s="1">
+        <v>134</v>
+      </c>
+      <c r="B135">
+        <v>7806891</v>
+      </c>
+      <c r="C135" t="s">
+        <v>68</v>
+      </c>
+      <c r="D135" t="s">
+        <v>69</v>
+      </c>
+      <c r="E135" s="2">
+        <v>45860.3125</v>
+      </c>
+      <c r="F135">
+        <v>23</v>
+      </c>
+      <c r="G135" t="s">
+        <v>72</v>
+      </c>
+      <c r="H135" t="s">
+        <v>81</v>
+      </c>
+      <c r="I135">
+        <v>1</v>
+      </c>
+      <c r="J135">
+        <v>0</v>
+      </c>
+      <c r="K135">
+        <v>1</v>
+      </c>
+      <c r="L135">
+        <v>1</v>
+      </c>
+      <c r="M135">
+        <v>1</v>
+      </c>
+      <c r="N135">
+        <v>2</v>
+      </c>
+      <c r="O135" t="s">
+        <v>172</v>
+      </c>
+      <c r="P135" t="s">
+        <v>185</v>
+      </c>
+      <c r="Q135">
+        <v>3.25</v>
+      </c>
+      <c r="R135">
+        <v>2.2</v>
+      </c>
+      <c r="S135">
+        <v>3.25</v>
+      </c>
+      <c r="T135">
+        <v>1.4</v>
+      </c>
+      <c r="U135">
+        <v>2.75</v>
+      </c>
+      <c r="V135">
+        <v>2.75</v>
+      </c>
+      <c r="W135">
+        <v>1.4</v>
+      </c>
+      <c r="X135">
+        <v>8</v>
+      </c>
+      <c r="Y135">
+        <v>1.08</v>
+      </c>
+      <c r="Z135">
+        <v>2.56</v>
+      </c>
+      <c r="AA135">
+        <v>3.06</v>
+      </c>
+      <c r="AB135">
+        <v>2.48</v>
+      </c>
+      <c r="AC135">
+        <v>1.06</v>
+      </c>
+      <c r="AD135">
+        <v>8.5</v>
+      </c>
+      <c r="AE135">
+        <v>1.31</v>
+      </c>
+      <c r="AF135">
+        <v>3.45</v>
+      </c>
+      <c r="AG135">
+        <v>1.91</v>
+      </c>
+      <c r="AH135">
+        <v>1.79</v>
+      </c>
+      <c r="AI135">
+        <v>1.67</v>
+      </c>
+      <c r="AJ135">
+        <v>2.1</v>
+      </c>
+      <c r="AK135">
+        <v>1.47</v>
+      </c>
+      <c r="AL135">
+        <v>1.33</v>
+      </c>
+      <c r="AM135">
+        <v>1.44</v>
+      </c>
+      <c r="AN135">
+        <v>1.36</v>
+      </c>
+      <c r="AO135">
+        <v>1.55</v>
+      </c>
+      <c r="AP135">
+        <v>1.33</v>
+      </c>
+      <c r="AQ135">
+        <v>1.5</v>
+      </c>
+      <c r="AR135">
+        <v>1.5</v>
+      </c>
+      <c r="AS135">
+        <v>1.75</v>
+      </c>
+      <c r="AT135">
+        <v>3.25</v>
+      </c>
+      <c r="AU135">
+        <v>5</v>
+      </c>
+      <c r="AV135">
+        <v>4</v>
+      </c>
+      <c r="AW135">
+        <v>3</v>
+      </c>
+      <c r="AX135">
+        <v>3</v>
+      </c>
+      <c r="AY135">
+        <v>8</v>
+      </c>
+      <c r="AZ135">
+        <v>7</v>
+      </c>
+      <c r="BA135">
+        <v>4</v>
+      </c>
+      <c r="BB135">
+        <v>6</v>
+      </c>
+      <c r="BC135">
+        <v>10</v>
+      </c>
+      <c r="BD135">
+        <v>2.05</v>
+      </c>
+      <c r="BE135">
+        <v>6.2</v>
+      </c>
+      <c r="BF135">
+        <v>2.25</v>
+      </c>
+      <c r="BG135">
+        <v>1.38</v>
+      </c>
+      <c r="BH135">
+        <v>2.71</v>
+      </c>
+      <c r="BI135">
+        <v>1.75</v>
+      </c>
+      <c r="BJ135">
+        <v>2.03</v>
+      </c>
+      <c r="BK135">
+        <v>2.21</v>
+      </c>
+      <c r="BL135">
+        <v>1.63</v>
+      </c>
+      <c r="BM135">
+        <v>2.88</v>
+      </c>
+      <c r="BN135">
+        <v>1.32</v>
+      </c>
+      <c r="BO135">
+        <v>4.1</v>
+      </c>
+      <c r="BP135">
+        <v>1.16</v>
       </c>
     </row>
   </sheetData>
